--- a/data/historico/semanas_318-321.xlsx
+++ b/data/historico/semanas_318-321.xlsx
@@ -31,8 +31,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 15min'!$A$2:$J$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$114</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Resumo Semanal'!$A$2:$AE$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Ranking'!$A$2:$E$42</definedName>
@@ -1433,16 +1433,16 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>19.75</v>
+        <v>20.8</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.03</v>
+        <v>5.01</v>
       </c>
       <c r="H7" s="4" t="n">
         <v>5</v>
@@ -1451,7 +1451,7 @@
         <v>4</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>5.06</v>
+        <v>3.85</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>0</v>
@@ -1460,7 +1460,7 @@
         <v>0</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -1475,49 +1475,49 @@
         <v>0</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="S7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>39.69</v>
+        <v>39.53</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>3.88</v>
+        <v>4.27</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>7.75</v>
+        <v>10.68</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="Y7" s="4" t="inlineStr">
         <is>
-          <t>R$ 133,63</t>
+          <t>R$ 127,28</t>
         </is>
       </c>
       <c r="Z7" s="4" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA7" s="4" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AB7" s="4" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AC7" s="4" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:05</t>
         </is>
       </c>
     </row>
@@ -5317,7 +5317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5329,7 +5329,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (18 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (17 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="D6" s="37" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="B7" s="37" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="C7" s="37" t="inlineStr">
@@ -5464,14 +5464,14 @@
       </c>
       <c r="D7" s="37" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="37" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="B8" s="37" t="inlineStr">
@@ -5486,139 +5486,139 @@
       </c>
       <c r="D8" s="37" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="37" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="38" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="C9" s="38" t="inlineStr">
+        <is>
+          <t>Levantamento de Índice</t>
+        </is>
+      </c>
+      <c r="D9" s="38" t="inlineStr">
+        <is>
+          <t>Todos os agentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="C10" s="37" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="inlineStr">
+        <is>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="39" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>03/08/2026</t>
+        </is>
+      </c>
+      <c r="C11" s="39" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D11" s="39" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="37" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>Férias/Atestado (automático)</t>
         </is>
       </c>
-      <c r="D9" s="37" t="inlineStr">
-        <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="38" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="38" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="C10" s="38" t="inlineStr">
-        <is>
-          <t>Levantamento de Índice</t>
-        </is>
-      </c>
-      <c r="D10" s="38" t="inlineStr">
+      <c r="D12" s="37" t="inlineStr">
+        <is>
+          <t>Cicero Isrrael Sanabria</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="38" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="38" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="38" t="inlineStr">
+        <is>
+          <t>Instalação de Ovitrampa</t>
+        </is>
+      </c>
+      <c r="D13" s="38" t="inlineStr">
         <is>
           <t>Todos os agentes</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="37" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="37" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="C11" s="37" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="37" t="inlineStr">
+        <is>
+          <t>07/08/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="37" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>Férias/Atestado (automático)</t>
         </is>
       </c>
-      <c r="D11" s="37" t="inlineStr">
-        <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="39" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="39" t="inlineStr">
-        <is>
-          <t>03/08/2026</t>
-        </is>
-      </c>
-      <c r="C12" s="39" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D12" s="39" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="37" t="inlineStr">
-        <is>
-          <t>06/08/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="37" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="C13" s="37" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D13" s="37" t="inlineStr">
-        <is>
-          <t>Cicero Isrrael Sanabria</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="38" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="38" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="C14" s="38" t="inlineStr">
-        <is>
-          <t>Instalação de Ovitrampa</t>
-        </is>
-      </c>
-      <c r="D14" s="38" t="inlineStr">
-        <is>
-          <t>Todos os agentes</t>
+      <c r="D14" s="37" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
     </row>
@@ -5640,36 +5640,36 @@
       </c>
       <c r="D15" s="37" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="37" t="inlineStr">
+      <c r="A16" s="39" t="inlineStr">
         <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="B16" s="37" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="C16" s="37" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D16" s="37" t="inlineStr">
-        <is>
-          <t>Ramona dos Santos Oliveira</t>
+      <c r="B16" s="39" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C16" s="39" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D16" s="39" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="39" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="B17" s="39" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="D17" s="39" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
     </row>
@@ -5706,56 +5706,34 @@
       </c>
       <c r="D18" s="39" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="39" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="39" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="C19" s="39" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D19" s="39" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="38" t="inlineStr">
+      <c r="A19" s="38" t="inlineStr">
         <is>
           <t>13/08/2026</t>
         </is>
       </c>
-      <c r="B20" s="38" t="inlineStr">
+      <c r="B19" s="38" t="inlineStr">
         <is>
           <t>13/08/2026</t>
         </is>
       </c>
-      <c r="C20" s="38" t="inlineStr">
+      <c r="C19" s="38" t="inlineStr">
         <is>
           <t>Recolha de Ovitrampa</t>
         </is>
       </c>
-      <c r="D20" s="38" t="inlineStr">
+      <c r="D19" s="38" t="inlineStr">
         <is>
           <t>Todos os agentes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D20"/>
+  <autoFilter ref="A2:D19"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -5965,19 +5943,19 @@
         </is>
       </c>
       <c r="C7" s="27" t="n">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="E7" s="27" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>39.69</v>
+        <v>39.53</v>
       </c>
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
@@ -7009,19 +6987,19 @@
         </is>
       </c>
       <c r="C43" s="24" t="n">
-        <v>4194</v>
+        <v>4219</v>
       </c>
       <c r="D43" s="24" t="n">
-        <v>1938</v>
+        <v>1954</v>
       </c>
       <c r="E43" s="24" t="n">
         <v>7</v>
       </c>
       <c r="F43" s="24" t="n">
-        <v>6139</v>
+        <v>6180</v>
       </c>
       <c r="G43" s="24" t="n">
-        <v>31.68</v>
+        <v>31.73</v>
       </c>
       <c r="H43" s="2" t="n"/>
       <c r="I43" s="2" t="n"/>
@@ -9916,7 +9894,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>12/08 a 13/08</t>
+          <t>12/08 a 14/08</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -9935,16 +9913,16 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>4.98</v>
+        <v>4.97</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>5</v>
@@ -9953,7 +9931,7 @@
         <v>4</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>9.09</v>
+        <v>5.8</v>
       </c>
       <c r="M19" s="4" t="n">
         <v>0</v>
@@ -9962,7 +9940,7 @@
         <v>0</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P19" s="4" t="n">
         <v>0</v>
@@ -9981,37 +9959,37 @@
       <c r="V19" s="4" t="inlineStr"/>
       <c r="W19" s="4" t="inlineStr"/>
       <c r="X19" s="4" t="n">
-        <v>4.43</v>
+        <v>4.91</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>8.869999999999999</v>
+        <v>14.72</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AA19" s="4" t="inlineStr">
         <is>
-          <t>R$ 121,12</t>
+          <t>R$ 116,00</t>
         </is>
       </c>
       <c r="AB19" s="4" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="AC19" s="4" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD19" s="4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AE19" s="4" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:00</t>
         </is>
       </c>
     </row>
@@ -16178,7 +16156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F321"/>
+  <dimension ref="A1:F322"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -16667,16 +16645,16 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>84</v>
+        <v>85.8</v>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
@@ -16691,7 +16669,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -16700,7 +16678,7 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>83.7</v>
+        <v>84</v>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
@@ -16715,16 +16693,16 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>83.3</v>
+        <v>83.7</v>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
@@ -16739,16 +16717,16 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>83</v>
+        <v>83.3</v>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
@@ -16763,7 +16741,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -16787,7 +16765,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -16796,7 +16774,7 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>82.2</v>
+        <v>83</v>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
@@ -16811,7 +16789,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -16820,7 +16798,7 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>81.3</v>
+        <v>82.2</v>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
@@ -16835,16 +16813,16 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Cris Milene Cardenas da Silva</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>79.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
@@ -18826,13 +18804,13 @@
         </is>
       </c>
       <c r="D107" s="47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E107" s="47" t="n">
         <v>1</v>
       </c>
       <c r="F107" s="47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
@@ -18874,7 +18852,7 @@
       </c>
       <c r="C109" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D109" s="48" t="n">
@@ -18900,7 +18878,7 @@
       </c>
       <c r="C110" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D110" s="48" t="n">
@@ -18926,17 +18904,17 @@
       </c>
       <c r="C111" s="48" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D111" s="48" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E111" s="48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F111" s="48" t="n">
-        <v>-18</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="112">
@@ -18952,69 +18930,69 @@
       </c>
       <c r="C112" s="48" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D112" s="48" t="n">
         <v>4</v>
       </c>
       <c r="E112" s="48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F112" s="48" t="n">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="48" t="inlineStr">
+        <is>
+          <t>Cris Milene Cardenas da Silva</t>
+        </is>
+      </c>
+      <c r="B113" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C113" s="48" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D113" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E113" s="48" t="n">
         <v>0.3</v>
       </c>
-      <c r="F112" s="48" t="n">
+      <c r="F113" s="48" t="n">
         <v>-2.4</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="47" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="47" t="inlineStr">
         <is>
           <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
-      <c r="B113" s="47" t="inlineStr">
+      <c r="B114" s="47" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C113" s="47" t="inlineStr">
+      <c r="C114" s="47" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D113" s="47" t="n">
+      <c r="D114" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="E113" s="47" t="n">
+      <c r="E114" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F113" s="47" t="n">
+      <c r="F114" s="47" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="48" t="inlineStr">
-        <is>
-          <t>Emidio Rainer Vilhalba</t>
-        </is>
-      </c>
-      <c r="B114" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C114" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D114" s="48" t="n">
-        <v>4</v>
-      </c>
-      <c r="E114" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F114" s="48" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="115">
@@ -19030,17 +19008,17 @@
       </c>
       <c r="C115" s="48" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D115" s="48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E115" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F115" s="48" t="n">
-        <v>-0.6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="116">
@@ -19056,17 +19034,17 @@
       </c>
       <c r="C116" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D116" s="48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E116" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F116" s="48" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="117">
@@ -19082,7 +19060,7 @@
       </c>
       <c r="C117" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D117" s="48" t="n">
@@ -19108,7 +19086,7 @@
       </c>
       <c r="C118" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D118" s="48" t="n">
@@ -19134,17 +19112,17 @@
       </c>
       <c r="C119" s="48" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D119" s="48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E119" s="48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F119" s="48" t="n">
-        <v>-9</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="120">
@@ -19160,43 +19138,43 @@
       </c>
       <c r="C120" s="48" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D120" s="48" t="n">
         <v>3</v>
       </c>
       <c r="E120" s="48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F120" s="48" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="48" t="inlineStr">
+        <is>
+          <t>Emidio Rainer Vilhalba</t>
+        </is>
+      </c>
+      <c r="B121" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C121" s="48" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D121" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E121" s="48" t="n">
         <v>0.3</v>
       </c>
-      <c r="F120" s="48" t="n">
+      <c r="F121" s="48" t="n">
         <v>-1.8</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="47" t="inlineStr">
-        <is>
-          <t>Evelyn Santana Santos Oliveira</t>
-        </is>
-      </c>
-      <c r="B121" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C121" s="47" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D121" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E121" s="47" t="n">
-        <v>5</v>
-      </c>
-      <c r="F121" s="47" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="122">
@@ -19212,43 +19190,43 @@
       </c>
       <c r="C122" s="47" t="inlineStr">
         <is>
-          <t>Dia com meta diária batida</t>
+          <t>Bônus: nenhuma visita rápida no período</t>
         </is>
       </c>
       <c r="D122" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E122" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F122" s="47" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="47" t="inlineStr">
+        <is>
+          <t>Evelyn Santana Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="B123" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C123" s="47" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D123" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F122" s="47" t="n">
+      <c r="E123" s="47" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="48" t="inlineStr">
-        <is>
-          <t>Evelyn Santana Santos Oliveira</t>
-        </is>
-      </c>
-      <c r="B123" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C123" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D123" s="48" t="n">
-        <v>7</v>
-      </c>
-      <c r="E123" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F123" s="48" t="n">
-        <v>-3.5</v>
+      <c r="F123" s="47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -19264,17 +19242,17 @@
       </c>
       <c r="C124" s="48" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D124" s="48" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E124" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F124" s="48" t="n">
-        <v>-0.6</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="125">
@@ -19290,17 +19268,17 @@
       </c>
       <c r="C125" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D125" s="48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E125" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F125" s="48" t="n">
-        <v>-1.8</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="126">
@@ -19316,7 +19294,7 @@
       </c>
       <c r="C126" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D126" s="48" t="n">
@@ -19342,17 +19320,17 @@
       </c>
       <c r="C127" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D127" s="48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E127" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F127" s="48" t="n">
-        <v>-3</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="128">
@@ -19368,43 +19346,43 @@
       </c>
       <c r="C128" s="48" t="inlineStr">
         <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D128" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="E128" s="48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F128" s="48" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="48" t="inlineStr">
+        <is>
+          <t>Evelyn Santana Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="B129" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C129" s="48" t="inlineStr">
+        <is>
           <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
-      <c r="D128" s="48" t="n">
+      <c r="D129" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E128" s="48" t="n">
+      <c r="E129" s="48" t="n">
         <v>1.5</v>
       </c>
-      <c r="F128" s="48" t="n">
+      <c r="F129" s="48" t="n">
         <v>-12</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="47" t="inlineStr">
-        <is>
-          <t>Fabiana de Figueredo Vieira</t>
-        </is>
-      </c>
-      <c r="B129" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C129" s="47" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D129" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E129" s="47" t="n">
-        <v>5</v>
-      </c>
-      <c r="F129" s="47" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="130">
@@ -19420,43 +19398,43 @@
       </c>
       <c r="C130" s="47" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D130" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F130" s="47" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="47" t="inlineStr">
+        <is>
+          <t>Fabiana de Figueredo Vieira</t>
+        </is>
+      </c>
+      <c r="B131" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C131" s="47" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D130" s="47" t="n">
+      <c r="D131" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="E130" s="47" t="n">
+      <c r="E131" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F130" s="47" t="n">
+      <c r="F131" s="47" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="48" t="inlineStr">
-        <is>
-          <t>Fabiana de Figueredo Vieira</t>
-        </is>
-      </c>
-      <c r="B131" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C131" s="48" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D131" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E131" s="48" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F131" s="48" t="n">
-        <v>-0.6</v>
       </c>
     </row>
     <row r="132">
@@ -19472,7 +19450,7 @@
       </c>
       <c r="C132" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D132" s="48" t="n">
@@ -19498,7 +19476,7 @@
       </c>
       <c r="C133" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D133" s="48" t="n">
@@ -19524,69 +19502,69 @@
       </c>
       <c r="C134" s="48" t="inlineStr">
         <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D134" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" s="48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F134" s="48" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="48" t="inlineStr">
+        <is>
+          <t>Fabiana de Figueredo Vieira</t>
+        </is>
+      </c>
+      <c r="B135" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C135" s="48" t="inlineStr">
+        <is>
           <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
-      <c r="D134" s="48" t="n">
+      <c r="D135" s="48" t="n">
         <v>2</v>
       </c>
-      <c r="E134" s="48" t="n">
+      <c r="E135" s="48" t="n">
         <v>1.5</v>
       </c>
-      <c r="F134" s="48" t="n">
+      <c r="F135" s="48" t="n">
         <v>-6</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="47" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="47" t="inlineStr">
         <is>
           <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
-      <c r="B135" s="47" t="inlineStr">
+      <c r="B136" s="47" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C135" s="47" t="inlineStr">
+      <c r="C136" s="47" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D135" s="47" t="n">
+      <c r="D136" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="E135" s="47" t="n">
+      <c r="E136" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F135" s="47" t="n">
+      <c r="F136" s="47" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="48" t="inlineStr">
-        <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
-        </is>
-      </c>
-      <c r="B136" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C136" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D136" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="E136" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F136" s="48" t="n">
-        <v>-2.5</v>
       </c>
     </row>
     <row r="137">
@@ -19602,17 +19580,17 @@
       </c>
       <c r="C137" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D137" s="48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E137" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F137" s="48" t="n">
-        <v>-0.6</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="138">
@@ -19628,17 +19606,17 @@
       </c>
       <c r="C138" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D138" s="48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E138" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F138" s="48" t="n">
-        <v>-1.8</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="139">
@@ -19654,17 +19632,17 @@
       </c>
       <c r="C139" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D139" s="48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E139" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F139" s="48" t="n">
-        <v>-2.4</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="140">
@@ -19680,17 +19658,17 @@
       </c>
       <c r="C140" s="48" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D140" s="48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E140" s="48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F140" s="48" t="n">
-        <v>-18</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="141">
@@ -19706,43 +19684,43 @@
       </c>
       <c r="C141" s="48" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D141" s="48" t="n">
+        <v>6</v>
+      </c>
+      <c r="E141" s="48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F141" s="48" t="n">
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="48" t="inlineStr">
+        <is>
+          <t>Gabriel Alan de Oliveira Martins</t>
+        </is>
+      </c>
+      <c r="B142" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C142" s="48" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D141" s="48" t="n">
+      <c r="D142" s="48" t="n">
         <v>2</v>
       </c>
-      <c r="E141" s="48" t="n">
+      <c r="E142" s="48" t="n">
         <v>0.3</v>
       </c>
-      <c r="F141" s="48" t="n">
+      <c r="F142" s="48" t="n">
         <v>-1.2</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="47" t="inlineStr">
-        <is>
-          <t>Geancarlos Ferreira Barrios</t>
-        </is>
-      </c>
-      <c r="B142" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C142" s="47" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D142" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E142" s="47" t="n">
-        <v>5</v>
-      </c>
-      <c r="F142" s="47" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="143">
@@ -19758,43 +19736,43 @@
       </c>
       <c r="C143" s="47" t="inlineStr">
         <is>
-          <t>Dia com meta diária batida</t>
+          <t>Bônus: nenhuma visita rápida no período</t>
         </is>
       </c>
       <c r="D143" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" s="47" t="n">
         <v>5</v>
-      </c>
-      <c r="E143" s="47" t="n">
-        <v>1</v>
       </c>
       <c r="F143" s="47" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="48" t="inlineStr">
+      <c r="A144" s="47" t="inlineStr">
         <is>
           <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
-      <c r="B144" s="48" t="inlineStr">
+      <c r="B144" s="47" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C144" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D144" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="E144" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F144" s="48" t="n">
-        <v>-1</v>
+      <c r="C144" s="47" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D144" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="E144" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F144" s="47" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="145">
@@ -19810,17 +19788,17 @@
       </c>
       <c r="C145" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D145" s="48" t="n">
         <v>2</v>
       </c>
       <c r="E145" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F145" s="48" t="n">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="146">
@@ -19836,7 +19814,7 @@
       </c>
       <c r="C146" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D146" s="48" t="n">
@@ -19862,17 +19840,17 @@
       </c>
       <c r="C147" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D147" s="48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E147" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F147" s="48" t="n">
-        <v>-1.8</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="148">
@@ -19888,43 +19866,43 @@
       </c>
       <c r="C148" s="48" t="inlineStr">
         <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D148" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E148" s="48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F148" s="48" t="n">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="48" t="inlineStr">
+        <is>
+          <t>Geancarlos Ferreira Barrios</t>
+        </is>
+      </c>
+      <c r="B149" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C149" s="48" t="inlineStr">
+        <is>
           <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
-      <c r="D148" s="48" t="n">
+      <c r="D149" s="48" t="n">
         <v>2</v>
       </c>
-      <c r="E148" s="48" t="n">
+      <c r="E149" s="48" t="n">
         <v>1.5</v>
       </c>
-      <c r="F148" s="48" t="n">
+      <c r="F149" s="48" t="n">
         <v>-6</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="47" t="inlineStr">
-        <is>
-          <t>Gilmar Bitencourt Luiz</t>
-        </is>
-      </c>
-      <c r="B149" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C149" s="47" t="inlineStr">
-        <is>
-          <t>Bônus: pontualidade perfeita no período</t>
-        </is>
-      </c>
-      <c r="D149" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E149" s="47" t="n">
-        <v>3</v>
-      </c>
-      <c r="F149" s="47" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="150">
@@ -19940,43 +19918,43 @@
       </c>
       <c r="C150" s="47" t="inlineStr">
         <is>
-          <t>Dia com meta diária batida</t>
+          <t>Bônus: pontualidade perfeita no período</t>
         </is>
       </c>
       <c r="D150" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E150" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="F150" s="47" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="47" t="inlineStr">
+        <is>
+          <t>Gilmar Bitencourt Luiz</t>
+        </is>
+      </c>
+      <c r="B151" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C151" s="47" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D151" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F150" s="47" t="n">
+      <c r="E151" s="47" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="48" t="inlineStr">
-        <is>
-          <t>Gilmar Bitencourt Luiz</t>
-        </is>
-      </c>
-      <c r="B151" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C151" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D151" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="E151" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F151" s="48" t="n">
-        <v>-1.5</v>
+      <c r="F151" s="47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -19992,17 +19970,17 @@
       </c>
       <c r="C152" s="48" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D152" s="48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E152" s="48" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="F152" s="48" t="n">
-        <v>-12</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="153">
@@ -20018,69 +19996,69 @@
       </c>
       <c r="C153" s="48" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D153" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E153" s="48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F153" s="48" t="n">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="48" t="inlineStr">
+        <is>
+          <t>Gilmar Bitencourt Luiz</t>
+        </is>
+      </c>
+      <c r="B154" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C154" s="48" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D153" s="48" t="n">
+      <c r="D154" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="E153" s="48" t="n">
+      <c r="E154" s="48" t="n">
         <v>0.3</v>
       </c>
-      <c r="F153" s="48" t="n">
+      <c r="F154" s="48" t="n">
         <v>-0.6</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="47" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="47" t="inlineStr">
         <is>
           <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
-      <c r="B154" s="47" t="inlineStr">
+      <c r="B155" s="47" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C154" s="47" t="inlineStr">
+      <c r="C155" s="47" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D154" s="47" t="n">
+      <c r="D155" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="E154" s="47" t="n">
+      <c r="E155" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F154" s="47" t="n">
+      <c r="F155" s="47" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="48" t="inlineStr">
-        <is>
-          <t>Gisele Lopes Justiniano</t>
-        </is>
-      </c>
-      <c r="B155" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C155" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D155" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="E155" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F155" s="48" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="156">
@@ -20096,17 +20074,17 @@
       </c>
       <c r="C156" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D156" s="48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E156" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F156" s="48" t="n">
-        <v>-1.8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="157">
@@ -20122,17 +20100,17 @@
       </c>
       <c r="C157" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D157" s="48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E157" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F157" s="48" t="n">
-        <v>-1.2</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="158">
@@ -20148,17 +20126,17 @@
       </c>
       <c r="C158" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D158" s="48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E158" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F158" s="48" t="n">
-        <v>-2.4</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="159">
@@ -20174,17 +20152,17 @@
       </c>
       <c r="C159" s="48" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D159" s="48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E159" s="48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F159" s="48" t="n">
-        <v>-6</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="160">
@@ -20200,17 +20178,17 @@
       </c>
       <c r="C160" s="48" t="inlineStr">
         <is>
-          <t>Visita em sequência suspeita</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D160" s="48" t="n">
         <v>2</v>
       </c>
       <c r="E160" s="48" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F160" s="48" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="161">
@@ -20226,69 +20204,69 @@
       </c>
       <c r="C161" s="48" t="inlineStr">
         <is>
+          <t>Visita em sequência suspeita</t>
+        </is>
+      </c>
+      <c r="D161" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E161" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" s="48" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="48" t="inlineStr">
+        <is>
+          <t>Gisele Lopes Justiniano</t>
+        </is>
+      </c>
+      <c r="B162" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C162" s="48" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D161" s="48" t="n">
+      <c r="D162" s="48" t="n">
         <v>9</v>
       </c>
-      <c r="E161" s="48" t="n">
+      <c r="E162" s="48" t="n">
         <v>0.3</v>
       </c>
-      <c r="F161" s="48" t="n">
+      <c r="F162" s="48" t="n">
         <v>-5.4</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="47" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="47" t="inlineStr">
         <is>
           <t>Gisele Olimpia Torres</t>
         </is>
       </c>
-      <c r="B162" s="47" t="inlineStr">
+      <c r="B163" s="47" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C162" s="47" t="inlineStr">
+      <c r="C163" s="47" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D162" s="47" t="n">
+      <c r="D163" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="E162" s="47" t="n">
+      <c r="E163" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F162" s="47" t="n">
+      <c r="F163" s="47" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="48" t="inlineStr">
-        <is>
-          <t>Gisele Olimpia Torres</t>
-        </is>
-      </c>
-      <c r="B163" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C163" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D163" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="E163" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F163" s="48" t="n">
-        <v>-1.5</v>
       </c>
     </row>
     <row r="164">
@@ -20304,17 +20282,17 @@
       </c>
       <c r="C164" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D164" s="48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E164" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F164" s="48" t="n">
-        <v>-0.6</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="165">
@@ -20330,17 +20308,17 @@
       </c>
       <c r="C165" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D165" s="48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E165" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F165" s="48" t="n">
-        <v>-1.8</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="166">
@@ -20356,17 +20334,17 @@
       </c>
       <c r="C166" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D166" s="48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E166" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F166" s="48" t="n">
-        <v>-1.2</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="167">
@@ -20382,17 +20360,17 @@
       </c>
       <c r="C167" s="48" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D167" s="48" t="n">
         <v>2</v>
       </c>
       <c r="E167" s="48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F167" s="48" t="n">
-        <v>-6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="168">
@@ -20408,69 +20386,69 @@
       </c>
       <c r="C168" s="48" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D168" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E168" s="48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F168" s="48" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="48" t="inlineStr">
+        <is>
+          <t>Gisele Olimpia Torres</t>
+        </is>
+      </c>
+      <c r="B169" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C169" s="48" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D168" s="48" t="n">
+      <c r="D169" s="48" t="n">
         <v>22</v>
       </c>
-      <c r="E168" s="48" t="n">
+      <c r="E169" s="48" t="n">
         <v>0.3</v>
       </c>
-      <c r="F168" s="48" t="n">
+      <c r="F169" s="48" t="n">
         <v>-13.2</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="47" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="47" t="inlineStr">
         <is>
           <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
-      <c r="B169" s="47" t="inlineStr">
+      <c r="B170" s="47" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C169" s="47" t="inlineStr">
+      <c r="C170" s="47" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D169" s="47" t="n">
+      <c r="D170" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="E169" s="47" t="n">
+      <c r="E170" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F169" s="47" t="n">
+      <c r="F170" s="47" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="48" t="inlineStr">
-        <is>
-          <t>Juliana Patricia Goncalves</t>
-        </is>
-      </c>
-      <c r="B170" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C170" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D170" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="E170" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F170" s="48" t="n">
-        <v>-2.5</v>
       </c>
     </row>
     <row r="171">
@@ -20486,17 +20464,17 @@
       </c>
       <c r="C171" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D171" s="48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E171" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F171" s="48" t="n">
-        <v>-1.8</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="172">
@@ -20512,17 +20490,17 @@
       </c>
       <c r="C172" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D172" s="48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E172" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F172" s="48" t="n">
-        <v>-1.2</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="173">
@@ -20538,17 +20516,17 @@
       </c>
       <c r="C173" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D173" s="48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E173" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F173" s="48" t="n">
-        <v>-2.4</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="174">
@@ -20564,17 +20542,17 @@
       </c>
       <c r="C174" s="48" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D174" s="48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E174" s="48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F174" s="48" t="n">
-        <v>-15</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="175">
@@ -20590,69 +20568,69 @@
       </c>
       <c r="C175" s="48" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D175" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="E175" s="48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F175" s="48" t="n">
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="48" t="inlineStr">
+        <is>
+          <t>Juliana Patricia Goncalves</t>
+        </is>
+      </c>
+      <c r="B176" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C176" s="48" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D175" s="48" t="n">
+      <c r="D176" s="48" t="n">
         <v>19</v>
       </c>
-      <c r="E175" s="48" t="n">
+      <c r="E176" s="48" t="n">
         <v>0.3</v>
       </c>
-      <c r="F175" s="48" t="n">
+      <c r="F176" s="48" t="n">
         <v>-11.4</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="47" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="47" t="inlineStr">
         <is>
           <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
-      <c r="B176" s="47" t="inlineStr">
+      <c r="B177" s="47" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C176" s="47" t="inlineStr">
+      <c r="C177" s="47" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D176" s="47" t="n">
+      <c r="D177" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="E176" s="47" t="n">
+      <c r="E177" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F176" s="47" t="n">
+      <c r="F177" s="47" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="48" t="inlineStr">
-        <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
-        </is>
-      </c>
-      <c r="B177" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C177" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D177" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E177" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F177" s="48" t="n">
-        <v>-0.5</v>
       </c>
     </row>
     <row r="178">
@@ -20668,17 +20646,17 @@
       </c>
       <c r="C178" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D178" s="48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E178" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F178" s="48" t="n">
-        <v>-1.2</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="179">
@@ -20694,17 +20672,17 @@
       </c>
       <c r="C179" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D179" s="48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E179" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F179" s="48" t="n">
-        <v>-1.8</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="180">
@@ -20720,17 +20698,17 @@
       </c>
       <c r="C180" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D180" s="48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E180" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F180" s="48" t="n">
-        <v>-1.2</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="181">
@@ -20746,17 +20724,17 @@
       </c>
       <c r="C181" s="48" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D181" s="48" t="n">
         <v>2</v>
       </c>
       <c r="E181" s="48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F181" s="48" t="n">
-        <v>-6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="182">
@@ -20772,69 +20750,69 @@
       </c>
       <c r="C182" s="48" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D182" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E182" s="48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F182" s="48" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="48" t="inlineStr">
+        <is>
+          <t>Kariele Jackeline Rodrigues Silva</t>
+        </is>
+      </c>
+      <c r="B183" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C183" s="48" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D182" s="48" t="n">
+      <c r="D183" s="48" t="n">
         <v>46</v>
       </c>
-      <c r="E182" s="48" t="n">
+      <c r="E183" s="48" t="n">
         <v>0.3</v>
       </c>
-      <c r="F182" s="48" t="n">
+      <c r="F183" s="48" t="n">
         <v>-27.6</v>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="47" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="47" t="inlineStr">
         <is>
           <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
-      <c r="B183" s="47" t="inlineStr">
+      <c r="B184" s="47" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C183" s="47" t="inlineStr">
+      <c r="C184" s="47" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D183" s="47" t="n">
+      <c r="D184" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="E183" s="47" t="n">
+      <c r="E184" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F183" s="47" t="n">
+      <c r="F184" s="47" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="48" t="inlineStr">
-        <is>
-          <t>Kátia Cilene Silveira Machado</t>
-        </is>
-      </c>
-      <c r="B184" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C184" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D184" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="E184" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F184" s="48" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="185">
@@ -20850,17 +20828,17 @@
       </c>
       <c r="C185" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D185" s="48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E185" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F185" s="48" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="186">
@@ -20876,17 +20854,17 @@
       </c>
       <c r="C186" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D186" s="48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E186" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F186" s="48" t="n">
-        <v>-1.8</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="187">
@@ -20902,17 +20880,17 @@
       </c>
       <c r="C187" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D187" s="48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E187" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F187" s="48" t="n">
-        <v>-3</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="188">
@@ -20928,17 +20906,17 @@
       </c>
       <c r="C188" s="48" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D188" s="48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E188" s="48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F188" s="48" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="189">
@@ -20954,17 +20932,17 @@
       </c>
       <c r="C189" s="48" t="inlineStr">
         <is>
-          <t>Visita fora do expediente/fim de semana</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D189" s="48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E189" s="48" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F189" s="48" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="190">
@@ -20980,69 +20958,69 @@
       </c>
       <c r="C190" s="48" t="inlineStr">
         <is>
+          <t>Visita fora do expediente/fim de semana</t>
+        </is>
+      </c>
+      <c r="D190" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E190" s="48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F190" s="48" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="48" t="inlineStr">
+        <is>
+          <t>Kátia Cilene Silveira Machado</t>
+        </is>
+      </c>
+      <c r="B191" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C191" s="48" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D190" s="48" t="n">
+      <c r="D191" s="48" t="n">
         <v>11</v>
       </c>
-      <c r="E190" s="48" t="n">
+      <c r="E191" s="48" t="n">
         <v>0.3</v>
       </c>
-      <c r="F190" s="48" t="n">
+      <c r="F191" s="48" t="n">
         <v>-6.6</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="47" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="47" t="inlineStr">
         <is>
           <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
-      <c r="B191" s="47" t="inlineStr">
+      <c r="B192" s="47" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C191" s="47" t="inlineStr">
+      <c r="C192" s="47" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D191" s="47" t="n">
+      <c r="D192" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="E191" s="47" t="n">
+      <c r="E192" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F191" s="47" t="n">
+      <c r="F192" s="47" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="48" t="inlineStr">
-        <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
-        </is>
-      </c>
-      <c r="B192" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C192" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D192" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="E192" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F192" s="48" t="n">
-        <v>-1.5</v>
       </c>
     </row>
     <row r="193">
@@ -21058,17 +21036,17 @@
       </c>
       <c r="C193" s="48" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D193" s="48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E193" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F193" s="48" t="n">
-        <v>-0.6</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="194">
@@ -21084,17 +21062,17 @@
       </c>
       <c r="C194" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D194" s="48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E194" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F194" s="48" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="195">
@@ -21110,17 +21088,17 @@
       </c>
       <c r="C195" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D195" s="48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E195" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F195" s="48" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="196">
@@ -21136,7 +21114,7 @@
       </c>
       <c r="C196" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D196" s="48" t="n">
@@ -21162,17 +21140,17 @@
       </c>
       <c r="C197" s="48" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D197" s="48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E197" s="48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F197" s="48" t="n">
-        <v>-12</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="198">
@@ -21188,69 +21166,69 @@
       </c>
       <c r="C198" s="48" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D198" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E198" s="48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F198" s="48" t="n">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="48" t="inlineStr">
+        <is>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
+        </is>
+      </c>
+      <c r="B199" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C199" s="48" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D198" s="48" t="n">
+      <c r="D199" s="48" t="n">
         <v>3</v>
       </c>
-      <c r="E198" s="48" t="n">
+      <c r="E199" s="48" t="n">
         <v>0.3</v>
       </c>
-      <c r="F198" s="48" t="n">
+      <c r="F199" s="48" t="n">
         <v>-1.8</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="47" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="47" t="inlineStr">
         <is>
           <t>Mateus Falcao de Souza</t>
         </is>
       </c>
-      <c r="B199" s="47" t="inlineStr">
+      <c r="B200" s="47" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C199" s="47" t="inlineStr">
+      <c r="C200" s="47" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D199" s="47" t="n">
+      <c r="D200" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="E199" s="47" t="n">
+      <c r="E200" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F199" s="47" t="n">
+      <c r="F200" s="47" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="48" t="inlineStr">
-        <is>
-          <t>Mateus Falcao de Souza</t>
-        </is>
-      </c>
-      <c r="B200" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C200" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D200" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="E200" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F200" s="48" t="n">
-        <v>-1.5</v>
       </c>
     </row>
     <row r="201">
@@ -21266,17 +21244,17 @@
       </c>
       <c r="C201" s="48" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D201" s="48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E201" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F201" s="48" t="n">
-        <v>-1.2</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="202">
@@ -21292,7 +21270,7 @@
       </c>
       <c r="C202" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D202" s="48" t="n">
@@ -21318,7 +21296,7 @@
       </c>
       <c r="C203" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D203" s="48" t="n">
@@ -21344,7 +21322,7 @@
       </c>
       <c r="C204" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D204" s="48" t="n">
@@ -21370,17 +21348,17 @@
       </c>
       <c r="C205" s="48" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D205" s="48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E205" s="48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F205" s="48" t="n">
-        <v>-3</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="206">
@@ -21396,69 +21374,69 @@
       </c>
       <c r="C206" s="48" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D206" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" s="48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F206" s="48" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="48" t="inlineStr">
+        <is>
+          <t>Mateus Falcao de Souza</t>
+        </is>
+      </c>
+      <c r="B207" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C207" s="48" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D206" s="48" t="n">
+      <c r="D207" s="48" t="n">
         <v>102</v>
       </c>
-      <c r="E206" s="48" t="n">
+      <c r="E207" s="48" t="n">
         <v>0.3</v>
       </c>
-      <c r="F206" s="48" t="n">
+      <c r="F207" s="48" t="n">
         <v>-61.2</v>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="47" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="47" t="inlineStr">
         <is>
           <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
-      <c r="B207" s="47" t="inlineStr">
+      <c r="B208" s="47" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C207" s="47" t="inlineStr">
+      <c r="C208" s="47" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D207" s="47" t="n">
+      <c r="D208" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="E207" s="47" t="n">
+      <c r="E208" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F207" s="47" t="n">
+      <c r="F208" s="47" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="48" t="inlineStr">
-        <is>
-          <t>Miglidiane Maciel Ajala</t>
-        </is>
-      </c>
-      <c r="B208" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C208" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D208" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="E208" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F208" s="48" t="n">
-        <v>-2.5</v>
       </c>
     </row>
     <row r="209">
@@ -21474,17 +21452,17 @@
       </c>
       <c r="C209" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D209" s="48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E209" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F209" s="48" t="n">
-        <v>-1.8</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="210">
@@ -21500,7 +21478,7 @@
       </c>
       <c r="C210" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D210" s="48" t="n">
@@ -21526,17 +21504,17 @@
       </c>
       <c r="C211" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D211" s="48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E211" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F211" s="48" t="n">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="212">
@@ -21552,17 +21530,17 @@
       </c>
       <c r="C212" s="48" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D212" s="48" t="n">
         <v>1</v>
       </c>
       <c r="E212" s="48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F212" s="48" t="n">
-        <v>-3</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="213">
@@ -21578,69 +21556,69 @@
       </c>
       <c r="C213" s="48" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D213" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E213" s="48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F213" s="48" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="48" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+      <c r="B214" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C214" s="48" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D213" s="48" t="n">
+      <c r="D214" s="48" t="n">
         <v>22</v>
       </c>
-      <c r="E213" s="48" t="n">
+      <c r="E214" s="48" t="n">
         <v>0.3</v>
       </c>
-      <c r="F213" s="48" t="n">
+      <c r="F214" s="48" t="n">
         <v>-13.2</v>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="47" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="47" t="inlineStr">
         <is>
           <t>Naime Cristina Freitas</t>
         </is>
       </c>
-      <c r="B214" s="47" t="inlineStr">
+      <c r="B215" s="47" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C214" s="47" t="inlineStr">
+      <c r="C215" s="47" t="inlineStr">
         <is>
           <t>Bônus: nenhuma visita rápida no período</t>
         </is>
       </c>
-      <c r="D214" s="47" t="n">
+      <c r="D215" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="E214" s="47" t="n">
+      <c r="E215" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="F214" s="47" t="n">
+      <c r="F215" s="47" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="48" t="inlineStr">
-        <is>
-          <t>Naime Cristina Freitas</t>
-        </is>
-      </c>
-      <c r="B215" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C215" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D215" s="48" t="n">
-        <v>4</v>
-      </c>
-      <c r="E215" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F215" s="48" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="216">
@@ -21656,17 +21634,17 @@
       </c>
       <c r="C216" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D216" s="48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E216" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F216" s="48" t="n">
-        <v>-0.6</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="217">
@@ -21682,7 +21660,7 @@
       </c>
       <c r="C217" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D217" s="48" t="n">
@@ -21708,69 +21686,69 @@
       </c>
       <c r="C218" s="48" t="inlineStr">
         <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D218" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E218" s="48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F218" s="48" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="48" t="inlineStr">
+        <is>
+          <t>Naime Cristina Freitas</t>
+        </is>
+      </c>
+      <c r="B219" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C219" s="48" t="inlineStr">
+        <is>
           <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
-      <c r="D218" s="48" t="n">
+      <c r="D219" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E218" s="48" t="n">
+      <c r="E219" s="48" t="n">
         <v>1.5</v>
       </c>
-      <c r="F218" s="48" t="n">
+      <c r="F219" s="48" t="n">
         <v>-12</v>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="47" t="inlineStr">
+    <row r="220">
+      <c r="A220" s="47" t="inlineStr">
         <is>
           <t>Rafael Ramos Recalde</t>
         </is>
       </c>
-      <c r="B219" s="47" t="inlineStr">
+      <c r="B220" s="47" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C219" s="47" t="inlineStr">
+      <c r="C220" s="47" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D219" s="47" t="n">
+      <c r="D220" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="E219" s="47" t="n">
+      <c r="E220" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F219" s="47" t="n">
+      <c r="F220" s="47" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="48" t="inlineStr">
-        <is>
-          <t>Rafael Ramos Recalde</t>
-        </is>
-      </c>
-      <c r="B220" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C220" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D220" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E220" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F220" s="48" t="n">
-        <v>-0.5</v>
       </c>
     </row>
     <row r="221">
@@ -21786,17 +21764,17 @@
       </c>
       <c r="C221" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D221" s="48" t="n">
         <v>1</v>
       </c>
       <c r="E221" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F221" s="48" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="222">
@@ -21812,17 +21790,17 @@
       </c>
       <c r="C222" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D222" s="48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E222" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F222" s="48" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="223">
@@ -21838,17 +21816,17 @@
       </c>
       <c r="C223" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D223" s="48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E223" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F223" s="48" t="n">
-        <v>-1.8</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="224">
@@ -21864,17 +21842,17 @@
       </c>
       <c r="C224" s="48" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D224" s="48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E224" s="48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F224" s="48" t="n">
-        <v>-6</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="225">
@@ -21890,43 +21868,43 @@
       </c>
       <c r="C225" s="48" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D225" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E225" s="48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F225" s="48" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="48" t="inlineStr">
+        <is>
+          <t>Rafael Ramos Recalde</t>
+        </is>
+      </c>
+      <c r="B226" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C226" s="48" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D225" s="48" t="n">
+      <c r="D226" s="48" t="n">
         <v>57</v>
       </c>
-      <c r="E225" s="48" t="n">
+      <c r="E226" s="48" t="n">
         <v>0.3</v>
       </c>
-      <c r="F225" s="48" t="n">
+      <c r="F226" s="48" t="n">
         <v>-34.2</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="47" t="inlineStr">
-        <is>
-          <t>Ramona dos Santos Oliveira</t>
-        </is>
-      </c>
-      <c r="B226" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C226" s="47" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D226" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E226" s="47" t="n">
-        <v>5</v>
-      </c>
-      <c r="F226" s="47" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="227">
@@ -21942,43 +21920,43 @@
       </c>
       <c r="C227" s="47" t="inlineStr">
         <is>
-          <t>Dia com meta diária batida</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D227" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E227" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F227" s="47" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="47" t="inlineStr">
+        <is>
+          <t>Ramona dos Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="B228" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C228" s="47" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D228" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F227" s="47" t="n">
+      <c r="E228" s="47" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="48" t="inlineStr">
-        <is>
-          <t>Ramona dos Santos Oliveira</t>
-        </is>
-      </c>
-      <c r="B228" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C228" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D228" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="E228" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F228" s="48" t="n">
-        <v>-1</v>
+      <c r="F228" s="47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -21994,17 +21972,17 @@
       </c>
       <c r="C229" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D229" s="48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E229" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F229" s="48" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="230">
@@ -22020,7 +21998,7 @@
       </c>
       <c r="C230" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D230" s="48" t="n">
@@ -22046,17 +22024,17 @@
       </c>
       <c r="C231" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D231" s="48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E231" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F231" s="48" t="n">
-        <v>-1.8</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="232">
@@ -22072,69 +22050,69 @@
       </c>
       <c r="C232" s="48" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D232" s="48" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E232" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F232" s="48" t="n">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="48" t="inlineStr">
+        <is>
+          <t>Ramona dos Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="B233" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C233" s="48" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D233" s="48" t="n">
+        <v>22</v>
+      </c>
+      <c r="E233" s="48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F233" s="48" t="n">
         <v>-13.2</v>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="47" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="47" t="inlineStr">
         <is>
           <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
-      <c r="B233" s="47" t="inlineStr">
+      <c r="B234" s="47" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C233" s="47" t="inlineStr">
+      <c r="C234" s="47" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D233" s="47" t="n">
+      <c r="D234" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="E233" s="47" t="n">
+      <c r="E234" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F233" s="47" t="n">
+      <c r="F234" s="47" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="48" t="inlineStr">
-        <is>
-          <t>Raquel Ortiz dos Santos</t>
-        </is>
-      </c>
-      <c r="B234" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C234" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D234" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="E234" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F234" s="48" t="n">
-        <v>-1.5</v>
       </c>
     </row>
     <row r="235">
@@ -22150,17 +22128,17 @@
       </c>
       <c r="C235" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D235" s="48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E235" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F235" s="48" t="n">
-        <v>-0.6</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="236">
@@ -22176,17 +22154,17 @@
       </c>
       <c r="C236" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D236" s="48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E236" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F236" s="48" t="n">
-        <v>-2.4</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="237">
@@ -22202,17 +22180,17 @@
       </c>
       <c r="C237" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D237" s="48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E237" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F237" s="48" t="n">
-        <v>-1.8</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="238">
@@ -22228,17 +22206,17 @@
       </c>
       <c r="C238" s="48" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D238" s="48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E238" s="48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F238" s="48" t="n">
-        <v>-12</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="239">
@@ -22254,17 +22232,17 @@
       </c>
       <c r="C239" s="48" t="inlineStr">
         <is>
-          <t>Visita fora do expediente/fim de semana</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D239" s="48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E239" s="48" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F239" s="48" t="n">
-        <v>-2</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="240">
@@ -22280,43 +22258,43 @@
       </c>
       <c r="C240" s="48" t="inlineStr">
         <is>
+          <t>Visita fora do expediente/fim de semana</t>
+        </is>
+      </c>
+      <c r="D240" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E240" s="48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F240" s="48" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="48" t="inlineStr">
+        <is>
+          <t>Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="B241" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C241" s="48" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D240" s="48" t="n">
+      <c r="D241" s="48" t="n">
         <v>49</v>
       </c>
-      <c r="E240" s="48" t="n">
+      <c r="E241" s="48" t="n">
         <v>0.3</v>
       </c>
-      <c r="F240" s="48" t="n">
+      <c r="F241" s="48" t="n">
         <v>-29.4</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="47" t="inlineStr">
-        <is>
-          <t>Rosalina Beniel Vargas</t>
-        </is>
-      </c>
-      <c r="B241" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C241" s="47" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D241" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E241" s="47" t="n">
-        <v>5</v>
-      </c>
-      <c r="F241" s="47" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="242">
@@ -22332,43 +22310,43 @@
       </c>
       <c r="C242" s="47" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D242" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E242" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F242" s="47" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="47" t="inlineStr">
+        <is>
+          <t>Rosalina Beniel Vargas</t>
+        </is>
+      </c>
+      <c r="B243" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C243" s="47" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D242" s="47" t="n">
+      <c r="D243" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="E242" s="47" t="n">
+      <c r="E243" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F242" s="47" t="n">
+      <c r="F243" s="47" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="48" t="inlineStr">
-        <is>
-          <t>Rosalina Beniel Vargas</t>
-        </is>
-      </c>
-      <c r="B243" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C243" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D243" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="E243" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F243" s="48" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="244">
@@ -22384,17 +22362,17 @@
       </c>
       <c r="C244" s="48" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D244" s="48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E244" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F244" s="48" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="245">
@@ -22410,7 +22388,7 @@
       </c>
       <c r="C245" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D245" s="48" t="n">
@@ -22436,7 +22414,7 @@
       </c>
       <c r="C246" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D246" s="48" t="n">
@@ -22462,7 +22440,7 @@
       </c>
       <c r="C247" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D247" s="48" t="n">
@@ -22488,69 +22466,69 @@
       </c>
       <c r="C248" s="48" t="inlineStr">
         <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D248" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E248" s="48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F248" s="48" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="48" t="inlineStr">
+        <is>
+          <t>Rosalina Beniel Vargas</t>
+        </is>
+      </c>
+      <c r="B249" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C249" s="48" t="inlineStr">
+        <is>
           <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
-      <c r="D248" s="48" t="n">
+      <c r="D249" s="48" t="n">
         <v>2</v>
       </c>
-      <c r="E248" s="48" t="n">
+      <c r="E249" s="48" t="n">
         <v>1.5</v>
       </c>
-      <c r="F248" s="48" t="n">
+      <c r="F249" s="48" t="n">
         <v>-6</v>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="47" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="47" t="inlineStr">
         <is>
           <t>Rozana Reis da Silva</t>
         </is>
       </c>
-      <c r="B249" s="47" t="inlineStr">
+      <c r="B250" s="47" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C249" s="47" t="inlineStr">
+      <c r="C250" s="47" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D249" s="47" t="n">
+      <c r="D250" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="E249" s="47" t="n">
+      <c r="E250" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F249" s="47" t="n">
+      <c r="F250" s="47" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="48" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="B250" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C250" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D250" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E250" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F250" s="48" t="n">
-        <v>-0.5</v>
       </c>
     </row>
     <row r="251">
@@ -22566,17 +22544,17 @@
       </c>
       <c r="C251" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D251" s="48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E251" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F251" s="48" t="n">
-        <v>-1.8</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="252">
@@ -22592,17 +22570,17 @@
       </c>
       <c r="C252" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D252" s="48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E252" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F252" s="48" t="n">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="253">
@@ -22618,7 +22596,7 @@
       </c>
       <c r="C253" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D253" s="48" t="n">
@@ -22644,17 +22622,17 @@
       </c>
       <c r="C254" s="48" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D254" s="48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E254" s="48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F254" s="48" t="n">
-        <v>-12</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="255">
@@ -22670,69 +22648,69 @@
       </c>
       <c r="C255" s="48" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D255" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E255" s="48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F255" s="48" t="n">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="48" t="inlineStr">
+        <is>
+          <t>Rozana Reis da Silva</t>
+        </is>
+      </c>
+      <c r="B256" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C256" s="48" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D255" s="48" t="n">
+      <c r="D256" s="48" t="n">
         <v>17</v>
       </c>
-      <c r="E255" s="48" t="n">
+      <c r="E256" s="48" t="n">
         <v>0.3</v>
       </c>
-      <c r="F255" s="48" t="n">
+      <c r="F256" s="48" t="n">
         <v>-10.2</v>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="47" t="inlineStr">
+    <row r="257">
+      <c r="A257" s="47" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="B256" s="47" t="inlineStr">
+      <c r="B257" s="47" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C256" s="47" t="inlineStr">
+      <c r="C257" s="47" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D256" s="47" t="n">
+      <c r="D257" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="E256" s="47" t="n">
+      <c r="E257" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F256" s="47" t="n">
+      <c r="F257" s="47" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="48" t="inlineStr">
-        <is>
-          <t>Rozentina Matos de Oliveira</t>
-        </is>
-      </c>
-      <c r="B257" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C257" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D257" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="E257" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F257" s="48" t="n">
-        <v>-1.5</v>
       </c>
     </row>
     <row r="258">
@@ -22748,17 +22726,17 @@
       </c>
       <c r="C258" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D258" s="48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E258" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F258" s="48" t="n">
-        <v>-1.2</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="259">
@@ -22774,7 +22752,7 @@
       </c>
       <c r="C259" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D259" s="48" t="n">
@@ -22800,17 +22778,17 @@
       </c>
       <c r="C260" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D260" s="48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E260" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F260" s="48" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="261">
@@ -22826,17 +22804,17 @@
       </c>
       <c r="C261" s="48" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D261" s="48" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E261" s="48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F261" s="48" t="n">
-        <v>-18</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="262">
@@ -22852,17 +22830,17 @@
       </c>
       <c r="C262" s="48" t="inlineStr">
         <is>
-          <t>Visita fora do expediente/fim de semana</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D262" s="48" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E262" s="48" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F262" s="48" t="n">
-        <v>-1</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="263">
@@ -22878,69 +22856,69 @@
       </c>
       <c r="C263" s="48" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Visita fora do expediente/fim de semana</t>
         </is>
       </c>
       <c r="D263" s="48" t="n">
         <v>1</v>
       </c>
       <c r="E263" s="48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F263" s="48" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="48" t="inlineStr">
+        <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B264" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C264" s="48" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D264" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E264" s="48" t="n">
         <v>0.3</v>
       </c>
-      <c r="F263" s="48" t="n">
+      <c r="F264" s="48" t="n">
         <v>-0.6</v>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" s="47" t="inlineStr">
+    <row r="265">
+      <c r="A265" s="47" t="inlineStr">
         <is>
           <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
-      <c r="B264" s="47" t="inlineStr">
+      <c r="B265" s="47" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C264" s="47" t="inlineStr">
+      <c r="C265" s="47" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D264" s="47" t="n">
+      <c r="D265" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="E264" s="47" t="n">
+      <c r="E265" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F264" s="47" t="n">
+      <c r="F265" s="47" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="48" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="B265" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C265" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D265" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="E265" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F265" s="48" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="266">
@@ -22956,17 +22934,17 @@
       </c>
       <c r="C266" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D266" s="48" t="n">
         <v>2</v>
       </c>
       <c r="E266" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F266" s="48" t="n">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="267">
@@ -22982,7 +22960,7 @@
       </c>
       <c r="C267" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D267" s="48" t="n">
@@ -23008,17 +22986,17 @@
       </c>
       <c r="C268" s="48" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D268" s="48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E268" s="48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F268" s="48" t="n">
-        <v>-9</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="269">
@@ -23034,43 +23012,43 @@
       </c>
       <c r="C269" s="48" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D269" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E269" s="48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F269" s="48" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="48" t="inlineStr">
+        <is>
+          <t>Sara Eliane Talaveira de Oliveira</t>
+        </is>
+      </c>
+      <c r="B270" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C270" s="48" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D269" s="48" t="n">
+      <c r="D270" s="48" t="n">
         <v>11</v>
       </c>
-      <c r="E269" s="48" t="n">
+      <c r="E270" s="48" t="n">
         <v>0.3</v>
       </c>
-      <c r="F269" s="48" t="n">
+      <c r="F270" s="48" t="n">
         <v>-6.6</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="47" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="B270" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C270" s="47" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D270" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E270" s="47" t="n">
-        <v>5</v>
-      </c>
-      <c r="F270" s="47" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="271">
@@ -23086,43 +23064,43 @@
       </c>
       <c r="C271" s="47" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D271" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E271" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F271" s="47" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="47" t="inlineStr">
+        <is>
+          <t>Selba Ramona Afonso</t>
+        </is>
+      </c>
+      <c r="B272" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C272" s="47" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D271" s="47" t="n">
+      <c r="D272" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="E271" s="47" t="n">
+      <c r="E272" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F271" s="47" t="n">
+      <c r="F272" s="47" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="48" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="B272" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C272" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D272" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E272" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F272" s="48" t="n">
-        <v>-0.5</v>
       </c>
     </row>
     <row r="273">
@@ -23138,17 +23116,17 @@
       </c>
       <c r="C273" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D273" s="48" t="n">
         <v>1</v>
       </c>
       <c r="E273" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F273" s="48" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="274">
@@ -23164,7 +23142,7 @@
       </c>
       <c r="C274" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D274" s="48" t="n">
@@ -23190,69 +23168,69 @@
       </c>
       <c r="C275" s="48" t="inlineStr">
         <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D275" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E275" s="48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F275" s="48" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="48" t="inlineStr">
+        <is>
+          <t>Selba Ramona Afonso</t>
+        </is>
+      </c>
+      <c r="B276" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C276" s="48" t="inlineStr">
+        <is>
           <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
-      <c r="D275" s="48" t="n">
+      <c r="D276" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="E275" s="48" t="n">
+      <c r="E276" s="48" t="n">
         <v>1.5</v>
       </c>
-      <c r="F275" s="48" t="n">
+      <c r="F276" s="48" t="n">
         <v>-12</v>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" s="47" t="inlineStr">
+    <row r="277">
+      <c r="A277" s="47" t="inlineStr">
         <is>
           <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
-      <c r="B276" s="47" t="inlineStr">
+      <c r="B277" s="47" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C276" s="47" t="inlineStr">
+      <c r="C277" s="47" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D276" s="47" t="n">
+      <c r="D277" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="E276" s="47" t="n">
+      <c r="E277" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F276" s="47" t="n">
+      <c r="F277" s="47" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="48" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-      <c r="B277" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C277" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D277" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="E277" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F277" s="48" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="278">
@@ -23268,17 +23246,17 @@
       </c>
       <c r="C278" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D278" s="48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E278" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F278" s="48" t="n">
-        <v>-2.4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="279">
@@ -23294,17 +23272,17 @@
       </c>
       <c r="C279" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D279" s="48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E279" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F279" s="48" t="n">
-        <v>-1.8</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="280">
@@ -23320,17 +23298,17 @@
       </c>
       <c r="C280" s="48" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D280" s="48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E280" s="48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F280" s="48" t="n">
-        <v>-6</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="281">
@@ -23346,43 +23324,43 @@
       </c>
       <c r="C281" s="48" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D281" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E281" s="48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F281" s="48" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="48" t="inlineStr">
+        <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B282" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C282" s="48" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D281" s="48" t="n">
+      <c r="D282" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="E281" s="48" t="n">
+      <c r="E282" s="48" t="n">
         <v>0.3</v>
       </c>
-      <c r="F281" s="48" t="n">
+      <c r="F282" s="48" t="n">
         <v>-3</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="47" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B282" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C282" s="47" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D282" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E282" s="47" t="n">
-        <v>5</v>
-      </c>
-      <c r="F282" s="47" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="283">
@@ -23398,43 +23376,43 @@
       </c>
       <c r="C283" s="47" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D283" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E283" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F283" s="47" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="47" t="inlineStr">
+        <is>
+          <t>Suely Aguiar Alves Luiz</t>
+        </is>
+      </c>
+      <c r="B284" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C284" s="47" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D283" s="47" t="n">
+      <c r="D284" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="E283" s="47" t="n">
+      <c r="E284" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F283" s="47" t="n">
+      <c r="F284" s="47" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="48" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B284" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C284" s="48" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D284" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="E284" s="48" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F284" s="48" t="n">
-        <v>-1.2</v>
       </c>
     </row>
     <row r="285">
@@ -23450,17 +23428,17 @@
       </c>
       <c r="C285" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D285" s="48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E285" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F285" s="48" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="286">
@@ -23476,17 +23454,17 @@
       </c>
       <c r="C286" s="48" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D286" s="48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E286" s="48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F286" s="48" t="n">
-        <v>-6</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="287">
@@ -23502,43 +23480,43 @@
       </c>
       <c r="C287" s="48" t="inlineStr">
         <is>
-          <t>Visita em sequência suspeita</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D287" s="48" t="n">
         <v>2</v>
       </c>
       <c r="E287" s="48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F287" s="48" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="48" t="inlineStr">
+        <is>
+          <t>Suely Aguiar Alves Luiz</t>
+        </is>
+      </c>
+      <c r="B288" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C288" s="48" t="inlineStr">
+        <is>
+          <t>Visita em sequência suspeita</t>
+        </is>
+      </c>
+      <c r="D288" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E288" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="F287" s="48" t="n">
+      <c r="F288" s="48" t="n">
         <v>-4</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="47" t="inlineStr">
-        <is>
-          <t>Tania Maria Montania</t>
-        </is>
-      </c>
-      <c r="B288" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C288" s="47" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D288" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E288" s="47" t="n">
-        <v>5</v>
-      </c>
-      <c r="F288" s="47" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="289">
@@ -23554,43 +23532,43 @@
       </c>
       <c r="C289" s="47" t="inlineStr">
         <is>
-          <t>Dia com meta diária batida</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D289" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E289" s="47" t="n">
         <v>5</v>
-      </c>
-      <c r="E289" s="47" t="n">
-        <v>1</v>
       </c>
       <c r="F289" s="47" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="48" t="inlineStr">
+      <c r="A290" s="47" t="inlineStr">
         <is>
           <t>Tania Maria Montania</t>
         </is>
       </c>
-      <c r="B290" s="48" t="inlineStr">
+      <c r="B290" s="47" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C290" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D290" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="E290" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F290" s="48" t="n">
-        <v>-1</v>
+      <c r="C290" s="47" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D290" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="E290" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F290" s="47" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="291">
@@ -23606,17 +23584,17 @@
       </c>
       <c r="C291" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D291" s="48" t="n">
         <v>2</v>
       </c>
       <c r="E291" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F291" s="48" t="n">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="292">
@@ -23632,17 +23610,17 @@
       </c>
       <c r="C292" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D292" s="48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E292" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F292" s="48" t="n">
-        <v>-1.8</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="293">
@@ -23658,17 +23636,17 @@
       </c>
       <c r="C293" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D293" s="48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E293" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F293" s="48" t="n">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="294">
@@ -23684,7 +23662,7 @@
       </c>
       <c r="C294" s="48" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D294" s="48" t="n">
@@ -23698,29 +23676,29 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="47" t="inlineStr">
-        <is>
-          <t>Wagner Tarlei Gomes</t>
-        </is>
-      </c>
-      <c r="B295" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C295" s="47" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D295" s="47" t="n">
+      <c r="A295" s="48" t="inlineStr">
+        <is>
+          <t>Tania Maria Montania</t>
+        </is>
+      </c>
+      <c r="B295" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C295" s="48" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D295" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="E295" s="47" t="n">
-        <v>5</v>
-      </c>
-      <c r="F295" s="47" t="n">
-        <v>5</v>
+      <c r="E295" s="48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F295" s="48" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="296">
@@ -23736,43 +23714,43 @@
       </c>
       <c r="C296" s="47" t="inlineStr">
         <is>
-          <t>Dia com meta diária batida</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D296" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E296" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F296" s="47" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="47" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="B297" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C297" s="47" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D297" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F296" s="47" t="n">
+      <c r="E297" s="47" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="48" t="inlineStr">
-        <is>
-          <t>Wagner Tarlei Gomes</t>
-        </is>
-      </c>
-      <c r="B297" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C297" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D297" s="48" t="n">
+      <c r="F297" s="47" t="n">
         <v>1</v>
-      </c>
-      <c r="E297" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F297" s="48" t="n">
-        <v>-0.5</v>
       </c>
     </row>
     <row r="298">
@@ -23788,17 +23766,17 @@
       </c>
       <c r="C298" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D298" s="48" t="n">
         <v>1</v>
       </c>
       <c r="E298" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F298" s="48" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="299">
@@ -23814,7 +23792,7 @@
       </c>
       <c r="C299" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D299" s="48" t="n">
@@ -23840,7 +23818,7 @@
       </c>
       <c r="C300" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D300" s="48" t="n">
@@ -23866,69 +23844,69 @@
       </c>
       <c r="C301" s="48" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D301" s="48" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E301" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F301" s="48" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="48" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="B302" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C302" s="48" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D302" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="E302" s="48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F302" s="48" t="n">
         <v>-4.8</v>
       </c>
     </row>
-    <row r="302">
-      <c r="A302" s="47" t="inlineStr">
+    <row r="303">
+      <c r="A303" s="47" t="inlineStr">
         <is>
           <t>Walquiria Araujo Flores</t>
         </is>
       </c>
-      <c r="B302" s="47" t="inlineStr">
+      <c r="B303" s="47" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C302" s="47" t="inlineStr">
+      <c r="C303" s="47" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D302" s="47" t="n">
+      <c r="D303" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="E302" s="47" t="n">
+      <c r="E303" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F302" s="47" t="n">
+      <c r="F303" s="47" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="48" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="B303" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C303" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D303" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="E303" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F303" s="48" t="n">
-        <v>-1.5</v>
       </c>
     </row>
     <row r="304">
@@ -23944,17 +23922,17 @@
       </c>
       <c r="C304" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D304" s="48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E304" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F304" s="48" t="n">
-        <v>-0.6</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="305">
@@ -23970,17 +23948,17 @@
       </c>
       <c r="C305" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D305" s="48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E305" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F305" s="48" t="n">
-        <v>-2.4</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="306">
@@ -23996,17 +23974,17 @@
       </c>
       <c r="C306" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D306" s="48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E306" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F306" s="48" t="n">
-        <v>-1.2</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="307">
@@ -24022,17 +24000,17 @@
       </c>
       <c r="C307" s="48" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D307" s="48" t="n">
         <v>2</v>
       </c>
       <c r="E307" s="48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F307" s="48" t="n">
-        <v>-6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="308">
@@ -24048,69 +24026,69 @@
       </c>
       <c r="C308" s="48" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D308" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E308" s="48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F308" s="48" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="48" t="inlineStr">
+        <is>
+          <t>Walquiria Araujo Flores</t>
+        </is>
+      </c>
+      <c r="B309" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C309" s="48" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D308" s="48" t="n">
+      <c r="D309" s="48" t="n">
         <v>15</v>
       </c>
-      <c r="E308" s="48" t="n">
+      <c r="E309" s="48" t="n">
         <v>0.3</v>
       </c>
-      <c r="F308" s="48" t="n">
+      <c r="F309" s="48" t="n">
         <v>-9</v>
       </c>
     </row>
-    <row r="309">
-      <c r="A309" s="47" t="inlineStr">
+    <row r="310">
+      <c r="A310" s="47" t="inlineStr">
         <is>
           <t>Wesley de Souza Leal</t>
         </is>
       </c>
-      <c r="B309" s="47" t="inlineStr">
+      <c r="B310" s="47" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C309" s="47" t="inlineStr">
+      <c r="C310" s="47" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D309" s="47" t="n">
+      <c r="D310" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="E309" s="47" t="n">
+      <c r="E310" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F309" s="47" t="n">
+      <c r="F310" s="47" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="48" t="inlineStr">
-        <is>
-          <t>Wesley de Souza Leal</t>
-        </is>
-      </c>
-      <c r="B310" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C310" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D310" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="E310" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F310" s="48" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="311">
@@ -24126,17 +24104,17 @@
       </c>
       <c r="C311" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D311" s="48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E311" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F311" s="48" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="312">
@@ -24152,17 +24130,17 @@
       </c>
       <c r="C312" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D312" s="48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E312" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F312" s="48" t="n">
-        <v>-1.8</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="313">
@@ -24178,17 +24156,17 @@
       </c>
       <c r="C313" s="48" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D313" s="48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E313" s="48" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F313" s="48" t="n">
-        <v>-6</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="314">
@@ -24204,43 +24182,43 @@
       </c>
       <c r="C314" s="48" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D314" s="48" t="n">
         <v>2</v>
       </c>
       <c r="E314" s="48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F314" s="48" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="48" t="inlineStr">
+        <is>
+          <t>Wesley de Souza Leal</t>
+        </is>
+      </c>
+      <c r="B315" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C315" s="48" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D315" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E315" s="48" t="n">
         <v>0.3</v>
       </c>
-      <c r="F314" s="48" t="n">
+      <c r="F315" s="48" t="n">
         <v>-1.2</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="47" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B315" s="47" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C315" s="47" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D315" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E315" s="47" t="n">
-        <v>5</v>
-      </c>
-      <c r="F315" s="47" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="316">
@@ -24256,43 +24234,43 @@
       </c>
       <c r="C316" s="47" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D316" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E316" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F316" s="47" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="47" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B317" s="47" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C317" s="47" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D316" s="47" t="n">
+      <c r="D317" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="E316" s="47" t="n">
+      <c r="E317" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F316" s="47" t="n">
+      <c r="F317" s="47" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="48" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B317" s="48" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C317" s="48" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D317" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="E317" s="48" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F317" s="48" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="318">
@@ -24308,17 +24286,17 @@
       </c>
       <c r="C318" s="48" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D318" s="48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E318" s="48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F318" s="48" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="319">
@@ -24334,17 +24312,17 @@
       </c>
       <c r="C319" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D319" s="48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E319" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F319" s="48" t="n">
-        <v>-1.8</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="320">
@@ -24360,7 +24338,7 @@
       </c>
       <c r="C320" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D320" s="48" t="n">
@@ -24386,16 +24364,42 @@
       </c>
       <c r="C321" s="48" t="inlineStr">
         <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D321" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E321" s="48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F321" s="48" t="n">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="48" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B322" s="48" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C322" s="48" t="inlineStr">
+        <is>
           <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
-      <c r="D321" s="48" t="n">
+      <c r="D322" s="48" t="n">
         <v>2</v>
       </c>
-      <c r="E321" s="48" t="n">
+      <c r="E322" s="48" t="n">
         <v>1.5</v>
       </c>
-      <c r="F321" s="48" t="n">
+      <c r="F322" s="48" t="n">
         <v>-6</v>
       </c>
     </row>
@@ -24959,56 +24963,56 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>410 - SALGADO FILHO</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F11" s="6" t="n">
+      <c r="D11" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Q010, Q011, Q012</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G11" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Q011, Q012</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>15.38</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>25.71</v>
-      </c>
-      <c r="N11" s="6" t="inlineStr">
-        <is>
-          <t>🟡 ATENÇÃO</t>
+      <c r="J11" s="4" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>32.89</v>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
@@ -31726,7 +31730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -31741,7 +31745,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (112 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
+          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (110 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -33050,11 +33054,11 @@
     </row>
     <row r="39">
       <c r="A39" s="34" t="n">
-        <v>470</v>
+        <v>1935</v>
       </c>
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>Cris Milene Cardenas da Silva</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="C39" s="34" t="inlineStr">
@@ -33085,11 +33089,11 @@
     </row>
     <row r="40">
       <c r="A40" s="34" t="n">
-        <v>1935</v>
+        <v>30</v>
       </c>
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="C40" s="34" t="inlineStr">
@@ -33120,11 +33124,11 @@
     </row>
     <row r="41">
       <c r="A41" s="34" t="n">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="B41" s="34" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="C41" s="34" t="inlineStr">
@@ -33144,7 +33148,7 @@
       </c>
       <c r="F41" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G41" s="34" t="inlineStr">
@@ -33155,11 +33159,11 @@
     </row>
     <row r="42">
       <c r="A42" s="34" t="n">
-        <v>73</v>
+        <v>1935</v>
       </c>
       <c r="B42" s="34" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="C42" s="34" t="inlineStr">
@@ -33190,11 +33194,11 @@
     </row>
     <row r="43">
       <c r="A43" s="34" t="n">
-        <v>470</v>
+        <v>30</v>
       </c>
       <c r="B43" s="34" t="inlineStr">
         <is>
-          <t>Cris Milene Cardenas da Silva</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="C43" s="34" t="inlineStr">
@@ -33225,31 +33229,31 @@
     </row>
     <row r="44">
       <c r="A44" s="34" t="n">
-        <v>1935</v>
+        <v>2917</v>
       </c>
       <c r="B44" s="34" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
       <c r="C44" s="34" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D44" s="34" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E44" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F44" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G44" s="34" t="inlineStr">
@@ -33260,31 +33264,31 @@
     </row>
     <row r="45">
       <c r="A45" s="34" t="n">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="B45" s="34" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="C45" s="34" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D45" s="34" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E45" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F45" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G45" s="34" t="inlineStr">
@@ -33295,11 +33299,11 @@
     </row>
     <row r="46">
       <c r="A46" s="34" t="n">
-        <v>2917</v>
+        <v>151</v>
       </c>
       <c r="B46" s="34" t="inlineStr">
         <is>
-          <t>Bianca Afonso Narbaez</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="C46" s="34" t="inlineStr">
@@ -33330,11 +33334,11 @@
     </row>
     <row r="47">
       <c r="A47" s="34" t="n">
-        <v>99</v>
+        <v>3127</v>
       </c>
       <c r="B47" s="34" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C47" s="34" t="inlineStr">
@@ -33365,11 +33369,11 @@
     </row>
     <row r="48">
       <c r="A48" s="34" t="n">
-        <v>151</v>
+        <v>465</v>
       </c>
       <c r="B48" s="34" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="C48" s="34" t="inlineStr">
@@ -33400,11 +33404,11 @@
     </row>
     <row r="49">
       <c r="A49" s="34" t="n">
-        <v>3127</v>
+        <v>81</v>
       </c>
       <c r="B49" s="34" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="C49" s="34" t="inlineStr">
@@ -33435,11 +33439,11 @@
     </row>
     <row r="50">
       <c r="A50" s="34" t="n">
-        <v>465</v>
+        <v>142</v>
       </c>
       <c r="B50" s="34" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C50" s="34" t="inlineStr">
@@ -33470,11 +33474,11 @@
     </row>
     <row r="51">
       <c r="A51" s="34" t="n">
-        <v>81</v>
+        <v>2917</v>
       </c>
       <c r="B51" s="34" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
       <c r="C51" s="34" t="inlineStr">
@@ -33494,7 +33498,7 @@
       </c>
       <c r="F51" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G51" s="34" t="inlineStr">
@@ -33505,11 +33509,11 @@
     </row>
     <row r="52">
       <c r="A52" s="34" t="n">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="B52" s="34" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="C52" s="34" t="inlineStr">
@@ -33529,7 +33533,7 @@
       </c>
       <c r="F52" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G52" s="34" t="inlineStr">
@@ -33540,11 +33544,11 @@
     </row>
     <row r="53">
       <c r="A53" s="34" t="n">
-        <v>2917</v>
+        <v>151</v>
       </c>
       <c r="B53" s="34" t="inlineStr">
         <is>
-          <t>Bianca Afonso Narbaez</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="C53" s="34" t="inlineStr">
@@ -33575,11 +33579,11 @@
     </row>
     <row r="54">
       <c r="A54" s="34" t="n">
-        <v>99</v>
+        <v>3127</v>
       </c>
       <c r="B54" s="34" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C54" s="34" t="inlineStr">
@@ -33610,11 +33614,11 @@
     </row>
     <row r="55">
       <c r="A55" s="34" t="n">
-        <v>151</v>
+        <v>2030</v>
       </c>
       <c r="B55" s="34" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="C55" s="34" t="inlineStr">
@@ -33645,11 +33649,11 @@
     </row>
     <row r="56">
       <c r="A56" s="34" t="n">
-        <v>3127</v>
+        <v>465</v>
       </c>
       <c r="B56" s="34" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="C56" s="34" t="inlineStr">
@@ -33680,11 +33684,11 @@
     </row>
     <row r="57">
       <c r="A57" s="34" t="n">
-        <v>2030</v>
+        <v>81</v>
       </c>
       <c r="B57" s="34" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="C57" s="34" t="inlineStr">
@@ -33715,11 +33719,11 @@
     </row>
     <row r="58">
       <c r="A58" s="34" t="n">
-        <v>465</v>
+        <v>142</v>
       </c>
       <c r="B58" s="34" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C58" s="34" t="inlineStr">
@@ -33750,11 +33754,11 @@
     </row>
     <row r="59">
       <c r="A59" s="34" t="n">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="B59" s="34" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="C59" s="34" t="inlineStr">
@@ -33764,17 +33768,17 @@
       </c>
       <c r="D59" s="34" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E59" s="34" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F59" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G59" s="34" t="inlineStr">
@@ -33785,11 +33789,11 @@
     </row>
     <row r="60">
       <c r="A60" s="34" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B60" s="34" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="C60" s="34" t="inlineStr">
@@ -33799,102 +33803,102 @@
       </c>
       <c r="D60" s="34" t="inlineStr">
         <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="E60" s="34" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="F60" s="34" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G60" s="34" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="35" t="n">
+        <v>2918</v>
+      </c>
+      <c r="B61" s="35" t="inlineStr">
+        <is>
+          <t>Claine Luisa Figueiredo Torraca</t>
+        </is>
+      </c>
+      <c r="C61" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="D61" s="35" t="inlineStr">
+        <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E60" s="34" t="inlineStr">
+      <c r="E61" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F60" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G60" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="34" t="n">
-        <v>151</v>
-      </c>
-      <c r="B61" s="34" t="inlineStr">
-        <is>
-          <t>Gilmar Bitencourt Luiz</t>
-        </is>
-      </c>
-      <c r="C61" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="D61" s="34" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="E61" s="34" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F61" s="34" t="inlineStr">
+      <c r="F61" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G61" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+      <c r="G61" s="35" t="inlineStr">
+        <is>
+          <t>TODA A EQUIPE (8 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="34" t="n">
-        <v>151</v>
-      </c>
-      <c r="B62" s="34" t="inlineStr">
-        <is>
-          <t>Gilmar Bitencourt Luiz</t>
-        </is>
-      </c>
-      <c r="C62" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="D62" s="34" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="E62" s="34" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F62" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G62" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+      <c r="A62" s="35" t="n">
+        <v>120</v>
+      </c>
+      <c r="B62" s="35" t="inlineStr">
+        <is>
+          <t>Emidio Rainer Vilhalba</t>
+        </is>
+      </c>
+      <c r="C62" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="D62" s="35" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E62" s="35" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="F62" s="35" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G62" s="35" t="inlineStr">
+        <is>
+          <t>TODA A EQUIPE (8 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="35" t="n">
-        <v>2918</v>
+        <v>1936</v>
       </c>
       <c r="B63" s="35" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C63" s="35" t="inlineStr">
@@ -33925,11 +33929,11 @@
     </row>
     <row r="64">
       <c r="A64" s="35" t="n">
-        <v>120</v>
+        <v>1938</v>
       </c>
       <c r="B64" s="35" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C64" s="35" t="inlineStr">
@@ -33960,11 +33964,11 @@
     </row>
     <row r="65">
       <c r="A65" s="35" t="n">
-        <v>1936</v>
+        <v>2721</v>
       </c>
       <c r="B65" s="35" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C65" s="35" t="inlineStr">
@@ -33995,11 +33999,11 @@
     </row>
     <row r="66">
       <c r="A66" s="35" t="n">
-        <v>1938</v>
+        <v>3038</v>
       </c>
       <c r="B66" s="35" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C66" s="35" t="inlineStr">
@@ -34030,11 +34034,11 @@
     </row>
     <row r="67">
       <c r="A67" s="35" t="n">
-        <v>2721</v>
+        <v>3128</v>
       </c>
       <c r="B67" s="35" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C67" s="35" t="inlineStr">
@@ -34065,11 +34069,11 @@
     </row>
     <row r="68">
       <c r="A68" s="35" t="n">
-        <v>3038</v>
+        <v>113</v>
       </c>
       <c r="B68" s="35" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C68" s="35" t="inlineStr">
@@ -34099,82 +34103,82 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="35" t="n">
-        <v>3128</v>
-      </c>
-      <c r="B69" s="35" t="inlineStr">
-        <is>
-          <t>Rosalina Beniel Vargas</t>
-        </is>
-      </c>
-      <c r="C69" s="35" t="inlineStr">
+      <c r="A69" s="34" t="n">
+        <v>2918</v>
+      </c>
+      <c r="B69" s="34" t="inlineStr">
+        <is>
+          <t>Claine Luisa Figueiredo Torraca</t>
+        </is>
+      </c>
+      <c r="C69" s="34" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D69" s="35" t="inlineStr">
+      <c r="D69" s="34" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E69" s="35" t="inlineStr">
+      <c r="E69" s="34" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F69" s="35" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G69" s="35" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (8 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+      <c r="F69" s="34" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G69" s="34" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="35" t="n">
-        <v>113</v>
-      </c>
-      <c r="B70" s="35" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="C70" s="35" t="inlineStr">
+      <c r="A70" s="34" t="n">
+        <v>120</v>
+      </c>
+      <c r="B70" s="34" t="inlineStr">
+        <is>
+          <t>Emidio Rainer Vilhalba</t>
+        </is>
+      </c>
+      <c r="C70" s="34" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D70" s="35" t="inlineStr">
+      <c r="D70" s="34" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E70" s="35" t="inlineStr">
+      <c r="E70" s="34" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F70" s="35" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G70" s="35" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (8 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+      <c r="F70" s="34" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G70" s="34" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="34" t="n">
-        <v>2918</v>
+        <v>1936</v>
       </c>
       <c r="B71" s="34" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C71" s="34" t="inlineStr">
@@ -34205,11 +34209,11 @@
     </row>
     <row r="72">
       <c r="A72" s="34" t="n">
-        <v>120</v>
+        <v>1938</v>
       </c>
       <c r="B72" s="34" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C72" s="34" t="inlineStr">
@@ -34240,11 +34244,11 @@
     </row>
     <row r="73">
       <c r="A73" s="34" t="n">
-        <v>1936</v>
+        <v>3038</v>
       </c>
       <c r="B73" s="34" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C73" s="34" t="inlineStr">
@@ -34275,11 +34279,11 @@
     </row>
     <row r="74">
       <c r="A74" s="34" t="n">
-        <v>1938</v>
+        <v>3128</v>
       </c>
       <c r="B74" s="34" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C74" s="34" t="inlineStr">
@@ -34310,11 +34314,11 @@
     </row>
     <row r="75">
       <c r="A75" s="34" t="n">
-        <v>3038</v>
+        <v>113</v>
       </c>
       <c r="B75" s="34" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C75" s="34" t="inlineStr">
@@ -34345,11 +34349,11 @@
     </row>
     <row r="76">
       <c r="A76" s="34" t="n">
-        <v>3128</v>
+        <v>1938</v>
       </c>
       <c r="B76" s="34" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C76" s="34" t="inlineStr">
@@ -34359,17 +34363,17 @@
       </c>
       <c r="D76" s="34" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E76" s="34" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F76" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G76" s="34" t="inlineStr">
@@ -34380,11 +34384,11 @@
     </row>
     <row r="77">
       <c r="A77" s="34" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B77" s="34" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C77" s="34" t="inlineStr">
@@ -34394,12 +34398,12 @@
       </c>
       <c r="D77" s="34" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E77" s="34" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F77" s="34" t="inlineStr">
@@ -34439,7 +34443,7 @@
       </c>
       <c r="F78" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G78" s="34" t="inlineStr">
@@ -34450,11 +34454,11 @@
     </row>
     <row r="79">
       <c r="A79" s="34" t="n">
-        <v>120</v>
+        <v>3038</v>
       </c>
       <c r="B79" s="34" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C79" s="34" t="inlineStr">
@@ -34464,17 +34468,17 @@
       </c>
       <c r="D79" s="34" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E79" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F79" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G79" s="34" t="inlineStr">
@@ -34485,11 +34489,11 @@
     </row>
     <row r="80">
       <c r="A80" s="34" t="n">
-        <v>1938</v>
+        <v>113</v>
       </c>
       <c r="B80" s="34" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C80" s="34" t="inlineStr">
@@ -34499,17 +34503,17 @@
       </c>
       <c r="D80" s="34" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E80" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F80" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G80" s="34" t="inlineStr">
@@ -34544,7 +34548,7 @@
       </c>
       <c r="F81" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G81" s="34" t="inlineStr">
@@ -34579,7 +34583,7 @@
       </c>
       <c r="F82" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G82" s="34" t="inlineStr">
@@ -34590,31 +34594,31 @@
     </row>
     <row r="83">
       <c r="A83" s="34" t="n">
-        <v>3038</v>
+        <v>110</v>
       </c>
       <c r="B83" s="34" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C83" s="34" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D83" s="34" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E83" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F83" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G83" s="34" t="inlineStr">
@@ -34625,31 +34629,31 @@
     </row>
     <row r="84">
       <c r="A84" s="34" t="n">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="B84" s="34" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C84" s="34" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D84" s="34" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E84" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G84" s="34" t="inlineStr">
@@ -34660,11 +34664,11 @@
     </row>
     <row r="85">
       <c r="A85" s="34" t="n">
-        <v>110</v>
+        <v>1943</v>
       </c>
       <c r="B85" s="34" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C85" s="34" t="inlineStr">
@@ -34695,11 +34699,11 @@
     </row>
     <row r="86">
       <c r="A86" s="34" t="n">
-        <v>80</v>
+        <v>2789</v>
       </c>
       <c r="B86" s="34" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C86" s="34" t="inlineStr">
@@ -34730,11 +34734,11 @@
     </row>
     <row r="87">
       <c r="A87" s="34" t="n">
-        <v>1943</v>
+        <v>149</v>
       </c>
       <c r="B87" s="34" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C87" s="34" t="inlineStr">
@@ -34765,11 +34769,11 @@
     </row>
     <row r="88">
       <c r="A88" s="34" t="n">
-        <v>2789</v>
+        <v>1942</v>
       </c>
       <c r="B88" s="34" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C88" s="34" t="inlineStr">
@@ -34800,11 +34804,11 @@
     </row>
     <row r="89">
       <c r="A89" s="34" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="B89" s="34" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C89" s="34" t="inlineStr">
@@ -34835,11 +34839,11 @@
     </row>
     <row r="90">
       <c r="A90" s="34" t="n">
-        <v>1942</v>
+        <v>1996</v>
       </c>
       <c r="B90" s="34" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C90" s="34" t="inlineStr">
@@ -34870,11 +34874,11 @@
     </row>
     <row r="91">
       <c r="A91" s="34" t="n">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="B91" s="34" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C91" s="34" t="inlineStr">
@@ -34905,11 +34909,11 @@
     </row>
     <row r="92">
       <c r="A92" s="34" t="n">
-        <v>1996</v>
+        <v>110</v>
       </c>
       <c r="B92" s="34" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C92" s="34" t="inlineStr">
@@ -34929,7 +34933,7 @@
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G92" s="34" t="inlineStr">
@@ -34940,11 +34944,11 @@
     </row>
     <row r="93">
       <c r="A93" s="34" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B93" s="34" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C93" s="34" t="inlineStr">
@@ -34964,7 +34968,7 @@
       </c>
       <c r="F93" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G93" s="34" t="inlineStr">
@@ -34975,11 +34979,11 @@
     </row>
     <row r="94">
       <c r="A94" s="34" t="n">
-        <v>110</v>
+        <v>1943</v>
       </c>
       <c r="B94" s="34" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C94" s="34" t="inlineStr">
@@ -35010,11 +35014,11 @@
     </row>
     <row r="95">
       <c r="A95" s="34" t="n">
-        <v>80</v>
+        <v>2789</v>
       </c>
       <c r="B95" s="34" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C95" s="34" t="inlineStr">
@@ -35045,11 +35049,11 @@
     </row>
     <row r="96">
       <c r="A96" s="34" t="n">
-        <v>1943</v>
+        <v>149</v>
       </c>
       <c r="B96" s="34" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C96" s="34" t="inlineStr">
@@ -35080,11 +35084,11 @@
     </row>
     <row r="97">
       <c r="A97" s="34" t="n">
-        <v>2789</v>
+        <v>1942</v>
       </c>
       <c r="B97" s="34" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C97" s="34" t="inlineStr">
@@ -35115,11 +35119,11 @@
     </row>
     <row r="98">
       <c r="A98" s="34" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="B98" s="34" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C98" s="34" t="inlineStr">
@@ -35150,11 +35154,11 @@
     </row>
     <row r="99">
       <c r="A99" s="34" t="n">
-        <v>1942</v>
+        <v>1996</v>
       </c>
       <c r="B99" s="34" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C99" s="34" t="inlineStr">
@@ -35185,11 +35189,11 @@
     </row>
     <row r="100">
       <c r="A100" s="34" t="n">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="B100" s="34" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C100" s="34" t="inlineStr">
@@ -35220,11 +35224,11 @@
     </row>
     <row r="101">
       <c r="A101" s="34" t="n">
-        <v>1996</v>
+        <v>157</v>
       </c>
       <c r="B101" s="34" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C101" s="34" t="inlineStr">
@@ -35255,11 +35259,11 @@
     </row>
     <row r="102">
       <c r="A102" s="34" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="B102" s="34" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C102" s="34" t="inlineStr">
@@ -35269,17 +35273,17 @@
       </c>
       <c r="D102" s="34" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E102" s="34" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G102" s="34" t="inlineStr">
@@ -35290,11 +35294,11 @@
     </row>
     <row r="103">
       <c r="A103" s="34" t="n">
-        <v>157</v>
+        <v>1943</v>
       </c>
       <c r="B103" s="34" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C103" s="34" t="inlineStr">
@@ -35304,17 +35308,17 @@
       </c>
       <c r="D103" s="34" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E103" s="34" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F103" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G103" s="34" t="inlineStr">
@@ -35349,7 +35353,7 @@
       </c>
       <c r="F104" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G104" s="34" t="inlineStr">
@@ -35360,11 +35364,11 @@
     </row>
     <row r="105">
       <c r="A105" s="34" t="n">
-        <v>1943</v>
+        <v>110</v>
       </c>
       <c r="B105" s="34" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C105" s="34" t="inlineStr">
@@ -35374,12 +35378,12 @@
       </c>
       <c r="D105" s="34" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E105" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F105" s="34" t="inlineStr">
@@ -35395,11 +35399,11 @@
     </row>
     <row r="106">
       <c r="A106" s="34" t="n">
-        <v>110</v>
+        <v>1943</v>
       </c>
       <c r="B106" s="34" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C106" s="34" t="inlineStr">
@@ -35409,17 +35413,17 @@
       </c>
       <c r="D106" s="34" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E106" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G106" s="34" t="inlineStr">
@@ -35430,11 +35434,11 @@
     </row>
     <row r="107">
       <c r="A107" s="34" t="n">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="B107" s="34" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C107" s="34" t="inlineStr">
@@ -35465,11 +35469,11 @@
     </row>
     <row r="108">
       <c r="A108" s="34" t="n">
-        <v>1943</v>
+        <v>110</v>
       </c>
       <c r="B108" s="34" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C108" s="34" t="inlineStr">
@@ -35489,7 +35493,7 @@
       </c>
       <c r="F108" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G108" s="34" t="inlineStr">
@@ -35500,11 +35504,11 @@
     </row>
     <row r="109">
       <c r="A109" s="34" t="n">
-        <v>161</v>
+        <v>1943</v>
       </c>
       <c r="B109" s="34" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C109" s="34" t="inlineStr">
@@ -35524,7 +35528,7 @@
       </c>
       <c r="F109" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G109" s="34" t="inlineStr">
@@ -35535,11 +35539,11 @@
     </row>
     <row r="110">
       <c r="A110" s="34" t="n">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="B110" s="34" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C110" s="34" t="inlineStr">
@@ -35570,11 +35574,11 @@
     </row>
     <row r="111">
       <c r="A111" s="34" t="n">
-        <v>1943</v>
+        <v>1996</v>
       </c>
       <c r="B111" s="34" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C111" s="34" t="inlineStr">
@@ -35605,11 +35609,11 @@
     </row>
     <row r="112">
       <c r="A112" s="34" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B112" s="34" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C112" s="34" t="inlineStr">
@@ -35638,78 +35642,8 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="34" t="n">
-        <v>1996</v>
-      </c>
-      <c r="B113" s="34" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="C113" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D113" s="34" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="E113" s="34" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F113" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G113" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="34" t="n">
-        <v>157</v>
-      </c>
-      <c r="B114" s="34" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="C114" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D114" s="34" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="E114" s="34" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F114" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G114" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G114"/>
+  <autoFilter ref="A2:G112"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/data/historico/semanas_318-321.xlsx
+++ b/data/historico/semanas_318-321.xlsx
@@ -30235,47 +30235,47 @@
     <row r="20">
       <c r="A20" s="27" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>16935897</t>
+          <t>16910075</t>
         </is>
       </c>
       <c r="D20" s="27" t="inlineStr">
         <is>
-          <t>417 - CENTRO 3</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E20" s="27" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="F20" s="27" t="inlineStr">
         <is>
-          <t>Avenida PRESIDENTE VARGAS</t>
+          <t>Rua CATANDUVA</t>
         </is>
       </c>
       <c r="G20" s="27" t="inlineStr">
         <is>
-          <t>725 - OU</t>
+          <t>490 - R</t>
         </is>
       </c>
       <c r="H20" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 09:40</t>
+          <t>13/08/2026 15:31</t>
         </is>
       </c>
       <c r="I20" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 09:58</t>
+          <t>13/08/2026 15:49</t>
         </is>
       </c>
       <c r="J20" s="27" t="n">
@@ -30335,47 +30335,47 @@
     <row r="22">
       <c r="A22" s="27" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C22" s="28" t="inlineStr">
         <is>
-          <t>16910075</t>
+          <t>16935897</t>
         </is>
       </c>
       <c r="D22" s="27" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>417 - CENTRO 3</t>
         </is>
       </c>
       <c r="E22" s="27" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F22" s="27" t="inlineStr">
         <is>
-          <t>Rua CATANDUVA</t>
+          <t>Avenida PRESIDENTE VARGAS</t>
         </is>
       </c>
       <c r="G22" s="27" t="inlineStr">
         <is>
-          <t>490 - R</t>
+          <t>725 - OU</t>
         </is>
       </c>
       <c r="H22" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:31</t>
+          <t>14/08/2026 09:40</t>
         </is>
       </c>
       <c r="I22" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:49</t>
+          <t>14/08/2026 09:58</t>
         </is>
       </c>
       <c r="J22" s="27" t="n">
@@ -30435,47 +30435,47 @@
     <row r="24">
       <c r="A24" s="27" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C24" s="28" t="inlineStr">
         <is>
-          <t>16932380</t>
+          <t>16881755</t>
         </is>
       </c>
       <c r="D24" s="27" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>406 - JARDIM PRIMAVERA</t>
         </is>
       </c>
       <c r="E24" s="27" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="F24" s="27" t="inlineStr">
         <is>
-          <t>Rua CURITIBA</t>
+          <t>Rua ELOAH VIEIRA DA SILVA</t>
         </is>
       </c>
       <c r="G24" s="27" t="inlineStr">
         <is>
-          <t>01 - TB</t>
+          <t>26 - 2 - TB</t>
         </is>
       </c>
       <c r="H24" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 15:51</t>
+          <t>12/08/2026 16:12</t>
         </is>
       </c>
       <c r="I24" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 16:08</t>
+          <t>12/08/2026 16:29</t>
         </is>
       </c>
       <c r="J24" s="27" t="n">
@@ -30485,47 +30485,47 @@
     <row r="25">
       <c r="A25" s="27" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>16904092</t>
+          <t>16910076</t>
         </is>
       </c>
       <c r="D25" s="27" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E25" s="27" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="F25" s="27" t="inlineStr">
         <is>
-          <t>Rua SÃO JOÃO DEL REI</t>
+          <t>Rua CATANDUVA</t>
         </is>
       </c>
       <c r="G25" s="27" t="inlineStr">
         <is>
-          <t>300 - R</t>
+          <t>166 - R</t>
         </is>
       </c>
       <c r="H25" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:14</t>
+          <t>13/08/2026 15:49</t>
         </is>
       </c>
       <c r="I25" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:31</t>
+          <t>13/08/2026 16:06</t>
         </is>
       </c>
       <c r="J25" s="27" t="n">
@@ -30635,47 +30635,47 @@
     <row r="28">
       <c r="A28" s="27" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>16910076</t>
+          <t>16932380</t>
         </is>
       </c>
       <c r="D28" s="27" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E28" s="27" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="F28" s="27" t="inlineStr">
         <is>
-          <t>Rua CATANDUVA</t>
+          <t>Rua CURITIBA</t>
         </is>
       </c>
       <c r="G28" s="27" t="inlineStr">
         <is>
-          <t>166 - R</t>
+          <t>01 - TB</t>
         </is>
       </c>
       <c r="H28" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:49</t>
+          <t>14/08/2026 15:51</t>
         </is>
       </c>
       <c r="I28" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 16:06</t>
+          <t>14/08/2026 16:08</t>
         </is>
       </c>
       <c r="J28" s="27" t="n">
@@ -30685,47 +30685,47 @@
     <row r="29">
       <c r="A29" s="27" t="inlineStr">
         <is>
-          <t>Raquel Ortiz dos Santos</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C29" s="28" t="inlineStr">
         <is>
-          <t>16881755</t>
+          <t>16904092</t>
         </is>
       </c>
       <c r="D29" s="27" t="inlineStr">
         <is>
-          <t>406 - JARDIM PRIMAVERA</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E29" s="27" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="F29" s="27" t="inlineStr">
         <is>
-          <t>Rua ELOAH VIEIRA DA SILVA</t>
+          <t>Rua SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="G29" s="27" t="inlineStr">
         <is>
-          <t>26 - 2 - TB</t>
+          <t>300 - R</t>
         </is>
       </c>
       <c r="H29" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 16:12</t>
+          <t>13/08/2026 15:14</t>
         </is>
       </c>
       <c r="I29" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 16:29</t>
+          <t>13/08/2026 15:31</t>
         </is>
       </c>
       <c r="J29" s="27" t="n">
@@ -30935,7 +30935,7 @@
     <row r="34">
       <c r="A34" s="27" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B34" s="27" t="inlineStr">
@@ -30945,37 +30945,37 @@
       </c>
       <c r="C34" s="28" t="inlineStr">
         <is>
-          <t>16929550</t>
+          <t>16932420</t>
         </is>
       </c>
       <c r="D34" s="27" t="inlineStr">
         <is>
-          <t>420 - FERROVIARIA</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E34" s="27" t="inlineStr">
         <is>
-          <t>Q003</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F34" s="27" t="inlineStr">
         <is>
-          <t>Rua ALAMEDA DOS TROLLES</t>
+          <t>Rua 18 DE JULHO</t>
         </is>
       </c>
       <c r="G34" s="27" t="inlineStr">
         <is>
-          <t>190 - R</t>
+          <t>187 - R</t>
         </is>
       </c>
       <c r="H34" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:31</t>
+          <t>14/08/2026 14:52</t>
         </is>
       </c>
       <c r="I34" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:47</t>
+          <t>14/08/2026 15:08</t>
         </is>
       </c>
       <c r="J34" s="27" t="n">
@@ -30985,7 +30985,7 @@
     <row r="35">
       <c r="A35" s="27" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B35" s="27" t="inlineStr">
@@ -30995,37 +30995,37 @@
       </c>
       <c r="C35" s="28" t="inlineStr">
         <is>
-          <t>16928880</t>
+          <t>16932419</t>
         </is>
       </c>
       <c r="D35" s="27" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E35" s="27" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F35" s="27" t="inlineStr">
         <is>
-          <t>Rua CALOGERAS</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="G35" s="27" t="inlineStr">
         <is>
-          <t>1325 - C</t>
+          <t>451 - R</t>
         </is>
       </c>
       <c r="H35" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 13:48</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="I35" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 14:04</t>
+          <t>14/08/2026 14:49</t>
         </is>
       </c>
       <c r="J35" s="27" t="n">
@@ -31035,7 +31035,7 @@
     <row r="36">
       <c r="A36" s="27" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="B36" s="27" t="inlineStr">
@@ -31045,37 +31045,37 @@
       </c>
       <c r="C36" s="28" t="inlineStr">
         <is>
-          <t>16932419</t>
+          <t>16929550</t>
         </is>
       </c>
       <c r="D36" s="27" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>420 - FERROVIARIA</t>
         </is>
       </c>
       <c r="E36" s="27" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q003</t>
         </is>
       </c>
       <c r="F36" s="27" t="inlineStr">
         <is>
-          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
+          <t>Rua ALAMEDA DOS TROLLES</t>
         </is>
       </c>
       <c r="G36" s="27" t="inlineStr">
         <is>
-          <t>451 - R</t>
+          <t>190 - R</t>
         </is>
       </c>
       <c r="H36" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>14/08/2026 14:31</t>
         </is>
       </c>
       <c r="I36" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:49</t>
+          <t>14/08/2026 14:47</t>
         </is>
       </c>
       <c r="J36" s="27" t="n">
@@ -31085,7 +31085,7 @@
     <row r="37">
       <c r="A37" s="27" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B37" s="27" t="inlineStr">
@@ -31095,37 +31095,37 @@
       </c>
       <c r="C37" s="28" t="inlineStr">
         <is>
-          <t>16932420</t>
+          <t>16928880</t>
         </is>
       </c>
       <c r="D37" s="27" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E37" s="27" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="F37" s="27" t="inlineStr">
         <is>
-          <t>Rua 18 DE JULHO</t>
+          <t>Rua CALOGERAS</t>
         </is>
       </c>
       <c r="G37" s="27" t="inlineStr">
         <is>
-          <t>187 - R</t>
+          <t>1325 - C</t>
         </is>
       </c>
       <c r="H37" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:52</t>
+          <t>12/08/2026 13:48</t>
         </is>
       </c>
       <c r="I37" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 15:08</t>
+          <t>12/08/2026 14:04</t>
         </is>
       </c>
       <c r="J37" s="27" t="n">

--- a/data/historico/semanas_318-321.xlsx
+++ b/data/historico/semanas_318-321.xlsx
@@ -31,8 +31,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 15min'!$A$2:$J$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$112</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Resumo Semanal'!$A$2:$AE$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Ranking'!$A$2:$E$42</definedName>
@@ -169,12 +169,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8E8E8"/>
+        <fgColor rgb="00FFD9A0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD9A0"/>
+        <fgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
     <fill>
@@ -5317,7 +5317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5329,7 +5329,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (17 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (15 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5361,12 +5361,12 @@
     <row r="3">
       <c r="A3" s="37" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="B3" s="37" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="C3" s="37" t="inlineStr">
@@ -5376,19 +5376,19 @@
       </c>
       <c r="D3" s="37" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="37" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="C4" s="37" t="inlineStr">
@@ -5398,19 +5398,19 @@
       </c>
       <c r="D4" s="37" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="37" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="B5" s="37" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="C5" s="37" t="inlineStr">
@@ -5420,14 +5420,14 @@
       </c>
       <c r="D5" s="37" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="37" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="B6" s="37" t="inlineStr">
@@ -5442,19 +5442,19 @@
       </c>
       <c r="D6" s="37" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="37" t="inlineStr">
         <is>
-          <t>20/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="B7" s="37" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="C7" s="37" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="D7" s="37" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="B8" s="37" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="C8" s="37" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="D8" s="37" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
     </row>
@@ -5601,53 +5601,53 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="37" t="inlineStr">
+      <c r="A14" s="39" t="inlineStr">
         <is>
           <t>07/08/2026</t>
         </is>
       </c>
-      <c r="B14" s="37" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="C14" s="37" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D14" s="37" t="inlineStr">
-        <is>
-          <t>Wagner Tarlei Gomes</t>
+      <c r="B14" s="39" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C14" s="39" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D14" s="39" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="37" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="37" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="C15" s="37" t="inlineStr">
-        <is>
-          <t>Férias/Atestado (automático)</t>
-        </is>
-      </c>
-      <c r="D15" s="37" t="inlineStr">
-        <is>
-          <t>Ramona dos Santos Oliveira</t>
+      <c r="A15" s="39" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="39" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="C15" s="39" t="inlineStr">
+        <is>
+          <t>Chuva (confirmada)</t>
+        </is>
+      </c>
+      <c r="D15" s="39" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="39" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="B16" s="39" t="inlineStr">
@@ -5662,78 +5662,34 @@
       </c>
       <c r="D16" s="39" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="39" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="39" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="C17" s="39" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D17" s="39" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="39" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="39" t="inlineStr">
-        <is>
-          <t>10/08/2026</t>
-        </is>
-      </c>
-      <c r="C18" s="39" t="inlineStr">
-        <is>
-          <t>Chuva (confirmada)</t>
-        </is>
-      </c>
-      <c r="D18" s="39" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="38" t="inlineStr">
+      <c r="A17" s="38" t="inlineStr">
         <is>
           <t>13/08/2026</t>
         </is>
       </c>
-      <c r="B19" s="38" t="inlineStr">
+      <c r="B17" s="38" t="inlineStr">
         <is>
           <t>13/08/2026</t>
         </is>
       </c>
-      <c r="C19" s="38" t="inlineStr">
+      <c r="C17" s="38" t="inlineStr">
         <is>
           <t>Recolha de Ovitrampa</t>
         </is>
       </c>
-      <c r="D19" s="38" t="inlineStr">
+      <c r="D17" s="38" t="inlineStr">
         <is>
           <t>Todos os agentes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D19"/>
+  <autoFilter ref="A2:D17"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -16309,16 +16265,16 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>98.90000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
@@ -16333,7 +16289,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -16342,7 +16298,7 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>98.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -16357,16 +16313,16 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>98.59999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
@@ -16381,7 +16337,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -16390,7 +16346,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>97.2</v>
+        <v>96.8</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
@@ -16405,16 +16361,16 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>96.8</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -16429,7 +16385,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -16438,7 +16394,7 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>94.40000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -16453,16 +16409,16 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>93.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
@@ -16472,25 +16428,25 @@
       <c r="F13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Wesley de Souza Leal</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Gilmar Bitencourt Luiz</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>🟢 EXCELENTE</t>
+      <c r="D14" s="6" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
         </is>
       </c>
       <c r="F14" s="2" t="n"/>
@@ -16501,16 +16457,16 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>89.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
@@ -16525,12 +16481,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D16" s="6" t="n">
@@ -16549,16 +16505,16 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Adriana de Jesus Saraiva</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>89.8</v>
+        <v>87.2</v>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
@@ -16573,16 +16529,16 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Ramona dos Santos Oliveira</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>88.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
@@ -16597,7 +16553,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Adriana de Jesus Saraiva</t>
+          <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -16606,7 +16562,7 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>87.2</v>
+        <v>85.8</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
@@ -16621,16 +16577,16 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>87.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
@@ -16645,16 +16601,16 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Cris Milene Cardenas da Silva</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>85.8</v>
+        <v>83.7</v>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
@@ -16669,16 +16625,16 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>84</v>
+        <v>83.3</v>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
@@ -16693,16 +16649,16 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>83.7</v>
+        <v>83</v>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
@@ -16717,16 +16673,16 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>83.3</v>
+        <v>83</v>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
@@ -16741,7 +16697,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -16750,7 +16706,7 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>83</v>
+        <v>82.2</v>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
@@ -16765,7 +16721,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -16774,7 +16730,7 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>83</v>
+        <v>81.3</v>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
@@ -16789,16 +16745,16 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>82.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
@@ -16813,16 +16769,16 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D28" s="6" t="n">
-        <v>81.3</v>
+        <v>79</v>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
@@ -16837,16 +16793,16 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>79.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
@@ -16861,16 +16817,16 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D30" s="6" t="n">
-        <v>79</v>
+        <v>78.7</v>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
@@ -16885,210 +16841,210 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="34" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="34" t="inlineStr">
+        <is>
+          <t>Gabriel Alan de Oliveira Martins</t>
+        </is>
+      </c>
+      <c r="C32" s="34" t="inlineStr">
+        <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>Gisele Olimpia Torres</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="D32" s="34" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="E32" s="34" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="34" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="34" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="C33" s="34" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D33" s="34" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="E33" s="34" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="34" t="inlineStr">
+        <is>
+          <t>Carlos Alberto Albiero</t>
+        </is>
+      </c>
+      <c r="C34" s="34" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D34" s="34" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="E34" s="34" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="34" t="inlineStr">
+        <is>
+          <t>Juliana Patricia Goncalves</t>
+        </is>
+      </c>
+      <c r="C35" s="34" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D35" s="34" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="E35" s="34" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="34" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="34" t="inlineStr">
+        <is>
+          <t>Ramona dos Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="C36" s="34" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D36" s="34" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="E36" s="34" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="34" t="inlineStr">
+        <is>
+          <t>Kariele Jackeline Rodrigues Silva</t>
+        </is>
+      </c>
+      <c r="C37" s="34" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D37" s="34" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="E37" s="34" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="34" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="34" t="inlineStr">
+        <is>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
+        </is>
+      </c>
+      <c r="C38" s="34" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
-        <v>78.7</v>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="D38" s="34" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="E38" s="34" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="34" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="34" t="inlineStr">
+        <is>
+          <t>Anderson Jose de Santana</t>
+        </is>
+      </c>
+      <c r="C39" s="34" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="35" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" s="35" t="inlineStr">
-        <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
-        </is>
-      </c>
-      <c r="C34" s="35" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="D34" s="35" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="E34" s="35" t="inlineStr">
-        <is>
-          <t>🟠 ATENÇÃO</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="35" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" s="35" t="inlineStr">
-        <is>
-          <t>Carlos Alberto Albiero</t>
-        </is>
-      </c>
-      <c r="C35" s="35" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="D35" s="35" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="E35" s="35" t="inlineStr">
-        <is>
-          <t>🟠 ATENÇÃO</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" s="35" t="inlineStr">
-        <is>
-          <t>Juliana Patricia Goncalves</t>
-        </is>
-      </c>
-      <c r="C36" s="35" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D36" s="35" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="E36" s="35" t="inlineStr">
-        <is>
-          <t>🟠 ATENÇÃO</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="35" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" s="35" t="inlineStr">
-        <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
-        </is>
-      </c>
-      <c r="C37" s="35" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D37" s="35" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="E37" s="35" t="inlineStr">
-        <is>
-          <t>🟠 ATENÇÃO</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="35" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" s="35" t="inlineStr">
-        <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
-        </is>
-      </c>
-      <c r="C38" s="35" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="D38" s="35" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="E38" s="35" t="inlineStr">
-        <is>
-          <t>🟠 ATENÇÃO</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="35" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" s="35" t="inlineStr">
-        <is>
-          <t>Anderson Jose de Santana</t>
-        </is>
-      </c>
-      <c r="C39" s="35" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D39" s="35" t="n">
+      <c r="D39" s="34" t="n">
         <v>62.3</v>
       </c>
-      <c r="E39" s="35" t="inlineStr">
+      <c r="E39" s="34" t="inlineStr">
         <is>
           <t>🟠 ATENÇÃO</t>
         </is>
@@ -21920,43 +21876,43 @@
       </c>
       <c r="C227" s="47" t="inlineStr">
         <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
+          <t>Dia com meta diária batida</t>
         </is>
       </c>
       <c r="D227" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E227" s="47" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F227" s="47" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="47" t="inlineStr">
+      <c r="A228" s="48" t="inlineStr">
         <is>
           <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
-      <c r="B228" s="47" t="inlineStr">
+      <c r="B228" s="48" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C228" s="47" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D228" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E228" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="F228" s="47" t="n">
-        <v>1</v>
+      <c r="C228" s="48" t="inlineStr">
+        <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D228" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E228" s="48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F228" s="48" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="229">
@@ -21972,17 +21928,17 @@
       </c>
       <c r="C229" s="48" t="inlineStr">
         <is>
-          <t>Dia sem bater a meta diária</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D229" s="48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E229" s="48" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F229" s="48" t="n">
-        <v>-1</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="230">
@@ -21998,7 +21954,7 @@
       </c>
       <c r="C230" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D230" s="48" t="n">
@@ -22024,17 +21980,17 @@
       </c>
       <c r="C231" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D231" s="48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E231" s="48" t="n">
         <v>0.3</v>
       </c>
       <c r="F231" s="48" t="n">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="232">
@@ -22050,17 +22006,17 @@
       </c>
       <c r="C232" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D232" s="48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E232" s="48" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="F232" s="48" t="n">
-        <v>-1.8</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="233">
@@ -23714,43 +23670,43 @@
       </c>
       <c r="C296" s="47" t="inlineStr">
         <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
+          <t>Dia com meta diária batida</t>
         </is>
       </c>
       <c r="D296" s="47" t="n">
         <v>1</v>
       </c>
       <c r="E296" s="47" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F296" s="47" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="47" t="inlineStr">
+      <c r="A297" s="48" t="inlineStr">
         <is>
           <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
-      <c r="B297" s="47" t="inlineStr">
+      <c r="B297" s="48" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C297" s="47" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D297" s="47" t="n">
+      <c r="C297" s="48" t="inlineStr">
+        <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D297" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="E297" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="F297" s="47" t="n">
-        <v>1</v>
+      <c r="E297" s="48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F297" s="48" t="n">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="298">
@@ -23766,17 +23722,17 @@
       </c>
       <c r="C298" s="48" t="inlineStr">
         <is>
-          <t>Dia sem bater a meta diária</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D298" s="48" t="n">
         <v>1</v>
       </c>
       <c r="E298" s="48" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F298" s="48" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="299">
@@ -23792,7 +23748,7 @@
       </c>
       <c r="C299" s="48" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D299" s="48" t="n">
@@ -23818,7 +23774,7 @@
       </c>
       <c r="C300" s="48" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D300" s="48" t="n">
@@ -23844,17 +23800,17 @@
       </c>
       <c r="C301" s="48" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D301" s="48" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E301" s="48" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="F301" s="48" t="n">
-        <v>-0.6</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="302">
@@ -31730,7 +31686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -31745,7 +31701,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (110 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
+          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (124 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -31823,7 +31779,7 @@
       </c>
       <c r="G3" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
@@ -31858,7 +31814,7 @@
       </c>
       <c r="G4" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
@@ -31893,7 +31849,7 @@
       </c>
       <c r="G5" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
@@ -31928,7 +31884,7 @@
       </c>
       <c r="G6" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
@@ -31963,7 +31919,7 @@
       </c>
       <c r="G7" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
@@ -31998,7 +31954,7 @@
       </c>
       <c r="G8" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
@@ -32033,7 +31989,7 @@
       </c>
       <c r="G9" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
@@ -32068,7 +32024,7 @@
       </c>
       <c r="G10" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
@@ -32103,1720 +32059,1720 @@
       </c>
       <c r="G11" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="34" t="n">
+        <v>116</v>
+      </c>
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D12" s="34" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="E12" s="34" t="inlineStr">
+        <is>
+          <t>Segunda</t>
+        </is>
+      </c>
+      <c r="F12" s="34" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G12" s="34" t="inlineStr">
+        <is>
+          <t>TODA A EQUIPE (10 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="n">
         <v>672</v>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>Adriana de Jesus Saraiva</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C13" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D12" s="34" t="inlineStr">
+      <c r="D13" s="35" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="E12" s="34" t="inlineStr">
+      <c r="E13" s="35" t="inlineStr">
         <is>
           <t>Segunda</t>
         </is>
       </c>
-      <c r="F12" s="34" t="inlineStr">
+      <c r="F13" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G12" s="34" t="inlineStr">
+      <c r="G13" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="34" t="n">
+    <row r="14">
+      <c r="A14" s="35" t="n">
         <v>85</v>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="C14" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D13" s="34" t="inlineStr">
+      <c r="D14" s="35" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="E13" s="34" t="inlineStr">
+      <c r="E14" s="35" t="inlineStr">
         <is>
           <t>Segunda</t>
         </is>
       </c>
-      <c r="F13" s="34" t="inlineStr">
+      <c r="F14" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G13" s="34" t="inlineStr">
+      <c r="G14" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="34" t="n">
+    <row r="15">
+      <c r="A15" s="35" t="n">
         <v>73</v>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D14" s="34" t="inlineStr">
+      <c r="D15" s="35" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="E14" s="34" t="inlineStr">
+      <c r="E15" s="35" t="inlineStr">
         <is>
           <t>Segunda</t>
         </is>
       </c>
-      <c r="F14" s="34" t="inlineStr">
+      <c r="F15" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G14" s="34" t="inlineStr">
+      <c r="G15" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="34" t="n">
+    <row r="16">
+      <c r="A16" s="35" t="n">
         <v>3101</v>
       </c>
-      <c r="B15" s="34" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Carlos Alberto Albiero</t>
         </is>
       </c>
-      <c r="C15" s="34" t="inlineStr">
+      <c r="C16" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D15" s="34" t="inlineStr">
+      <c r="D16" s="35" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="E15" s="34" t="inlineStr">
+      <c r="E16" s="35" t="inlineStr">
         <is>
           <t>Segunda</t>
         </is>
       </c>
-      <c r="F15" s="34" t="inlineStr">
+      <c r="F16" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G15" s="34" t="inlineStr">
+      <c r="G16" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="34" t="n">
+    <row r="17">
+      <c r="A17" s="35" t="n">
         <v>470</v>
       </c>
-      <c r="B16" s="34" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
-      <c r="C16" s="34" t="inlineStr">
+      <c r="C17" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D16" s="34" t="inlineStr">
+      <c r="D17" s="35" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="E16" s="34" t="inlineStr">
+      <c r="E17" s="35" t="inlineStr">
         <is>
           <t>Segunda</t>
         </is>
       </c>
-      <c r="F16" s="34" t="inlineStr">
+      <c r="F17" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G16" s="34" t="inlineStr">
+      <c r="G17" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="34" t="n">
+    <row r="18">
+      <c r="A18" s="35" t="n">
         <v>1935</v>
       </c>
-      <c r="B17" s="34" t="inlineStr">
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
-      <c r="C17" s="34" t="inlineStr">
+      <c r="C18" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D17" s="34" t="inlineStr">
+      <c r="D18" s="35" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="E17" s="34" t="inlineStr">
+      <c r="E18" s="35" t="inlineStr">
         <is>
           <t>Segunda</t>
         </is>
       </c>
-      <c r="F17" s="34" t="inlineStr">
+      <c r="F18" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G17" s="34" t="inlineStr">
+      <c r="G18" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="34" t="n">
+    <row r="19">
+      <c r="A19" s="35" t="n">
         <v>79</v>
       </c>
-      <c r="B18" s="34" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
-      <c r="C18" s="34" t="inlineStr">
+      <c r="C19" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D18" s="34" t="inlineStr">
+      <c r="D19" s="35" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="E18" s="34" t="inlineStr">
+      <c r="E19" s="35" t="inlineStr">
         <is>
           <t>Segunda</t>
         </is>
       </c>
-      <c r="F18" s="34" t="inlineStr">
+      <c r="F19" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G18" s="34" t="inlineStr">
+      <c r="G19" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="34" t="n">
+    <row r="20">
+      <c r="A20" s="35" t="n">
         <v>30</v>
       </c>
-      <c r="B19" s="34" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="C19" s="34" t="inlineStr">
+      <c r="C20" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D19" s="34" t="inlineStr">
+      <c r="D20" s="35" t="inlineStr">
         <is>
           <t>10/08/2026</t>
         </is>
       </c>
-      <c r="E19" s="34" t="inlineStr">
+      <c r="E20" s="35" t="inlineStr">
         <is>
           <t>Segunda</t>
         </is>
       </c>
-      <c r="F19" s="34" t="inlineStr">
+      <c r="F20" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G19" s="34" t="inlineStr">
+      <c r="G20" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="34" t="n">
+    <row r="21">
+      <c r="A21" s="35" t="n">
+        <v>116</v>
+      </c>
+      <c r="B21" s="35" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="C21" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="inlineStr">
+        <is>
+          <t>10/08/2026</t>
+        </is>
+      </c>
+      <c r="E21" s="35" t="inlineStr">
+        <is>
+          <t>Segunda</t>
+        </is>
+      </c>
+      <c r="F21" s="35" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G21" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="n">
         <v>672</v>
       </c>
-      <c r="B20" s="34" t="inlineStr">
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>Adriana de Jesus Saraiva</t>
         </is>
       </c>
-      <c r="C20" s="34" t="inlineStr">
+      <c r="C22" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D20" s="34" t="inlineStr">
+      <c r="D22" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E20" s="34" t="inlineStr">
+      <c r="E22" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F20" s="34" t="inlineStr">
+      <c r="F22" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G20" s="34" t="inlineStr">
+      <c r="G22" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="34" t="n">
+    <row r="23">
+      <c r="A23" s="35" t="n">
         <v>85</v>
       </c>
-      <c r="B21" s="34" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
-      <c r="C21" s="34" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D21" s="34" t="inlineStr">
+      <c r="D23" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E21" s="34" t="inlineStr">
+      <c r="E23" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F21" s="34" t="inlineStr">
+      <c r="F23" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G21" s="34" t="inlineStr">
+      <c r="G23" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="34" t="n">
+    <row r="24">
+      <c r="A24" s="35" t="n">
         <v>73</v>
       </c>
-      <c r="B22" s="34" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
-      <c r="C22" s="34" t="inlineStr">
+      <c r="C24" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D22" s="34" t="inlineStr">
+      <c r="D24" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E22" s="34" t="inlineStr">
+      <c r="E24" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F22" s="34" t="inlineStr">
+      <c r="F24" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G22" s="34" t="inlineStr">
+      <c r="G24" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="34" t="n">
+    <row r="25">
+      <c r="A25" s="35" t="n">
         <v>470</v>
       </c>
-      <c r="B23" s="34" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
-      <c r="C23" s="34" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D23" s="34" t="inlineStr">
+      <c r="D25" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E23" s="34" t="inlineStr">
+      <c r="E25" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F23" s="34" t="inlineStr">
+      <c r="F25" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G23" s="34" t="inlineStr">
+      <c r="G25" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="34" t="n">
+    <row r="26">
+      <c r="A26" s="35" t="n">
         <v>3037</v>
       </c>
-      <c r="B24" s="34" t="inlineStr">
+      <c r="B26" s="35" t="inlineStr">
         <is>
           <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
-      <c r="C24" s="34" t="inlineStr">
+      <c r="C26" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D24" s="34" t="inlineStr">
+      <c r="D26" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E24" s="34" t="inlineStr">
+      <c r="E26" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F24" s="34" t="inlineStr">
+      <c r="F26" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G24" s="34" t="inlineStr">
+      <c r="G26" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="34" t="n">
+    <row r="27">
+      <c r="A27" s="35" t="n">
         <v>1935</v>
       </c>
-      <c r="B25" s="34" t="inlineStr">
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
-      <c r="C25" s="34" t="inlineStr">
+      <c r="C27" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D25" s="34" t="inlineStr">
+      <c r="D27" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E25" s="34" t="inlineStr">
+      <c r="E27" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F25" s="34" t="inlineStr">
+      <c r="F27" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G25" s="34" t="inlineStr">
+      <c r="G27" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="34" t="n">
+    <row r="28">
+      <c r="A28" s="35" t="n">
         <v>79</v>
       </c>
-      <c r="B26" s="34" t="inlineStr">
+      <c r="B28" s="35" t="inlineStr">
         <is>
           <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
-      <c r="C26" s="34" t="inlineStr">
+      <c r="C28" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D26" s="34" t="inlineStr">
+      <c r="D28" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E26" s="34" t="inlineStr">
+      <c r="E28" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F26" s="34" t="inlineStr">
+      <c r="F28" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G26" s="34" t="inlineStr">
+      <c r="G28" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="34" t="n">
+    <row r="29">
+      <c r="A29" s="35" t="n">
+        <v>116</v>
+      </c>
+      <c r="B29" s="35" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="C29" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D29" s="35" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E29" s="35" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="F29" s="35" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G29" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="35" t="n">
         <v>672</v>
       </c>
-      <c r="B27" s="34" t="inlineStr">
+      <c r="B30" s="35" t="inlineStr">
         <is>
           <t>Adriana de Jesus Saraiva</t>
         </is>
       </c>
-      <c r="C27" s="34" t="inlineStr">
+      <c r="C30" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D27" s="34" t="inlineStr">
+      <c r="D30" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E27" s="34" t="inlineStr">
+      <c r="E30" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F27" s="34" t="inlineStr">
+      <c r="F30" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G27" s="34" t="inlineStr">
+      <c r="G30" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="34" t="n">
+    <row r="31">
+      <c r="A31" s="35" t="n">
         <v>85</v>
       </c>
-      <c r="B28" s="34" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
-      <c r="C28" s="34" t="inlineStr">
+      <c r="C31" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D28" s="34" t="inlineStr">
+      <c r="D31" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E28" s="34" t="inlineStr">
+      <c r="E31" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F28" s="34" t="inlineStr">
+      <c r="F31" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G28" s="34" t="inlineStr">
+      <c r="G31" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="34" t="n">
+    <row r="32">
+      <c r="A32" s="35" t="n">
         <v>73</v>
       </c>
-      <c r="B29" s="34" t="inlineStr">
+      <c r="B32" s="35" t="inlineStr">
         <is>
           <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
-      <c r="C29" s="34" t="inlineStr">
+      <c r="C32" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D29" s="34" t="inlineStr">
+      <c r="D32" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E29" s="34" t="inlineStr">
+      <c r="E32" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F29" s="34" t="inlineStr">
+      <c r="F32" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G29" s="34" t="inlineStr">
+      <c r="G32" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="34" t="n">
+    <row r="33">
+      <c r="A33" s="35" t="n">
         <v>3101</v>
       </c>
-      <c r="B30" s="34" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr">
         <is>
           <t>Carlos Alberto Albiero</t>
         </is>
       </c>
-      <c r="C30" s="34" t="inlineStr">
+      <c r="C33" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D30" s="34" t="inlineStr">
+      <c r="D33" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E30" s="34" t="inlineStr">
+      <c r="E33" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F30" s="34" t="inlineStr">
+      <c r="F33" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G30" s="34" t="inlineStr">
+      <c r="G33" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="34" t="n">
+    <row r="34">
+      <c r="A34" s="35" t="n">
         <v>470</v>
       </c>
-      <c r="B31" s="34" t="inlineStr">
+      <c r="B34" s="35" t="inlineStr">
         <is>
           <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
-      <c r="C31" s="34" t="inlineStr">
+      <c r="C34" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D31" s="34" t="inlineStr">
+      <c r="D34" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E31" s="34" t="inlineStr">
+      <c r="E34" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F31" s="34" t="inlineStr">
+      <c r="F34" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G31" s="34" t="inlineStr">
+      <c r="G34" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="34" t="n">
+    <row r="35">
+      <c r="A35" s="35" t="n">
         <v>3037</v>
       </c>
-      <c r="B32" s="34" t="inlineStr">
+      <c r="B35" s="35" t="inlineStr">
         <is>
           <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
-      <c r="C32" s="34" t="inlineStr">
+      <c r="C35" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D32" s="34" t="inlineStr">
+      <c r="D35" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E32" s="34" t="inlineStr">
+      <c r="E35" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F32" s="34" t="inlineStr">
+      <c r="F35" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G32" s="34" t="inlineStr">
+      <c r="G35" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="34" t="n">
+    <row r="36">
+      <c r="A36" s="35" t="n">
         <v>1935</v>
       </c>
-      <c r="B33" s="34" t="inlineStr">
+      <c r="B36" s="35" t="inlineStr">
         <is>
           <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
-      <c r="C33" s="34" t="inlineStr">
+      <c r="C36" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D33" s="34" t="inlineStr">
+      <c r="D36" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E33" s="34" t="inlineStr">
+      <c r="E36" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F33" s="34" t="inlineStr">
+      <c r="F36" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G33" s="34" t="inlineStr">
+      <c r="G36" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="34" t="n">
+    <row r="37">
+      <c r="A37" s="35" t="n">
         <v>79</v>
       </c>
-      <c r="B34" s="34" t="inlineStr">
+      <c r="B37" s="35" t="inlineStr">
         <is>
           <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
-      <c r="C34" s="34" t="inlineStr">
+      <c r="C37" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D34" s="34" t="inlineStr">
+      <c r="D37" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E34" s="34" t="inlineStr">
+      <c r="E37" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F34" s="34" t="inlineStr">
+      <c r="F37" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G34" s="34" t="inlineStr">
+      <c r="G37" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="34" t="n">
+    <row r="38">
+      <c r="A38" s="35" t="n">
+        <v>116</v>
+      </c>
+      <c r="B38" s="35" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="C38" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D38" s="35" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E38" s="35" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="F38" s="35" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G38" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="35" t="n">
         <v>30</v>
       </c>
-      <c r="B35" s="34" t="inlineStr">
+      <c r="B39" s="35" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="C35" s="34" t="inlineStr">
+      <c r="C39" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D35" s="34" t="inlineStr">
+      <c r="D39" s="35" t="inlineStr">
         <is>
           <t>12/08/2026</t>
         </is>
       </c>
-      <c r="E35" s="34" t="inlineStr">
+      <c r="E39" s="35" t="inlineStr">
         <is>
           <t>Quarta</t>
         </is>
       </c>
-      <c r="F35" s="34" t="inlineStr">
+      <c r="F39" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G35" s="34" t="inlineStr">
+      <c r="G39" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="34" t="n">
+    <row r="40">
+      <c r="A40" s="35" t="n">
+        <v>116</v>
+      </c>
+      <c r="B40" s="35" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="C40" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D40" s="35" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="E40" s="35" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="F40" s="35" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G40" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="35" t="n">
         <v>3037</v>
       </c>
-      <c r="B36" s="34" t="inlineStr">
+      <c r="B41" s="35" t="inlineStr">
         <is>
           <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
-      <c r="C36" s="34" t="inlineStr">
+      <c r="C41" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D36" s="34" t="inlineStr">
+      <c r="D41" s="35" t="inlineStr">
         <is>
           <t>12/08/2026</t>
         </is>
       </c>
-      <c r="E36" s="34" t="inlineStr">
+      <c r="E41" s="35" t="inlineStr">
         <is>
           <t>Quarta</t>
         </is>
       </c>
-      <c r="F36" s="34" t="inlineStr">
+      <c r="F41" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G36" s="34" t="inlineStr">
+      <c r="G41" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="34" t="n">
+    <row r="42">
+      <c r="A42" s="35" t="n">
         <v>30</v>
       </c>
-      <c r="B37" s="34" t="inlineStr">
+      <c r="B42" s="35" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="C37" s="34" t="inlineStr">
+      <c r="C42" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D37" s="34" t="inlineStr">
+      <c r="D42" s="35" t="inlineStr">
         <is>
           <t>12/08/2026</t>
         </is>
       </c>
-      <c r="E37" s="34" t="inlineStr">
+      <c r="E42" s="35" t="inlineStr">
         <is>
           <t>Quarta</t>
         </is>
       </c>
-      <c r="F37" s="34" t="inlineStr">
+      <c r="F42" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G37" s="34" t="inlineStr">
+      <c r="G42" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="34" t="n">
+    <row r="43">
+      <c r="A43" s="35" t="n">
+        <v>116</v>
+      </c>
+      <c r="B43" s="35" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="C43" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D43" s="35" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="E43" s="35" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="F43" s="35" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G43" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="35" t="n">
         <v>73</v>
       </c>
-      <c r="B38" s="34" t="inlineStr">
+      <c r="B44" s="35" t="inlineStr">
         <is>
           <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
-      <c r="C38" s="34" t="inlineStr">
+      <c r="C44" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D38" s="34" t="inlineStr">
+      <c r="D44" s="35" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="E38" s="34" t="inlineStr">
+      <c r="E44" s="35" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="F38" s="34" t="inlineStr">
+      <c r="F44" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G38" s="34" t="inlineStr">
+      <c r="G44" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="34" t="n">
+    <row r="45">
+      <c r="A45" s="35" t="n">
         <v>1935</v>
       </c>
-      <c r="B39" s="34" t="inlineStr">
+      <c r="B45" s="35" t="inlineStr">
         <is>
           <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
-      <c r="C39" s="34" t="inlineStr">
+      <c r="C45" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D39" s="34" t="inlineStr">
+      <c r="D45" s="35" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="E39" s="34" t="inlineStr">
+      <c r="E45" s="35" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="F39" s="34" t="inlineStr">
+      <c r="F45" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G39" s="34" t="inlineStr">
+      <c r="G45" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="34" t="n">
+    <row r="46">
+      <c r="A46" s="35" t="n">
         <v>30</v>
       </c>
-      <c r="B40" s="34" t="inlineStr">
+      <c r="B46" s="35" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="C40" s="34" t="inlineStr">
+      <c r="C46" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D40" s="34" t="inlineStr">
+      <c r="D46" s="35" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="E40" s="34" t="inlineStr">
+      <c r="E46" s="35" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="F40" s="34" t="inlineStr">
+      <c r="F46" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G40" s="34" t="inlineStr">
+      <c r="G46" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="34" t="n">
+    <row r="47">
+      <c r="A47" s="35" t="n">
+        <v>116</v>
+      </c>
+      <c r="B47" s="35" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="C47" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D47" s="35" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="E47" s="35" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="F47" s="35" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G47" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="35" t="n">
         <v>73</v>
       </c>
-      <c r="B41" s="34" t="inlineStr">
+      <c r="B48" s="35" t="inlineStr">
         <is>
           <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
-      <c r="C41" s="34" t="inlineStr">
+      <c r="C48" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D41" s="34" t="inlineStr">
+      <c r="D48" s="35" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="E41" s="34" t="inlineStr">
+      <c r="E48" s="35" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="F41" s="34" t="inlineStr">
+      <c r="F48" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G41" s="34" t="inlineStr">
+      <c r="G48" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="34" t="n">
+    <row r="49">
+      <c r="A49" s="35" t="n">
         <v>1935</v>
       </c>
-      <c r="B42" s="34" t="inlineStr">
+      <c r="B49" s="35" t="inlineStr">
         <is>
           <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
-      <c r="C42" s="34" t="inlineStr">
+      <c r="C49" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D42" s="34" t="inlineStr">
+      <c r="D49" s="35" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="E42" s="34" t="inlineStr">
+      <c r="E49" s="35" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="F42" s="34" t="inlineStr">
+      <c r="F49" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G42" s="34" t="inlineStr">
+      <c r="G49" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="34" t="n">
+    <row r="50">
+      <c r="A50" s="35" t="n">
         <v>30</v>
       </c>
-      <c r="B43" s="34" t="inlineStr">
+      <c r="B50" s="35" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="C43" s="34" t="inlineStr">
+      <c r="C50" s="35" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D43" s="34" t="inlineStr">
+      <c r="D50" s="35" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="E43" s="34" t="inlineStr">
+      <c r="E50" s="35" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="F43" s="34" t="inlineStr">
+      <c r="F50" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G43" s="34" t="inlineStr">
+      <c r="G50" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="34" t="n">
+    <row r="51">
+      <c r="A51" s="35" t="n">
+        <v>116</v>
+      </c>
+      <c r="B51" s="35" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="C51" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D51" s="35" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="E51" s="35" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="F51" s="35" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G51" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="35" t="n">
         <v>2917</v>
       </c>
-      <c r="B44" s="34" t="inlineStr">
+      <c r="B52" s="35" t="inlineStr">
         <is>
           <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
-      <c r="C44" s="34" t="inlineStr">
+      <c r="C52" s="35" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="D44" s="34" t="inlineStr">
+      <c r="D52" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E44" s="34" t="inlineStr">
+      <c r="E52" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F44" s="34" t="inlineStr">
+      <c r="F52" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G44" s="34" t="inlineStr">
+      <c r="G52" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="34" t="n">
+    <row r="53">
+      <c r="A53" s="35" t="n">
         <v>99</v>
       </c>
-      <c r="B45" s="34" t="inlineStr">
+      <c r="B53" s="35" t="inlineStr">
         <is>
           <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
-      <c r="C45" s="34" t="inlineStr">
+      <c r="C53" s="35" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="D45" s="34" t="inlineStr">
+      <c r="D53" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E45" s="34" t="inlineStr">
+      <c r="E53" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F45" s="34" t="inlineStr">
+      <c r="F53" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G45" s="34" t="inlineStr">
+      <c r="G53" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="34" t="n">
+    <row r="54">
+      <c r="A54" s="35" t="n">
         <v>151</v>
       </c>
-      <c r="B46" s="34" t="inlineStr">
+      <c r="B54" s="35" t="inlineStr">
         <is>
           <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
-      <c r="C46" s="34" t="inlineStr">
+      <c r="C54" s="35" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="D46" s="34" t="inlineStr">
+      <c r="D54" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E46" s="34" t="inlineStr">
+      <c r="E54" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F46" s="34" t="inlineStr">
+      <c r="F54" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G46" s="34" t="inlineStr">
+      <c r="G54" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="34" t="n">
+    <row r="55">
+      <c r="A55" s="35" t="n">
         <v>3127</v>
       </c>
-      <c r="B47" s="34" t="inlineStr">
+      <c r="B55" s="35" t="inlineStr">
         <is>
           <t>Gisele Olimpia Torres</t>
         </is>
       </c>
-      <c r="C47" s="34" t="inlineStr">
+      <c r="C55" s="35" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="D47" s="34" t="inlineStr">
+      <c r="D55" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E47" s="34" t="inlineStr">
+      <c r="E55" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F47" s="34" t="inlineStr">
+      <c r="F55" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G47" s="34" t="inlineStr">
+      <c r="G55" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="34" t="n">
+    <row r="56">
+      <c r="A56" s="35" t="n">
         <v>465</v>
       </c>
-      <c r="B48" s="34" t="inlineStr">
+      <c r="B56" s="35" t="inlineStr">
         <is>
           <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
-      <c r="C48" s="34" t="inlineStr">
+      <c r="C56" s="35" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="D48" s="34" t="inlineStr">
+      <c r="D56" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E48" s="34" t="inlineStr">
+      <c r="E56" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F48" s="34" t="inlineStr">
+      <c r="F56" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G48" s="34" t="inlineStr">
+      <c r="G56" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="34" t="n">
+    <row r="57">
+      <c r="A57" s="35" t="n">
         <v>81</v>
       </c>
-      <c r="B49" s="34" t="inlineStr">
+      <c r="B57" s="35" t="inlineStr">
         <is>
           <t>Wesley de Souza Leal</t>
         </is>
       </c>
-      <c r="C49" s="34" t="inlineStr">
+      <c r="C57" s="35" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="D49" s="34" t="inlineStr">
+      <c r="D57" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E49" s="34" t="inlineStr">
+      <c r="E57" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F49" s="34" t="inlineStr">
+      <c r="F57" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G49" s="34" t="inlineStr">
+      <c r="G57" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="34" t="n">
+    <row r="58">
+      <c r="A58" s="35" t="n">
         <v>142</v>
       </c>
-      <c r="B50" s="34" t="inlineStr">
+      <c r="B58" s="35" t="inlineStr">
         <is>
           <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
-      <c r="C50" s="34" t="inlineStr">
+      <c r="C58" s="35" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="D50" s="34" t="inlineStr">
+      <c r="D58" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E50" s="34" t="inlineStr">
+      <c r="E58" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F50" s="34" t="inlineStr">
+      <c r="F58" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G50" s="34" t="inlineStr">
+      <c r="G58" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="34" t="n">
+    <row r="59">
+      <c r="A59" s="35" t="n">
         <v>2917</v>
       </c>
-      <c r="B51" s="34" t="inlineStr">
+      <c r="B59" s="35" t="inlineStr">
         <is>
           <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
-      <c r="C51" s="34" t="inlineStr">
+      <c r="C59" s="35" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="D51" s="34" t="inlineStr">
+      <c r="D59" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E51" s="34" t="inlineStr">
+      <c r="E59" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F51" s="34" t="inlineStr">
+      <c r="F59" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G51" s="34" t="inlineStr">
+      <c r="G59" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="34" t="n">
+    <row r="60">
+      <c r="A60" s="35" t="n">
         <v>99</v>
       </c>
-      <c r="B52" s="34" t="inlineStr">
+      <c r="B60" s="35" t="inlineStr">
         <is>
           <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
-      <c r="C52" s="34" t="inlineStr">
+      <c r="C60" s="35" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="D52" s="34" t="inlineStr">
+      <c r="D60" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E52" s="34" t="inlineStr">
+      <c r="E60" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F52" s="34" t="inlineStr">
+      <c r="F60" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G52" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="34" t="n">
-        <v>151</v>
-      </c>
-      <c r="B53" s="34" t="inlineStr">
-        <is>
-          <t>Gilmar Bitencourt Luiz</t>
-        </is>
-      </c>
-      <c r="C53" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="D53" s="34" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="E53" s="34" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F53" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G53" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="34" t="n">
-        <v>3127</v>
-      </c>
-      <c r="B54" s="34" t="inlineStr">
-        <is>
-          <t>Gisele Olimpia Torres</t>
-        </is>
-      </c>
-      <c r="C54" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="D54" s="34" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="E54" s="34" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F54" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G54" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="34" t="n">
-        <v>2030</v>
-      </c>
-      <c r="B55" s="34" t="inlineStr">
-        <is>
-          <t>Mateus Falcao de Souza</t>
-        </is>
-      </c>
-      <c r="C55" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="D55" s="34" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="E55" s="34" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F55" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G55" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="34" t="n">
-        <v>465</v>
-      </c>
-      <c r="B56" s="34" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="C56" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="D56" s="34" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="E56" s="34" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F56" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G56" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="34" t="n">
-        <v>81</v>
-      </c>
-      <c r="B57" s="34" t="inlineStr">
-        <is>
-          <t>Wesley de Souza Leal</t>
-        </is>
-      </c>
-      <c r="C57" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="D57" s="34" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="E57" s="34" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F57" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G57" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="34" t="n">
-        <v>142</v>
-      </c>
-      <c r="B58" s="34" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="C58" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="D58" s="34" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="E58" s="34" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F58" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G58" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="34" t="n">
-        <v>151</v>
-      </c>
-      <c r="B59" s="34" t="inlineStr">
-        <is>
-          <t>Gilmar Bitencourt Luiz</t>
-        </is>
-      </c>
-      <c r="C59" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="D59" s="34" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="E59" s="34" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F59" s="34" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G59" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="34" t="n">
-        <v>151</v>
-      </c>
-      <c r="B60" s="34" t="inlineStr">
-        <is>
-          <t>Gilmar Bitencourt Luiz</t>
-        </is>
-      </c>
-      <c r="C60" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="D60" s="34" t="inlineStr">
-        <is>
-          <t>14/08/2026</t>
-        </is>
-      </c>
-      <c r="E60" s="34" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F60" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G60" s="34" t="inlineStr">
+      <c r="G60" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
@@ -33824,16 +33780,16 @@
     </row>
     <row r="61">
       <c r="A61" s="35" t="n">
-        <v>2918</v>
+        <v>151</v>
       </c>
       <c r="B61" s="35" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="C61" s="35" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D61" s="35" t="inlineStr">
@@ -33848,27 +33804,27 @@
       </c>
       <c r="F61" s="35" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G61" s="35" t="inlineStr">
         <is>
-          <t>TODA A EQUIPE (8 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="35" t="n">
-        <v>120</v>
+        <v>3127</v>
       </c>
       <c r="B62" s="35" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C62" s="35" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D62" s="35" t="inlineStr">
@@ -33883,27 +33839,27 @@
       </c>
       <c r="F62" s="35" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G62" s="35" t="inlineStr">
         <is>
-          <t>TODA A EQUIPE (8 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="35" t="n">
-        <v>1936</v>
+        <v>2030</v>
       </c>
       <c r="B63" s="35" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="C63" s="35" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D63" s="35" t="inlineStr">
@@ -33918,27 +33874,27 @@
       </c>
       <c r="F63" s="35" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G63" s="35" t="inlineStr">
         <is>
-          <t>TODA A EQUIPE (8 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="35" t="n">
-        <v>1938</v>
+        <v>465</v>
       </c>
       <c r="B64" s="35" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="C64" s="35" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D64" s="35" t="inlineStr">
@@ -33953,27 +33909,27 @@
       </c>
       <c r="F64" s="35" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G64" s="35" t="inlineStr">
         <is>
-          <t>TODA A EQUIPE (8 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="35" t="n">
-        <v>2721</v>
+        <v>81</v>
       </c>
       <c r="B65" s="35" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="C65" s="35" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D65" s="35" t="inlineStr">
@@ -33988,27 +33944,27 @@
       </c>
       <c r="F65" s="35" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G65" s="35" t="inlineStr">
         <is>
-          <t>TODA A EQUIPE (8 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="35" t="n">
-        <v>3038</v>
+        <v>142</v>
       </c>
       <c r="B66" s="35" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C66" s="35" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D66" s="35" t="inlineStr">
@@ -34023,37 +33979,37 @@
       </c>
       <c r="F66" s="35" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G66" s="35" t="inlineStr">
         <is>
-          <t>TODA A EQUIPE (8 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="35" t="n">
-        <v>3128</v>
+        <v>151</v>
       </c>
       <c r="B67" s="35" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="C67" s="35" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D67" s="35" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E67" s="35" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F67" s="35" t="inlineStr">
@@ -34063,42 +34019,42 @@
       </c>
       <c r="G67" s="35" t="inlineStr">
         <is>
-          <t>TODA A EQUIPE (8 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="35" t="n">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="B68" s="35" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="C68" s="35" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D68" s="35" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E68" s="35" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F68" s="35" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G68" s="35" t="inlineStr">
         <is>
-          <t>TODA A EQUIPE (8 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
@@ -34128,12 +34084,12 @@
       </c>
       <c r="F69" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G69" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (8 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
@@ -34163,12 +34119,12 @@
       </c>
       <c r="F70" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G70" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (8 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
@@ -34198,12 +34154,12 @@
       </c>
       <c r="F71" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G71" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (8 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
@@ -34233,22 +34189,22 @@
       </c>
       <c r="F72" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G72" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (8 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="34" t="n">
-        <v>3038</v>
+        <v>2721</v>
       </c>
       <c r="B73" s="34" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C73" s="34" t="inlineStr">
@@ -34268,22 +34224,22 @@
       </c>
       <c r="F73" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G73" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (8 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="34" t="n">
-        <v>3128</v>
+        <v>3038</v>
       </c>
       <c r="B74" s="34" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C74" s="34" t="inlineStr">
@@ -34303,22 +34259,22 @@
       </c>
       <c r="F74" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G74" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (8 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="34" t="n">
-        <v>113</v>
+        <v>3128</v>
       </c>
       <c r="B75" s="34" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C75" s="34" t="inlineStr">
@@ -34338,885 +34294,885 @@
       </c>
       <c r="F75" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G75" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (8 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="34" t="n">
+        <v>113</v>
+      </c>
+      <c r="B76" s="34" t="inlineStr">
+        <is>
+          <t>Selba Ramona Afonso</t>
+        </is>
+      </c>
+      <c r="C76" s="34" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="D76" s="34" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E76" s="34" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="F76" s="34" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G76" s="34" t="inlineStr">
+        <is>
+          <t>TODA A EQUIPE (8 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="35" t="n">
+        <v>2918</v>
+      </c>
+      <c r="B77" s="35" t="inlineStr">
+        <is>
+          <t>Claine Luisa Figueiredo Torraca</t>
+        </is>
+      </c>
+      <c r="C77" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="D77" s="35" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E77" s="35" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="F77" s="35" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G77" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="35" t="n">
+        <v>120</v>
+      </c>
+      <c r="B78" s="35" t="inlineStr">
+        <is>
+          <t>Emidio Rainer Vilhalba</t>
+        </is>
+      </c>
+      <c r="C78" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="D78" s="35" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E78" s="35" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="F78" s="35" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G78" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="35" t="n">
+        <v>1936</v>
+      </c>
+      <c r="B79" s="35" t="inlineStr">
+        <is>
+          <t>Geancarlos Ferreira Barrios</t>
+        </is>
+      </c>
+      <c r="C79" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="D79" s="35" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E79" s="35" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="F79" s="35" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G79" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="35" t="n">
         <v>1938</v>
       </c>
-      <c r="B76" s="34" t="inlineStr">
+      <c r="B80" s="35" t="inlineStr">
         <is>
           <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
-      <c r="C76" s="34" t="inlineStr">
+      <c r="C80" s="35" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D76" s="34" t="inlineStr">
+      <c r="D80" s="35" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E80" s="35" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="F80" s="35" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G80" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="35" t="n">
+        <v>3038</v>
+      </c>
+      <c r="B81" s="35" t="inlineStr">
+        <is>
+          <t>Naime Cristina Freitas</t>
+        </is>
+      </c>
+      <c r="C81" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="D81" s="35" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E81" s="35" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="F81" s="35" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G81" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="35" t="n">
+        <v>3128</v>
+      </c>
+      <c r="B82" s="35" t="inlineStr">
+        <is>
+          <t>Rosalina Beniel Vargas</t>
+        </is>
+      </c>
+      <c r="C82" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="D82" s="35" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E82" s="35" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="F82" s="35" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G82" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="35" t="n">
+        <v>113</v>
+      </c>
+      <c r="B83" s="35" t="inlineStr">
+        <is>
+          <t>Selba Ramona Afonso</t>
+        </is>
+      </c>
+      <c r="C83" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="D83" s="35" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E83" s="35" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="F83" s="35" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G83" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="35" t="n">
+        <v>1938</v>
+      </c>
+      <c r="B84" s="35" t="inlineStr">
+        <is>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
+        </is>
+      </c>
+      <c r="C84" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="D84" s="35" t="inlineStr">
         <is>
           <t>12/08/2026</t>
         </is>
       </c>
-      <c r="E76" s="34" t="inlineStr">
+      <c r="E84" s="35" t="inlineStr">
         <is>
           <t>Quarta</t>
         </is>
       </c>
-      <c r="F76" s="34" t="inlineStr">
+      <c r="F84" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G76" s="34" t="inlineStr">
+      <c r="G84" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="34" t="n">
+    <row r="85">
+      <c r="A85" s="35" t="n">
         <v>120</v>
       </c>
-      <c r="B77" s="34" t="inlineStr">
+      <c r="B85" s="35" t="inlineStr">
         <is>
           <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
-      <c r="C77" s="34" t="inlineStr">
+      <c r="C85" s="35" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D77" s="34" t="inlineStr">
+      <c r="D85" s="35" t="inlineStr">
         <is>
           <t>12/08/2026</t>
         </is>
       </c>
-      <c r="E77" s="34" t="inlineStr">
+      <c r="E85" s="35" t="inlineStr">
         <is>
           <t>Quarta</t>
         </is>
       </c>
-      <c r="F77" s="34" t="inlineStr">
+      <c r="F85" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G77" s="34" t="inlineStr">
+      <c r="G85" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="34" t="n">
+    <row r="86">
+      <c r="A86" s="35" t="n">
         <v>1938</v>
       </c>
-      <c r="B78" s="34" t="inlineStr">
+      <c r="B86" s="35" t="inlineStr">
         <is>
           <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
-      <c r="C78" s="34" t="inlineStr">
+      <c r="C86" s="35" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D78" s="34" t="inlineStr">
+      <c r="D86" s="35" t="inlineStr">
         <is>
           <t>12/08/2026</t>
         </is>
       </c>
-      <c r="E78" s="34" t="inlineStr">
+      <c r="E86" s="35" t="inlineStr">
         <is>
           <t>Quarta</t>
         </is>
       </c>
-      <c r="F78" s="34" t="inlineStr">
+      <c r="F86" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G78" s="34" t="inlineStr">
+      <c r="G86" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="34" t="n">
+    <row r="87">
+      <c r="A87" s="35" t="n">
         <v>3038</v>
       </c>
-      <c r="B79" s="34" t="inlineStr">
+      <c r="B87" s="35" t="inlineStr">
         <is>
           <t>Naime Cristina Freitas</t>
         </is>
       </c>
-      <c r="C79" s="34" t="inlineStr">
+      <c r="C87" s="35" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D79" s="34" t="inlineStr">
+      <c r="D87" s="35" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="E79" s="34" t="inlineStr">
+      <c r="E87" s="35" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="F79" s="34" t="inlineStr">
+      <c r="F87" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G79" s="34" t="inlineStr">
+      <c r="G87" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="34" t="n">
+    <row r="88">
+      <c r="A88" s="35" t="n">
         <v>113</v>
       </c>
-      <c r="B80" s="34" t="inlineStr">
+      <c r="B88" s="35" t="inlineStr">
         <is>
           <t>Selba Ramona Afonso</t>
         </is>
       </c>
-      <c r="C80" s="34" t="inlineStr">
+      <c r="C88" s="35" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D80" s="34" t="inlineStr">
+      <c r="D88" s="35" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="E80" s="34" t="inlineStr">
+      <c r="E88" s="35" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="F80" s="34" t="inlineStr">
+      <c r="F88" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G80" s="34" t="inlineStr">
+      <c r="G88" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="34" t="n">
+    <row r="89">
+      <c r="A89" s="35" t="n">
         <v>3038</v>
       </c>
-      <c r="B81" s="34" t="inlineStr">
+      <c r="B89" s="35" t="inlineStr">
         <is>
           <t>Naime Cristina Freitas</t>
         </is>
       </c>
-      <c r="C81" s="34" t="inlineStr">
+      <c r="C89" s="35" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D81" s="34" t="inlineStr">
+      <c r="D89" s="35" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="E81" s="34" t="inlineStr">
+      <c r="E89" s="35" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="F81" s="34" t="inlineStr">
+      <c r="F89" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G81" s="34" t="inlineStr">
+      <c r="G89" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="34" t="n">
+    <row r="90">
+      <c r="A90" s="35" t="n">
         <v>113</v>
       </c>
-      <c r="B82" s="34" t="inlineStr">
+      <c r="B90" s="35" t="inlineStr">
         <is>
           <t>Selba Ramona Afonso</t>
         </is>
       </c>
-      <c r="C82" s="34" t="inlineStr">
+      <c r="C90" s="35" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D82" s="34" t="inlineStr">
+      <c r="D90" s="35" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="E82" s="34" t="inlineStr">
+      <c r="E90" s="35" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="F82" s="34" t="inlineStr">
+      <c r="F90" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G82" s="34" t="inlineStr">
+      <c r="G90" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="34" t="n">
+    <row r="91">
+      <c r="A91" s="35" t="n">
         <v>110</v>
       </c>
-      <c r="B83" s="34" t="inlineStr">
+      <c r="B91" s="35" t="inlineStr">
         <is>
           <t>Anderson Jose de Santana</t>
         </is>
       </c>
-      <c r="C83" s="34" t="inlineStr">
+      <c r="C91" s="35" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D83" s="34" t="inlineStr">
+      <c r="D91" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E83" s="34" t="inlineStr">
+      <c r="E91" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F83" s="34" t="inlineStr">
+      <c r="F91" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G83" s="34" t="inlineStr">
+      <c r="G91" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="34" t="n">
+    <row r="92">
+      <c r="A92" s="35" t="n">
         <v>80</v>
       </c>
-      <c r="B84" s="34" t="inlineStr">
+      <c r="B92" s="35" t="inlineStr">
         <is>
           <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
-      <c r="C84" s="34" t="inlineStr">
+      <c r="C92" s="35" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D84" s="34" t="inlineStr">
+      <c r="D92" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E84" s="34" t="inlineStr">
+      <c r="E92" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F84" s="34" t="inlineStr">
+      <c r="F92" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G84" s="34" t="inlineStr">
+      <c r="G92" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="34" t="n">
+    <row r="93">
+      <c r="A93" s="35" t="n">
         <v>1943</v>
       </c>
-      <c r="B85" s="34" t="inlineStr">
+      <c r="B93" s="35" t="inlineStr">
         <is>
           <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
-      <c r="C85" s="34" t="inlineStr">
+      <c r="C93" s="35" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D85" s="34" t="inlineStr">
+      <c r="D93" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E85" s="34" t="inlineStr">
+      <c r="E93" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F85" s="34" t="inlineStr">
+      <c r="F93" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G85" s="34" t="inlineStr">
+      <c r="G93" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="34" t="n">
+    <row r="94">
+      <c r="A94" s="35" t="n">
         <v>2789</v>
       </c>
-      <c r="B86" s="34" t="inlineStr">
+      <c r="B94" s="35" t="inlineStr">
         <is>
           <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
-      <c r="C86" s="34" t="inlineStr">
+      <c r="C94" s="35" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D86" s="34" t="inlineStr">
+      <c r="D94" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E86" s="34" t="inlineStr">
+      <c r="E94" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F86" s="34" t="inlineStr">
+      <c r="F94" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G86" s="34" t="inlineStr">
+      <c r="G94" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="34" t="n">
+    <row r="95">
+      <c r="A95" s="35" t="n">
         <v>149</v>
       </c>
-      <c r="B87" s="34" t="inlineStr">
+      <c r="B95" s="35" t="inlineStr">
         <is>
           <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
-      <c r="C87" s="34" t="inlineStr">
+      <c r="C95" s="35" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D87" s="34" t="inlineStr">
+      <c r="D95" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E87" s="34" t="inlineStr">
+      <c r="E95" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F87" s="34" t="inlineStr">
+      <c r="F95" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G87" s="34" t="inlineStr">
+      <c r="G95" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="34" t="n">
+    <row r="96">
+      <c r="A96" s="35" t="n">
         <v>1942</v>
       </c>
-      <c r="B88" s="34" t="inlineStr">
+      <c r="B96" s="35" t="inlineStr">
         <is>
           <t>Rafael Ramos Recalde</t>
         </is>
       </c>
-      <c r="C88" s="34" t="inlineStr">
+      <c r="C96" s="35" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D88" s="34" t="inlineStr">
+      <c r="D96" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E88" s="34" t="inlineStr">
+      <c r="E96" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F88" s="34" t="inlineStr">
+      <c r="F96" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G88" s="34" t="inlineStr">
+      <c r="G96" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="34" t="n">
+    <row r="97">
+      <c r="A97" s="35" t="n">
+        <v>124</v>
+      </c>
+      <c r="B97" s="35" t="inlineStr">
+        <is>
+          <t>Ramona dos Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="C97" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D97" s="35" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E97" s="35" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="F97" s="35" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G97" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="35" t="n">
         <v>161</v>
       </c>
-      <c r="B89" s="34" t="inlineStr">
+      <c r="B98" s="35" t="inlineStr">
         <is>
           <t>Rozana Reis da Silva</t>
         </is>
       </c>
-      <c r="C89" s="34" t="inlineStr">
+      <c r="C98" s="35" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D89" s="34" t="inlineStr">
+      <c r="D98" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E89" s="34" t="inlineStr">
+      <c r="E98" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F89" s="34" t="inlineStr">
+      <c r="F98" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G89" s="34" t="inlineStr">
+      <c r="G98" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="34" t="n">
+    <row r="99">
+      <c r="A99" s="35" t="n">
         <v>1996</v>
       </c>
-      <c r="B90" s="34" t="inlineStr">
+      <c r="B99" s="35" t="inlineStr">
         <is>
           <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
-      <c r="C90" s="34" t="inlineStr">
+      <c r="C99" s="35" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D90" s="34" t="inlineStr">
+      <c r="D99" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E90" s="34" t="inlineStr">
+      <c r="E99" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F90" s="34" t="inlineStr">
+      <c r="F99" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G90" s="34" t="inlineStr">
+      <c r="G99" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="34" t="n">
+    <row r="100">
+      <c r="A100" s="35" t="n">
         <v>86</v>
       </c>
-      <c r="B91" s="34" t="inlineStr">
+      <c r="B100" s="35" t="inlineStr">
         <is>
           <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
-      <c r="C91" s="34" t="inlineStr">
+      <c r="C100" s="35" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D91" s="34" t="inlineStr">
+      <c r="D100" s="35" t="inlineStr">
         <is>
           <t>11/08/2026</t>
         </is>
       </c>
-      <c r="E91" s="34" t="inlineStr">
+      <c r="E100" s="35" t="inlineStr">
         <is>
           <t>Terça</t>
         </is>
       </c>
-      <c r="F91" s="34" t="inlineStr">
+      <c r="F100" s="35" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G91" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="34" t="n">
-        <v>110</v>
-      </c>
-      <c r="B92" s="34" t="inlineStr">
-        <is>
-          <t>Anderson Jose de Santana</t>
-        </is>
-      </c>
-      <c r="C92" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D92" s="34" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="E92" s="34" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F92" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G92" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="34" t="n">
-        <v>80</v>
-      </c>
-      <c r="B93" s="34" t="inlineStr">
-        <is>
-          <t>Gisele Lopes Justiniano</t>
-        </is>
-      </c>
-      <c r="C93" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D93" s="34" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="E93" s="34" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F93" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G93" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="34" t="n">
-        <v>1943</v>
-      </c>
-      <c r="B94" s="34" t="inlineStr">
-        <is>
-          <t>Juliana Patricia Goncalves</t>
-        </is>
-      </c>
-      <c r="C94" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D94" s="34" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="E94" s="34" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F94" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G94" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="34" t="n">
-        <v>2789</v>
-      </c>
-      <c r="B95" s="34" t="inlineStr">
-        <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
-        </is>
-      </c>
-      <c r="C95" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D95" s="34" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="E95" s="34" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F95" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G95" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="34" t="n">
-        <v>149</v>
-      </c>
-      <c r="B96" s="34" t="inlineStr">
-        <is>
-          <t>Kátia Cilene Silveira Machado</t>
-        </is>
-      </c>
-      <c r="C96" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D96" s="34" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="E96" s="34" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F96" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G96" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="34" t="n">
-        <v>1942</v>
-      </c>
-      <c r="B97" s="34" t="inlineStr">
-        <is>
-          <t>Rafael Ramos Recalde</t>
-        </is>
-      </c>
-      <c r="C97" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D97" s="34" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="E97" s="34" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F97" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G97" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="34" t="n">
-        <v>161</v>
-      </c>
-      <c r="B98" s="34" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="C98" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D98" s="34" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="E98" s="34" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F98" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G98" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="34" t="n">
-        <v>1996</v>
-      </c>
-      <c r="B99" s="34" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="C99" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D99" s="34" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="E99" s="34" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F99" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G99" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="34" t="n">
-        <v>86</v>
-      </c>
-      <c r="B100" s="34" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-      <c r="C100" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D100" s="34" t="inlineStr">
-        <is>
-          <t>11/08/2026</t>
-        </is>
-      </c>
-      <c r="E100" s="34" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F100" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G100" s="34" t="inlineStr">
+      <c r="G100" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
@@ -35224,11 +35180,11 @@
     </row>
     <row r="101">
       <c r="A101" s="34" t="n">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="B101" s="34" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C101" s="34" t="inlineStr">
@@ -35253,17 +35209,17 @@
       </c>
       <c r="G101" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (11 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="34" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="B102" s="34" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C102" s="34" t="inlineStr">
@@ -35273,22 +35229,22 @@
       </c>
       <c r="D102" s="34" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E102" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G102" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (11 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
@@ -35308,32 +35264,32 @@
       </c>
       <c r="D103" s="34" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E103" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F103" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G103" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (11 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="34" t="n">
-        <v>110</v>
+        <v>2789</v>
       </c>
       <c r="B104" s="34" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C104" s="34" t="inlineStr">
@@ -35343,12 +35299,12 @@
       </c>
       <c r="D104" s="34" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E104" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F104" s="34" t="inlineStr">
@@ -35358,17 +35314,17 @@
       </c>
       <c r="G104" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (11 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="34" t="n">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="B105" s="34" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C105" s="34" t="inlineStr">
@@ -35378,32 +35334,32 @@
       </c>
       <c r="D105" s="34" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E105" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F105" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G105" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (11 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="34" t="n">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="B106" s="34" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C106" s="34" t="inlineStr">
@@ -35413,32 +35369,32 @@
       </c>
       <c r="D106" s="34" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E106" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G106" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (11 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="34" t="n">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="B107" s="34" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
       <c r="C107" s="34" t="inlineStr">
@@ -35448,32 +35404,32 @@
       </c>
       <c r="D107" s="34" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E107" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F107" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G107" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (11 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="34" t="n">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="B108" s="34" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C108" s="34" t="inlineStr">
@@ -35483,12 +35439,12 @@
       </c>
       <c r="D108" s="34" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E108" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F108" s="34" t="inlineStr">
@@ -35498,17 +35454,17 @@
       </c>
       <c r="G108" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (11 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="34" t="n">
-        <v>1943</v>
+        <v>1996</v>
       </c>
       <c r="B109" s="34" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C109" s="34" t="inlineStr">
@@ -35518,12 +35474,12 @@
       </c>
       <c r="D109" s="34" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E109" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F109" s="34" t="inlineStr">
@@ -35533,17 +35489,17 @@
       </c>
       <c r="G109" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (11 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="34" t="n">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="B110" s="34" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C110" s="34" t="inlineStr">
@@ -35553,12 +35509,12 @@
       </c>
       <c r="D110" s="34" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E110" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F110" s="34" t="inlineStr">
@@ -35568,82 +35524,572 @@
       </c>
       <c r="G110" s="34" t="inlineStr">
         <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+          <t>TODA A EQUIPE (11 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="34" t="n">
+        <v>157</v>
+      </c>
+      <c r="B111" s="34" t="inlineStr">
+        <is>
+          <t>Walquiria Araujo Flores</t>
+        </is>
+      </c>
+      <c r="C111" s="34" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D111" s="34" t="inlineStr">
+        <is>
+          <t>11/08/2026</t>
+        </is>
+      </c>
+      <c r="E111" s="34" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="F111" s="34" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G111" s="34" t="inlineStr">
+        <is>
+          <t>TODA A EQUIPE (11 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="35" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="35" t="inlineStr">
+        <is>
+          <t>Anderson Jose de Santana</t>
+        </is>
+      </c>
+      <c r="C112" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D112" s="35" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="E112" s="35" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="F112" s="35" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G112" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="35" t="n">
+        <v>1943</v>
+      </c>
+      <c r="B113" s="35" t="inlineStr">
+        <is>
+          <t>Juliana Patricia Goncalves</t>
+        </is>
+      </c>
+      <c r="C113" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D113" s="35" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="E113" s="35" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="F113" s="35" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G113" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="35" t="n">
+        <v>124</v>
+      </c>
+      <c r="B114" s="35" t="inlineStr">
+        <is>
+          <t>Ramona dos Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="C114" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D114" s="35" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="E114" s="35" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="F114" s="35" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G114" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="35" t="n">
+        <v>110</v>
+      </c>
+      <c r="B115" s="35" t="inlineStr">
+        <is>
+          <t>Anderson Jose de Santana</t>
+        </is>
+      </c>
+      <c r="C115" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D115" s="35" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="E115" s="35" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="F115" s="35" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G115" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="35" t="n">
+        <v>124</v>
+      </c>
+      <c r="B116" s="35" t="inlineStr">
+        <is>
+          <t>Ramona dos Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="C116" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D116" s="35" t="inlineStr">
+        <is>
+          <t>12/08/2026</t>
+        </is>
+      </c>
+      <c r="E116" s="35" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="F116" s="35" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G116" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="35" t="n">
+        <v>110</v>
+      </c>
+      <c r="B117" s="35" t="inlineStr">
+        <is>
+          <t>Anderson Jose de Santana</t>
+        </is>
+      </c>
+      <c r="C117" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D117" s="35" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="E117" s="35" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="F117" s="35" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G117" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="35" t="n">
+        <v>1943</v>
+      </c>
+      <c r="B118" s="35" t="inlineStr">
+        <is>
+          <t>Juliana Patricia Goncalves</t>
+        </is>
+      </c>
+      <c r="C118" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D118" s="35" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="E118" s="35" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="F118" s="35" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G118" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="35" t="n">
+        <v>124</v>
+      </c>
+      <c r="B119" s="35" t="inlineStr">
+        <is>
+          <t>Ramona dos Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="C119" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D119" s="35" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="E119" s="35" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="F119" s="35" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G119" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="35" t="n">
+        <v>161</v>
+      </c>
+      <c r="B120" s="35" t="inlineStr">
+        <is>
+          <t>Rozana Reis da Silva</t>
+        </is>
+      </c>
+      <c r="C120" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D120" s="35" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="E120" s="35" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="F120" s="35" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G120" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="35" t="n">
+        <v>110</v>
+      </c>
+      <c r="B121" s="35" t="inlineStr">
+        <is>
+          <t>Anderson Jose de Santana</t>
+        </is>
+      </c>
+      <c r="C121" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D121" s="35" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="E121" s="35" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="F121" s="35" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G121" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="35" t="n">
+        <v>1943</v>
+      </c>
+      <c r="B122" s="35" t="inlineStr">
+        <is>
+          <t>Juliana Patricia Goncalves</t>
+        </is>
+      </c>
+      <c r="C122" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D122" s="35" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="E122" s="35" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="F122" s="35" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G122" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="35" t="n">
+        <v>124</v>
+      </c>
+      <c r="B123" s="35" t="inlineStr">
+        <is>
+          <t>Ramona dos Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="C123" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D123" s="35" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="E123" s="35" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="F123" s="35" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G123" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="35" t="n">
+        <v>161</v>
+      </c>
+      <c r="B124" s="35" t="inlineStr">
+        <is>
+          <t>Rozana Reis da Silva</t>
+        </is>
+      </c>
+      <c r="C124" s="35" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D124" s="35" t="inlineStr">
+        <is>
+          <t>14/08/2026</t>
+        </is>
+      </c>
+      <c r="E124" s="35" t="inlineStr">
+        <is>
+          <t>Sexta</t>
+        </is>
+      </c>
+      <c r="F124" s="35" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="G124" s="35" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="35" t="n">
         <v>1996</v>
       </c>
-      <c r="B111" s="34" t="inlineStr">
+      <c r="B125" s="35" t="inlineStr">
         <is>
           <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
-      <c r="C111" s="34" t="inlineStr">
+      <c r="C125" s="35" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D111" s="34" t="inlineStr">
+      <c r="D125" s="35" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="E111" s="34" t="inlineStr">
+      <c r="E125" s="35" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="F111" s="34" t="inlineStr">
+      <c r="F125" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G111" s="34" t="inlineStr">
+      <c r="G125" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="34" t="n">
+    <row r="126">
+      <c r="A126" s="35" t="n">
         <v>157</v>
       </c>
-      <c r="B112" s="34" t="inlineStr">
+      <c r="B126" s="35" t="inlineStr">
         <is>
           <t>Walquiria Araujo Flores</t>
         </is>
       </c>
-      <c r="C112" s="34" t="inlineStr">
+      <c r="C126" s="35" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="D112" s="34" t="inlineStr">
+      <c r="D126" s="35" t="inlineStr">
         <is>
           <t>14/08/2026</t>
         </is>
       </c>
-      <c r="E112" s="34" t="inlineStr">
+      <c r="E126" s="35" t="inlineStr">
         <is>
           <t>Sexta</t>
         </is>
       </c>
-      <c r="F112" s="34" t="inlineStr">
+      <c r="F126" s="35" t="inlineStr">
         <is>
           <t>Tarde</t>
         </is>
       </c>
-      <c r="G112" s="34" t="inlineStr">
+      <c r="G126" s="35" t="inlineStr">
         <is>
           <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:G112"/>
+  <autoFilter ref="A2:G126"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/data/historico/semanas_318-321.xlsx
+++ b/data/historico/semanas_318-321.xlsx
@@ -30191,47 +30191,47 @@
     <row r="20">
       <c r="A20" s="27" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>16910075</t>
+          <t>16935897</t>
         </is>
       </c>
       <c r="D20" s="27" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>417 - CENTRO 3</t>
         </is>
       </c>
       <c r="E20" s="27" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F20" s="27" t="inlineStr">
         <is>
-          <t>Rua CATANDUVA</t>
+          <t>Avenida PRESIDENTE VARGAS</t>
         </is>
       </c>
       <c r="G20" s="27" t="inlineStr">
         <is>
-          <t>490 - R</t>
+          <t>725 - OU</t>
         </is>
       </c>
       <c r="H20" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:31</t>
+          <t>14/08/2026 09:40</t>
         </is>
       </c>
       <c r="I20" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:49</t>
+          <t>14/08/2026 09:58</t>
         </is>
       </c>
       <c r="J20" s="27" t="n">
@@ -30291,47 +30291,47 @@
     <row r="22">
       <c r="A22" s="27" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C22" s="28" t="inlineStr">
         <is>
-          <t>16935897</t>
+          <t>16910075</t>
         </is>
       </c>
       <c r="D22" s="27" t="inlineStr">
         <is>
-          <t>417 - CENTRO 3</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E22" s="27" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="F22" s="27" t="inlineStr">
         <is>
-          <t>Avenida PRESIDENTE VARGAS</t>
+          <t>Rua CATANDUVA</t>
         </is>
       </c>
       <c r="G22" s="27" t="inlineStr">
         <is>
-          <t>725 - OU</t>
+          <t>490 - R</t>
         </is>
       </c>
       <c r="H22" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 09:40</t>
+          <t>13/08/2026 15:31</t>
         </is>
       </c>
       <c r="I22" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 09:58</t>
+          <t>13/08/2026 15:49</t>
         </is>
       </c>
       <c r="J22" s="27" t="n">
@@ -30391,47 +30391,47 @@
     <row r="24">
       <c r="A24" s="27" t="inlineStr">
         <is>
-          <t>Raquel Ortiz dos Santos</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C24" s="28" t="inlineStr">
         <is>
-          <t>16881755</t>
+          <t>16932380</t>
         </is>
       </c>
       <c r="D24" s="27" t="inlineStr">
         <is>
-          <t>406 - JARDIM PRIMAVERA</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E24" s="27" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="F24" s="27" t="inlineStr">
         <is>
-          <t>Rua ELOAH VIEIRA DA SILVA</t>
+          <t>Rua CURITIBA</t>
         </is>
       </c>
       <c r="G24" s="27" t="inlineStr">
         <is>
-          <t>26 - 2 - TB</t>
+          <t>01 - TB</t>
         </is>
       </c>
       <c r="H24" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 16:12</t>
+          <t>14/08/2026 15:51</t>
         </is>
       </c>
       <c r="I24" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 16:29</t>
+          <t>14/08/2026 16:08</t>
         </is>
       </c>
       <c r="J24" s="27" t="n">
@@ -30441,47 +30441,47 @@
     <row r="25">
       <c r="A25" s="27" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B25" s="27" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>16910076</t>
+          <t>16904092</t>
         </is>
       </c>
       <c r="D25" s="27" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E25" s="27" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="F25" s="27" t="inlineStr">
         <is>
-          <t>Rua CATANDUVA</t>
+          <t>Rua SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="G25" s="27" t="inlineStr">
         <is>
-          <t>166 - R</t>
+          <t>300 - R</t>
         </is>
       </c>
       <c r="H25" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:49</t>
+          <t>13/08/2026 15:14</t>
         </is>
       </c>
       <c r="I25" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 16:06</t>
+          <t>13/08/2026 15:31</t>
         </is>
       </c>
       <c r="J25" s="27" t="n">
@@ -30591,47 +30591,47 @@
     <row r="28">
       <c r="A28" s="27" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B28" s="27" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>16932380</t>
+          <t>16910076</t>
         </is>
       </c>
       <c r="D28" s="27" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E28" s="27" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="F28" s="27" t="inlineStr">
         <is>
-          <t>Rua CURITIBA</t>
+          <t>Rua CATANDUVA</t>
         </is>
       </c>
       <c r="G28" s="27" t="inlineStr">
         <is>
-          <t>01 - TB</t>
+          <t>166 - R</t>
         </is>
       </c>
       <c r="H28" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 15:51</t>
+          <t>13/08/2026 15:49</t>
         </is>
       </c>
       <c r="I28" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 16:08</t>
+          <t>13/08/2026 16:06</t>
         </is>
       </c>
       <c r="J28" s="27" t="n">
@@ -30641,47 +30641,47 @@
     <row r="29">
       <c r="A29" s="27" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
       <c r="B29" s="27" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C29" s="28" t="inlineStr">
         <is>
-          <t>16904092</t>
+          <t>16881755</t>
         </is>
       </c>
       <c r="D29" s="27" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>406 - JARDIM PRIMAVERA</t>
         </is>
       </c>
       <c r="E29" s="27" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="F29" s="27" t="inlineStr">
         <is>
-          <t>Rua SÃO JOÃO DEL REI</t>
+          <t>Rua ELOAH VIEIRA DA SILVA</t>
         </is>
       </c>
       <c r="G29" s="27" t="inlineStr">
         <is>
-          <t>300 - R</t>
+          <t>26 - 2 - TB</t>
         </is>
       </c>
       <c r="H29" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:14</t>
+          <t>12/08/2026 16:12</t>
         </is>
       </c>
       <c r="I29" s="27" t="inlineStr">
         <is>
-          <t>13/08/2026 15:31</t>
+          <t>12/08/2026 16:29</t>
         </is>
       </c>
       <c r="J29" s="27" t="n">
@@ -30891,7 +30891,7 @@
     <row r="34">
       <c r="A34" s="27" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="B34" s="27" t="inlineStr">
@@ -30901,37 +30901,37 @@
       </c>
       <c r="C34" s="28" t="inlineStr">
         <is>
-          <t>16932420</t>
+          <t>16929550</t>
         </is>
       </c>
       <c r="D34" s="27" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>420 - FERROVIARIA</t>
         </is>
       </c>
       <c r="E34" s="27" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q003</t>
         </is>
       </c>
       <c r="F34" s="27" t="inlineStr">
         <is>
-          <t>Rua 18 DE JULHO</t>
+          <t>Rua ALAMEDA DOS TROLLES</t>
         </is>
       </c>
       <c r="G34" s="27" t="inlineStr">
         <is>
-          <t>187 - R</t>
+          <t>190 - R</t>
         </is>
       </c>
       <c r="H34" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:52</t>
+          <t>14/08/2026 14:31</t>
         </is>
       </c>
       <c r="I34" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 15:08</t>
+          <t>14/08/2026 14:47</t>
         </is>
       </c>
       <c r="J34" s="27" t="n">
@@ -30941,7 +30941,7 @@
     <row r="35">
       <c r="A35" s="27" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B35" s="27" t="inlineStr">
@@ -30951,37 +30951,37 @@
       </c>
       <c r="C35" s="28" t="inlineStr">
         <is>
-          <t>16932419</t>
+          <t>16928880</t>
         </is>
       </c>
       <c r="D35" s="27" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E35" s="27" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="F35" s="27" t="inlineStr">
         <is>
-          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
+          <t>Rua CALOGERAS</t>
         </is>
       </c>
       <c r="G35" s="27" t="inlineStr">
         <is>
-          <t>451 - R</t>
+          <t>1325 - C</t>
         </is>
       </c>
       <c r="H35" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>12/08/2026 13:48</t>
         </is>
       </c>
       <c r="I35" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:49</t>
+          <t>12/08/2026 14:04</t>
         </is>
       </c>
       <c r="J35" s="27" t="n">
@@ -30991,7 +30991,7 @@
     <row r="36">
       <c r="A36" s="27" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B36" s="27" t="inlineStr">
@@ -31001,37 +31001,37 @@
       </c>
       <c r="C36" s="28" t="inlineStr">
         <is>
-          <t>16929550</t>
+          <t>16932419</t>
         </is>
       </c>
       <c r="D36" s="27" t="inlineStr">
         <is>
-          <t>420 - FERROVIARIA</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E36" s="27" t="inlineStr">
         <is>
-          <t>Q003</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F36" s="27" t="inlineStr">
         <is>
-          <t>Rua ALAMEDA DOS TROLLES</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="G36" s="27" t="inlineStr">
         <is>
-          <t>190 - R</t>
+          <t>451 - R</t>
         </is>
       </c>
       <c r="H36" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:31</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="I36" s="27" t="inlineStr">
         <is>
-          <t>14/08/2026 14:47</t>
+          <t>14/08/2026 14:49</t>
         </is>
       </c>
       <c r="J36" s="27" t="n">
@@ -31041,7 +31041,7 @@
     <row r="37">
       <c r="A37" s="27" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B37" s="27" t="inlineStr">
@@ -31051,37 +31051,37 @@
       </c>
       <c r="C37" s="28" t="inlineStr">
         <is>
-          <t>16928880</t>
+          <t>16932420</t>
         </is>
       </c>
       <c r="D37" s="27" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E37" s="27" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F37" s="27" t="inlineStr">
         <is>
-          <t>Rua CALOGERAS</t>
+          <t>Rua 18 DE JULHO</t>
         </is>
       </c>
       <c r="G37" s="27" t="inlineStr">
         <is>
-          <t>1325 - C</t>
+          <t>187 - R</t>
         </is>
       </c>
       <c r="H37" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 13:48</t>
+          <t>14/08/2026 14:52</t>
         </is>
       </c>
       <c r="I37" s="27" t="inlineStr">
         <is>
-          <t>12/08/2026 14:04</t>
+          <t>14/08/2026 15:08</t>
         </is>
       </c>
       <c r="J37" s="27" t="n">

--- a/data/historico/semanas_318-321.xlsx
+++ b/data/historico/semanas_318-321.xlsx
@@ -51735,7 +51735,7 @@
       </c>
       <c r="C96" s="30" t="inlineStr">
         <is>
-          <t>17017079</t>
+          <t>17017093</t>
         </is>
       </c>
       <c r="D96" s="29" t="inlineStr">
@@ -51755,17 +51755,17 @@
       </c>
       <c r="G96" s="29" t="inlineStr">
         <is>
-          <t>57 - R</t>
+          <t>69 - R</t>
         </is>
       </c>
       <c r="H96" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:16</t>
+          <t>17/08/2026 15:44</t>
         </is>
       </c>
       <c r="I96" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:32</t>
+          <t>17/08/2026 16:00</t>
         </is>
       </c>
       <c r="J96" s="29" t="n">
@@ -51785,7 +51785,7 @@
       </c>
       <c r="C97" s="30" t="inlineStr">
         <is>
-          <t>17017093</t>
+          <t>17017079</t>
         </is>
       </c>
       <c r="D97" s="29" t="inlineStr">
@@ -51805,17 +51805,17 @@
       </c>
       <c r="G97" s="29" t="inlineStr">
         <is>
-          <t>69 - R</t>
+          <t>57 - R</t>
         </is>
       </c>
       <c r="H97" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 15:44</t>
+          <t>17/08/2026 09:16</t>
         </is>
       </c>
       <c r="I97" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 16:00</t>
+          <t>17/08/2026 09:32</t>
         </is>
       </c>
       <c r="J97" s="29" t="n">

--- a/data/historico/semanas_318-321.xlsx
+++ b/data/historico/semanas_318-321.xlsx
@@ -25,8 +25,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo Geral'!$A$2:$AC$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por Área'!$A$2:$N$108</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Visitas Duplicadas'!$A$2:$J$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Visitas Suspeitas'!$A$2:$K$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Visitas Duplicadas'!$A$2:$J$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Visitas Suspeitas'!$A$2:$K$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Visitas Negativas'!$A$2:$K$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 15min'!$A$2:$J$121</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$53</definedName>
@@ -3442,25 +3442,25 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="E26" s="4" t="n">
         <v>12</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>23.42</v>
+        <v>22.67</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.12</v>
+        <v>5.29</v>
       </c>
       <c r="H26" s="4" t="n">
         <v>5</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>6.41</v>
+        <v>3.31</v>
       </c>
       <c r="K26" s="4" t="n">
         <v>0</v>
@@ -3472,10 +3472,10 @@
         <v>8</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="P26" s="4" t="n">
         <v>0</v>
@@ -3484,16 +3484,16 @@
         <v>0</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="S26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>48.44</v>
+        <v>49.16</v>
       </c>
       <c r="V26" s="4" t="n">
         <v>4.68</v>
@@ -6814,19 +6814,19 @@
         </is>
       </c>
       <c r="C26" s="29" t="n">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="D26" s="29" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E26" s="29" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="29" t="n">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="G26" s="29" t="n">
-        <v>48.44</v>
+        <v>49.16</v>
       </c>
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="n"/>
@@ -7365,19 +7365,19 @@
         </is>
       </c>
       <c r="C45" s="26" t="n">
-        <v>10880</v>
+        <v>10871</v>
       </c>
       <c r="D45" s="26" t="n">
-        <v>4859</v>
+        <v>4858</v>
       </c>
       <c r="E45" s="26" t="n">
         <v>14</v>
       </c>
       <c r="F45" s="26" t="n">
-        <v>15753</v>
+        <v>15743</v>
       </c>
       <c r="G45" s="26" t="n">
-        <v>30.93</v>
+        <v>30.95</v>
       </c>
       <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="n"/>
@@ -12388,105 +12388,105 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>17/08 a 21/08</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>🟡 ATENÇÃO</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="n">
-        <v>136</v>
-      </c>
-      <c r="G34" s="5" t="n">
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>127</v>
+      </c>
+      <c r="G34" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H34" s="5" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="J34" s="5" t="n">
+      <c r="H34" s="4" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="J34" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="K34" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>10.29</v>
-      </c>
-      <c r="M34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="5" t="n">
+      <c r="K34" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="P34" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q34" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="R34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="5" t="inlineStr"/>
-      <c r="U34" s="5" t="inlineStr"/>
-      <c r="V34" s="5" t="inlineStr"/>
-      <c r="W34" s="5" t="inlineStr"/>
-      <c r="X34" s="5" t="n">
+      <c r="L34" s="4" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="M34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P34" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q34" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="R34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="4" t="inlineStr"/>
+      <c r="U34" s="4" t="inlineStr"/>
+      <c r="V34" s="4" t="inlineStr"/>
+      <c r="W34" s="4" t="inlineStr"/>
+      <c r="X34" s="4" t="n">
         <v>5.5</v>
       </c>
-      <c r="Y34" s="5" t="n">
+      <c r="Y34" s="4" t="n">
         <v>27.52</v>
       </c>
-      <c r="Z34" s="5" t="n">
+      <c r="Z34" s="4" t="n">
         <v>2.23</v>
       </c>
-      <c r="AA34" s="5" t="inlineStr">
+      <c r="AA34" s="4" t="inlineStr">
         <is>
           <t>R$ 98,98</t>
         </is>
       </c>
-      <c r="AB34" s="5" t="inlineStr">
+      <c r="AB34" s="4" t="inlineStr">
         <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="AC34" s="5" t="inlineStr">
+      <c r="AC34" s="4" t="inlineStr">
         <is>
           <t>10:27</t>
         </is>
       </c>
-      <c r="AD34" s="5" t="inlineStr">
+      <c r="AD34" s="4" t="inlineStr">
         <is>
           <t>13:46</t>
         </is>
       </c>
-      <c r="AE34" s="5" t="inlineStr">
+      <c r="AE34" s="4" t="inlineStr">
         <is>
           <t>16:21</t>
         </is>
@@ -25861,61 +25861,61 @@
       </c>
       <c r="B33" s="38" t="inlineStr">
         <is>
+          <t>Claine Luisa Figueiredo Torraca</t>
+        </is>
+      </c>
+      <c r="C33" s="38" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="D33" s="38" t="n">
+        <v>12</v>
+      </c>
+      <c r="E33" s="38" t="n">
+        <v>15</v>
+      </c>
+      <c r="F33" s="38" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" s="38" t="n">
+        <v>70.12</v>
+      </c>
+      <c r="H33" s="38" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="38" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="38" t="inlineStr">
+        <is>
           <t>Carlos Alberto Albiero</t>
         </is>
       </c>
-      <c r="C33" s="38" t="inlineStr">
+      <c r="C34" s="38" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D33" s="38" t="n">
+      <c r="D34" s="38" t="n">
         <v>13</v>
       </c>
-      <c r="E33" s="38" t="n">
+      <c r="E34" s="38" t="n">
         <v>16</v>
       </c>
-      <c r="F33" s="38" t="n">
+      <c r="F34" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="G33" s="38" t="n">
+      <c r="G34" s="38" t="n">
         <v>64.29000000000001</v>
       </c>
-      <c r="H33" s="38" t="inlineStr">
+      <c r="H34" s="38" t="inlineStr">
         <is>
           <t>🟠 ATENÇÃO</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>Kátia Cilene Silveira Machado</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G34" s="6" t="n">
-        <v>57.38</v>
-      </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
         </is>
       </c>
     </row>
@@ -25925,25 +25925,25 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>56.42</v>
+        <v>57.38</v>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
@@ -25957,25 +25957,25 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D36" s="6" t="n">
         <v>11</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>56.05</v>
+        <v>56.42</v>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
@@ -25989,25 +25989,25 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>15</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>55.12</v>
+        <v>56.05</v>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
@@ -26021,25 +26021,25 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D38" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>53.69</v>
+        <v>55.12</v>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
@@ -26053,25 +26053,25 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Raquel Ortiz dos Santos</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>52.97</v>
+        <v>53.69</v>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
@@ -26085,25 +26085,25 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D40" s="6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E40" s="6" t="n">
         <v>16</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>52.9</v>
+        <v>52.97</v>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
@@ -26117,25 +26117,25 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E41" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>40.12</v>
+        <v>52.9</v>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
@@ -26149,25 +26149,25 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D42" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E42" s="6" t="n">
         <v>15</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>38.62</v>
+        <v>40.12</v>
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         </is>
       </c>
       <c r="D125" s="52" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E125" s="52" t="n">
         <v>0.3</v>
@@ -28776,7 +28776,7 @@
         <v>0.375</v>
       </c>
       <c r="H125" s="52" t="n">
-        <v>-12</v>
+        <v>-5.25</v>
       </c>
     </row>
     <row r="126">
@@ -28796,7 +28796,7 @@
         </is>
       </c>
       <c r="D126" s="52" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E126" s="52" t="n">
         <v>1</v>
@@ -28808,7 +28808,7 @@
         <v>1.25</v>
       </c>
       <c r="H126" s="52" t="n">
-        <v>-40</v>
+        <v>-17.5</v>
       </c>
     </row>
     <row r="127">
@@ -28828,7 +28828,7 @@
         </is>
       </c>
       <c r="D127" s="52" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E127" s="52" t="n">
         <v>0.2</v>
@@ -28840,7 +28840,7 @@
         <v>0.25</v>
       </c>
       <c r="H127" s="52" t="n">
-        <v>-4.5</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="128">
@@ -39961,56 +39961,56 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
-      <c r="D56" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="F56" s="5" t="n">
+      <c r="D56" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="F56" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G56" s="5" t="n">
+      <c r="G56" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="H56" s="4" t="inlineStr">
         <is>
           <t>Q014, Q015, Q029, Q030</t>
         </is>
       </c>
-      <c r="I56" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J56" s="5" t="n">
-        <v>16.33</v>
-      </c>
-      <c r="K56" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="L56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="5" t="n">
-        <v>48.96</v>
-      </c>
-      <c r="N56" s="5" t="inlineStr">
-        <is>
-          <t>🟡 ATENÇÃO</t>
+      <c r="I56" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J56" s="4" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="K56" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="4" t="n">
+        <v>51.11</v>
+      </c>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
         </is>
       </c>
     </row>
@@ -40031,10 +40031,10 @@
         </is>
       </c>
       <c r="D57" s="4" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>5.03</v>
+        <v>5.2</v>
       </c>
       <c r="F57" s="4" t="n">
         <v>5</v>
@@ -40048,10 +40048,10 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>7.14</v>
+        <v>4.1</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>95</v>
@@ -40060,7 +40060,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="4" t="n">
-        <v>42.99</v>
+        <v>43.78</v>
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -42969,7 +42969,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VISITAS DUPLICADAS (32 registros) — CONFIRME E EXCLUA NO SISTEMA</t>
+          <t>VISITAS DUPLICADAS (14 registros) — CONFIRME E EXCLUA NO SISTEMA</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -43463,37 +43463,37 @@
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
-          <t>17078217</t>
+          <t>17019173</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>Rua XAVANTES</t>
+          <t>Rua CARAMBOLEIRA</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
         <is>
-          <t>567 - 2 - TB</t>
+          <t>105 - 1 - TB</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
         <is>
-          <t>21/08/2026 09:50</t>
+          <t>19/08/2026 09:36</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
         <is>
-          <t>21/08/2026 09:55</t>
+          <t>19/08/2026 09:36</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -43515,37 +43515,37 @@
       </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
-          <t>17078216</t>
+          <t>17019174</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>Rua XAVANTES</t>
+          <t>Rua CARAMBOLEIRA</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
-          <t>567 - 2 - TB</t>
+          <t>105 - 1 - TB</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
         <is>
-          <t>21/08/2026 09:50</t>
+          <t>19/08/2026 09:36</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
-          <t>21/08/2026 09:50</t>
+          <t>19/08/2026 09:42</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -43567,37 +43567,37 @@
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
-          <t>17078208</t>
+          <t>17019195</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>Rua GUARANTA</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
         <is>
-          <t>617 - 1 - TB</t>
+          <t>106 - 2 - TB</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
         <is>
-          <t>21/08/2026 09:21</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
         <is>
-          <t>21/08/2026 09:21</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -43619,37 +43619,37 @@
       </c>
       <c r="C14" s="21" t="inlineStr">
         <is>
-          <t>17078209</t>
+          <t>17019196</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>Rua GUARANTA</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
-          <t>617 - 1 - TB</t>
+          <t>106 - 2 - TB</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
-          <t>21/08/2026 09:21</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
-          <t>21/08/2026 09:27</t>
+          <t>19/08/2026 14:24</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -43671,37 +43671,37 @@
       </c>
       <c r="C15" s="21" t="inlineStr">
         <is>
-          <t>17048102</t>
+          <t>17019200</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
         <is>
-          <t>Q004</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>Rua NOGUEIRA</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
         <is>
-          <t>669 - 3 - TB</t>
+          <t>55 - 1 - TB</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
         <is>
-          <t>20/08/2026 13:35</t>
+          <t>19/08/2026 14:33</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
         <is>
-          <t>20/08/2026 13:35</t>
+          <t>19/08/2026 14:33</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -43723,37 +43723,37 @@
       </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
-          <t>17048103</t>
+          <t>17019201</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Q004</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>Rua NOGUEIRA</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
         <is>
-          <t>669 - 3 - TB</t>
+          <t>55 - 1 - TB</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
         <is>
-          <t>20/08/2026 13:35</t>
+          <t>19/08/2026 14:33</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
         <is>
-          <t>20/08/2026 13:41</t>
+          <t>19/08/2026 14:38</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -43762,944 +43762,8 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>17078203</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>Q006</t>
-        </is>
-      </c>
-      <c r="F17" s="20" t="inlineStr">
-        <is>
-          <t>Rua GUARANTA</t>
-        </is>
-      </c>
-      <c r="G17" s="20" t="inlineStr">
-        <is>
-          <t>677 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H17" s="20" t="inlineStr">
-        <is>
-          <t>21/08/2026 09:12</t>
-        </is>
-      </c>
-      <c r="I17" s="20" t="inlineStr">
-        <is>
-          <t>21/08/2026 09:12</t>
-        </is>
-      </c>
-      <c r="J17" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>17078204</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr">
-        <is>
-          <t>Q006</t>
-        </is>
-      </c>
-      <c r="F18" s="20" t="inlineStr">
-        <is>
-          <t>Rua GUARANTA</t>
-        </is>
-      </c>
-      <c r="G18" s="20" t="inlineStr">
-        <is>
-          <t>677 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H18" s="20" t="inlineStr">
-        <is>
-          <t>21/08/2026 09:12</t>
-        </is>
-      </c>
-      <c r="I18" s="20" t="inlineStr">
-        <is>
-          <t>21/08/2026 09:18</t>
-        </is>
-      </c>
-      <c r="J18" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>17019173</t>
-        </is>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr">
-        <is>
-          <t>Q029</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>Rua CARAMBOLEIRA</t>
-        </is>
-      </c>
-      <c r="G19" s="20" t="inlineStr">
-        <is>
-          <t>105 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H19" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 09:36</t>
-        </is>
-      </c>
-      <c r="I19" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 09:36</t>
-        </is>
-      </c>
-      <c r="J19" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>17019174</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
-        <is>
-          <t>Q029</t>
-        </is>
-      </c>
-      <c r="F20" s="20" t="inlineStr">
-        <is>
-          <t>Rua CARAMBOLEIRA</t>
-        </is>
-      </c>
-      <c r="G20" s="20" t="inlineStr">
-        <is>
-          <t>105 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H20" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 09:36</t>
-        </is>
-      </c>
-      <c r="I20" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 09:42</t>
-        </is>
-      </c>
-      <c r="J20" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
-        <is>
-          <t>17019193</t>
-        </is>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E21" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>Rua CARAMBOLEIRA</t>
-        </is>
-      </c>
-      <c r="G21" s="20" t="inlineStr">
-        <is>
-          <t>106 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H21" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:12</t>
-        </is>
-      </c>
-      <c r="I21" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:12</t>
-        </is>
-      </c>
-      <c r="J21" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>17019194</t>
-        </is>
-      </c>
-      <c r="D22" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F22" s="20" t="inlineStr">
-        <is>
-          <t>Rua CARAMBOLEIRA</t>
-        </is>
-      </c>
-      <c r="G22" s="20" t="inlineStr">
-        <is>
-          <t>106 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H22" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:12</t>
-        </is>
-      </c>
-      <c r="I22" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:18</t>
-        </is>
-      </c>
-      <c r="J22" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>17019196</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="G23" s="20" t="inlineStr">
-        <is>
-          <t>106 - 2 - TB</t>
-        </is>
-      </c>
-      <c r="H23" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:18</t>
-        </is>
-      </c>
-      <c r="I23" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:24</t>
-        </is>
-      </c>
-      <c r="J23" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>17019195</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F24" s="20" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="G24" s="20" t="inlineStr">
-        <is>
-          <t>106 - 2 - TB</t>
-        </is>
-      </c>
-      <c r="H24" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:18</t>
-        </is>
-      </c>
-      <c r="I24" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:18</t>
-        </is>
-      </c>
-      <c r="J24" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>17019182</t>
-        </is>
-      </c>
-      <c r="D25" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F25" s="20" t="inlineStr">
-        <is>
-          <t>Rua CARAMBOLEIRA</t>
-        </is>
-      </c>
-      <c r="G25" s="20" t="inlineStr">
-        <is>
-          <t>18 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H25" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 10:11</t>
-        </is>
-      </c>
-      <c r="I25" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 10:11</t>
-        </is>
-      </c>
-      <c r="J25" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="inlineStr">
-        <is>
-          <t>17019183</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F26" s="20" t="inlineStr">
-        <is>
-          <t>Rua CARAMBOLEIRA</t>
-        </is>
-      </c>
-      <c r="G26" s="20" t="inlineStr">
-        <is>
-          <t>18 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H26" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 10:11</t>
-        </is>
-      </c>
-      <c r="I26" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 10:16</t>
-        </is>
-      </c>
-      <c r="J26" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C27" s="21" t="inlineStr">
-        <is>
-          <t>17019158</t>
-        </is>
-      </c>
-      <c r="D27" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E27" s="20" t="inlineStr">
-        <is>
-          <t>Q029</t>
-        </is>
-      </c>
-      <c r="F27" s="20" t="inlineStr">
-        <is>
-          <t>Rua CAJUEIRO</t>
-        </is>
-      </c>
-      <c r="G27" s="20" t="inlineStr">
-        <is>
-          <t>26 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H27" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 08:45</t>
-        </is>
-      </c>
-      <c r="I27" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 08:45</t>
-        </is>
-      </c>
-      <c r="J27" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>17019159</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>Q029</t>
-        </is>
-      </c>
-      <c r="F28" s="20" t="inlineStr">
-        <is>
-          <t>Rua CAJUEIRO</t>
-        </is>
-      </c>
-      <c r="G28" s="20" t="inlineStr">
-        <is>
-          <t>26 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H28" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 08:45</t>
-        </is>
-      </c>
-      <c r="I28" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 08:51</t>
-        </is>
-      </c>
-      <c r="J28" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C29" s="21" t="inlineStr">
-        <is>
-          <t>17019200</t>
-        </is>
-      </c>
-      <c r="D29" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E29" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F29" s="20" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="G29" s="20" t="inlineStr">
-        <is>
-          <t>55 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H29" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:33</t>
-        </is>
-      </c>
-      <c r="I29" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:33</t>
-        </is>
-      </c>
-      <c r="J29" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C30" s="21" t="inlineStr">
-        <is>
-          <t>17019201</t>
-        </is>
-      </c>
-      <c r="D30" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E30" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F30" s="20" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="G30" s="20" t="inlineStr">
-        <is>
-          <t>55 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H30" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:33</t>
-        </is>
-      </c>
-      <c r="I30" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:38</t>
-        </is>
-      </c>
-      <c r="J30" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>17019184</t>
-        </is>
-      </c>
-      <c r="D31" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E31" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F31" s="20" t="inlineStr">
-        <is>
-          <t>Rua CARAMBOLEIRA</t>
-        </is>
-      </c>
-      <c r="G31" s="20" t="inlineStr">
-        <is>
-          <t>84 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H31" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 10:17</t>
-        </is>
-      </c>
-      <c r="I31" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 10:17</t>
-        </is>
-      </c>
-      <c r="J31" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>17019185</t>
-        </is>
-      </c>
-      <c r="D32" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E32" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F32" s="20" t="inlineStr">
-        <is>
-          <t>Rua CARAMBOLEIRA</t>
-        </is>
-      </c>
-      <c r="G32" s="20" t="inlineStr">
-        <is>
-          <t>84 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H32" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 10:17</t>
-        </is>
-      </c>
-      <c r="I32" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 10:23</t>
-        </is>
-      </c>
-      <c r="J32" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B33" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C33" s="21" t="inlineStr">
-        <is>
-          <t>17019165</t>
-        </is>
-      </c>
-      <c r="D33" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E33" s="20" t="inlineStr">
-        <is>
-          <t>Q029</t>
-        </is>
-      </c>
-      <c r="F33" s="20" t="inlineStr">
-        <is>
-          <t>Rua CAJUEIRO</t>
-        </is>
-      </c>
-      <c r="G33" s="20" t="inlineStr">
-        <is>
-          <t>96 - 01 - TB</t>
-        </is>
-      </c>
-      <c r="H33" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 09:08</t>
-        </is>
-      </c>
-      <c r="I33" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 09:08</t>
-        </is>
-      </c>
-      <c r="J33" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B34" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C34" s="21" t="inlineStr">
-        <is>
-          <t>17019166</t>
-        </is>
-      </c>
-      <c r="D34" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E34" s="20" t="inlineStr">
-        <is>
-          <t>Q029</t>
-        </is>
-      </c>
-      <c r="F34" s="20" t="inlineStr">
-        <is>
-          <t>Rua CAJUEIRO</t>
-        </is>
-      </c>
-      <c r="G34" s="20" t="inlineStr">
-        <is>
-          <t>96 - 01 - TB</t>
-        </is>
-      </c>
-      <c r="H34" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 09:08</t>
-        </is>
-      </c>
-      <c r="I34" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 09:16</t>
-        </is>
-      </c>
-      <c r="J34" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:J34"/>
+  <autoFilter ref="A2:J16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -44718,24 +43782,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -44747,7 +43793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -44766,7 +43812,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VISITAS EM SEQUÊNCIA SUSPEITA (50 registros) — CHEGADA NO MESMO MINUTO DA VISITA ANTERIOR</t>
+          <t>VISITAS EM SEQUÊNCIA SUSPEITA (32 registros) — CHEGADA NO MESMO MINUTO DA VISITA ANTERIOR</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -45271,7 +44317,7 @@
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>17019158</t>
+          <t>17019173</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -45286,22 +44332,22 @@
       </c>
       <c r="G11" s="23" t="inlineStr">
         <is>
-          <t>Rua CAJUEIRO</t>
+          <t>Rua CARAMBOLEIRA</t>
         </is>
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
-          <t>26 - 1 - TB</t>
+          <t>105 - 1 - TB</t>
         </is>
       </c>
       <c r="I11" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 08:45</t>
+          <t>19/08/2026 09:36</t>
         </is>
       </c>
       <c r="J11" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 08:45</t>
+          <t>19/08/2026 09:36</t>
         </is>
       </c>
       <c r="K11" s="23" t="inlineStr"/>
@@ -45322,7 +44368,7 @@
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>17019159</t>
+          <t>17019174</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -45337,22 +44383,22 @@
       </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
-          <t>Rua CAJUEIRO</t>
+          <t>Rua CARAMBOLEIRA</t>
         </is>
       </c>
       <c r="H12" s="23" t="inlineStr">
         <is>
-          <t>26 - 1 - TB</t>
+          <t>105 - 1 - TB</t>
         </is>
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 08:45</t>
+          <t>19/08/2026 09:36</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 08:51</t>
+          <t>19/08/2026 09:42</t>
         </is>
       </c>
       <c r="K12" s="23" t="n">
@@ -45375,7 +44421,7 @@
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>17019165</t>
+          <t>17019195</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -45385,27 +44431,27 @@
       </c>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="G13" s="23" t="inlineStr">
         <is>
-          <t>Rua CAJUEIRO</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="H13" s="23" t="inlineStr">
         <is>
-          <t>96 - 01 - TB</t>
+          <t>106 - 2 - TB</t>
         </is>
       </c>
       <c r="I13" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:08</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="J13" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:08</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="K13" s="23" t="inlineStr"/>
@@ -45426,7 +44472,7 @@
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>17019166</t>
+          <t>17019196</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -45436,27 +44482,27 @@
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
-          <t>Rua CAJUEIRO</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">
         <is>
-          <t>96 - 01 - TB</t>
+          <t>106 - 2 - TB</t>
         </is>
       </c>
       <c r="I14" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:08</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:16</t>
+          <t>19/08/2026 14:24</t>
         </is>
       </c>
       <c r="K14" s="23" t="n">
@@ -45479,7 +44525,7 @@
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>17019173</t>
+          <t>17019200</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -45489,27 +44535,27 @@
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="G15" s="23" t="inlineStr">
         <is>
-          <t>Rua CARAMBOLEIRA</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="H15" s="23" t="inlineStr">
         <is>
-          <t>105 - 1 - TB</t>
+          <t>55 - 1 - TB</t>
         </is>
       </c>
       <c r="I15" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:36</t>
+          <t>19/08/2026 14:33</t>
         </is>
       </c>
       <c r="J15" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:36</t>
+          <t>19/08/2026 14:33</t>
         </is>
       </c>
       <c r="K15" s="23" t="inlineStr"/>
@@ -45530,7 +44576,7 @@
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>17019174</t>
+          <t>17019201</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -45540,27 +44586,27 @@
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
         <is>
-          <t>Rua CARAMBOLEIRA</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">
         <is>
-          <t>105 - 1 - TB</t>
+          <t>55 - 1 - TB</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:36</t>
+          <t>19/08/2026 14:33</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:42</t>
+          <t>19/08/2026 14:38</t>
         </is>
       </c>
       <c r="K16" s="23" t="n">
@@ -45579,41 +44625,41 @@
         </is>
       </c>
       <c r="C17" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>17019182</t>
+          <t>17101465</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>429 - COOPHA FRONTEIRA</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q036</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
         <is>
-          <t>Rua CARAMBOLEIRA</t>
+          <t>Rua FERNANDO PERALTA</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
         <is>
-          <t>18 - 1 - TB</t>
+          <t>269 - R</t>
         </is>
       </c>
       <c r="I17" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 10:11</t>
+          <t>24/08/2026 09:06</t>
         </is>
       </c>
       <c r="J17" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 10:11</t>
+          <t>24/08/2026 09:06</t>
         </is>
       </c>
       <c r="K17" s="23" t="inlineStr"/>
@@ -45630,41 +44676,41 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>17019183</t>
+          <t>17101466</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>429 - COOPHA FRONTEIRA</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q036</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
         <is>
-          <t>Rua CARAMBOLEIRA</t>
+          <t>Rua FERNANDO PERALTA</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
         <is>
-          <t>18 - 1 - TB</t>
+          <t>269 - R</t>
         </is>
       </c>
       <c r="I18" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 10:11</t>
+          <t>24/08/2026 09:06</t>
         </is>
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 10:16</t>
+          <t>24/08/2026 09:12</t>
         </is>
       </c>
       <c r="K18" s="23" t="n">
@@ -45683,41 +44729,41 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>17019184</t>
+          <t>17101491</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>429 - COOPHA FRONTEIRA</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q036</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
         <is>
-          <t>Rua CARAMBOLEIRA</t>
+          <t>Avenida BELMIRO DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="H19" s="23" t="inlineStr">
         <is>
-          <t>84 - 1 - TB</t>
+          <t>1197 - 1 - TB</t>
         </is>
       </c>
       <c r="I19" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 10:17</t>
+          <t>24/08/2026 10:27</t>
         </is>
       </c>
       <c r="J19" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 10:17</t>
+          <t>24/08/2026 10:33</t>
         </is>
       </c>
       <c r="K19" s="23" t="inlineStr"/>
@@ -45734,41 +44780,41 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>17019185</t>
+          <t>17101490</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>429 - COOPHA FRONTEIRA</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q036</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>Rua CARAMBOLEIRA</t>
+          <t>Avenida BELMIRO DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
         <is>
-          <t>84 - 1 - TB</t>
+          <t>1197 - 1 - TB</t>
         </is>
       </c>
       <c r="I20" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 10:17</t>
+          <t>24/08/2026 10:27</t>
         </is>
       </c>
       <c r="J20" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 10:23</t>
+          <t>24/08/2026 10:27</t>
         </is>
       </c>
       <c r="K20" s="23" t="n">
@@ -45787,41 +44833,41 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>17019193</t>
+          <t>17101497</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>429 - COOPHA FRONTEIRA</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q037</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
         <is>
-          <t>Rua CARAMBOLEIRA</t>
+          <t>Rua FRANCISCO PUIG</t>
         </is>
       </c>
       <c r="H21" s="23" t="inlineStr">
         <is>
-          <t>106 - 1 - TB</t>
+          <t>371 - 1 - TB</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:12</t>
+          <t>24/08/2026 14:16</t>
         </is>
       </c>
       <c r="J21" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:12</t>
+          <t>24/08/2026 14:16</t>
         </is>
       </c>
       <c r="K21" s="23" t="inlineStr"/>
@@ -45838,41 +44884,41 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>17019194</t>
+          <t>17101498</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>429 - COOPHA FRONTEIRA</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q037</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">
         <is>
-          <t>Rua CARAMBOLEIRA</t>
+          <t>Rua FRANCISCO PUIG</t>
         </is>
       </c>
       <c r="H22" s="23" t="inlineStr">
         <is>
-          <t>106 - 1 - TB</t>
+          <t>371 - 1 - TB</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:12</t>
+          <t>24/08/2026 14:16</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:18</t>
+          <t>24/08/2026 14:21</t>
         </is>
       </c>
       <c r="K22" s="23" t="n">
@@ -45891,41 +44937,41 @@
         </is>
       </c>
       <c r="C23" s="23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>17019196</t>
+          <t>17133570</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>429 - COOPHA FRONTEIRA</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q039</t>
         </is>
       </c>
       <c r="G23" s="23" t="inlineStr">
         <is>
-          <t>Rua AMEIXEIRA</t>
+          <t>Rua NAPOLEÃO ALVES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="H23" s="23" t="inlineStr">
         <is>
-          <t>106 - 2 - TB</t>
+          <t>249 - R</t>
         </is>
       </c>
       <c r="I23" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:18</t>
+          <t>25/08/2026 14:06</t>
         </is>
       </c>
       <c r="J23" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:24</t>
+          <t>25/08/2026 14:06</t>
         </is>
       </c>
       <c r="K23" s="23" t="inlineStr"/>
@@ -45942,41 +44988,41 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>17019195</t>
+          <t>17133571</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>429 - COOPHA FRONTEIRA</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q039</t>
         </is>
       </c>
       <c r="G24" s="23" t="inlineStr">
         <is>
-          <t>Rua AMEIXEIRA</t>
+          <t>Rua NAPOLEÃO ALVES DE OLIVEIRA</t>
         </is>
       </c>
       <c r="H24" s="23" t="inlineStr">
         <is>
-          <t>106 - 2 - TB</t>
+          <t>249 - R</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:18</t>
+          <t>25/08/2026 14:06</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:18</t>
+          <t>25/08/2026 14:12</t>
         </is>
       </c>
       <c r="K24" s="23" t="n">
@@ -45986,7 +45032,7 @@
     <row r="25">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="B25" s="23" t="inlineStr">
@@ -45995,41 +45041,41 @@
         </is>
       </c>
       <c r="C25" s="23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>17019200</t>
+          <t>16959229</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>430 - VILA RENÔ</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
         <is>
-          <t>Rua AMEIXEIRA</t>
+          <t>Avenida URUMBELA</t>
         </is>
       </c>
       <c r="H25" s="23" t="inlineStr">
         <is>
-          <t>55 - 1 - TB</t>
+          <t>890 - 10 - R</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:33</t>
+          <t>18/08/2026 09:50</t>
         </is>
       </c>
       <c r="J25" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:33</t>
+          <t>18/08/2026 09:51</t>
         </is>
       </c>
       <c r="K25" s="23" t="inlineStr"/>
@@ -46037,7 +45083,7 @@
     <row r="26">
       <c r="A26" s="23" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="B26" s="23" t="inlineStr">
@@ -46046,41 +45092,41 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>17019201</t>
+          <t>16959228</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>430 - VILA RENÔ</t>
         </is>
       </c>
       <c r="F26" s="23" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">
         <is>
-          <t>Rua AMEIXEIRA</t>
+          <t>Avenida URUMBELA</t>
         </is>
       </c>
       <c r="H26" s="23" t="inlineStr">
         <is>
-          <t>55 - 1 - TB</t>
+          <t>890 - 9 - C</t>
         </is>
       </c>
       <c r="I26" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:33</t>
+          <t>18/08/2026 09:50</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:38</t>
+          <t>18/08/2026 09:50</t>
         </is>
       </c>
       <c r="K26" s="23" t="n">
@@ -46090,7 +45136,7 @@
     <row r="27">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="B27" s="23" t="inlineStr">
@@ -46099,11 +45145,11 @@
         </is>
       </c>
       <c r="C27" s="23" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>17048102</t>
+          <t>17127483</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
@@ -46113,27 +45159,27 @@
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t>Q004</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="G27" s="23" t="inlineStr">
         <is>
-          <t>Rua NOGUEIRA</t>
+          <t>Rua SAMAMBAIA</t>
         </is>
       </c>
       <c r="H27" s="23" t="inlineStr">
         <is>
-          <t>669 - 3 - TB</t>
+          <t>214 - 4 - R</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
         <is>
-          <t>20/08/2026 13:35</t>
+          <t>25/08/2026 14:20</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
         <is>
-          <t>20/08/2026 13:35</t>
+          <t>25/08/2026 14:21</t>
         </is>
       </c>
       <c r="K27" s="23" t="inlineStr"/>
@@ -46141,7 +45187,7 @@
     <row r="28">
       <c r="A28" s="23" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="B28" s="23" t="inlineStr">
@@ -46150,11 +45196,11 @@
         </is>
       </c>
       <c r="C28" s="23" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>17048103</t>
+          <t>17127482</t>
         </is>
       </c>
       <c r="E28" s="23" t="inlineStr">
@@ -46164,27 +45210,27 @@
       </c>
       <c r="F28" s="23" t="inlineStr">
         <is>
-          <t>Q004</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
-          <t>Rua NOGUEIRA</t>
+          <t>Rua SAMAMBAIA</t>
         </is>
       </c>
       <c r="H28" s="23" t="inlineStr">
         <is>
-          <t>669 - 3 - TB</t>
+          <t>214 - 3 - R</t>
         </is>
       </c>
       <c r="I28" s="23" t="inlineStr">
         <is>
-          <t>20/08/2026 13:35</t>
+          <t>25/08/2026 14:20</t>
         </is>
       </c>
       <c r="J28" s="23" t="inlineStr">
         <is>
-          <t>20/08/2026 13:41</t>
+          <t>25/08/2026 14:20</t>
         </is>
       </c>
       <c r="K28" s="23" t="n">
@@ -46194,50 +45240,50 @@
     <row r="29">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C29" s="23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>17078203</t>
+          <t>16920467</t>
         </is>
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>435 - JARDIM PRIMOR</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
         <is>
-          <t>Rua GUARANTA</t>
+          <t>Rua PARANAGUA</t>
         </is>
       </c>
       <c r="H29" s="23" t="inlineStr">
         <is>
-          <t>677 - 1 - TB</t>
+          <t>20 - 3 - C</t>
         </is>
       </c>
       <c r="I29" s="23" t="inlineStr">
         <is>
-          <t>21/08/2026 09:12</t>
+          <t>13/08/2026 16:30</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">
         <is>
-          <t>21/08/2026 09:12</t>
+          <t>13/08/2026 16:30</t>
         </is>
       </c>
       <c r="K29" s="23" t="inlineStr"/>
@@ -46245,50 +45291,50 @@
     <row r="30">
       <c r="A30" s="23" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C30" s="23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
-          <t>17078204</t>
+          <t>16920468</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>435 - JARDIM PRIMOR</t>
         </is>
       </c>
       <c r="F30" s="23" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
         <is>
-          <t>Rua GUARANTA</t>
+          <t>Rua PARANAGUA</t>
         </is>
       </c>
       <c r="H30" s="23" t="inlineStr">
         <is>
-          <t>677 - 1 - TB</t>
+          <t>20 - 5 - C</t>
         </is>
       </c>
       <c r="I30" s="23" t="inlineStr">
         <is>
-          <t>21/08/2026 09:12</t>
+          <t>13/08/2026 16:30</t>
         </is>
       </c>
       <c r="J30" s="23" t="inlineStr">
         <is>
-          <t>21/08/2026 09:18</t>
+          <t>13/08/2026 16:30</t>
         </is>
       </c>
       <c r="K30" s="23" t="n">
@@ -46298,7 +45344,7 @@
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="B31" s="23" t="inlineStr">
@@ -46307,41 +45353,41 @@
         </is>
       </c>
       <c r="C31" s="23" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>17078208</t>
+          <t>17131125</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>431 - PANAMBI</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
         <is>
-          <t>Rua GUARANTA</t>
+          <t>Rua CAMPO GRANDE</t>
         </is>
       </c>
       <c r="H31" s="23" t="inlineStr">
         <is>
-          <t>617 - 1 - TB</t>
+          <t>55 - R</t>
         </is>
       </c>
       <c r="I31" s="23" t="inlineStr">
         <is>
-          <t>21/08/2026 09:21</t>
+          <t>25/08/2026 14:19</t>
         </is>
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>21/08/2026 09:21</t>
+          <t>25/08/2026 14:25</t>
         </is>
       </c>
       <c r="K31" s="23" t="inlineStr"/>
@@ -46349,7 +45395,7 @@
     <row r="32">
       <c r="A32" s="23" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="B32" s="23" t="inlineStr">
@@ -46358,41 +45404,41 @@
         </is>
       </c>
       <c r="C32" s="23" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>17078209</t>
+          <t>17131126</t>
         </is>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>431 - PANAMBI</t>
         </is>
       </c>
       <c r="F32" s="23" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
-          <t>Rua GUARANTA</t>
+          <t>Rua CAMPO GRANDE</t>
         </is>
       </c>
       <c r="H32" s="23" t="inlineStr">
         <is>
-          <t>617 - 1 - TB</t>
+          <t>23 - 1 - R</t>
         </is>
       </c>
       <c r="I32" s="23" t="inlineStr">
         <is>
-          <t>21/08/2026 09:21</t>
+          <t>25/08/2026 14:19</t>
         </is>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>21/08/2026 09:27</t>
+          <t>25/08/2026 14:25</t>
         </is>
       </c>
       <c r="K32" s="23" t="n">
@@ -46402,50 +45448,50 @@
     <row r="33">
       <c r="A33" s="23" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C33" s="23" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>17078217</t>
+          <t>16932408</t>
         </is>
       </c>
       <c r="E33" s="23" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="G33" s="23" t="inlineStr">
         <is>
-          <t>Rua XAVANTES</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="H33" s="23" t="inlineStr">
         <is>
-          <t>567 - 2 - TB</t>
+          <t>491 - TB</t>
         </is>
       </c>
       <c r="I33" s="23" t="inlineStr">
         <is>
-          <t>21/08/2026 09:50</t>
+          <t>14/08/2026 10:00</t>
         </is>
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>21/08/2026 09:55</t>
+          <t>14/08/2026 10:06</t>
         </is>
       </c>
       <c r="K33" s="23" t="inlineStr"/>
@@ -46453,1110 +45499,174 @@
     <row r="34">
       <c r="A34" s="23" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>17078216</t>
+          <t>16932412</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="F34" s="23" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="G34" s="23" t="inlineStr">
         <is>
-          <t>Rua XAVANTES</t>
+          <t>Rua MARACAJU</t>
         </is>
       </c>
       <c r="H34" s="23" t="inlineStr">
         <is>
-          <t>567 - 2 - TB</t>
+          <t>194 - 3 - R</t>
         </is>
       </c>
       <c r="I34" s="23" t="inlineStr">
         <is>
-          <t>21/08/2026 09:50</t>
+          <t>14/08/2026 10:00</t>
         </is>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>21/08/2026 09:50</t>
+          <t>14/08/2026 10:07</t>
         </is>
       </c>
       <c r="K34" s="23" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B35" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C35" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="24" t="inlineStr">
-        <is>
-          <t>17101465</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="F35" s="23" t="inlineStr">
-        <is>
-          <t>Q036</t>
-        </is>
-      </c>
-      <c r="G35" s="23" t="inlineStr">
-        <is>
-          <t>Rua FERNANDO PERALTA</t>
-        </is>
-      </c>
-      <c r="H35" s="23" t="inlineStr">
-        <is>
-          <t>269 - R</t>
-        </is>
-      </c>
-      <c r="I35" s="23" t="inlineStr">
-        <is>
-          <t>24/08/2026 09:06</t>
-        </is>
-      </c>
-      <c r="J35" s="23" t="inlineStr">
-        <is>
-          <t>24/08/2026 09:06</t>
-        </is>
-      </c>
-      <c r="K35" s="23" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B36" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C36" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="24" t="inlineStr">
-        <is>
-          <t>17101466</t>
-        </is>
-      </c>
-      <c r="E36" s="23" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="F36" s="23" t="inlineStr">
-        <is>
-          <t>Q036</t>
-        </is>
-      </c>
-      <c r="G36" s="23" t="inlineStr">
-        <is>
-          <t>Rua FERNANDO PERALTA</t>
-        </is>
-      </c>
-      <c r="H36" s="23" t="inlineStr">
-        <is>
-          <t>269 - R</t>
-        </is>
-      </c>
-      <c r="I36" s="23" t="inlineStr">
-        <is>
-          <t>24/08/2026 09:06</t>
-        </is>
-      </c>
-      <c r="J36" s="23" t="inlineStr">
-        <is>
-          <t>24/08/2026 09:12</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="37">
-      <c r="A37" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B37" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C37" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="D37" s="24" t="inlineStr">
-        <is>
-          <t>17101491</t>
-        </is>
-      </c>
-      <c r="E37" s="23" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="F37" s="23" t="inlineStr">
-        <is>
-          <t>Q036</t>
-        </is>
-      </c>
-      <c r="G37" s="23" t="inlineStr">
-        <is>
-          <t>Avenida BELMIRO DE ALBUQUERQUE</t>
-        </is>
-      </c>
-      <c r="H37" s="23" t="inlineStr">
-        <is>
-          <t>1197 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="I37" s="23" t="inlineStr">
-        <is>
-          <t>24/08/2026 10:27</t>
-        </is>
-      </c>
-      <c r="J37" s="23" t="inlineStr">
-        <is>
-          <t>24/08/2026 10:33</t>
-        </is>
-      </c>
-      <c r="K37" s="23" t="inlineStr"/>
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>LEGENDA — CLASSIFICAÇÃO (baseada em % de Visitas Rápidas)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B38" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C38" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" s="24" t="inlineStr">
-        <is>
-          <t>17101490</t>
-        </is>
-      </c>
-      <c r="E38" s="23" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="F38" s="23" t="inlineStr">
-        <is>
-          <t>Q036</t>
-        </is>
-      </c>
-      <c r="G38" s="23" t="inlineStr">
-        <is>
-          <t>Avenida BELMIRO DE ALBUQUERQUE</t>
-        </is>
-      </c>
-      <c r="H38" s="23" t="inlineStr">
-        <is>
-          <t>1197 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="I38" s="23" t="inlineStr">
-        <is>
-          <t>24/08/2026 10:27</t>
-        </is>
-      </c>
-      <c r="J38" s="23" t="inlineStr">
-        <is>
-          <t>24/08/2026 10:27</t>
-        </is>
-      </c>
-      <c r="K38" s="23" t="n">
-        <v>0</v>
-      </c>
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>% Rápidas até 10%</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B39" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C39" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="D39" s="24" t="inlineStr">
-        <is>
-          <t>17101497</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="F39" s="23" t="inlineStr">
-        <is>
-          <t>Q037</t>
-        </is>
-      </c>
-      <c r="G39" s="23" t="inlineStr">
-        <is>
-          <t>Rua FRANCISCO PUIG</t>
-        </is>
-      </c>
-      <c r="H39" s="23" t="inlineStr">
-        <is>
-          <t>371 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="I39" s="23" t="inlineStr">
-        <is>
-          <t>24/08/2026 14:16</t>
-        </is>
-      </c>
-      <c r="J39" s="23" t="inlineStr">
-        <is>
-          <t>24/08/2026 14:16</t>
-        </is>
-      </c>
-      <c r="K39" s="23" t="inlineStr"/>
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>🟡 ATENÇÃO</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>% Rápidas entre 11% e 20%</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B40" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C40" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="D40" s="24" t="inlineStr">
-        <is>
-          <t>17101498</t>
-        </is>
-      </c>
-      <c r="E40" s="23" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="F40" s="23" t="inlineStr">
-        <is>
-          <t>Q037</t>
-        </is>
-      </c>
-      <c r="G40" s="23" t="inlineStr">
-        <is>
-          <t>Rua FRANCISCO PUIG</t>
-        </is>
-      </c>
-      <c r="H40" s="23" t="inlineStr">
-        <is>
-          <t>371 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="I40" s="23" t="inlineStr">
-        <is>
-          <t>24/08/2026 14:16</t>
-        </is>
-      </c>
-      <c r="J40" s="23" t="inlineStr">
-        <is>
-          <t>24/08/2026 14:21</t>
-        </is>
-      </c>
-      <c r="K40" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B41" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C41" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="D41" s="24" t="inlineStr">
-        <is>
-          <t>17133570</t>
-        </is>
-      </c>
-      <c r="E41" s="23" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="F41" s="23" t="inlineStr">
-        <is>
-          <t>Q039</t>
-        </is>
-      </c>
-      <c r="G41" s="23" t="inlineStr">
-        <is>
-          <t>Rua NAPOLEÃO ALVES DE OLIVEIRA</t>
-        </is>
-      </c>
-      <c r="H41" s="23" t="inlineStr">
-        <is>
-          <t>249 - R</t>
-        </is>
-      </c>
-      <c r="I41" s="23" t="inlineStr">
-        <is>
-          <t>25/08/2026 14:06</t>
-        </is>
-      </c>
-      <c r="J41" s="23" t="inlineStr">
-        <is>
-          <t>25/08/2026 14:06</t>
-        </is>
-      </c>
-      <c r="K41" s="23" t="inlineStr"/>
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>% Rápidas acima de 20%</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="23" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B42" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C42" s="23" t="n">
-        <v>4</v>
-      </c>
-      <c r="D42" s="24" t="inlineStr">
-        <is>
-          <t>17133571</t>
-        </is>
-      </c>
-      <c r="E42" s="23" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="F42" s="23" t="inlineStr">
-        <is>
-          <t>Q039</t>
-        </is>
-      </c>
-      <c r="G42" s="23" t="inlineStr">
-        <is>
-          <t>Rua NAPOLEÃO ALVES DE OLIVEIRA</t>
-        </is>
-      </c>
-      <c r="H42" s="23" t="inlineStr">
-        <is>
-          <t>249 - R</t>
-        </is>
-      </c>
-      <c r="I42" s="23" t="inlineStr">
-        <is>
-          <t>25/08/2026 14:06</t>
-        </is>
-      </c>
-      <c r="J42" s="23" t="inlineStr">
-        <is>
-          <t>25/08/2026 14:12</t>
-        </is>
-      </c>
-      <c r="K42" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="23" t="inlineStr">
-        <is>
-          <t>Emidio Rainer Vilhalba</t>
-        </is>
-      </c>
-      <c r="B43" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C43" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="24" t="inlineStr">
-        <is>
-          <t>16959229</t>
-        </is>
-      </c>
-      <c r="E43" s="23" t="inlineStr">
-        <is>
-          <t>430 - VILA RENÔ</t>
-        </is>
-      </c>
-      <c r="F43" s="23" t="inlineStr">
-        <is>
-          <t>Q034</t>
-        </is>
-      </c>
-      <c r="G43" s="23" t="inlineStr">
-        <is>
-          <t>Avenida URUMBELA</t>
-        </is>
-      </c>
-      <c r="H43" s="23" t="inlineStr">
-        <is>
-          <t>890 - 10 - R</t>
-        </is>
-      </c>
-      <c r="I43" s="23" t="inlineStr">
-        <is>
-          <t>18/08/2026 09:50</t>
-        </is>
-      </c>
-      <c r="J43" s="23" t="inlineStr">
-        <is>
-          <t>18/08/2026 09:51</t>
-        </is>
-      </c>
-      <c r="K43" s="23" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="23" t="inlineStr">
-        <is>
-          <t>Emidio Rainer Vilhalba</t>
-        </is>
-      </c>
-      <c r="B44" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C44" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="24" t="inlineStr">
-        <is>
-          <t>16959228</t>
-        </is>
-      </c>
-      <c r="E44" s="23" t="inlineStr">
-        <is>
-          <t>430 - VILA RENÔ</t>
-        </is>
-      </c>
-      <c r="F44" s="23" t="inlineStr">
-        <is>
-          <t>Q034</t>
-        </is>
-      </c>
-      <c r="G44" s="23" t="inlineStr">
-        <is>
-          <t>Avenida URUMBELA</t>
-        </is>
-      </c>
-      <c r="H44" s="23" t="inlineStr">
-        <is>
-          <t>890 - 9 - C</t>
-        </is>
-      </c>
-      <c r="I44" s="23" t="inlineStr">
-        <is>
-          <t>18/08/2026 09:50</t>
-        </is>
-      </c>
-      <c r="J44" s="23" t="inlineStr">
-        <is>
-          <t>18/08/2026 09:50</t>
-        </is>
-      </c>
-      <c r="K44" s="23" t="n">
-        <v>0</v>
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>⚠️ SEQUÊNCIA SUSPEITA</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="45" customHeight="1">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>Duas ou mais visitas consecutivas do mesmo agente registradas no MESMO MINUTO de chegada são marcadas como suspeitas (o e-Visita não registra segundos, então o critério de negócio de 50s de diferença equivale, na prática, a 'mesmo minuto') — sugere lançamento em lote no sistema, não visita real de campo. Colunas: 'Visitas em Sequência Suspeita' (total de visitas envolvidas) e 'Maior Sequência Suspeita' (maior número de visitas seguidas nessa condição). Na aba 'Visitas Suspeitas', a coluna 'Diferença p/ Anterior (s)*' fica em branco quando o alerta da linha veio do par com a visita SEGUINTE (não da anterior).</t>
+        </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="23" t="inlineStr">
-        <is>
-          <t>Emidio Rainer Vilhalba</t>
-        </is>
-      </c>
-      <c r="B45" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C45" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" s="24" t="inlineStr">
-        <is>
-          <t>17127483</t>
-        </is>
-      </c>
-      <c r="E45" s="23" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="F45" s="23" t="inlineStr">
-        <is>
-          <t>Q024</t>
-        </is>
-      </c>
-      <c r="G45" s="23" t="inlineStr">
-        <is>
-          <t>Rua SAMAMBAIA</t>
-        </is>
-      </c>
-      <c r="H45" s="23" t="inlineStr">
-        <is>
-          <t>214 - 4 - R</t>
-        </is>
-      </c>
-      <c r="I45" s="23" t="inlineStr">
-        <is>
-          <t>25/08/2026 14:20</t>
-        </is>
-      </c>
-      <c r="J45" s="23" t="inlineStr">
-        <is>
-          <t>25/08/2026 14:21</t>
-        </is>
-      </c>
-      <c r="K45" s="23" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="23" t="inlineStr">
-        <is>
-          <t>Emidio Rainer Vilhalba</t>
-        </is>
-      </c>
-      <c r="B46" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C46" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" s="24" t="inlineStr">
-        <is>
-          <t>17127482</t>
-        </is>
-      </c>
-      <c r="E46" s="23" t="inlineStr">
-        <is>
-          <t>429 - COOPHA FRONTEIRA</t>
-        </is>
-      </c>
-      <c r="F46" s="23" t="inlineStr">
-        <is>
-          <t>Q024</t>
-        </is>
-      </c>
-      <c r="G46" s="23" t="inlineStr">
-        <is>
-          <t>Rua SAMAMBAIA</t>
-        </is>
-      </c>
-      <c r="H46" s="23" t="inlineStr">
-        <is>
-          <t>214 - 3 - R</t>
-        </is>
-      </c>
-      <c r="I46" s="23" t="inlineStr">
-        <is>
-          <t>25/08/2026 14:20</t>
-        </is>
-      </c>
-      <c r="J46" s="23" t="inlineStr">
-        <is>
-          <t>25/08/2026 14:20</t>
-        </is>
-      </c>
-      <c r="K46" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="23" t="inlineStr">
-        <is>
-          <t>Gisele Lopes Justiniano</t>
-        </is>
-      </c>
-      <c r="B47" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C47" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="24" t="inlineStr">
-        <is>
-          <t>16920467</t>
-        </is>
-      </c>
-      <c r="E47" s="23" t="inlineStr">
-        <is>
-          <t>435 - JARDIM PRIMOR</t>
-        </is>
-      </c>
-      <c r="F47" s="23" t="inlineStr">
-        <is>
-          <t>Q021</t>
-        </is>
-      </c>
-      <c r="G47" s="23" t="inlineStr">
-        <is>
-          <t>Rua PARANAGUA</t>
-        </is>
-      </c>
-      <c r="H47" s="23" t="inlineStr">
-        <is>
-          <t>20 - 3 - C</t>
-        </is>
-      </c>
-      <c r="I47" s="23" t="inlineStr">
-        <is>
-          <t>13/08/2026 16:30</t>
-        </is>
-      </c>
-      <c r="J47" s="23" t="inlineStr">
-        <is>
-          <t>13/08/2026 16:30</t>
-        </is>
-      </c>
-      <c r="K47" s="23" t="inlineStr"/>
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>🍽️ VISITAS NO HORÁRIO DE ALMOÇO</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="70" customHeight="1">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>Coluna 'Visitas no Almoço (11h15-12h45)' conta as visitas com chegada registrada nesse intervalo — o horário oficial de almoço é 11h15 às 12h45, JÁ COM 15 MINUTOS DE TOLERÂNCIA em cada borda (visitas entre 11h-11h15 ou 12h45-13h não são tratadas como violação, só como 'fora do expediente' genérico) — use para checar se o agente está trabalhando no horário de almoço ou se há erro de lançamento. Essas visitas ficam de fora do cálculo de 'Início/Fim Manhã' e 'Início/Fim Tarde', que usam a primeira chegada e a última saída de cada dia (não a média de todos os horários), para refletir melhor o início e o fim reais do expediente.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="23" t="inlineStr">
-        <is>
-          <t>Gisele Lopes Justiniano</t>
-        </is>
-      </c>
-      <c r="B48" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C48" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="24" t="inlineStr">
-        <is>
-          <t>16920468</t>
-        </is>
-      </c>
-      <c r="E48" s="23" t="inlineStr">
-        <is>
-          <t>435 - JARDIM PRIMOR</t>
-        </is>
-      </c>
-      <c r="F48" s="23" t="inlineStr">
-        <is>
-          <t>Q021</t>
-        </is>
-      </c>
-      <c r="G48" s="23" t="inlineStr">
-        <is>
-          <t>Rua PARANAGUA</t>
-        </is>
-      </c>
-      <c r="H48" s="23" t="inlineStr">
-        <is>
-          <t>20 - 5 - C</t>
-        </is>
-      </c>
-      <c r="I48" s="23" t="inlineStr">
-        <is>
-          <t>13/08/2026 16:30</t>
-        </is>
-      </c>
-      <c r="J48" s="23" t="inlineStr">
-        <is>
-          <t>13/08/2026 16:30</t>
-        </is>
-      </c>
-      <c r="K48" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="23" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="B49" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C49" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" s="24" t="inlineStr">
-        <is>
-          <t>17131125</t>
-        </is>
-      </c>
-      <c r="E49" s="23" t="inlineStr">
-        <is>
-          <t>431 - PANAMBI</t>
-        </is>
-      </c>
-      <c r="F49" s="23" t="inlineStr">
-        <is>
-          <t>Q027</t>
-        </is>
-      </c>
-      <c r="G49" s="23" t="inlineStr">
-        <is>
-          <t>Rua CAMPO GRANDE</t>
-        </is>
-      </c>
-      <c r="H49" s="23" t="inlineStr">
-        <is>
-          <t>55 - R</t>
-        </is>
-      </c>
-      <c r="I49" s="23" t="inlineStr">
-        <is>
-          <t>25/08/2026 14:19</t>
-        </is>
-      </c>
-      <c r="J49" s="23" t="inlineStr">
-        <is>
-          <t>25/08/2026 14:25</t>
-        </is>
-      </c>
-      <c r="K49" s="23" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="23" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="B50" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C50" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" s="24" t="inlineStr">
-        <is>
-          <t>17131126</t>
-        </is>
-      </c>
-      <c r="E50" s="23" t="inlineStr">
-        <is>
-          <t>431 - PANAMBI</t>
-        </is>
-      </c>
-      <c r="F50" s="23" t="inlineStr">
-        <is>
-          <t>Q027</t>
-        </is>
-      </c>
-      <c r="G50" s="23" t="inlineStr">
-        <is>
-          <t>Rua CAMPO GRANDE</t>
-        </is>
-      </c>
-      <c r="H50" s="23" t="inlineStr">
-        <is>
-          <t>23 - 1 - R</t>
-        </is>
-      </c>
-      <c r="I50" s="23" t="inlineStr">
-        <is>
-          <t>25/08/2026 14:19</t>
-        </is>
-      </c>
-      <c r="J50" s="23" t="inlineStr">
-        <is>
-          <t>25/08/2026 14:25</t>
-        </is>
-      </c>
-      <c r="K50" s="23" t="n">
-        <v>0</v>
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>💰 HORAS TRABALHADAS, HORAS ÚTEIS E CUSTO DA HORA ÚTIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>'Horas Trabalhadas' = jornada total do dia (primeira chegada até a última saída), descontando a sobreposição com o horário de almoço — depois tira-se a média entre os dias/semanas trabalhados, 'Horas Úteis' = soma das durações de visita no dia (tempo realmente dentro de imóveis), sem contar deslocamento entre visitas, 'Custo Hora Útil' = salário mensal do agente (R$ 4863,00, equivalente a 3 salários mínimos federais) dividido pelas horas úteis mensais estimadas (Média Horas Úteis/Dia × 22 dias úteis/mês). Quanto menos tempo o agente passa efetivamente em visita por dia, mais caro fica o custo por hora útil.</t>
+        </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="23" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B51" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C51" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" s="24" t="inlineStr">
-        <is>
-          <t>16932408</t>
-        </is>
-      </c>
-      <c r="E51" s="23" t="inlineStr">
-        <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
-        </is>
-      </c>
-      <c r="F51" s="23" t="inlineStr">
-        <is>
-          <t>Q016</t>
-        </is>
-      </c>
-      <c r="G51" s="23" t="inlineStr">
-        <is>
-          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
-        </is>
-      </c>
-      <c r="H51" s="23" t="inlineStr">
-        <is>
-          <t>491 - TB</t>
-        </is>
-      </c>
-      <c r="I51" s="23" t="inlineStr">
-        <is>
-          <t>14/08/2026 10:00</t>
-        </is>
-      </c>
-      <c r="J51" s="23" t="inlineStr">
-        <is>
-          <t>14/08/2026 10:06</t>
-        </is>
-      </c>
-      <c r="K51" s="23" t="inlineStr"/>
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="23" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B52" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C52" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D52" s="24" t="inlineStr">
-        <is>
-          <t>16932412</t>
-        </is>
-      </c>
-      <c r="E52" s="23" t="inlineStr">
-        <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
-        </is>
-      </c>
-      <c r="F52" s="23" t="inlineStr">
-        <is>
-          <t>Q016</t>
-        </is>
-      </c>
-      <c r="G52" s="23" t="inlineStr">
-        <is>
-          <t>Rua MARACAJU</t>
-        </is>
-      </c>
-      <c r="H52" s="23" t="inlineStr">
-        <is>
-          <t>194 - 3 - R</t>
-        </is>
-      </c>
-      <c r="I52" s="23" t="inlineStr">
-        <is>
-          <t>14/08/2026 10:00</t>
-        </is>
-      </c>
-      <c r="J52" s="23" t="inlineStr">
-        <is>
-          <t>14/08/2026 10:07</t>
-        </is>
-      </c>
-      <c r="K52" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>LEGENDA — CLASSIFICAÇÃO (baseada em % de Visitas Rápidas)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>🟢 NORMAL</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>% Rápidas até 10%</t>
-        </is>
-      </c>
-      <c r="C56" s="10" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>🟡 ATENÇÃO</t>
-        </is>
-      </c>
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t>% Rápidas entre 11% e 20%</t>
-        </is>
-      </c>
-      <c r="C57" s="10" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
-        </is>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t>% Rápidas acima de 20%</t>
-        </is>
-      </c>
-      <c r="C58" s="10" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="13" t="inlineStr">
-        <is>
-          <t>⚠️ SEQUÊNCIA SUSPEITA</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="45" customHeight="1">
-      <c r="A61" s="14" t="inlineStr">
-        <is>
-          <t>Duas ou mais visitas consecutivas do mesmo agente registradas no MESMO MINUTO de chegada são marcadas como suspeitas (o e-Visita não registra segundos, então o critério de negócio de 50s de diferença equivale, na prática, a 'mesmo minuto') — sugere lançamento em lote no sistema, não visita real de campo. Colunas: 'Visitas em Sequência Suspeita' (total de visitas envolvidas) e 'Maior Sequência Suspeita' (maior número de visitas seguidas nessa condição). Na aba 'Visitas Suspeitas', a coluna 'Diferença p/ Anterior (s)*' fica em branco quando o alerta da linha veio do par com a visita SEGUINTE (não da anterior).</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="15" t="inlineStr">
-        <is>
-          <t>🍽️ VISITAS NO HORÁRIO DE ALMOÇO</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="70" customHeight="1">
-      <c r="A64" s="14" t="inlineStr">
-        <is>
-          <t>Coluna 'Visitas no Almoço (11h15-12h45)' conta as visitas com chegada registrada nesse intervalo — o horário oficial de almoço é 11h15 às 12h45, JÁ COM 15 MINUTOS DE TOLERÂNCIA em cada borda (visitas entre 11h-11h15 ou 12h45-13h não são tratadas como violação, só como 'fora do expediente' genérico) — use para checar se o agente está trabalhando no horário de almoço ou se há erro de lançamento. Essas visitas ficam de fora do cálculo de 'Início/Fim Manhã' e 'Início/Fim Tarde', que usam a primeira chegada e a última saída de cada dia (não a média de todos os horários), para refletir melhor o início e o fim reais do expediente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="16" t="inlineStr">
-        <is>
-          <t>💰 HORAS TRABALHADAS, HORAS ÚTEIS E CUSTO DA HORA ÚTIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" s="14" t="inlineStr">
-        <is>
-          <t>'Horas Trabalhadas' = jornada total do dia (primeira chegada até a última saída), descontando a sobreposição com o horário de almoço — depois tira-se a média entre os dias/semanas trabalhados, 'Horas Úteis' = soma das durações de visita no dia (tempo realmente dentro de imóveis), sem contar deslocamento entre visitas, 'Custo Hora Útil' = salário mensal do agente (R$ 4863,00, equivalente a 3 salários mínimos federais) dividido pelas horas úteis mensais estimadas (Média Horas Úteis/Dia × 22 dias úteis/mês). Quanto menos tempo o agente passa efetivamente em visita por dia, mais caro fica o custo por hora útil.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="17" t="inlineStr">
-        <is>
-          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="17" t="inlineStr">
+      <c r="A52" s="17" t="inlineStr">
         <is>
           <t>ℹ️ Visitas com duração NEGATIVA (saída antes da chegada — provável bug do sistema) foram excluídas do cálculo de Média/Mediana e estão detalhadas na aba 'Visitas Negativas', para investigação junto ao suporte do e-Visita.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:K52"/>
+  <autoFilter ref="A2:K34"/>
   <mergeCells count="13">
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A66:C66"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="A48:C48"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A52:C52"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId1"/>
@@ -47591,24 +45701,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D39" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D41" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D43" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D44" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D45" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D46" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D47" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D48" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D49" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D50" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D51" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D52" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -49283,47 +47375,47 @@
     <row r="29">
       <c r="A29" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B29" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>16986159</t>
+          <t>16997935</t>
         </is>
       </c>
       <c r="D29" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E29" s="29" t="inlineStr">
         <is>
-          <t>Q036</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="F29" s="29" t="inlineStr">
         <is>
-          <t>Avenida ADJALMA SALDANHA</t>
+          <t>Rua CARLOS DRUMOND DE ANDRADE</t>
         </is>
       </c>
       <c r="G29" s="29" t="inlineStr">
         <is>
-          <t>873 - R</t>
+          <t>1157 - R</t>
         </is>
       </c>
       <c r="H29" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 13:15</t>
+          <t>19/08/2026 09:04</t>
         </is>
       </c>
       <c r="I29" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 13:38</t>
+          <t>19/08/2026 09:27</t>
         </is>
       </c>
       <c r="J29" s="29" t="n">
@@ -49383,47 +47475,47 @@
     <row r="31">
       <c r="A31" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B31" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C31" s="30" t="inlineStr">
         <is>
-          <t>16997935</t>
+          <t>16986159</t>
         </is>
       </c>
       <c r="D31" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E31" s="29" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q036</t>
         </is>
       </c>
       <c r="F31" s="29" t="inlineStr">
         <is>
-          <t>Rua CARLOS DRUMOND DE ANDRADE</t>
+          <t>Avenida ADJALMA SALDANHA</t>
         </is>
       </c>
       <c r="G31" s="29" t="inlineStr">
         <is>
-          <t>1157 - R</t>
+          <t>873 - R</t>
         </is>
       </c>
       <c r="H31" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:04</t>
+          <t>18/08/2026 13:15</t>
         </is>
       </c>
       <c r="I31" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:27</t>
+          <t>18/08/2026 13:38</t>
         </is>
       </c>
       <c r="J31" s="29" t="n">
@@ -49833,7 +47925,7 @@
     <row r="40">
       <c r="A40" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="B40" s="29" t="inlineStr">
@@ -49843,37 +47935,37 @@
       </c>
       <c r="C40" s="30" t="inlineStr">
         <is>
-          <t>17027695</t>
+          <t>17009505</t>
         </is>
       </c>
       <c r="D40" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>422 - VILA TORRES</t>
         </is>
       </c>
       <c r="E40" s="29" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="F40" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA BRANCA</t>
+          <t>Rua MANOEL DIAS DE PINHO</t>
         </is>
       </c>
       <c r="G40" s="29" t="inlineStr">
         <is>
-          <t>140 - R</t>
+          <t>625 - 1 - C</t>
         </is>
       </c>
       <c r="H40" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 08:57</t>
+          <t>19/08/2026 15:31</t>
         </is>
       </c>
       <c r="I40" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:18</t>
+          <t>19/08/2026 15:52</t>
         </is>
       </c>
       <c r="J40" s="29" t="n">
@@ -49983,7 +48075,7 @@
     <row r="43">
       <c r="A43" s="29" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B43" s="29" t="inlineStr">
@@ -49993,37 +48085,37 @@
       </c>
       <c r="C43" s="30" t="inlineStr">
         <is>
-          <t>17009505</t>
+          <t>17027695</t>
         </is>
       </c>
       <c r="D43" s="29" t="inlineStr">
         <is>
-          <t>422 - VILA TORRES</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E43" s="29" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="F43" s="29" t="inlineStr">
         <is>
-          <t>Rua MANOEL DIAS DE PINHO</t>
+          <t>Rua ROSA BRANCA</t>
         </is>
       </c>
       <c r="G43" s="29" t="inlineStr">
         <is>
-          <t>625 - 1 - C</t>
+          <t>140 - R</t>
         </is>
       </c>
       <c r="H43" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 15:31</t>
+          <t>19/08/2026 08:57</t>
         </is>
       </c>
       <c r="I43" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 15:52</t>
+          <t>19/08/2026 09:18</t>
         </is>
       </c>
       <c r="J43" s="29" t="n">
@@ -50833,7 +48925,7 @@
     <row r="60">
       <c r="A60" s="29" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B60" s="29" t="inlineStr">
@@ -50843,37 +48935,37 @@
       </c>
       <c r="C60" s="30" t="inlineStr">
         <is>
-          <t>17043615</t>
+          <t>16986947</t>
         </is>
       </c>
       <c r="D60" s="29" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>420 - FERROVIARIA</t>
         </is>
       </c>
       <c r="E60" s="29" t="inlineStr">
         <is>
-          <t>Q035</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="F60" s="29" t="inlineStr">
         <is>
-          <t>Rua FELIPE DE BRUM</t>
+          <t>Beco PROJETADA 06 FERROVIARIA</t>
         </is>
       </c>
       <c r="G60" s="29" t="inlineStr">
         <is>
-          <t>900 - R</t>
+          <t>113 - R</t>
         </is>
       </c>
       <c r="H60" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 14:30</t>
+          <t>18/08/2026 08:15</t>
         </is>
       </c>
       <c r="I60" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 14:48</t>
+          <t>18/08/2026 08:33</t>
         </is>
       </c>
       <c r="J60" s="29" t="n">
@@ -50983,7 +49075,7 @@
     <row r="63">
       <c r="A63" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B63" s="29" t="inlineStr">
@@ -50993,7 +49085,7 @@
       </c>
       <c r="C63" s="30" t="inlineStr">
         <is>
-          <t>17034408</t>
+          <t>17051418</t>
         </is>
       </c>
       <c r="D63" s="29" t="inlineStr">
@@ -51003,27 +49095,27 @@
       </c>
       <c r="E63" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="F63" s="29" t="inlineStr">
         <is>
-          <t>Rua JABAQUARA</t>
+          <t>Rua AFONSO DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="G63" s="29" t="inlineStr">
         <is>
-          <t>1370 - 4 - R</t>
+          <t>231 - 3 - R</t>
         </is>
       </c>
       <c r="H63" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:05</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="I63" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:23</t>
+          <t>19/08/2026 14:36</t>
         </is>
       </c>
       <c r="J63" s="29" t="n">
@@ -51033,47 +49125,47 @@
     <row r="64">
       <c r="A64" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B64" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C64" s="30" t="inlineStr">
         <is>
-          <t>17051418</t>
+          <t>17043615</t>
         </is>
       </c>
       <c r="D64" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E64" s="29" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q035</t>
         </is>
       </c>
       <c r="F64" s="29" t="inlineStr">
         <is>
-          <t>Rua AFONSO DE ALBUQUERQUE</t>
+          <t>Rua FELIPE DE BRUM</t>
         </is>
       </c>
       <c r="G64" s="29" t="inlineStr">
         <is>
-          <t>231 - 3 - R</t>
+          <t>900 - R</t>
         </is>
       </c>
       <c r="H64" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 14:18</t>
+          <t>20/08/2026 14:30</t>
         </is>
       </c>
       <c r="I64" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 14:36</t>
+          <t>20/08/2026 14:48</t>
         </is>
       </c>
       <c r="J64" s="29" t="n">
@@ -51283,47 +49375,47 @@
     <row r="69">
       <c r="A69" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B69" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C69" s="30" t="inlineStr">
         <is>
-          <t>16986947</t>
+          <t>17034408</t>
         </is>
       </c>
       <c r="D69" s="29" t="inlineStr">
         <is>
-          <t>420 - FERROVIARIA</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E69" s="29" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F69" s="29" t="inlineStr">
         <is>
-          <t>Beco PROJETADA 06 FERROVIARIA</t>
+          <t>Rua JABAQUARA</t>
         </is>
       </c>
       <c r="G69" s="29" t="inlineStr">
         <is>
-          <t>113 - R</t>
+          <t>1370 - 4 - R</t>
         </is>
       </c>
       <c r="H69" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 08:15</t>
+          <t>19/08/2026 10:05</t>
         </is>
       </c>
       <c r="I69" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 08:33</t>
+          <t>19/08/2026 10:23</t>
         </is>
       </c>
       <c r="J69" s="29" t="n">
@@ -51983,7 +50075,7 @@
     <row r="83">
       <c r="A83" s="29" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B83" s="29" t="inlineStr">
@@ -51993,37 +50085,37 @@
       </c>
       <c r="C83" s="30" t="inlineStr">
         <is>
-          <t>17043629</t>
+          <t>17073307</t>
         </is>
       </c>
       <c r="D83" s="29" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E83" s="29" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F83" s="29" t="inlineStr">
         <is>
-          <t>Rua ARAPONGAS</t>
+          <t>Avenida ANTONIO JOAO</t>
         </is>
       </c>
       <c r="G83" s="29" t="inlineStr">
         <is>
-          <t>142 - R</t>
+          <t>1477 - R</t>
         </is>
       </c>
       <c r="H83" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 15:52</t>
+          <t>20/08/2026 13:54</t>
         </is>
       </c>
       <c r="I83" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 16:09</t>
+          <t>20/08/2026 14:11</t>
         </is>
       </c>
       <c r="J83" s="29" t="n">
@@ -52033,47 +50125,47 @@
     <row r="84">
       <c r="A84" s="29" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B84" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C84" s="30" t="inlineStr">
         <is>
-          <t>17014581</t>
+          <t>17070288</t>
         </is>
       </c>
       <c r="D84" s="29" t="inlineStr">
         <is>
-          <t>433 - ÁREA A - RESIDENCIAL PONTA PORÃ 1</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E84" s="29" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="F84" s="29" t="inlineStr">
         <is>
-          <t>Rua GUARANTA</t>
+          <t>Rua JABAQUARA</t>
         </is>
       </c>
       <c r="G84" s="29" t="inlineStr">
         <is>
-          <t>295 - 1 - TB</t>
+          <t>1490 - C</t>
         </is>
       </c>
       <c r="H84" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:45</t>
+          <t>21/08/2026 15:07</t>
         </is>
       </c>
       <c r="I84" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:02</t>
+          <t>21/08/2026 15:24</t>
         </is>
       </c>
       <c r="J84" s="29" t="n">
@@ -52093,7 +50185,7 @@
       </c>
       <c r="C85" s="30" t="inlineStr">
         <is>
-          <t>17070288</t>
+          <t>17070286</t>
         </is>
       </c>
       <c r="D85" s="29" t="inlineStr">
@@ -52103,27 +50195,27 @@
       </c>
       <c r="E85" s="29" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F85" s="29" t="inlineStr">
         <is>
-          <t>Rua JABAQUARA</t>
+          <t>Rua GUAÍBA</t>
         </is>
       </c>
       <c r="G85" s="29" t="inlineStr">
         <is>
-          <t>1490 - C</t>
+          <t>1262 - C</t>
         </is>
       </c>
       <c r="H85" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 15:07</t>
+          <t>21/08/2026 14:40</t>
         </is>
       </c>
       <c r="I85" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 15:24</t>
+          <t>21/08/2026 14:57</t>
         </is>
       </c>
       <c r="J85" s="29" t="n">
@@ -52133,7 +50225,7 @@
     <row r="86">
       <c r="A86" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B86" s="29" t="inlineStr">
@@ -52143,37 +50235,37 @@
       </c>
       <c r="C86" s="30" t="inlineStr">
         <is>
-          <t>17070286</t>
+          <t>17022532</t>
         </is>
       </c>
       <c r="D86" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E86" s="29" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F86" s="29" t="inlineStr">
         <is>
-          <t>Rua GUAÍBA</t>
+          <t>Rua MARINGA</t>
         </is>
       </c>
       <c r="G86" s="29" t="inlineStr">
         <is>
-          <t>1262 - C</t>
+          <t>807 - R</t>
         </is>
       </c>
       <c r="H86" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 14:40</t>
+          <t>17/08/2026 09:53</t>
         </is>
       </c>
       <c r="I86" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 14:57</t>
+          <t>17/08/2026 10:10</t>
         </is>
       </c>
       <c r="J86" s="29" t="n">
@@ -52483,47 +50575,47 @@
     <row r="93">
       <c r="A93" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="B93" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C93" s="30" t="inlineStr">
         <is>
-          <t>17073307</t>
+          <t>17014581</t>
         </is>
       </c>
       <c r="D93" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>433 - ÁREA A - RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E93" s="29" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F93" s="29" t="inlineStr">
         <is>
-          <t>Avenida ANTONIO JOAO</t>
+          <t>Rua GUARANTA</t>
         </is>
       </c>
       <c r="G93" s="29" t="inlineStr">
         <is>
-          <t>1477 - R</t>
+          <t>295 - 1 - TB</t>
         </is>
       </c>
       <c r="H93" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 13:54</t>
+          <t>19/08/2026 09:45</t>
         </is>
       </c>
       <c r="I93" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 14:11</t>
+          <t>19/08/2026 10:02</t>
         </is>
       </c>
       <c r="J93" s="29" t="n">
@@ -52533,7 +50625,7 @@
     <row r="94">
       <c r="A94" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B94" s="29" t="inlineStr">
@@ -52543,37 +50635,37 @@
       </c>
       <c r="C94" s="30" t="inlineStr">
         <is>
-          <t>17073314</t>
+          <t>17043629</t>
         </is>
       </c>
       <c r="D94" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E94" s="29" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="F94" s="29" t="inlineStr">
         <is>
-          <t>Avenida ANTONIO JOAO</t>
+          <t>Rua ARAPONGAS</t>
         </is>
       </c>
       <c r="G94" s="29" t="inlineStr">
         <is>
-          <t>1371 - OU</t>
+          <t>142 - R</t>
         </is>
       </c>
       <c r="H94" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 15:23</t>
+          <t>20/08/2026 15:52</t>
         </is>
       </c>
       <c r="I94" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 15:40</t>
+          <t>20/08/2026 16:09</t>
         </is>
       </c>
       <c r="J94" s="29" t="n">
@@ -52583,47 +50675,47 @@
     <row r="95">
       <c r="A95" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B95" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C95" s="30" t="inlineStr">
         <is>
-          <t>17022532</t>
+          <t>17073314</t>
         </is>
       </c>
       <c r="D95" s="29" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E95" s="29" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F95" s="29" t="inlineStr">
         <is>
-          <t>Rua MARINGA</t>
+          <t>Avenida ANTONIO JOAO</t>
         </is>
       </c>
       <c r="G95" s="29" t="inlineStr">
         <is>
-          <t>807 - R</t>
+          <t>1371 - OU</t>
         </is>
       </c>
       <c r="H95" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:53</t>
+          <t>20/08/2026 15:23</t>
         </is>
       </c>
       <c r="I95" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 10:10</t>
+          <t>20/08/2026 15:40</t>
         </is>
       </c>
       <c r="J95" s="29" t="n">
@@ -53333,7 +51425,7 @@
     <row r="110">
       <c r="A110" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="B110" s="29" t="inlineStr">
@@ -53343,37 +51435,37 @@
       </c>
       <c r="C110" s="30" t="inlineStr">
         <is>
-          <t>17033729</t>
+          <t>16957579</t>
         </is>
       </c>
       <c r="D110" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>407 - MOOCA</t>
         </is>
       </c>
       <c r="E110" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q041</t>
         </is>
       </c>
       <c r="F110" s="29" t="inlineStr">
         <is>
-          <t>Rua VICENTE  AZAMBUJA</t>
+          <t>Rua VALPARAISO</t>
         </is>
       </c>
       <c r="G110" s="29" t="inlineStr">
         <is>
-          <t>1407 - R</t>
+          <t>335 - R</t>
         </is>
       </c>
       <c r="H110" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 08:45</t>
+          <t>17/08/2026 08:59</t>
         </is>
       </c>
       <c r="I110" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:01</t>
+          <t>17/08/2026 09:15</t>
         </is>
       </c>
       <c r="J110" s="29" t="n">
@@ -53383,7 +51475,7 @@
     <row r="111">
       <c r="A111" s="29" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B111" s="29" t="inlineStr">
@@ -53393,37 +51485,37 @@
       </c>
       <c r="C111" s="30" t="inlineStr">
         <is>
-          <t>16957579</t>
+          <t>17033729</t>
         </is>
       </c>
       <c r="D111" s="29" t="inlineStr">
         <is>
-          <t>407 - MOOCA</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E111" s="29" t="inlineStr">
         <is>
-          <t>Q041</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F111" s="29" t="inlineStr">
         <is>
-          <t>Rua VALPARAISO</t>
+          <t>Rua VICENTE  AZAMBUJA</t>
         </is>
       </c>
       <c r="G111" s="29" t="inlineStr">
         <is>
-          <t>335 - R</t>
+          <t>1407 - R</t>
         </is>
       </c>
       <c r="H111" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 08:59</t>
+          <t>19/08/2026 08:45</t>
         </is>
       </c>
       <c r="I111" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:15</t>
+          <t>19/08/2026 09:01</t>
         </is>
       </c>
       <c r="J111" s="29" t="n">
@@ -53433,47 +51525,47 @@
     <row r="112">
       <c r="A112" s="29" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B112" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C112" s="30" t="inlineStr">
         <is>
-          <t>17055208</t>
+          <t>17017079</t>
         </is>
       </c>
       <c r="D112" s="29" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇÕES</t>
+          <t>420 - FERROVIARIA</t>
         </is>
       </c>
       <c r="E112" s="29" t="inlineStr">
         <is>
-          <t>Q036</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F112" s="29" t="inlineStr">
         <is>
-          <t>Rua DIGNO TORRES GIMENEZ</t>
+          <t>Travessa PROJETADA 06 FERROVIARIA</t>
         </is>
       </c>
       <c r="G112" s="29" t="inlineStr">
         <is>
-          <t>590 - 2 - R</t>
+          <t>57 - R</t>
         </is>
       </c>
       <c r="H112" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 08:57</t>
+          <t>17/08/2026 09:16</t>
         </is>
       </c>
       <c r="I112" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 09:13</t>
+          <t>17/08/2026 09:32</t>
         </is>
       </c>
       <c r="J112" s="29" t="n">
@@ -53483,47 +51575,47 @@
     <row r="113">
       <c r="A113" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="B113" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C113" s="30" t="inlineStr">
         <is>
-          <t>17017079</t>
+          <t>17055208</t>
         </is>
       </c>
       <c r="D113" s="29" t="inlineStr">
         <is>
-          <t>420 - FERROVIARIA</t>
+          <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
       <c r="E113" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q036</t>
         </is>
       </c>
       <c r="F113" s="29" t="inlineStr">
         <is>
-          <t>Travessa PROJETADA 06 FERROVIARIA</t>
+          <t>Rua DIGNO TORRES GIMENEZ</t>
         </is>
       </c>
       <c r="G113" s="29" t="inlineStr">
         <is>
-          <t>57 - R</t>
+          <t>590 - 2 - R</t>
         </is>
       </c>
       <c r="H113" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:16</t>
+          <t>21/08/2026 08:57</t>
         </is>
       </c>
       <c r="I113" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:32</t>
+          <t>21/08/2026 09:13</t>
         </is>
       </c>
       <c r="J113" s="29" t="n">

--- a/data/historico/semanas_318-321.xlsx
+++ b/data/historico/semanas_318-321.xlsx
@@ -47303,47 +47303,47 @@
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B18" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C18" s="30" t="inlineStr">
         <is>
-          <t>16928890</t>
+          <t>17070282</t>
         </is>
       </c>
       <c r="D18" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E18" s="29" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="F18" s="29" t="inlineStr">
         <is>
-          <t>Rua JOAQUIM PEREIRA TEIXEIRA</t>
+          <t>Rua BARRA VELHA</t>
         </is>
       </c>
       <c r="G18" s="29" t="inlineStr">
         <is>
-          <t>707 - R</t>
+          <t>696 - R</t>
         </is>
       </c>
       <c r="H18" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 16:28</t>
+          <t>21/08/2026 09:59</t>
         </is>
       </c>
       <c r="I18" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 16:56</t>
+          <t>21/08/2026 10:27</t>
         </is>
       </c>
       <c r="J18" s="29" t="n">
@@ -47353,47 +47353,47 @@
     <row r="19">
       <c r="A19" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B19" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>17070282</t>
+          <t>16928890</t>
         </is>
       </c>
       <c r="D19" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E19" s="29" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="F19" s="29" t="inlineStr">
         <is>
-          <t>Rua BARRA VELHA</t>
+          <t>Rua JOAQUIM PEREIRA TEIXEIRA</t>
         </is>
       </c>
       <c r="G19" s="29" t="inlineStr">
         <is>
-          <t>696 - R</t>
+          <t>707 - R</t>
         </is>
       </c>
       <c r="H19" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 09:59</t>
+          <t>12/08/2026 16:28</t>
         </is>
       </c>
       <c r="I19" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 10:27</t>
+          <t>12/08/2026 16:56</t>
         </is>
       </c>
       <c r="J19" s="29" t="n">
@@ -47403,47 +47403,47 @@
     <row r="20">
       <c r="A20" s="29" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="B20" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C20" s="30" t="inlineStr">
         <is>
-          <t>17128500</t>
+          <t>16990895</t>
         </is>
       </c>
       <c r="D20" s="29" t="inlineStr">
         <is>
-          <t>443 - KAMEL SAAD 1</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E20" s="29" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="F20" s="29" t="inlineStr">
         <is>
-          <t>Rua DAS ROSAS</t>
+          <t>Rua TIETE</t>
         </is>
       </c>
       <c r="G20" s="29" t="inlineStr">
         <is>
-          <t>03 - R</t>
+          <t>513 - R</t>
         </is>
       </c>
       <c r="H20" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 10:11</t>
+          <t>17/08/2026 09:24</t>
         </is>
       </c>
       <c r="I20" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 10:38</t>
+          <t>17/08/2026 09:51</t>
         </is>
       </c>
       <c r="J20" s="29" t="n">
@@ -47453,7 +47453,7 @@
     <row r="21">
       <c r="A21" s="29" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B21" s="29" t="inlineStr">
@@ -47463,37 +47463,37 @@
       </c>
       <c r="C21" s="30" t="inlineStr">
         <is>
-          <t>16990895</t>
+          <t>17076987</t>
         </is>
       </c>
       <c r="D21" s="29" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
       <c r="E21" s="29" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q012</t>
         </is>
       </c>
       <c r="F21" s="29" t="inlineStr">
         <is>
-          <t>Rua TIETE</t>
+          <t>Rua Anselmo Soares</t>
         </is>
       </c>
       <c r="G21" s="29" t="inlineStr">
         <is>
-          <t>513 - R</t>
+          <t>700 - 9 - TB</t>
         </is>
       </c>
       <c r="H21" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:24</t>
+          <t>19/08/2026 14:12</t>
         </is>
       </c>
       <c r="I21" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:51</t>
+          <t>19/08/2026 14:39</t>
         </is>
       </c>
       <c r="J21" s="29" t="n">
@@ -47503,47 +47503,47 @@
     <row r="22">
       <c r="A22" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="B22" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C22" s="30" t="inlineStr">
         <is>
-          <t>17076987</t>
+          <t>17128500</t>
         </is>
       </c>
       <c r="D22" s="29" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL</t>
+          <t>443 - KAMEL SAAD 1</t>
         </is>
       </c>
       <c r="E22" s="29" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="F22" s="29" t="inlineStr">
         <is>
-          <t>Rua Anselmo Soares</t>
+          <t>Rua DAS ROSAS</t>
         </is>
       </c>
       <c r="G22" s="29" t="inlineStr">
         <is>
-          <t>700 - 9 - TB</t>
+          <t>03 - R</t>
         </is>
       </c>
       <c r="H22" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 14:12</t>
+          <t>25/08/2026 10:11</t>
         </is>
       </c>
       <c r="I22" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 14:39</t>
+          <t>25/08/2026 10:38</t>
         </is>
       </c>
       <c r="J22" s="29" t="n">
@@ -47553,7 +47553,7 @@
     <row r="23">
       <c r="A23" s="29" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="B23" s="29" t="inlineStr">
@@ -47563,37 +47563,37 @@
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>16713145</t>
+          <t>17026385</t>
         </is>
       </c>
       <c r="D23" s="29" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇÕES</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E23" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F23" s="29" t="inlineStr">
         <is>
-          <t>Avenida JARDIM AMERICA</t>
+          <t>Rua JABAQUARA</t>
         </is>
       </c>
       <c r="G23" s="29" t="inlineStr">
         <is>
-          <t>245 - R</t>
+          <t>26 - 2 - OU</t>
         </is>
       </c>
       <c r="H23" s="29" t="inlineStr">
         <is>
-          <t>03/08/2026 09:50</t>
+          <t>19/08/2026 09:27</t>
         </is>
       </c>
       <c r="I23" s="29" t="inlineStr">
         <is>
-          <t>03/08/2026 10:16</t>
+          <t>19/08/2026 09:53</t>
         </is>
       </c>
       <c r="J23" s="29" t="n">
@@ -47603,7 +47603,7 @@
     <row r="24">
       <c r="A24" s="29" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B24" s="29" t="inlineStr">
@@ -47613,37 +47613,37 @@
       </c>
       <c r="C24" s="30" t="inlineStr">
         <is>
-          <t>17026385</t>
+          <t>17076990</t>
         </is>
       </c>
       <c r="D24" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q012</t>
         </is>
       </c>
       <c r="F24" s="29" t="inlineStr">
         <is>
-          <t>Rua JABAQUARA</t>
+          <t>Rua Anselmo Soares</t>
         </is>
       </c>
       <c r="G24" s="29" t="inlineStr">
         <is>
-          <t>26 - 2 - OU</t>
+          <t>28 - 2 - TB</t>
         </is>
       </c>
       <c r="H24" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:27</t>
+          <t>19/08/2026 15:03</t>
         </is>
       </c>
       <c r="I24" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:53</t>
+          <t>19/08/2026 15:29</t>
         </is>
       </c>
       <c r="J24" s="29" t="n">
@@ -47653,47 +47653,47 @@
     <row r="25">
       <c r="A25" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B25" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>17076990</t>
+          <t>17027677</t>
         </is>
       </c>
       <c r="D25" s="29" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E25" s="29" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F25" s="29" t="inlineStr">
         <is>
-          <t>Rua Anselmo Soares</t>
+          <t>Rua SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="G25" s="29" t="inlineStr">
         <is>
-          <t>28 - 2 - TB</t>
+          <t>20 - R</t>
         </is>
       </c>
       <c r="H25" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 15:03</t>
+          <t>18/08/2026 10:24</t>
         </is>
       </c>
       <c r="I25" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 15:29</t>
+          <t>18/08/2026 10:50</t>
         </is>
       </c>
       <c r="J25" s="29" t="n">
@@ -47703,47 +47703,47 @@
     <row r="26">
       <c r="A26" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="B26" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C26" s="30" t="inlineStr">
         <is>
-          <t>17027677</t>
+          <t>16713145</t>
         </is>
       </c>
       <c r="D26" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
       <c r="E26" s="29" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F26" s="29" t="inlineStr">
         <is>
-          <t>Rua SÃO JOÃO DEL REI</t>
+          <t>Avenida JARDIM AMERICA</t>
         </is>
       </c>
       <c r="G26" s="29" t="inlineStr">
         <is>
-          <t>20 - R</t>
+          <t>245 - R</t>
         </is>
       </c>
       <c r="H26" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 10:24</t>
+          <t>03/08/2026 09:50</t>
         </is>
       </c>
       <c r="I26" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 10:50</t>
+          <t>03/08/2026 10:16</t>
         </is>
       </c>
       <c r="J26" s="29" t="n">
@@ -47803,7 +47803,7 @@
     <row r="28">
       <c r="A28" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B28" s="29" t="inlineStr">
@@ -47813,37 +47813,37 @@
       </c>
       <c r="C28" s="30" t="inlineStr">
         <is>
-          <t>16997935</t>
+          <t>17077037</t>
         </is>
       </c>
       <c r="D28" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
       <c r="E28" s="29" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="F28" s="29" t="inlineStr">
         <is>
-          <t>Rua CARLOS DRUMOND DE ANDRADE</t>
+          <t>Rua INÁCIO SUBTIL OLIVEIRA</t>
         </is>
       </c>
       <c r="G28" s="29" t="inlineStr">
         <is>
-          <t>1157 - R</t>
+          <t>517 - R</t>
         </is>
       </c>
       <c r="H28" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:04</t>
+          <t>21/08/2026 08:51</t>
         </is>
       </c>
       <c r="I28" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:27</t>
+          <t>21/08/2026 09:14</t>
         </is>
       </c>
       <c r="J28" s="29" t="n">
@@ -47903,47 +47903,47 @@
     <row r="30">
       <c r="A30" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B30" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C30" s="30" t="inlineStr">
         <is>
-          <t>17077037</t>
+          <t>16986159</t>
         </is>
       </c>
       <c r="D30" s="29" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E30" s="29" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q036</t>
         </is>
       </c>
       <c r="F30" s="29" t="inlineStr">
         <is>
-          <t>Rua INÁCIO SUBTIL OLIVEIRA</t>
+          <t>Avenida ADJALMA SALDANHA</t>
         </is>
       </c>
       <c r="G30" s="29" t="inlineStr">
         <is>
-          <t>517 - R</t>
+          <t>873 - R</t>
         </is>
       </c>
       <c r="H30" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 08:51</t>
+          <t>18/08/2026 13:15</t>
         </is>
       </c>
       <c r="I30" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 09:14</t>
+          <t>18/08/2026 13:38</t>
         </is>
       </c>
       <c r="J30" s="29" t="n">
@@ -47963,7 +47963,7 @@
       </c>
       <c r="C31" s="30" t="inlineStr">
         <is>
-          <t>16986159</t>
+          <t>17071087</t>
         </is>
       </c>
       <c r="D31" s="29" t="inlineStr">
@@ -47973,27 +47973,27 @@
       </c>
       <c r="E31" s="29" t="inlineStr">
         <is>
-          <t>Q036</t>
+          <t>Q042</t>
         </is>
       </c>
       <c r="F31" s="29" t="inlineStr">
         <is>
-          <t>Avenida ADJALMA SALDANHA</t>
+          <t>Rua POLICARPO DAVILA</t>
         </is>
       </c>
       <c r="G31" s="29" t="inlineStr">
         <is>
-          <t>873 - R</t>
+          <t>769 - R</t>
         </is>
       </c>
       <c r="H31" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 13:15</t>
+          <t>21/08/2026 14:34</t>
         </is>
       </c>
       <c r="I31" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 13:38</t>
+          <t>21/08/2026 14:57</t>
         </is>
       </c>
       <c r="J31" s="29" t="n">
@@ -48003,47 +48003,47 @@
     <row r="32">
       <c r="A32" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B32" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C32" s="30" t="inlineStr">
         <is>
-          <t>17071087</t>
+          <t>16997935</t>
         </is>
       </c>
       <c r="D32" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E32" s="29" t="inlineStr">
         <is>
-          <t>Q042</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="F32" s="29" t="inlineStr">
         <is>
-          <t>Rua POLICARPO DAVILA</t>
+          <t>Rua CARLOS DRUMOND DE ANDRADE</t>
         </is>
       </c>
       <c r="G32" s="29" t="inlineStr">
         <is>
-          <t>769 - R</t>
+          <t>1157 - R</t>
         </is>
       </c>
       <c r="H32" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 14:34</t>
+          <t>19/08/2026 09:04</t>
         </is>
       </c>
       <c r="I32" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 14:57</t>
+          <t>19/08/2026 09:27</t>
         </is>
       </c>
       <c r="J32" s="29" t="n">
@@ -48103,47 +48103,47 @@
     <row r="34">
       <c r="A34" s="29" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
       <c r="B34" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C34" s="30" t="inlineStr">
         <is>
-          <t>17011667</t>
+          <t>17018827</t>
         </is>
       </c>
       <c r="D34" s="29" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>403 - JARDIM UNIVERSITARIO</t>
         </is>
       </c>
       <c r="E34" s="29" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F34" s="29" t="inlineStr">
         <is>
-          <t>Rua HONOROPOLIS</t>
+          <t>Rua DR HELIO BRANDAO</t>
         </is>
       </c>
       <c r="G34" s="29" t="inlineStr">
         <is>
-          <t>541 - R</t>
+          <t>227 - C</t>
         </is>
       </c>
       <c r="H34" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 08:55</t>
+          <t>19/08/2026 08:44</t>
         </is>
       </c>
       <c r="I34" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:17</t>
+          <t>19/08/2026 09:06</t>
         </is>
       </c>
       <c r="J34" s="29" t="n">
@@ -48153,47 +48153,47 @@
     <row r="35">
       <c r="A35" s="29" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B35" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>17131247</t>
+          <t>16762598</t>
         </is>
       </c>
       <c r="D35" s="29" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E35" s="29" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="F35" s="29" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Rua FRANCISCO FAUSTO MACENAS</t>
         </is>
       </c>
       <c r="G35" s="29" t="inlineStr">
         <is>
-          <t>210 - C</t>
+          <t>651 - 1 - R</t>
         </is>
       </c>
       <c r="H35" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 08:43</t>
+          <t>05/08/2026 10:06</t>
         </is>
       </c>
       <c r="I35" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:05</t>
+          <t>05/08/2026 10:28</t>
         </is>
       </c>
       <c r="J35" s="29" t="n">
@@ -48203,7 +48203,7 @@
     <row r="36">
       <c r="A36" s="29" t="inlineStr">
         <is>
-          <t>Cris Milene Cardenas da Silva</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B36" s="29" t="inlineStr">
@@ -48213,37 +48213,37 @@
       </c>
       <c r="C36" s="30" t="inlineStr">
         <is>
-          <t>17018827</t>
+          <t>17148181</t>
         </is>
       </c>
       <c r="D36" s="29" t="inlineStr">
         <is>
-          <t>403 - JARDIM UNIVERSITARIO</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E36" s="29" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F36" s="29" t="inlineStr">
         <is>
-          <t>Rua DR HELIO BRANDAO</t>
+          <t>Rua ARNALDO VASQUES</t>
         </is>
       </c>
       <c r="G36" s="29" t="inlineStr">
         <is>
-          <t>227 - C</t>
+          <t>325 - R</t>
         </is>
       </c>
       <c r="H36" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 08:44</t>
+          <t>26/08/2026 13:43</t>
         </is>
       </c>
       <c r="I36" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:06</t>
+          <t>26/08/2026 14:05</t>
         </is>
       </c>
       <c r="J36" s="29" t="n">
@@ -48253,22 +48253,22 @@
     <row r="37">
       <c r="A37" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="B37" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C37" s="30" t="inlineStr">
         <is>
-          <t>16762598</t>
+          <t>17125360</t>
         </is>
       </c>
       <c r="D37" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>439 - BOSQUE CARANDÁ</t>
         </is>
       </c>
       <c r="E37" s="29" t="inlineStr">
@@ -48278,22 +48278,22 @@
       </c>
       <c r="F37" s="29" t="inlineStr">
         <is>
-          <t>Rua FRANCISCO FAUSTO MACENAS</t>
+          <t>Avenida PERPETUO SOCORRO</t>
         </is>
       </c>
       <c r="G37" s="29" t="inlineStr">
         <is>
-          <t>651 - 1 - R</t>
+          <t>03 - OU</t>
         </is>
       </c>
       <c r="H37" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 10:06</t>
+          <t>25/08/2026 09:35</t>
         </is>
       </c>
       <c r="I37" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 10:28</t>
+          <t>25/08/2026 09:57</t>
         </is>
       </c>
       <c r="J37" s="29" t="n">
@@ -48303,47 +48303,47 @@
     <row r="38">
       <c r="A38" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B38" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C38" s="30" t="inlineStr">
         <is>
-          <t>17130213</t>
+          <t>17011667</t>
         </is>
       </c>
       <c r="D38" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E38" s="29" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="F38" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA AZUL</t>
+          <t>Rua HONOROPOLIS</t>
         </is>
       </c>
       <c r="G38" s="29" t="inlineStr">
         <is>
-          <t>222 - R</t>
+          <t>541 - R</t>
         </is>
       </c>
       <c r="H38" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:33</t>
+          <t>19/08/2026 08:55</t>
         </is>
       </c>
       <c r="I38" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:55</t>
+          <t>19/08/2026 09:17</t>
         </is>
       </c>
       <c r="J38" s="29" t="n">
@@ -48353,47 +48353,47 @@
     <row r="39">
       <c r="A39" s="29" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B39" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>17125360</t>
+          <t>17130213</t>
         </is>
       </c>
       <c r="D39" s="29" t="inlineStr">
         <is>
-          <t>439 - BOSQUE CARANDÁ</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E39" s="29" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F39" s="29" t="inlineStr">
         <is>
-          <t>Avenida PERPETUO SOCORRO</t>
+          <t>Rua ROSA AZUL</t>
         </is>
       </c>
       <c r="G39" s="29" t="inlineStr">
         <is>
-          <t>03 - OU</t>
+          <t>222 - R</t>
         </is>
       </c>
       <c r="H39" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:35</t>
+          <t>25/08/2026 15:33</t>
         </is>
       </c>
       <c r="I39" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:57</t>
+          <t>25/08/2026 15:55</t>
         </is>
       </c>
       <c r="J39" s="29" t="n">
@@ -48403,47 +48403,47 @@
     <row r="40">
       <c r="A40" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B40" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C40" s="30" t="inlineStr">
         <is>
-          <t>17148181</t>
+          <t>17131247</t>
         </is>
       </c>
       <c r="D40" s="29" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E40" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F40" s="29" t="inlineStr">
         <is>
-          <t>Rua ARNALDO VASQUES</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="G40" s="29" t="inlineStr">
         <is>
-          <t>325 - R</t>
+          <t>210 - C</t>
         </is>
       </c>
       <c r="H40" s="29" t="inlineStr">
         <is>
-          <t>26/08/2026 13:43</t>
+          <t>25/08/2026 08:43</t>
         </is>
       </c>
       <c r="I40" s="29" t="inlineStr">
         <is>
-          <t>26/08/2026 14:05</t>
+          <t>25/08/2026 09:05</t>
         </is>
       </c>
       <c r="J40" s="29" t="n">
@@ -48453,47 +48453,47 @@
     <row r="41">
       <c r="A41" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="B41" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C41" s="30" t="inlineStr">
         <is>
-          <t>17027695</t>
+          <t>16960082</t>
         </is>
       </c>
       <c r="D41" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E41" s="29" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F41" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA BRANCA</t>
+          <t>Rua FORTALEZA</t>
         </is>
       </c>
       <c r="G41" s="29" t="inlineStr">
         <is>
-          <t>140 - R</t>
+          <t>622 - R</t>
         </is>
       </c>
       <c r="H41" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 08:57</t>
+          <t>18/08/2026 09:32</t>
         </is>
       </c>
       <c r="I41" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:18</t>
+          <t>18/08/2026 09:53</t>
         </is>
       </c>
       <c r="J41" s="29" t="n">
@@ -48503,47 +48503,47 @@
     <row r="42">
       <c r="A42" s="29" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B42" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C42" s="30" t="inlineStr">
         <is>
-          <t>17009505</t>
+          <t>17130068</t>
         </is>
       </c>
       <c r="D42" s="29" t="inlineStr">
         <is>
-          <t>422 - VILA TORRES</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E42" s="29" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="F42" s="29" t="inlineStr">
         <is>
-          <t>Rua MANOEL DIAS DE PINHO</t>
+          <t>Rua AREIA BRANCA</t>
         </is>
       </c>
       <c r="G42" s="29" t="inlineStr">
         <is>
-          <t>625 - 1 - C</t>
+          <t>1194 - R</t>
         </is>
       </c>
       <c r="H42" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 15:31</t>
+          <t>25/08/2026 15:16</t>
         </is>
       </c>
       <c r="I42" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 15:52</t>
+          <t>25/08/2026 15:37</t>
         </is>
       </c>
       <c r="J42" s="29" t="n">
@@ -48553,47 +48553,47 @@
     <row r="43">
       <c r="A43" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B43" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C43" s="30" t="inlineStr">
         <is>
-          <t>17130068</t>
+          <t>17027695</t>
         </is>
       </c>
       <c r="D43" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E43" s="29" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="F43" s="29" t="inlineStr">
         <is>
-          <t>Rua AREIA BRANCA</t>
+          <t>Rua ROSA BRANCA</t>
         </is>
       </c>
       <c r="G43" s="29" t="inlineStr">
         <is>
-          <t>1194 - R</t>
+          <t>140 - R</t>
         </is>
       </c>
       <c r="H43" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:16</t>
+          <t>19/08/2026 08:57</t>
         </is>
       </c>
       <c r="I43" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:37</t>
+          <t>19/08/2026 09:18</t>
         </is>
       </c>
       <c r="J43" s="29" t="n">
@@ -48653,47 +48653,47 @@
     <row r="45">
       <c r="A45" s="29" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="B45" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C45" s="30" t="inlineStr">
         <is>
-          <t>16960082</t>
+          <t>17009505</t>
         </is>
       </c>
       <c r="D45" s="29" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>422 - VILA TORRES</t>
         </is>
       </c>
       <c r="E45" s="29" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="F45" s="29" t="inlineStr">
         <is>
-          <t>Rua FORTALEZA</t>
+          <t>Rua MANOEL DIAS DE PINHO</t>
         </is>
       </c>
       <c r="G45" s="29" t="inlineStr">
         <is>
-          <t>622 - R</t>
+          <t>625 - 1 - C</t>
         </is>
       </c>
       <c r="H45" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 09:32</t>
+          <t>19/08/2026 15:31</t>
         </is>
       </c>
       <c r="I45" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 09:53</t>
+          <t>19/08/2026 15:52</t>
         </is>
       </c>
       <c r="J45" s="29" t="n">
@@ -48703,47 +48703,47 @@
     <row r="46">
       <c r="A46" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B46" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C46" s="30" t="inlineStr">
         <is>
-          <t>17112709</t>
+          <t>16938750</t>
         </is>
       </c>
       <c r="D46" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E46" s="29" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="F46" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA AZUL</t>
+          <t>Rua SAO CRISTOVAO</t>
         </is>
       </c>
       <c r="G46" s="29" t="inlineStr">
         <is>
-          <t>295 - 1 - R</t>
+          <t>14 - 1 - R</t>
         </is>
       </c>
       <c r="H46" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:00</t>
+          <t>14/08/2026 09:53</t>
         </is>
       </c>
       <c r="I46" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:20</t>
+          <t>14/08/2026 10:13</t>
         </is>
       </c>
       <c r="J46" s="29" t="n">
@@ -48753,47 +48753,47 @@
     <row r="47">
       <c r="A47" s="29" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B47" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C47" s="30" t="inlineStr">
         <is>
-          <t>16879459</t>
+          <t>16762591</t>
         </is>
       </c>
       <c r="D47" s="29" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E47" s="29" t="inlineStr">
         <is>
-          <t>Q025</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="F47" s="29" t="inlineStr">
         <is>
-          <t>Rua EPTACIO PESSOA</t>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
         </is>
       </c>
       <c r="G47" s="29" t="inlineStr">
         <is>
-          <t>245 - 1 - R</t>
+          <t>486 - OU</t>
         </is>
       </c>
       <c r="H47" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 10:11</t>
+          <t>05/08/2026 08:45</t>
         </is>
       </c>
       <c r="I47" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 10:31</t>
+          <t>05/08/2026 09:05</t>
         </is>
       </c>
       <c r="J47" s="29" t="n">
@@ -48803,47 +48803,47 @@
     <row r="48">
       <c r="A48" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B48" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C48" s="30" t="inlineStr">
         <is>
-          <t>16938750</t>
+          <t>17098947</t>
         </is>
       </c>
       <c r="D48" s="29" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E48" s="29" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F48" s="29" t="inlineStr">
         <is>
-          <t>Rua SAO CRISTOVAO</t>
+          <t>Rua FELIPE DE BRUM</t>
         </is>
       </c>
       <c r="G48" s="29" t="inlineStr">
         <is>
-          <t>14 - 1 - R</t>
+          <t>75 - R</t>
         </is>
       </c>
       <c r="H48" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 09:53</t>
+          <t>24/08/2026 09:26</t>
         </is>
       </c>
       <c r="I48" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 10:13</t>
+          <t>24/08/2026 09:46</t>
         </is>
       </c>
       <c r="J48" s="29" t="n">
@@ -48853,47 +48853,47 @@
     <row r="49">
       <c r="A49" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B49" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C49" s="30" t="inlineStr">
         <is>
-          <t>16762591</t>
+          <t>17112709</t>
         </is>
       </c>
       <c r="D49" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E49" s="29" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F49" s="29" t="inlineStr">
         <is>
-          <t>Rua ROBERTO BUENO DA SILVA</t>
+          <t>Rua ROSA AZUL</t>
         </is>
       </c>
       <c r="G49" s="29" t="inlineStr">
         <is>
-          <t>486 - OU</t>
+          <t>295 - 1 - R</t>
         </is>
       </c>
       <c r="H49" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 08:45</t>
+          <t>24/08/2026 15:00</t>
         </is>
       </c>
       <c r="I49" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 09:05</t>
+          <t>24/08/2026 15:20</t>
         </is>
       </c>
       <c r="J49" s="29" t="n">
@@ -48903,47 +48903,47 @@
     <row r="50">
       <c r="A50" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="B50" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C50" s="30" t="inlineStr">
         <is>
-          <t>17098947</t>
+          <t>17028733</t>
         </is>
       </c>
       <c r="D50" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>407 - MOOCA</t>
         </is>
       </c>
       <c r="E50" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q043</t>
         </is>
       </c>
       <c r="F50" s="29" t="inlineStr">
         <is>
-          <t>Rua FELIPE DE BRUM</t>
+          <t>Rua GEOVAI</t>
         </is>
       </c>
       <c r="G50" s="29" t="inlineStr">
         <is>
-          <t>75 - R</t>
+          <t>213 - 1 - R</t>
         </is>
       </c>
       <c r="H50" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:26</t>
+          <t>19/08/2026 14:39</t>
         </is>
       </c>
       <c r="I50" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:46</t>
+          <t>19/08/2026 14:59</t>
         </is>
       </c>
       <c r="J50" s="29" t="n">
@@ -48953,47 +48953,47 @@
     <row r="51">
       <c r="A51" s="29" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B51" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C51" s="30" t="inlineStr">
         <is>
-          <t>17028733</t>
+          <t>16879459</t>
         </is>
       </c>
       <c r="D51" s="29" t="inlineStr">
         <is>
-          <t>407 - MOOCA</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E51" s="29" t="inlineStr">
         <is>
-          <t>Q043</t>
+          <t>Q025</t>
         </is>
       </c>
       <c r="F51" s="29" t="inlineStr">
         <is>
-          <t>Rua GEOVAI</t>
+          <t>Rua EPTACIO PESSOA</t>
         </is>
       </c>
       <c r="G51" s="29" t="inlineStr">
         <is>
-          <t>213 - 1 - R</t>
+          <t>245 - 1 - R</t>
         </is>
       </c>
       <c r="H51" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 14:39</t>
+          <t>12/08/2026 10:11</t>
         </is>
       </c>
       <c r="I51" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 14:59</t>
+          <t>12/08/2026 10:31</t>
         </is>
       </c>
       <c r="J51" s="29" t="n">
@@ -49053,7 +49053,7 @@
     <row r="53">
       <c r="A53" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B53" s="29" t="inlineStr">
@@ -49063,7 +49063,7 @@
       </c>
       <c r="C53" s="30" t="inlineStr">
         <is>
-          <t>17066233</t>
+          <t>16971726</t>
         </is>
       </c>
       <c r="D53" s="29" t="inlineStr">
@@ -49073,27 +49073,27 @@
       </c>
       <c r="E53" s="29" t="inlineStr">
         <is>
-          <t>Q005</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="F53" s="29" t="inlineStr">
         <is>
-          <t>Rua CAPÃO BONITO</t>
+          <t>Rua VICENTE  AZAMBUJA</t>
         </is>
       </c>
       <c r="G53" s="29" t="inlineStr">
         <is>
-          <t>191 - R</t>
+          <t>15 - R</t>
         </is>
       </c>
       <c r="H53" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:01</t>
+          <t>18/08/2026 08:29</t>
         </is>
       </c>
       <c r="I53" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:20</t>
+          <t>18/08/2026 08:48</t>
         </is>
       </c>
       <c r="J53" s="29" t="n">
@@ -49103,7 +49103,7 @@
     <row r="54">
       <c r="A54" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="B54" s="29" t="inlineStr">
@@ -49113,37 +49113,37 @@
       </c>
       <c r="C54" s="30" t="inlineStr">
         <is>
-          <t>16971726</t>
+          <t>17068744</t>
         </is>
       </c>
       <c r="D54" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
       <c r="E54" s="29" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q037</t>
         </is>
       </c>
       <c r="F54" s="29" t="inlineStr">
         <is>
-          <t>Rua VICENTE  AZAMBUJA</t>
+          <t>Rua CORONEL PONCE</t>
         </is>
       </c>
       <c r="G54" s="29" t="inlineStr">
         <is>
-          <t>15 - R</t>
+          <t>04 - OU</t>
         </is>
       </c>
       <c r="H54" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 08:29</t>
+          <t>21/08/2026 15:05</t>
         </is>
       </c>
       <c r="I54" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 08:48</t>
+          <t>21/08/2026 15:24</t>
         </is>
       </c>
       <c r="J54" s="29" t="n">
@@ -49153,47 +49153,47 @@
     <row r="55">
       <c r="A55" s="29" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B55" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C55" s="30" t="inlineStr">
         <is>
-          <t>16947422</t>
+          <t>17098960</t>
         </is>
       </c>
       <c r="D55" s="29" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E55" s="29" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F55" s="29" t="inlineStr">
         <is>
-          <t>Avenida BELMIRO DE ALBUQUERQUE</t>
+          <t>Avenida COMANDANTE CARDOSO</t>
         </is>
       </c>
       <c r="G55" s="29" t="inlineStr">
         <is>
-          <t>2727 - R</t>
+          <t>360 - 1 - R</t>
         </is>
       </c>
       <c r="H55" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 08:56</t>
+          <t>24/08/2026 15:24</t>
         </is>
       </c>
       <c r="I55" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 09:15</t>
+          <t>24/08/2026 15:43</t>
         </is>
       </c>
       <c r="J55" s="29" t="n">
@@ -49203,47 +49203,47 @@
     <row r="56">
       <c r="A56" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="B56" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C56" s="30" t="inlineStr">
         <is>
-          <t>16759239</t>
+          <t>16947422</t>
         </is>
       </c>
       <c r="D56" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E56" s="29" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="F56" s="29" t="inlineStr">
         <is>
-          <t>Rua AEROPORTO VIRACOPOS</t>
+          <t>Avenida BELMIRO DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="G56" s="29" t="inlineStr">
         <is>
-          <t>920 - 1 - R</t>
+          <t>2727 - R</t>
         </is>
       </c>
       <c r="H56" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 15:01</t>
+          <t>14/08/2026 08:56</t>
         </is>
       </c>
       <c r="I56" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 15:20</t>
+          <t>14/08/2026 09:15</t>
         </is>
       </c>
       <c r="J56" s="29" t="n">
@@ -49253,7 +49253,7 @@
     <row r="57">
       <c r="A57" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="B57" s="29" t="inlineStr">
@@ -49263,37 +49263,37 @@
       </c>
       <c r="C57" s="30" t="inlineStr">
         <is>
-          <t>17098960</t>
+          <t>16759717</t>
         </is>
       </c>
       <c r="D57" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>421 - JARDIM IPANEMA</t>
         </is>
       </c>
       <c r="E57" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q035</t>
         </is>
       </c>
       <c r="F57" s="29" t="inlineStr">
         <is>
-          <t>Avenida COMANDANTE CARDOSO</t>
+          <t>Rua BALTAZAR SALDANHA</t>
         </is>
       </c>
       <c r="G57" s="29" t="inlineStr">
         <is>
-          <t>360 - 1 - R</t>
+          <t>779 - OU</t>
         </is>
       </c>
       <c r="H57" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:24</t>
+          <t>05/08/2026 09:03</t>
         </is>
       </c>
       <c r="I57" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:43</t>
+          <t>05/08/2026 09:22</t>
         </is>
       </c>
       <c r="J57" s="29" t="n">
@@ -49303,47 +49303,47 @@
     <row r="58">
       <c r="A58" s="29" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B58" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C58" s="30" t="inlineStr">
         <is>
-          <t>16758244</t>
+          <t>16759239</t>
         </is>
       </c>
       <c r="D58" s="29" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇÕES</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E58" s="29" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="F58" s="29" t="inlineStr">
         <is>
-          <t>Avenida PROCURADOR DR. WILSON DIAS DE PINHO</t>
+          <t>Rua AEROPORTO VIRACOPOS</t>
         </is>
       </c>
       <c r="G58" s="29" t="inlineStr">
         <is>
-          <t>175 - 1 - C</t>
+          <t>920 - 1 - R</t>
         </is>
       </c>
       <c r="H58" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 07:41</t>
+          <t>05/08/2026 15:01</t>
         </is>
       </c>
       <c r="I58" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 08:00</t>
+          <t>05/08/2026 15:20</t>
         </is>
       </c>
       <c r="J58" s="29" t="n">
@@ -49353,47 +49353,47 @@
     <row r="59">
       <c r="A59" s="29" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="B59" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C59" s="30" t="inlineStr">
         <is>
-          <t>16759717</t>
+          <t>16758244</t>
         </is>
       </c>
       <c r="D59" s="29" t="inlineStr">
         <is>
-          <t>421 - JARDIM IPANEMA</t>
+          <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
       <c r="E59" s="29" t="inlineStr">
         <is>
-          <t>Q035</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="F59" s="29" t="inlineStr">
         <is>
-          <t>Rua BALTAZAR SALDANHA</t>
+          <t>Avenida PROCURADOR DR. WILSON DIAS DE PINHO</t>
         </is>
       </c>
       <c r="G59" s="29" t="inlineStr">
         <is>
-          <t>779 - OU</t>
+          <t>175 - 1 - C</t>
         </is>
       </c>
       <c r="H59" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 09:03</t>
+          <t>05/08/2026 07:41</t>
         </is>
       </c>
       <c r="I59" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 09:22</t>
+          <t>05/08/2026 08:00</t>
         </is>
       </c>
       <c r="J59" s="29" t="n">
@@ -49403,7 +49403,7 @@
     <row r="60">
       <c r="A60" s="29" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B60" s="29" t="inlineStr">
@@ -49413,37 +49413,37 @@
       </c>
       <c r="C60" s="30" t="inlineStr">
         <is>
-          <t>17068744</t>
+          <t>17066233</t>
         </is>
       </c>
       <c r="D60" s="29" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇÕES</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E60" s="29" t="inlineStr">
         <is>
-          <t>Q037</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="F60" s="29" t="inlineStr">
         <is>
-          <t>Rua CORONEL PONCE</t>
+          <t>Rua CAPÃO BONITO</t>
         </is>
       </c>
       <c r="G60" s="29" t="inlineStr">
         <is>
-          <t>04 - OU</t>
+          <t>191 - R</t>
         </is>
       </c>
       <c r="H60" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 15:05</t>
+          <t>17/08/2026 09:01</t>
         </is>
       </c>
       <c r="I60" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 15:24</t>
+          <t>17/08/2026 09:20</t>
         </is>
       </c>
       <c r="J60" s="29" t="n">
@@ -49453,7 +49453,7 @@
     <row r="61">
       <c r="A61" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B61" s="29" t="inlineStr">
@@ -49463,37 +49463,37 @@
       </c>
       <c r="C61" s="30" t="inlineStr">
         <is>
-          <t>17130027</t>
+          <t>17092097</t>
         </is>
       </c>
       <c r="D61" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E61" s="29" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F61" s="29" t="inlineStr">
         <is>
-          <t>Rua BARRA VELHA</t>
+          <t>Rua ARNALDO VASQUES</t>
         </is>
       </c>
       <c r="G61" s="29" t="inlineStr">
         <is>
-          <t>1154 - R</t>
+          <t>347 - R</t>
         </is>
       </c>
       <c r="H61" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:31</t>
+          <t>24/08/2026 09:00</t>
         </is>
       </c>
       <c r="I61" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:49</t>
+          <t>24/08/2026 09:18</t>
         </is>
       </c>
       <c r="J61" s="29" t="n">
@@ -49503,7 +49503,7 @@
     <row r="62">
       <c r="A62" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B62" s="29" t="inlineStr">
@@ -49513,37 +49513,37 @@
       </c>
       <c r="C62" s="30" t="inlineStr">
         <is>
-          <t>16910075</t>
+          <t>17130027</t>
         </is>
       </c>
       <c r="D62" s="29" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E62" s="29" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="F62" s="29" t="inlineStr">
         <is>
-          <t>Rua CATANDUVA</t>
+          <t>Rua BARRA VELHA</t>
         </is>
       </c>
       <c r="G62" s="29" t="inlineStr">
         <is>
-          <t>490 - R</t>
+          <t>1154 - R</t>
         </is>
       </c>
       <c r="H62" s="29" t="inlineStr">
         <is>
-          <t>13/08/2026 15:31</t>
+          <t>25/08/2026 09:31</t>
         </is>
       </c>
       <c r="I62" s="29" t="inlineStr">
         <is>
-          <t>13/08/2026 15:49</t>
+          <t>25/08/2026 09:49</t>
         </is>
       </c>
       <c r="J62" s="29" t="n">
@@ -49553,47 +49553,47 @@
     <row r="63">
       <c r="A63" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B63" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C63" s="30" t="inlineStr">
         <is>
-          <t>17092097</t>
+          <t>17043615</t>
         </is>
       </c>
       <c r="D63" s="29" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E63" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q035</t>
         </is>
       </c>
       <c r="F63" s="29" t="inlineStr">
         <is>
-          <t>Rua ARNALDO VASQUES</t>
+          <t>Rua FELIPE DE BRUM</t>
         </is>
       </c>
       <c r="G63" s="29" t="inlineStr">
         <is>
-          <t>347 - R</t>
+          <t>900 - R</t>
         </is>
       </c>
       <c r="H63" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:00</t>
+          <t>20/08/2026 14:30</t>
         </is>
       </c>
       <c r="I63" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:18</t>
+          <t>20/08/2026 14:48</t>
         </is>
       </c>
       <c r="J63" s="29" t="n">
@@ -49603,7 +49603,7 @@
     <row r="64">
       <c r="A64" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="B64" s="29" t="inlineStr">
@@ -49613,12 +49613,12 @@
       </c>
       <c r="C64" s="30" t="inlineStr">
         <is>
-          <t>17051418</t>
+          <t>16758314</t>
         </is>
       </c>
       <c r="D64" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
       <c r="E64" s="29" t="inlineStr">
@@ -49628,22 +49628,22 @@
       </c>
       <c r="F64" s="29" t="inlineStr">
         <is>
-          <t>Rua AFONSO DE ALBUQUERQUE</t>
+          <t>Rua CAMANDANTE LINCON PAIVA</t>
         </is>
       </c>
       <c r="G64" s="29" t="inlineStr">
         <is>
-          <t>231 - 3 - R</t>
+          <t>637 - C</t>
         </is>
       </c>
       <c r="H64" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 14:18</t>
+          <t>05/08/2026 16:25</t>
         </is>
       </c>
       <c r="I64" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 14:36</t>
+          <t>05/08/2026 16:43</t>
         </is>
       </c>
       <c r="J64" s="29" t="n">
@@ -49653,7 +49653,7 @@
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B65" s="29" t="inlineStr">
@@ -49663,7 +49663,7 @@
       </c>
       <c r="C65" s="30" t="inlineStr">
         <is>
-          <t>17034408</t>
+          <t>17051418</t>
         </is>
       </c>
       <c r="D65" s="29" t="inlineStr">
@@ -49673,27 +49673,27 @@
       </c>
       <c r="E65" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="F65" s="29" t="inlineStr">
         <is>
-          <t>Rua JABAQUARA</t>
+          <t>Rua AFONSO DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="G65" s="29" t="inlineStr">
         <is>
-          <t>1370 - 4 - R</t>
+          <t>231 - 3 - R</t>
         </is>
       </c>
       <c r="H65" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:05</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="I65" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:23</t>
+          <t>19/08/2026 14:36</t>
         </is>
       </c>
       <c r="J65" s="29" t="n">
@@ -49753,7 +49753,7 @@
     <row r="67">
       <c r="A67" s="29" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B67" s="29" t="inlineStr">
@@ -49763,37 +49763,37 @@
       </c>
       <c r="C67" s="30" t="inlineStr">
         <is>
-          <t>16758314</t>
+          <t>17034408</t>
         </is>
       </c>
       <c r="D67" s="29" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇÕES</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E67" s="29" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F67" s="29" t="inlineStr">
         <is>
-          <t>Rua CAMANDANTE LINCON PAIVA</t>
+          <t>Rua JABAQUARA</t>
         </is>
       </c>
       <c r="G67" s="29" t="inlineStr">
         <is>
-          <t>637 - C</t>
+          <t>1370 - 4 - R</t>
         </is>
       </c>
       <c r="H67" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 16:25</t>
+          <t>19/08/2026 10:05</t>
         </is>
       </c>
       <c r="I67" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 16:43</t>
+          <t>19/08/2026 10:23</t>
         </is>
       </c>
       <c r="J67" s="29" t="n">
@@ -49903,47 +49903,47 @@
     <row r="70">
       <c r="A70" s="29" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B70" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>17043615</t>
+          <t>16910075</t>
         </is>
       </c>
       <c r="D70" s="29" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E70" s="29" t="inlineStr">
         <is>
-          <t>Q035</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="F70" s="29" t="inlineStr">
         <is>
-          <t>Rua FELIPE DE BRUM</t>
+          <t>Rua CATANDUVA</t>
         </is>
       </c>
       <c r="G70" s="29" t="inlineStr">
         <is>
-          <t>900 - R</t>
+          <t>490 - R</t>
         </is>
       </c>
       <c r="H70" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 14:30</t>
+          <t>13/08/2026 15:31</t>
         </is>
       </c>
       <c r="I70" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 14:48</t>
+          <t>13/08/2026 15:49</t>
         </is>
       </c>
       <c r="J70" s="29" t="n">
@@ -49953,7 +49953,7 @@
     <row r="71">
       <c r="A71" s="29" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B71" s="29" t="inlineStr">
@@ -49963,37 +49963,37 @@
       </c>
       <c r="C71" s="30" t="inlineStr">
         <is>
-          <t>17133115</t>
+          <t>17043629</t>
         </is>
       </c>
       <c r="D71" s="29" t="inlineStr">
         <is>
-          <t>412 - COHAB</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E71" s="29" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="F71" s="29" t="inlineStr">
         <is>
-          <t>Rua VALENCIO DE BRUM</t>
+          <t>Rua ARAPONGAS</t>
         </is>
       </c>
       <c r="G71" s="29" t="inlineStr">
         <is>
-          <t>536 - R</t>
+          <t>142 - R</t>
         </is>
       </c>
       <c r="H71" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:33</t>
+          <t>20/08/2026 15:52</t>
         </is>
       </c>
       <c r="I71" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:50</t>
+          <t>20/08/2026 16:09</t>
         </is>
       </c>
       <c r="J71" s="29" t="n">
@@ -50013,7 +50013,7 @@
       </c>
       <c r="C72" s="30" t="inlineStr">
         <is>
-          <t>16960075</t>
+          <t>17072136</t>
         </is>
       </c>
       <c r="D72" s="29" t="inlineStr">
@@ -50023,27 +50023,27 @@
       </c>
       <c r="E72" s="29" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="F72" s="29" t="inlineStr">
         <is>
-          <t>Rua SALIM DERZI</t>
+          <t>Rua TOMBADOR</t>
         </is>
       </c>
       <c r="G72" s="29" t="inlineStr">
         <is>
-          <t>58 - R</t>
+          <t>684 - R</t>
         </is>
       </c>
       <c r="H72" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 15:47</t>
+          <t>21/08/2026 10:12</t>
         </is>
       </c>
       <c r="I72" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 16:04</t>
+          <t>21/08/2026 10:29</t>
         </is>
       </c>
       <c r="J72" s="29" t="n">
@@ -50063,7 +50063,7 @@
       </c>
       <c r="C73" s="30" t="inlineStr">
         <is>
-          <t>16960061</t>
+          <t>16960075</t>
         </is>
       </c>
       <c r="D73" s="29" t="inlineStr">
@@ -50083,17 +50083,17 @@
       </c>
       <c r="G73" s="29" t="inlineStr">
         <is>
-          <t>118 - R</t>
+          <t>58 - R</t>
         </is>
       </c>
       <c r="H73" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 10:37</t>
+          <t>17/08/2026 15:47</t>
         </is>
       </c>
       <c r="I73" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 10:54</t>
+          <t>17/08/2026 16:04</t>
         </is>
       </c>
       <c r="J73" s="29" t="n">
@@ -50103,7 +50103,7 @@
     <row r="74">
       <c r="A74" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
       <c r="B74" s="29" t="inlineStr">
@@ -50113,37 +50113,37 @@
       </c>
       <c r="C74" s="30" t="inlineStr">
         <is>
-          <t>17073307</t>
+          <t>17133115</t>
         </is>
       </c>
       <c r="D74" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>412 - COHAB</t>
         </is>
       </c>
       <c r="E74" s="29" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="F74" s="29" t="inlineStr">
         <is>
-          <t>Avenida ANTONIO JOAO</t>
+          <t>Rua VALENCIO DE BRUM</t>
         </is>
       </c>
       <c r="G74" s="29" t="inlineStr">
         <is>
-          <t>1477 - R</t>
+          <t>536 - R</t>
         </is>
       </c>
       <c r="H74" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 13:54</t>
+          <t>25/08/2026 09:33</t>
         </is>
       </c>
       <c r="I74" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 14:11</t>
+          <t>25/08/2026 09:50</t>
         </is>
       </c>
       <c r="J74" s="29" t="n">
@@ -50353,7 +50353,7 @@
     <row r="79">
       <c r="A79" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B79" s="29" t="inlineStr">
@@ -50363,7 +50363,7 @@
       </c>
       <c r="C79" s="30" t="inlineStr">
         <is>
-          <t>16971696</t>
+          <t>17022532</t>
         </is>
       </c>
       <c r="D79" s="29" t="inlineStr">
@@ -50373,27 +50373,27 @@
       </c>
       <c r="E79" s="29" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F79" s="29" t="inlineStr">
         <is>
-          <t>Rua TENENTE SAMUEL DE ALMEIDA</t>
+          <t>Rua MARINGA</t>
         </is>
       </c>
       <c r="G79" s="29" t="inlineStr">
         <is>
-          <t>630 - 1 - R</t>
+          <t>807 - R</t>
         </is>
       </c>
       <c r="H79" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 10:58</t>
+          <t>17/08/2026 09:53</t>
         </is>
       </c>
       <c r="I79" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 11:15</t>
+          <t>17/08/2026 10:10</t>
         </is>
       </c>
       <c r="J79" s="29" t="n">
@@ -50403,7 +50403,7 @@
     <row r="80">
       <c r="A80" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B80" s="29" t="inlineStr">
@@ -50413,37 +50413,37 @@
       </c>
       <c r="C80" s="30" t="inlineStr">
         <is>
-          <t>16739131</t>
+          <t>17070288</t>
         </is>
       </c>
       <c r="D80" s="29" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E80" s="29" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="F80" s="29" t="inlineStr">
         <is>
-          <t>Rua BARRA BONITA</t>
+          <t>Rua JABAQUARA</t>
         </is>
       </c>
       <c r="G80" s="29" t="inlineStr">
         <is>
-          <t>50 - R</t>
+          <t>1490 - C</t>
         </is>
       </c>
       <c r="H80" s="29" t="inlineStr">
         <is>
-          <t>04/08/2026 15:37</t>
+          <t>21/08/2026 15:07</t>
         </is>
       </c>
       <c r="I80" s="29" t="inlineStr">
         <is>
-          <t>04/08/2026 15:54</t>
+          <t>21/08/2026 15:24</t>
         </is>
       </c>
       <c r="J80" s="29" t="n">
@@ -50503,7 +50503,7 @@
     <row r="82">
       <c r="A82" s="29" t="inlineStr">
         <is>
-          <t>Raquel Ortiz dos Santos</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B82" s="29" t="inlineStr">
@@ -50513,37 +50513,37 @@
       </c>
       <c r="C82" s="30" t="inlineStr">
         <is>
-          <t>16881755</t>
+          <t>16739131</t>
         </is>
       </c>
       <c r="D82" s="29" t="inlineStr">
         <is>
-          <t>406 - JARDIM PRIMAVERA</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E82" s="29" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="F82" s="29" t="inlineStr">
         <is>
-          <t>Rua ELOAH VIEIRA DA SILVA</t>
+          <t>Rua BARRA BONITA</t>
         </is>
       </c>
       <c r="G82" s="29" t="inlineStr">
         <is>
-          <t>26 - 2 - TB</t>
+          <t>50 - R</t>
         </is>
       </c>
       <c r="H82" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 16:12</t>
+          <t>04/08/2026 15:37</t>
         </is>
       </c>
       <c r="I82" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 16:29</t>
+          <t>04/08/2026 15:54</t>
         </is>
       </c>
       <c r="J82" s="29" t="n">
@@ -50553,47 +50553,47 @@
     <row r="83">
       <c r="A83" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
       <c r="B83" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C83" s="30" t="inlineStr">
         <is>
-          <t>17041447</t>
+          <t>16881755</t>
         </is>
       </c>
       <c r="D83" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>406 - JARDIM PRIMAVERA</t>
         </is>
       </c>
       <c r="E83" s="29" t="inlineStr">
         <is>
-          <t>Q038</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="F83" s="29" t="inlineStr">
         <is>
-          <t>Rua DAS PEROBAS</t>
+          <t>Rua ELOAH VIEIRA DA SILVA</t>
         </is>
       </c>
       <c r="G83" s="29" t="inlineStr">
         <is>
-          <t>1018 - R</t>
+          <t>26 - 2 - TB</t>
         </is>
       </c>
       <c r="H83" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 14:48</t>
+          <t>12/08/2026 16:12</t>
         </is>
       </c>
       <c r="I83" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 15:05</t>
+          <t>12/08/2026 16:29</t>
         </is>
       </c>
       <c r="J83" s="29" t="n">
@@ -50603,47 +50603,47 @@
     <row r="84">
       <c r="A84" s="29" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B84" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C84" s="30" t="inlineStr">
         <is>
-          <t>17043629</t>
+          <t>16971696</t>
         </is>
       </c>
       <c r="D84" s="29" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E84" s="29" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="F84" s="29" t="inlineStr">
         <is>
-          <t>Rua ARAPONGAS</t>
+          <t>Rua TENENTE SAMUEL DE ALMEIDA</t>
         </is>
       </c>
       <c r="G84" s="29" t="inlineStr">
         <is>
-          <t>142 - R</t>
+          <t>630 - 1 - R</t>
         </is>
       </c>
       <c r="H84" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 15:52</t>
+          <t>17/08/2026 10:58</t>
         </is>
       </c>
       <c r="I84" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 16:09</t>
+          <t>17/08/2026 11:15</t>
         </is>
       </c>
       <c r="J84" s="29" t="n">
@@ -50703,47 +50703,47 @@
     <row r="86">
       <c r="A86" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B86" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C86" s="30" t="inlineStr">
         <is>
-          <t>17070286</t>
+          <t>17073314</t>
         </is>
       </c>
       <c r="D86" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E86" s="29" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F86" s="29" t="inlineStr">
         <is>
-          <t>Rua GUAÍBA</t>
+          <t>Avenida ANTONIO JOAO</t>
         </is>
       </c>
       <c r="G86" s="29" t="inlineStr">
         <is>
-          <t>1262 - C</t>
+          <t>1371 - OU</t>
         </is>
       </c>
       <c r="H86" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 14:40</t>
+          <t>20/08/2026 15:23</t>
         </is>
       </c>
       <c r="I86" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 14:57</t>
+          <t>20/08/2026 15:40</t>
         </is>
       </c>
       <c r="J86" s="29" t="n">
@@ -50753,47 +50753,47 @@
     <row r="87">
       <c r="A87" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="B87" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C87" s="30" t="inlineStr">
         <is>
-          <t>17070288</t>
+          <t>17014581</t>
         </is>
       </c>
       <c r="D87" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>433 - ÁREA A - RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E87" s="29" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F87" s="29" t="inlineStr">
         <is>
-          <t>Rua JABAQUARA</t>
+          <t>Rua GUARANTA</t>
         </is>
       </c>
       <c r="G87" s="29" t="inlineStr">
         <is>
-          <t>1490 - C</t>
+          <t>295 - 1 - TB</t>
         </is>
       </c>
       <c r="H87" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 15:07</t>
+          <t>19/08/2026 09:45</t>
         </is>
       </c>
       <c r="I87" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 15:24</t>
+          <t>19/08/2026 10:02</t>
         </is>
       </c>
       <c r="J87" s="29" t="n">
@@ -50803,7 +50803,7 @@
     <row r="88">
       <c r="A88" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B88" s="29" t="inlineStr">
@@ -50813,37 +50813,37 @@
       </c>
       <c r="C88" s="30" t="inlineStr">
         <is>
-          <t>17022532</t>
+          <t>17064916</t>
         </is>
       </c>
       <c r="D88" s="29" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E88" s="29" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="F88" s="29" t="inlineStr">
         <is>
-          <t>Rua MARINGA</t>
+          <t>Rua RIACHO DOCE</t>
         </is>
       </c>
       <c r="G88" s="29" t="inlineStr">
         <is>
-          <t>807 - R</t>
+          <t>78 - R</t>
         </is>
       </c>
       <c r="H88" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:53</t>
+          <t>18/08/2026 14:00</t>
         </is>
       </c>
       <c r="I88" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 10:10</t>
+          <t>18/08/2026 14:17</t>
         </is>
       </c>
       <c r="J88" s="29" t="n">
@@ -50853,7 +50853,7 @@
     <row r="89">
       <c r="A89" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B89" s="29" t="inlineStr">
@@ -50863,7 +50863,7 @@
       </c>
       <c r="C89" s="30" t="inlineStr">
         <is>
-          <t>17064916</t>
+          <t>17070286</t>
         </is>
       </c>
       <c r="D89" s="29" t="inlineStr">
@@ -50873,27 +50873,27 @@
       </c>
       <c r="E89" s="29" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F89" s="29" t="inlineStr">
         <is>
-          <t>Rua RIACHO DOCE</t>
+          <t>Rua GUAÍBA</t>
         </is>
       </c>
       <c r="G89" s="29" t="inlineStr">
         <is>
-          <t>78 - R</t>
+          <t>1262 - C</t>
         </is>
       </c>
       <c r="H89" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 14:00</t>
+          <t>21/08/2026 14:40</t>
         </is>
       </c>
       <c r="I89" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 14:17</t>
+          <t>21/08/2026 14:57</t>
         </is>
       </c>
       <c r="J89" s="29" t="n">
@@ -51003,7 +51003,7 @@
     <row r="92">
       <c r="A92" s="29" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="B92" s="29" t="inlineStr">
@@ -51013,37 +51013,37 @@
       </c>
       <c r="C92" s="30" t="inlineStr">
         <is>
-          <t>17072136</t>
+          <t>17100546</t>
         </is>
       </c>
       <c r="D92" s="29" t="inlineStr">
         <is>
-          <t>443 - KAMEL SAAD 1</t>
+          <t>440 - JARDIM IBIRAPUERA</t>
         </is>
       </c>
       <c r="E92" s="29" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="F92" s="29" t="inlineStr">
         <is>
-          <t>Rua TOMBADOR</t>
+          <t>Avenida BELMIRO DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="G92" s="29" t="inlineStr">
         <is>
-          <t>684 - R</t>
+          <t>3933 - R</t>
         </is>
       </c>
       <c r="H92" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 10:12</t>
+          <t>21/08/2026 14:04</t>
         </is>
       </c>
       <c r="I92" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 10:29</t>
+          <t>21/08/2026 14:21</t>
         </is>
       </c>
       <c r="J92" s="29" t="n">
@@ -51053,7 +51053,7 @@
     <row r="93">
       <c r="A93" s="29" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="B93" s="29" t="inlineStr">
@@ -51063,37 +51063,37 @@
       </c>
       <c r="C93" s="30" t="inlineStr">
         <is>
-          <t>17100546</t>
+          <t>16960061</t>
         </is>
       </c>
       <c r="D93" s="29" t="inlineStr">
         <is>
-          <t>440 - JARDIM IBIRAPUERA</t>
+          <t>443 - KAMEL SAAD 1</t>
         </is>
       </c>
       <c r="E93" s="29" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F93" s="29" t="inlineStr">
         <is>
-          <t>Avenida BELMIRO DE ALBUQUERQUE</t>
+          <t>Rua SALIM DERZI</t>
         </is>
       </c>
       <c r="G93" s="29" t="inlineStr">
         <is>
-          <t>3933 - R</t>
+          <t>118 - R</t>
         </is>
       </c>
       <c r="H93" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 14:04</t>
+          <t>17/08/2026 10:37</t>
         </is>
       </c>
       <c r="I93" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 14:21</t>
+          <t>17/08/2026 10:54</t>
         </is>
       </c>
       <c r="J93" s="29" t="n">
@@ -51113,7 +51113,7 @@
       </c>
       <c r="C94" s="30" t="inlineStr">
         <is>
-          <t>17073314</t>
+          <t>17073307</t>
         </is>
       </c>
       <c r="D94" s="29" t="inlineStr">
@@ -51133,17 +51133,17 @@
       </c>
       <c r="G94" s="29" t="inlineStr">
         <is>
-          <t>1371 - OU</t>
+          <t>1477 - R</t>
         </is>
       </c>
       <c r="H94" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 15:23</t>
+          <t>20/08/2026 13:54</t>
         </is>
       </c>
       <c r="I94" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 15:40</t>
+          <t>20/08/2026 14:11</t>
         </is>
       </c>
       <c r="J94" s="29" t="n">
@@ -51153,7 +51153,7 @@
     <row r="95">
       <c r="A95" s="29" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B95" s="29" t="inlineStr">
@@ -51163,37 +51163,37 @@
       </c>
       <c r="C95" s="30" t="inlineStr">
         <is>
-          <t>17014581</t>
+          <t>17041447</t>
         </is>
       </c>
       <c r="D95" s="29" t="inlineStr">
         <is>
-          <t>433 - ÁREA A - RESIDENCIAL PONTA PORÃ 1</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E95" s="29" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q038</t>
         </is>
       </c>
       <c r="F95" s="29" t="inlineStr">
         <is>
-          <t>Rua GUARANTA</t>
+          <t>Rua DAS PEROBAS</t>
         </is>
       </c>
       <c r="G95" s="29" t="inlineStr">
         <is>
-          <t>295 - 1 - TB</t>
+          <t>1018 - R</t>
         </is>
       </c>
       <c r="H95" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:45</t>
+          <t>20/08/2026 14:48</t>
         </is>
       </c>
       <c r="I95" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:02</t>
+          <t>20/08/2026 15:05</t>
         </is>
       </c>
       <c r="J95" s="29" t="n">
@@ -51803,7 +51803,7 @@
     <row r="108">
       <c r="A108" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B108" s="29" t="inlineStr">
@@ -51813,37 +51813,37 @@
       </c>
       <c r="C108" s="30" t="inlineStr">
         <is>
-          <t>16971668</t>
+          <t>17033729</t>
         </is>
       </c>
       <c r="D108" s="29" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E108" s="29" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F108" s="29" t="inlineStr">
         <is>
-          <t>Rua SAO CRISTOVAO</t>
+          <t>Rua VICENTE  AZAMBUJA</t>
         </is>
       </c>
       <c r="G108" s="29" t="inlineStr">
         <is>
-          <t>917 - 8 - R</t>
+          <t>1407 - R</t>
         </is>
       </c>
       <c r="H108" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 08:51</t>
+          <t>19/08/2026 08:45</t>
         </is>
       </c>
       <c r="I108" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:07</t>
+          <t>19/08/2026 09:01</t>
         </is>
       </c>
       <c r="J108" s="29" t="n">
@@ -51853,7 +51853,7 @@
     <row r="109">
       <c r="A109" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B109" s="29" t="inlineStr">
@@ -51863,37 +51863,37 @@
       </c>
       <c r="C109" s="30" t="inlineStr">
         <is>
-          <t>17076991</t>
+          <t>16971668</t>
         </is>
       </c>
       <c r="D109" s="29" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E109" s="29" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="F109" s="29" t="inlineStr">
         <is>
-          <t>Rua Anselmo Soares</t>
+          <t>Rua SAO CRISTOVAO</t>
         </is>
       </c>
       <c r="G109" s="29" t="inlineStr">
         <is>
-          <t>700 - OU</t>
+          <t>917 - 8 - R</t>
         </is>
       </c>
       <c r="H109" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 15:29</t>
+          <t>17/08/2026 08:51</t>
         </is>
       </c>
       <c r="I109" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 15:45</t>
+          <t>17/08/2026 09:07</t>
         </is>
       </c>
       <c r="J109" s="29" t="n">
@@ -52003,7 +52003,7 @@
     <row r="112">
       <c r="A112" s="29" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="B112" s="29" t="inlineStr">
@@ -52013,37 +52013,37 @@
       </c>
       <c r="C112" s="30" t="inlineStr">
         <is>
-          <t>16957579</t>
+          <t>17055208</t>
         </is>
       </c>
       <c r="D112" s="29" t="inlineStr">
         <is>
-          <t>407 - MOOCA</t>
+          <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
       <c r="E112" s="29" t="inlineStr">
         <is>
-          <t>Q041</t>
+          <t>Q036</t>
         </is>
       </c>
       <c r="F112" s="29" t="inlineStr">
         <is>
-          <t>Rua VALPARAISO</t>
+          <t>Rua DIGNO TORRES GIMENEZ</t>
         </is>
       </c>
       <c r="G112" s="29" t="inlineStr">
         <is>
-          <t>335 - R</t>
+          <t>590 - 2 - R</t>
         </is>
       </c>
       <c r="H112" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 08:59</t>
+          <t>21/08/2026 08:57</t>
         </is>
       </c>
       <c r="I112" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:15</t>
+          <t>21/08/2026 09:13</t>
         </is>
       </c>
       <c r="J112" s="29" t="n">
@@ -52053,7 +52053,7 @@
     <row r="113">
       <c r="A113" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B113" s="29" t="inlineStr">
@@ -52063,37 +52063,37 @@
       </c>
       <c r="C113" s="30" t="inlineStr">
         <is>
-          <t>17033729</t>
+          <t>17076991</t>
         </is>
       </c>
       <c r="D113" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
       <c r="E113" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q012</t>
         </is>
       </c>
       <c r="F113" s="29" t="inlineStr">
         <is>
-          <t>Rua VICENTE  AZAMBUJA</t>
+          <t>Rua Anselmo Soares</t>
         </is>
       </c>
       <c r="G113" s="29" t="inlineStr">
         <is>
-          <t>1407 - R</t>
+          <t>700 - OU</t>
         </is>
       </c>
       <c r="H113" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 08:45</t>
+          <t>19/08/2026 15:29</t>
         </is>
       </c>
       <c r="I113" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:01</t>
+          <t>19/08/2026 15:45</t>
         </is>
       </c>
       <c r="J113" s="29" t="n">
@@ -52153,7 +52153,7 @@
     <row r="115">
       <c r="A115" s="29" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="B115" s="29" t="inlineStr">
@@ -52163,37 +52163,37 @@
       </c>
       <c r="C115" s="30" t="inlineStr">
         <is>
-          <t>17055208</t>
+          <t>16957579</t>
         </is>
       </c>
       <c r="D115" s="29" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇÕES</t>
+          <t>407 - MOOCA</t>
         </is>
       </c>
       <c r="E115" s="29" t="inlineStr">
         <is>
-          <t>Q036</t>
+          <t>Q041</t>
         </is>
       </c>
       <c r="F115" s="29" t="inlineStr">
         <is>
-          <t>Rua DIGNO TORRES GIMENEZ</t>
+          <t>Rua VALPARAISO</t>
         </is>
       </c>
       <c r="G115" s="29" t="inlineStr">
         <is>
-          <t>590 - 2 - R</t>
+          <t>335 - R</t>
         </is>
       </c>
       <c r="H115" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 08:57</t>
+          <t>17/08/2026 08:59</t>
         </is>
       </c>
       <c r="I115" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 09:13</t>
+          <t>17/08/2026 09:15</t>
         </is>
       </c>
       <c r="J115" s="29" t="n">
@@ -52303,7 +52303,7 @@
     <row r="118">
       <c r="A118" s="29" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="B118" s="29" t="inlineStr">
@@ -52313,37 +52313,37 @@
       </c>
       <c r="C118" s="30" t="inlineStr">
         <is>
-          <t>16982670</t>
+          <t>16988946</t>
         </is>
       </c>
       <c r="D118" s="29" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>435 - JARDIM PRIMOR</t>
         </is>
       </c>
       <c r="E118" s="29" t="inlineStr">
         <is>
-          <t>Q037</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="F118" s="29" t="inlineStr">
         <is>
-          <t>Rua SALVADOR</t>
+          <t>Rua PIRACICABA</t>
         </is>
       </c>
       <c r="G118" s="29" t="inlineStr">
         <is>
-          <t>479 - R</t>
+          <t>32 - R</t>
         </is>
       </c>
       <c r="H118" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 14:14</t>
+          <t>17/08/2026 08:50</t>
         </is>
       </c>
       <c r="I118" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 14:30</t>
+          <t>17/08/2026 09:06</t>
         </is>
       </c>
       <c r="J118" s="29" t="n">
@@ -52353,7 +52353,7 @@
     <row r="119">
       <c r="A119" s="29" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B119" s="29" t="inlineStr">
@@ -52363,37 +52363,37 @@
       </c>
       <c r="C119" s="30" t="inlineStr">
         <is>
-          <t>16988946</t>
+          <t>16982670</t>
         </is>
       </c>
       <c r="D119" s="29" t="inlineStr">
         <is>
-          <t>435 - JARDIM PRIMOR</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E119" s="29" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q037</t>
         </is>
       </c>
       <c r="F119" s="29" t="inlineStr">
         <is>
-          <t>Rua PIRACICABA</t>
+          <t>Rua SALVADOR</t>
         </is>
       </c>
       <c r="G119" s="29" t="inlineStr">
         <is>
-          <t>32 - R</t>
+          <t>479 - R</t>
         </is>
       </c>
       <c r="H119" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 08:50</t>
+          <t>17/08/2026 14:14</t>
         </is>
       </c>
       <c r="I119" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:06</t>
+          <t>17/08/2026 14:30</t>
         </is>
       </c>
       <c r="J119" s="29" t="n">

--- a/data/historico/semanas_318-321.xlsx
+++ b/data/historico/semanas_318-321.xlsx
@@ -28,7 +28,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Visitas Duplicadas'!$A$2:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Visitas Suspeitas'!$A$2:$K$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Visitas Negativas'!$A$2:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 15min'!$A$2:$J$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 15min'!$A$2:$J$122</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$246</definedName>
@@ -1035,16 +1035,16 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>15</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>26</v>
+        <v>25.93</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>5.07</v>
+        <v>5.04</v>
       </c>
       <c r="H3" s="4" t="n">
         <v>5</v>
@@ -1053,10 +1053,10 @@
         <v>5</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3" s="4" t="n">
         <v>0</v>
@@ -1083,23 +1083,23 @@
         <v>1</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>26.69</v>
+        <v>26.74</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>5.75</v>
+        <v>4.63</v>
       </c>
       <c r="W3" s="4" t="n">
-        <v>21.58</v>
+        <v>17.35</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Y3" s="4" t="inlineStr">
         <is>
-          <t>R$ 100,63</t>
+          <t>R$ 101,40</t>
         </is>
       </c>
       <c r="Z3" s="4" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AA3" s="4" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AB3" s="4" t="inlineStr">
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="C3" s="29" t="n">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D3" s="29" t="n">
         <v>141</v>
@@ -6156,10 +6156,10 @@
         <v>1</v>
       </c>
       <c r="F3" s="29" t="n">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G3" s="29" t="n">
-        <v>26.69</v>
+        <v>26.74</v>
       </c>
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
@@ -7365,7 +7365,7 @@
         </is>
       </c>
       <c r="C45" s="26" t="n">
-        <v>11675</v>
+        <v>11674</v>
       </c>
       <c r="D45" s="26" t="n">
         <v>5280</v>
@@ -7374,7 +7374,7 @@
         <v>16</v>
       </c>
       <c r="F45" s="26" t="n">
-        <v>16971</v>
+        <v>16970</v>
       </c>
       <c r="G45" s="26" t="n">
         <v>31.21</v>
@@ -9495,16 +9495,16 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>5</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>4.96</v>
+        <v>4.9</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>5</v>
@@ -9516,7 +9516,7 @@
         <v>0.65</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -9541,17 +9541,17 @@
       <c r="V5" s="4" t="inlineStr"/>
       <c r="W5" s="4" t="inlineStr"/>
       <c r="X5" s="4" t="n">
-        <v>8.73</v>
+        <v>5.34</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>43.63</v>
+        <v>26.72</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AA5" s="4" t="inlineStr">
         <is>
-          <t>R$ 86,80</t>
+          <t>R$ 88,54</t>
         </is>
       </c>
       <c r="AB5" s="4" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="AC5" s="4" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD5" s="4" t="inlineStr">
@@ -25449,7 +25449,7 @@
         <v>6</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>93.73</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         </is>
       </c>
       <c r="D51" s="52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E51" s="52" t="n">
         <v>0.3</v>
@@ -26714,7 +26714,7 @@
         <v>0.34</v>
       </c>
       <c r="H51" s="52" t="n">
-        <v>-0.68</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="52">
@@ -37581,13 +37581,13 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>4.88</v>
+        <v>4.56</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>2</v>
@@ -37601,7 +37601,7 @@
         <v>1</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>3.03</v>
+        <v>3.12</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>18</v>
@@ -37610,7 +37610,7 @@
         <v>0</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>35.29</v>
+        <v>36</v>
       </c>
       <c r="N3" s="4" t="inlineStr">
         <is>
@@ -46467,7 +46467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -46485,7 +46485,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VISITAS COM DURAÇÃO ACIMA DE 15MIN (121 registros) — AUDITORIA DE POSSÍVEL MANIPULAÇÃO DE HORÁRIO (LANÇAMENTO PELO COMPUTADOR); NO CÁLCULO DE MÉDIA/MEDIANA ENTRAM COMO 15MIN</t>
+          <t>VISITAS COM DURAÇÃO ACIMA DE 15MIN (120 registros) — AUDITORIA DE POSSÍVEL MANIPULAÇÃO DE HORÁRIO (LANÇAMENTO PELO COMPUTADOR); NO CÁLCULO DE MÉDIA/MEDIANA ENTRAM COMO 15MIN</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -46603,107 +46603,107 @@
     <row r="4">
       <c r="A4" s="29" t="inlineStr">
         <is>
-          <t>Adriana de Jesus Saraiva</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="B4" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C4" s="30" t="inlineStr">
         <is>
-          <t>17005200</t>
+          <t>17071308</t>
         </is>
       </c>
       <c r="D4" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>445 - JARDIM IVONE</t>
         </is>
       </c>
       <c r="E4" s="29" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q051</t>
         </is>
       </c>
       <c r="F4" s="29" t="inlineStr">
         <is>
-          <t>Rua VICENTE  AZAMBUJA</t>
+          <t>Rua TUPA</t>
         </is>
       </c>
       <c r="G4" s="29" t="inlineStr">
         <is>
-          <t>1650 - R</t>
+          <t>437 - R</t>
         </is>
       </c>
       <c r="H4" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 08:51</t>
+          <t>21/08/2026 15:33</t>
         </is>
       </c>
       <c r="I4" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 08:59</t>
+          <t>21/08/2026 16:55</t>
         </is>
       </c>
       <c r="J4" s="29" t="n">
-        <v>1448</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="29" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Adriana de Jesus Saraiva</t>
         </is>
       </c>
       <c r="B5" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C5" s="30" t="inlineStr">
         <is>
-          <t>17071308</t>
+          <t>16819573</t>
         </is>
       </c>
       <c r="D5" s="29" t="inlineStr">
         <is>
-          <t>445 - JARDIM IVONE</t>
+          <t>404 - JARDIM DOS ESTADOS</t>
         </is>
       </c>
       <c r="E5" s="29" t="inlineStr">
         <is>
-          <t>Q051</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="F5" s="29" t="inlineStr">
         <is>
-          <t>Rua TUPA</t>
+          <t>Rua NICANDRO ERNESTO DE CAMPOS</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
         <is>
-          <t>437 - R</t>
+          <t>808 - OU</t>
         </is>
       </c>
       <c r="H5" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 15:33</t>
+          <t>07/08/2026 15:15</t>
         </is>
       </c>
       <c r="I5" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 16:55</t>
+          <t>07/08/2026 16:34</t>
         </is>
       </c>
       <c r="J5" s="29" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>Adriana de Jesus Saraiva</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">
@@ -46713,47 +46713,47 @@
       </c>
       <c r="C6" s="30" t="inlineStr">
         <is>
-          <t>16819573</t>
+          <t>17066639</t>
         </is>
       </c>
       <c r="D6" s="29" t="inlineStr">
         <is>
-          <t>404 - JARDIM DOS ESTADOS</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E6" s="29" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F6" s="29" t="inlineStr">
         <is>
-          <t>Rua NICANDRO ERNESTO DE CAMPOS</t>
+          <t>Rua DOS ANJOS</t>
         </is>
       </c>
       <c r="G6" s="29" t="inlineStr">
         <is>
-          <t>808 - OU</t>
+          <t>40 - R</t>
         </is>
       </c>
       <c r="H6" s="29" t="inlineStr">
         <is>
-          <t>07/08/2026 15:15</t>
+          <t>17/08/2026 09:00</t>
         </is>
       </c>
       <c r="I6" s="29" t="inlineStr">
         <is>
-          <t>07/08/2026 16:34</t>
+          <t>17/08/2026 10:12</t>
         </is>
       </c>
       <c r="J6" s="29" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B7" s="29" t="inlineStr">
@@ -46763,7 +46763,7 @@
       </c>
       <c r="C7" s="30" t="inlineStr">
         <is>
-          <t>17066639</t>
+          <t>16983739</t>
         </is>
       </c>
       <c r="D7" s="29" t="inlineStr">
@@ -46773,31 +46773,31 @@
       </c>
       <c r="E7" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="F7" s="29" t="inlineStr">
         <is>
-          <t>Rua DOS ANJOS</t>
+          <t>Rua AREIA BRANCA</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
         <is>
-          <t>40 - R</t>
+          <t>1334 - R</t>
         </is>
       </c>
       <c r="H7" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:00</t>
+          <t>18/08/2026 15:45</t>
         </is>
       </c>
       <c r="I7" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 10:12</t>
+          <t>18/08/2026 16:50</t>
         </is>
       </c>
       <c r="J7" s="29" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
@@ -46813,7 +46813,7 @@
       </c>
       <c r="C8" s="30" t="inlineStr">
         <is>
-          <t>16983739</t>
+          <t>17130082</t>
         </is>
       </c>
       <c r="D8" s="29" t="inlineStr">
@@ -46823,87 +46823,87 @@
       </c>
       <c r="E8" s="29" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q037</t>
         </is>
       </c>
       <c r="F8" s="29" t="inlineStr">
         <is>
-          <t>Rua AREIA BRANCA</t>
+          <t>Rua LUIZ DE CAMÕES</t>
         </is>
       </c>
       <c r="G8" s="29" t="inlineStr">
         <is>
-          <t>1334 - R</t>
+          <t>01 - R</t>
         </is>
       </c>
       <c r="H8" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 15:45</t>
+          <t>25/08/2026 16:19</t>
         </is>
       </c>
       <c r="I8" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 16:50</t>
+          <t>25/08/2026 17:04</t>
         </is>
       </c>
       <c r="J8" s="29" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="B9" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C9" s="30" t="inlineStr">
         <is>
-          <t>17130082</t>
+          <t>17072167</t>
         </is>
       </c>
       <c r="D9" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>443 - KAMEL SAAD 1</t>
         </is>
       </c>
       <c r="E9" s="29" t="inlineStr">
         <is>
-          <t>Q037</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F9" s="29" t="inlineStr">
         <is>
-          <t>Rua LUIZ DE CAMÕES</t>
+          <t>Rua BERENICE MIRANDA LINO</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
         <is>
-          <t>01 - R</t>
+          <t>661 - R</t>
         </is>
       </c>
       <c r="H9" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 16:19</t>
+          <t>21/08/2026 14:53</t>
         </is>
       </c>
       <c r="I9" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 17:04</t>
+          <t>21/08/2026 15:34</t>
         </is>
       </c>
       <c r="J9" s="29" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="B10" s="29" t="inlineStr">
@@ -46913,87 +46913,87 @@
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>17072167</t>
+          <t>16908057</t>
         </is>
       </c>
       <c r="D10" s="29" t="inlineStr">
         <is>
-          <t>443 - KAMEL SAAD 1</t>
+          <t>445 - JARDIM IVONE</t>
         </is>
       </c>
       <c r="E10" s="29" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="F10" s="29" t="inlineStr">
         <is>
-          <t>Rua BERENICE MIRANDA LINO</t>
+          <t>Rua GALILEU GALILEI</t>
         </is>
       </c>
       <c r="G10" s="29" t="inlineStr">
         <is>
-          <t>661 - R</t>
+          <t>520 - 1 - TB</t>
         </is>
       </c>
       <c r="H10" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 14:53</t>
+          <t>13/08/2026 16:11</t>
         </is>
       </c>
       <c r="I10" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 15:34</t>
+          <t>13/08/2026 16:50</t>
         </is>
       </c>
       <c r="J10" s="29" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C11" s="30" t="inlineStr">
         <is>
-          <t>16908057</t>
+          <t>17067290</t>
         </is>
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>445 - JARDIM IVONE</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F11" s="29" t="inlineStr">
         <is>
-          <t>Rua GALILEU GALILEI</t>
+          <t>Rua SÃO JORGE</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
         <is>
-          <t>520 - 1 - TB</t>
+          <t>69 - R</t>
         </is>
       </c>
       <c r="H11" s="29" t="inlineStr">
         <is>
-          <t>13/08/2026 16:11</t>
+          <t>17/08/2026 10:15</t>
         </is>
       </c>
       <c r="I11" s="29" t="inlineStr">
         <is>
-          <t>13/08/2026 16:50</t>
+          <t>17/08/2026 10:54</t>
         </is>
       </c>
       <c r="J11" s="29" t="n">
@@ -47003,7 +47003,7 @@
     <row r="12">
       <c r="A12" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B12" s="29" t="inlineStr">
@@ -47013,7 +47013,7 @@
       </c>
       <c r="C12" s="30" t="inlineStr">
         <is>
-          <t>17067290</t>
+          <t>16903746</t>
         </is>
       </c>
       <c r="D12" s="29" t="inlineStr">
@@ -47023,81 +47023,81 @@
       </c>
       <c r="E12" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q003</t>
         </is>
       </c>
       <c r="F12" s="29" t="inlineStr">
         <is>
-          <t>Rua SÃO JORGE</t>
+          <t>Rua VICENTE  AZAMBUJA</t>
         </is>
       </c>
       <c r="G12" s="29" t="inlineStr">
         <is>
-          <t>69 - R</t>
+          <t>1781 - R</t>
         </is>
       </c>
       <c r="H12" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 10:15</t>
+          <t>13/08/2026 08:30</t>
         </is>
       </c>
       <c r="I12" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 10:54</t>
+          <t>13/08/2026 09:07</t>
         </is>
       </c>
       <c r="J12" s="29" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B13" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C13" s="30" t="inlineStr">
         <is>
-          <t>16903746</t>
+          <t>16874935</t>
         </is>
       </c>
       <c r="D13" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E13" s="29" t="inlineStr">
         <is>
-          <t>Q003</t>
+          <t>Q025</t>
         </is>
       </c>
       <c r="F13" s="29" t="inlineStr">
         <is>
-          <t>Rua VICENTE  AZAMBUJA</t>
+          <t>Rua RECIFE</t>
         </is>
       </c>
       <c r="G13" s="29" t="inlineStr">
         <is>
-          <t>1781 - R</t>
+          <t>332 - R</t>
         </is>
       </c>
       <c r="H13" s="29" t="inlineStr">
         <is>
-          <t>13/08/2026 08:30</t>
+          <t>12/08/2026 10:15</t>
         </is>
       </c>
       <c r="I13" s="29" t="inlineStr">
         <is>
-          <t>13/08/2026 09:07</t>
+          <t>12/08/2026 10:50</t>
         </is>
       </c>
       <c r="J13" s="29" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -47113,7 +47113,7 @@
       </c>
       <c r="C14" s="30" t="inlineStr">
         <is>
-          <t>16874935</t>
+          <t>17044818</t>
         </is>
       </c>
       <c r="D14" s="29" t="inlineStr">
@@ -47123,87 +47123,87 @@
       </c>
       <c r="E14" s="29" t="inlineStr">
         <is>
-          <t>Q025</t>
+          <t>Q036</t>
         </is>
       </c>
       <c r="F14" s="29" t="inlineStr">
         <is>
-          <t>Rua RECIFE</t>
+          <t>Rua CORINTO</t>
         </is>
       </c>
       <c r="G14" s="29" t="inlineStr">
         <is>
-          <t>332 - R</t>
+          <t>451 - R</t>
         </is>
       </c>
       <c r="H14" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 10:15</t>
+          <t>20/08/2026 16:04</t>
         </is>
       </c>
       <c r="I14" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 10:50</t>
+          <t>20/08/2026 16:37</t>
         </is>
       </c>
       <c r="J14" s="29" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="29" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Carlos Alberto Albiero</t>
         </is>
       </c>
       <c r="B15" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C15" s="30" t="inlineStr">
         <is>
-          <t>17044818</t>
+          <t>17013196</t>
         </is>
       </c>
       <c r="D15" s="29" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>409 - ANDREAZZA</t>
         </is>
       </c>
       <c r="E15" s="29" t="inlineStr">
         <is>
-          <t>Q036</t>
+          <t>Q039</t>
         </is>
       </c>
       <c r="F15" s="29" t="inlineStr">
         <is>
-          <t>Rua CORINTO</t>
+          <t>Rua AURELIO BARBOSA VAREIRO JUNIOR</t>
         </is>
       </c>
       <c r="G15" s="29" t="inlineStr">
         <is>
-          <t>451 - R</t>
+          <t>76 - 1 - TB</t>
         </is>
       </c>
       <c r="H15" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 16:04</t>
+          <t>19/08/2026 15:08</t>
         </is>
       </c>
       <c r="I15" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 16:37</t>
+          <t>19/08/2026 15:40</t>
         </is>
       </c>
       <c r="J15" s="29" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="29" t="inlineStr">
         <is>
-          <t>Carlos Alberto Albiero</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B16" s="29" t="inlineStr">
@@ -47213,47 +47213,47 @@
       </c>
       <c r="C16" s="30" t="inlineStr">
         <is>
-          <t>17013196</t>
+          <t>16910074</t>
         </is>
       </c>
       <c r="D16" s="29" t="inlineStr">
         <is>
-          <t>409 - ANDREAZZA</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E16" s="29" t="inlineStr">
         <is>
-          <t>Q039</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="F16" s="29" t="inlineStr">
         <is>
-          <t>Rua AURELIO BARBOSA VAREIRO JUNIOR</t>
+          <t>Rua CATANDUVA</t>
         </is>
       </c>
       <c r="G16" s="29" t="inlineStr">
         <is>
-          <t>76 - 1 - TB</t>
+          <t>165 - R</t>
         </is>
       </c>
       <c r="H16" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 15:08</t>
+          <t>13/08/2026 15:00</t>
         </is>
       </c>
       <c r="I16" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 15:40</t>
+          <t>13/08/2026 15:31</t>
         </is>
       </c>
       <c r="J16" s="29" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B17" s="29" t="inlineStr">
@@ -47263,87 +47263,87 @@
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>16910074</t>
+          <t>17070282</t>
         </is>
       </c>
       <c r="D17" s="29" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E17" s="29" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="F17" s="29" t="inlineStr">
         <is>
-          <t>Rua CATANDUVA</t>
+          <t>Rua BARRA VELHA</t>
         </is>
       </c>
       <c r="G17" s="29" t="inlineStr">
         <is>
-          <t>165 - R</t>
+          <t>696 - R</t>
         </is>
       </c>
       <c r="H17" s="29" t="inlineStr">
         <is>
-          <t>13/08/2026 15:00</t>
+          <t>21/08/2026 09:59</t>
         </is>
       </c>
       <c r="I17" s="29" t="inlineStr">
         <is>
-          <t>13/08/2026 15:31</t>
+          <t>21/08/2026 10:27</t>
         </is>
       </c>
       <c r="J17" s="29" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B18" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C18" s="30" t="inlineStr">
         <is>
-          <t>17070282</t>
+          <t>16928890</t>
         </is>
       </c>
       <c r="D18" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E18" s="29" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="F18" s="29" t="inlineStr">
         <is>
-          <t>Rua BARRA VELHA</t>
+          <t>Rua JOAQUIM PEREIRA TEIXEIRA</t>
         </is>
       </c>
       <c r="G18" s="29" t="inlineStr">
         <is>
-          <t>696 - R</t>
+          <t>707 - R</t>
         </is>
       </c>
       <c r="H18" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 09:59</t>
+          <t>12/08/2026 16:28</t>
         </is>
       </c>
       <c r="I18" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 10:27</t>
+          <t>12/08/2026 16:56</t>
         </is>
       </c>
       <c r="J18" s="29" t="n">
@@ -47353,22 +47353,22 @@
     <row r="19">
       <c r="A19" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="B19" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>16928890</t>
+          <t>16990895</t>
         </is>
       </c>
       <c r="D19" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E19" s="29" t="inlineStr">
@@ -47378,72 +47378,72 @@
       </c>
       <c r="F19" s="29" t="inlineStr">
         <is>
-          <t>Rua JOAQUIM PEREIRA TEIXEIRA</t>
+          <t>Rua TIETE</t>
         </is>
       </c>
       <c r="G19" s="29" t="inlineStr">
         <is>
-          <t>707 - R</t>
+          <t>513 - R</t>
         </is>
       </c>
       <c r="H19" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 16:28</t>
+          <t>17/08/2026 09:24</t>
         </is>
       </c>
       <c r="I19" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 16:56</t>
+          <t>17/08/2026 09:51</t>
         </is>
       </c>
       <c r="J19" s="29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="29" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="B20" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C20" s="30" t="inlineStr">
         <is>
-          <t>16990895</t>
+          <t>17128500</t>
         </is>
       </c>
       <c r="D20" s="29" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>443 - KAMEL SAAD 1</t>
         </is>
       </c>
       <c r="E20" s="29" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="F20" s="29" t="inlineStr">
         <is>
-          <t>Rua TIETE</t>
+          <t>Rua DAS ROSAS</t>
         </is>
       </c>
       <c r="G20" s="29" t="inlineStr">
         <is>
-          <t>513 - R</t>
+          <t>03 - R</t>
         </is>
       </c>
       <c r="H20" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:24</t>
+          <t>25/08/2026 10:11</t>
         </is>
       </c>
       <c r="I20" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:51</t>
+          <t>25/08/2026 10:38</t>
         </is>
       </c>
       <c r="J20" s="29" t="n">
@@ -47503,51 +47503,51 @@
     <row r="22">
       <c r="A22" s="29" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B22" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C22" s="30" t="inlineStr">
         <is>
-          <t>17128500</t>
+          <t>17027677</t>
         </is>
       </c>
       <c r="D22" s="29" t="inlineStr">
         <is>
-          <t>443 - KAMEL SAAD 1</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E22" s="29" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F22" s="29" t="inlineStr">
         <is>
-          <t>Rua DAS ROSAS</t>
+          <t>Rua SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="G22" s="29" t="inlineStr">
         <is>
-          <t>03 - R</t>
+          <t>20 - R</t>
         </is>
       </c>
       <c r="H22" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 10:11</t>
+          <t>18/08/2026 10:24</t>
         </is>
       </c>
       <c r="I22" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 10:38</t>
+          <t>18/08/2026 10:50</t>
         </is>
       </c>
       <c r="J22" s="29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
@@ -47653,47 +47653,47 @@
     <row r="25">
       <c r="A25" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="B25" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C25" s="30" t="inlineStr">
         <is>
-          <t>17027677</t>
+          <t>16713145</t>
         </is>
       </c>
       <c r="D25" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
       <c r="E25" s="29" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F25" s="29" t="inlineStr">
         <is>
-          <t>Rua SÃO JOÃO DEL REI</t>
+          <t>Avenida JARDIM AMERICA</t>
         </is>
       </c>
       <c r="G25" s="29" t="inlineStr">
         <is>
-          <t>20 - R</t>
+          <t>245 - R</t>
         </is>
       </c>
       <c r="H25" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 10:24</t>
+          <t>03/08/2026 09:50</t>
         </is>
       </c>
       <c r="I25" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 10:50</t>
+          <t>03/08/2026 10:16</t>
         </is>
       </c>
       <c r="J25" s="29" t="n">
@@ -47703,7 +47703,7 @@
     <row r="26">
       <c r="A26" s="29" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
       <c r="B26" s="29" t="inlineStr">
@@ -47713,47 +47713,47 @@
       </c>
       <c r="C26" s="30" t="inlineStr">
         <is>
-          <t>16713145</t>
+          <t>16956974</t>
         </is>
       </c>
       <c r="D26" s="29" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇÕES</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E26" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F26" s="29" t="inlineStr">
         <is>
-          <t>Avenida JARDIM AMERICA</t>
+          <t>Rua GENERAL AMÉRICO MARINHO LUTZ</t>
         </is>
       </c>
       <c r="G26" s="29" t="inlineStr">
         <is>
-          <t>245 - R</t>
+          <t>657 - R</t>
         </is>
       </c>
       <c r="H26" s="29" t="inlineStr">
         <is>
-          <t>03/08/2026 09:50</t>
+          <t>17/08/2026 09:40</t>
         </is>
       </c>
       <c r="I26" s="29" t="inlineStr">
         <is>
-          <t>03/08/2026 10:16</t>
+          <t>17/08/2026 10:05</t>
         </is>
       </c>
       <c r="J26" s="29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="29" t="inlineStr">
         <is>
-          <t>Cris Milene Cardenas da Silva</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B27" s="29" t="inlineStr">
@@ -47763,47 +47763,47 @@
       </c>
       <c r="C27" s="30" t="inlineStr">
         <is>
-          <t>16956974</t>
+          <t>17077037</t>
         </is>
       </c>
       <c r="D27" s="29" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
       <c r="E27" s="29" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="F27" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL AMÉRICO MARINHO LUTZ</t>
+          <t>Rua INÁCIO SUBTIL OLIVEIRA</t>
         </is>
       </c>
       <c r="G27" s="29" t="inlineStr">
         <is>
-          <t>657 - R</t>
+          <t>517 - R</t>
         </is>
       </c>
       <c r="H27" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:40</t>
+          <t>21/08/2026 08:51</t>
         </is>
       </c>
       <c r="I27" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 10:05</t>
+          <t>21/08/2026 09:14</t>
         </is>
       </c>
       <c r="J27" s="29" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
       <c r="B28" s="29" t="inlineStr">
@@ -47813,37 +47813,37 @@
       </c>
       <c r="C28" s="30" t="inlineStr">
         <is>
-          <t>17077037</t>
+          <t>17102942</t>
         </is>
       </c>
       <c r="D28" s="29" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL</t>
+          <t>403 - JARDIM UNIVERSITARIO</t>
         </is>
       </c>
       <c r="E28" s="29" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q036</t>
         </is>
       </c>
       <c r="F28" s="29" t="inlineStr">
         <is>
-          <t>Rua INÁCIO SUBTIL OLIVEIRA</t>
+          <t>Rua NELSON HUNGRIA</t>
         </is>
       </c>
       <c r="G28" s="29" t="inlineStr">
         <is>
-          <t>517 - R</t>
+          <t>194 - R</t>
         </is>
       </c>
       <c r="H28" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 08:51</t>
+          <t>24/08/2026 08:29</t>
         </is>
       </c>
       <c r="I28" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 09:14</t>
+          <t>24/08/2026 08:52</t>
         </is>
       </c>
       <c r="J28" s="29" t="n">
@@ -47853,47 +47853,47 @@
     <row r="29">
       <c r="A29" s="29" t="inlineStr">
         <is>
-          <t>Cris Milene Cardenas da Silva</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B29" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C29" s="30" t="inlineStr">
         <is>
-          <t>17102942</t>
+          <t>17071087</t>
         </is>
       </c>
       <c r="D29" s="29" t="inlineStr">
         <is>
-          <t>403 - JARDIM UNIVERSITARIO</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E29" s="29" t="inlineStr">
         <is>
-          <t>Q036</t>
+          <t>Q042</t>
         </is>
       </c>
       <c r="F29" s="29" t="inlineStr">
         <is>
-          <t>Rua NELSON HUNGRIA</t>
+          <t>Rua POLICARPO DAVILA</t>
         </is>
       </c>
       <c r="G29" s="29" t="inlineStr">
         <is>
-          <t>194 - R</t>
+          <t>769 - R</t>
         </is>
       </c>
       <c r="H29" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 08:29</t>
+          <t>21/08/2026 14:34</t>
         </is>
       </c>
       <c r="I29" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 08:52</t>
+          <t>21/08/2026 14:57</t>
         </is>
       </c>
       <c r="J29" s="29" t="n">
@@ -47903,47 +47903,47 @@
     <row r="30">
       <c r="A30" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B30" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C30" s="30" t="inlineStr">
         <is>
-          <t>16986159</t>
+          <t>16997935</t>
         </is>
       </c>
       <c r="D30" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E30" s="29" t="inlineStr">
         <is>
-          <t>Q036</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="F30" s="29" t="inlineStr">
         <is>
-          <t>Avenida ADJALMA SALDANHA</t>
+          <t>Rua CARLOS DRUMOND DE ANDRADE</t>
         </is>
       </c>
       <c r="G30" s="29" t="inlineStr">
         <is>
-          <t>873 - R</t>
+          <t>1157 - R</t>
         </is>
       </c>
       <c r="H30" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 13:15</t>
+          <t>19/08/2026 09:04</t>
         </is>
       </c>
       <c r="I30" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 13:38</t>
+          <t>19/08/2026 09:27</t>
         </is>
       </c>
       <c r="J30" s="29" t="n">
@@ -47963,7 +47963,7 @@
       </c>
       <c r="C31" s="30" t="inlineStr">
         <is>
-          <t>17071087</t>
+          <t>16986159</t>
         </is>
       </c>
       <c r="D31" s="29" t="inlineStr">
@@ -47973,27 +47973,27 @@
       </c>
       <c r="E31" s="29" t="inlineStr">
         <is>
-          <t>Q042</t>
+          <t>Q036</t>
         </is>
       </c>
       <c r="F31" s="29" t="inlineStr">
         <is>
-          <t>Rua POLICARPO DAVILA</t>
+          <t>Avenida ADJALMA SALDANHA</t>
         </is>
       </c>
       <c r="G31" s="29" t="inlineStr">
         <is>
-          <t>769 - R</t>
+          <t>873 - R</t>
         </is>
       </c>
       <c r="H31" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 14:34</t>
+          <t>18/08/2026 13:15</t>
         </is>
       </c>
       <c r="I31" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 14:57</t>
+          <t>18/08/2026 13:38</t>
         </is>
       </c>
       <c r="J31" s="29" t="n">
@@ -48003,7 +48003,7 @@
     <row r="32">
       <c r="A32" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="B32" s="29" t="inlineStr">
@@ -48013,37 +48013,37 @@
       </c>
       <c r="C32" s="30" t="inlineStr">
         <is>
-          <t>16997935</t>
+          <t>17076414</t>
         </is>
       </c>
       <c r="D32" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>402 - JARDIM MARAMBAIA</t>
         </is>
       </c>
       <c r="E32" s="29" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="F32" s="29" t="inlineStr">
         <is>
-          <t>Rua CARLOS DRUMOND DE ANDRADE</t>
+          <t>Rua WEIMAR TORRES</t>
         </is>
       </c>
       <c r="G32" s="29" t="inlineStr">
         <is>
-          <t>1157 - R</t>
+          <t>774 - R</t>
         </is>
       </c>
       <c r="H32" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:04</t>
+          <t>21/08/2026 15:30</t>
         </is>
       </c>
       <c r="I32" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:27</t>
+          <t>21/08/2026 15:53</t>
         </is>
       </c>
       <c r="J32" s="29" t="n">
@@ -48053,97 +48053,97 @@
     <row r="33">
       <c r="A33" s="29" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B33" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>17076414</t>
+          <t>17011667</t>
         </is>
       </c>
       <c r="D33" s="29" t="inlineStr">
         <is>
-          <t>402 - JARDIM MARAMBAIA</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E33" s="29" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="F33" s="29" t="inlineStr">
         <is>
-          <t>Rua WEIMAR TORRES</t>
+          <t>Rua HONOROPOLIS</t>
         </is>
       </c>
       <c r="G33" s="29" t="inlineStr">
         <is>
-          <t>774 - R</t>
+          <t>541 - R</t>
         </is>
       </c>
       <c r="H33" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 15:30</t>
+          <t>19/08/2026 08:55</t>
         </is>
       </c>
       <c r="I33" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 15:53</t>
+          <t>19/08/2026 09:17</t>
         </is>
       </c>
       <c r="J33" s="29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="29" t="inlineStr">
         <is>
-          <t>Cris Milene Cardenas da Silva</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B34" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C34" s="30" t="inlineStr">
         <is>
-          <t>17018827</t>
+          <t>17131247</t>
         </is>
       </c>
       <c r="D34" s="29" t="inlineStr">
         <is>
-          <t>403 - JARDIM UNIVERSITARIO</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E34" s="29" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F34" s="29" t="inlineStr">
         <is>
-          <t>Rua DR HELIO BRANDAO</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="G34" s="29" t="inlineStr">
         <is>
-          <t>227 - C</t>
+          <t>210 - C</t>
         </is>
       </c>
       <c r="H34" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 08:44</t>
+          <t>25/08/2026 08:43</t>
         </is>
       </c>
       <c r="I34" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:06</t>
+          <t>25/08/2026 09:05</t>
         </is>
       </c>
       <c r="J34" s="29" t="n">
@@ -48153,47 +48153,47 @@
     <row r="35">
       <c r="A35" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
       <c r="B35" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>16762598</t>
+          <t>17018827</t>
         </is>
       </c>
       <c r="D35" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>403 - JARDIM UNIVERSITARIO</t>
         </is>
       </c>
       <c r="E35" s="29" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F35" s="29" t="inlineStr">
         <is>
-          <t>Rua FRANCISCO FAUSTO MACENAS</t>
+          <t>Rua DR HELIO BRANDAO</t>
         </is>
       </c>
       <c r="G35" s="29" t="inlineStr">
         <is>
-          <t>651 - 1 - R</t>
+          <t>227 - C</t>
         </is>
       </c>
       <c r="H35" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 10:06</t>
+          <t>19/08/2026 08:44</t>
         </is>
       </c>
       <c r="I35" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 10:28</t>
+          <t>19/08/2026 09:06</t>
         </is>
       </c>
       <c r="J35" s="29" t="n">
@@ -48203,47 +48203,47 @@
     <row r="36">
       <c r="A36" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B36" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C36" s="30" t="inlineStr">
         <is>
-          <t>17148181</t>
+          <t>16762598</t>
         </is>
       </c>
       <c r="D36" s="29" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E36" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="F36" s="29" t="inlineStr">
         <is>
-          <t>Rua ARNALDO VASQUES</t>
+          <t>Rua FRANCISCO FAUSTO MACENAS</t>
         </is>
       </c>
       <c r="G36" s="29" t="inlineStr">
         <is>
-          <t>325 - R</t>
+          <t>651 - 1 - R</t>
         </is>
       </c>
       <c r="H36" s="29" t="inlineStr">
         <is>
-          <t>26/08/2026 13:43</t>
+          <t>05/08/2026 10:06</t>
         </is>
       </c>
       <c r="I36" s="29" t="inlineStr">
         <is>
-          <t>26/08/2026 14:05</t>
+          <t>05/08/2026 10:28</t>
         </is>
       </c>
       <c r="J36" s="29" t="n">
@@ -48253,47 +48253,47 @@
     <row r="37">
       <c r="A37" s="29" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B37" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C37" s="30" t="inlineStr">
         <is>
-          <t>17125360</t>
+          <t>17130213</t>
         </is>
       </c>
       <c r="D37" s="29" t="inlineStr">
         <is>
-          <t>439 - BOSQUE CARANDÁ</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E37" s="29" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F37" s="29" t="inlineStr">
         <is>
-          <t>Avenida PERPETUO SOCORRO</t>
+          <t>Rua ROSA AZUL</t>
         </is>
       </c>
       <c r="G37" s="29" t="inlineStr">
         <is>
-          <t>03 - OU</t>
+          <t>222 - R</t>
         </is>
       </c>
       <c r="H37" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:35</t>
+          <t>25/08/2026 15:33</t>
         </is>
       </c>
       <c r="I37" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:57</t>
+          <t>25/08/2026 15:55</t>
         </is>
       </c>
       <c r="J37" s="29" t="n">
@@ -48303,7 +48303,7 @@
     <row r="38">
       <c r="A38" s="29" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="B38" s="29" t="inlineStr">
@@ -48313,37 +48313,37 @@
       </c>
       <c r="C38" s="30" t="inlineStr">
         <is>
-          <t>17011667</t>
+          <t>17125360</t>
         </is>
       </c>
       <c r="D38" s="29" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>439 - BOSQUE CARANDÁ</t>
         </is>
       </c>
       <c r="E38" s="29" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="F38" s="29" t="inlineStr">
         <is>
-          <t>Rua HONOROPOLIS</t>
+          <t>Avenida PERPETUO SOCORRO</t>
         </is>
       </c>
       <c r="G38" s="29" t="inlineStr">
         <is>
-          <t>541 - R</t>
+          <t>03 - OU</t>
         </is>
       </c>
       <c r="H38" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 08:55</t>
+          <t>25/08/2026 09:35</t>
         </is>
       </c>
       <c r="I38" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:17</t>
+          <t>25/08/2026 09:57</t>
         </is>
       </c>
       <c r="J38" s="29" t="n">
@@ -48353,47 +48353,47 @@
     <row r="39">
       <c r="A39" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B39" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>17130213</t>
+          <t>17148181</t>
         </is>
       </c>
       <c r="D39" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E39" s="29" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F39" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA AZUL</t>
+          <t>Rua ARNALDO VASQUES</t>
         </is>
       </c>
       <c r="G39" s="29" t="inlineStr">
         <is>
-          <t>222 - R</t>
+          <t>325 - R</t>
         </is>
       </c>
       <c r="H39" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:33</t>
+          <t>26/08/2026 13:43</t>
         </is>
       </c>
       <c r="I39" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:55</t>
+          <t>26/08/2026 14:05</t>
         </is>
       </c>
       <c r="J39" s="29" t="n">
@@ -48403,7 +48403,7 @@
     <row r="40">
       <c r="A40" s="29" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B40" s="29" t="inlineStr">
@@ -48413,87 +48413,87 @@
       </c>
       <c r="C40" s="30" t="inlineStr">
         <is>
-          <t>17131247</t>
+          <t>17027695</t>
         </is>
       </c>
       <c r="D40" s="29" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E40" s="29" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="F40" s="29" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Rua ROSA BRANCA</t>
         </is>
       </c>
       <c r="G40" s="29" t="inlineStr">
         <is>
-          <t>210 - C</t>
+          <t>140 - R</t>
         </is>
       </c>
       <c r="H40" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 08:43</t>
+          <t>19/08/2026 08:57</t>
         </is>
       </c>
       <c r="I40" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:05</t>
+          <t>19/08/2026 09:18</t>
         </is>
       </c>
       <c r="J40" s="29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="29" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="B41" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C41" s="30" t="inlineStr">
         <is>
-          <t>16960082</t>
+          <t>17009505</t>
         </is>
       </c>
       <c r="D41" s="29" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>422 - VILA TORRES</t>
         </is>
       </c>
       <c r="E41" s="29" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="F41" s="29" t="inlineStr">
         <is>
-          <t>Rua FORTALEZA</t>
+          <t>Rua MANOEL DIAS DE PINHO</t>
         </is>
       </c>
       <c r="G41" s="29" t="inlineStr">
         <is>
-          <t>622 - R</t>
+          <t>625 - 1 - C</t>
         </is>
       </c>
       <c r="H41" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 09:32</t>
+          <t>19/08/2026 15:31</t>
         </is>
       </c>
       <c r="I41" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 09:53</t>
+          <t>19/08/2026 15:52</t>
         </is>
       </c>
       <c r="J41" s="29" t="n">
@@ -48553,47 +48553,47 @@
     <row r="43">
       <c r="A43" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="B43" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C43" s="30" t="inlineStr">
         <is>
-          <t>17027695</t>
+          <t>16804508</t>
         </is>
       </c>
       <c r="D43" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>407 - MOOCA</t>
         </is>
       </c>
       <c r="E43" s="29" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q038</t>
         </is>
       </c>
       <c r="F43" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA BRANCA</t>
+          <t>Rua CEARÁ</t>
         </is>
       </c>
       <c r="G43" s="29" t="inlineStr">
         <is>
-          <t>140 - R</t>
+          <t>01 - TB</t>
         </is>
       </c>
       <c r="H43" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 08:57</t>
+          <t>06/08/2026 15:16</t>
         </is>
       </c>
       <c r="I43" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:18</t>
+          <t>06/08/2026 15:37</t>
         </is>
       </c>
       <c r="J43" s="29" t="n">
@@ -48603,47 +48603,47 @@
     <row r="44">
       <c r="A44" s="29" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="B44" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C44" s="30" t="inlineStr">
         <is>
-          <t>16804508</t>
+          <t>16960082</t>
         </is>
       </c>
       <c r="D44" s="29" t="inlineStr">
         <is>
-          <t>407 - MOOCA</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E44" s="29" t="inlineStr">
         <is>
-          <t>Q038</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F44" s="29" t="inlineStr">
         <is>
-          <t>Rua CEARÁ</t>
+          <t>Rua FORTALEZA</t>
         </is>
       </c>
       <c r="G44" s="29" t="inlineStr">
         <is>
-          <t>01 - TB</t>
+          <t>622 - R</t>
         </is>
       </c>
       <c r="H44" s="29" t="inlineStr">
         <is>
-          <t>06/08/2026 15:16</t>
+          <t>18/08/2026 09:32</t>
         </is>
       </c>
       <c r="I44" s="29" t="inlineStr">
         <is>
-          <t>06/08/2026 15:37</t>
+          <t>18/08/2026 09:53</t>
         </is>
       </c>
       <c r="J44" s="29" t="n">
@@ -48653,7 +48653,7 @@
     <row r="45">
       <c r="A45" s="29" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B45" s="29" t="inlineStr">
@@ -48663,87 +48663,87 @@
       </c>
       <c r="C45" s="30" t="inlineStr">
         <is>
-          <t>17009505</t>
+          <t>17112709</t>
         </is>
       </c>
       <c r="D45" s="29" t="inlineStr">
         <is>
-          <t>422 - VILA TORRES</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E45" s="29" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F45" s="29" t="inlineStr">
         <is>
-          <t>Rua MANOEL DIAS DE PINHO</t>
+          <t>Rua ROSA AZUL</t>
         </is>
       </c>
       <c r="G45" s="29" t="inlineStr">
         <is>
-          <t>625 - 1 - C</t>
+          <t>295 - 1 - R</t>
         </is>
       </c>
       <c r="H45" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 15:31</t>
+          <t>24/08/2026 15:00</t>
         </is>
       </c>
       <c r="I45" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 15:52</t>
+          <t>24/08/2026 15:20</t>
         </is>
       </c>
       <c r="J45" s="29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B46" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C46" s="30" t="inlineStr">
         <is>
-          <t>16938750</t>
+          <t>16879459</t>
         </is>
       </c>
       <c r="D46" s="29" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E46" s="29" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q025</t>
         </is>
       </c>
       <c r="F46" s="29" t="inlineStr">
         <is>
-          <t>Rua SAO CRISTOVAO</t>
+          <t>Rua EPTACIO PESSOA</t>
         </is>
       </c>
       <c r="G46" s="29" t="inlineStr">
         <is>
-          <t>14 - 1 - R</t>
+          <t>245 - 1 - R</t>
         </is>
       </c>
       <c r="H46" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 09:53</t>
+          <t>12/08/2026 10:11</t>
         </is>
       </c>
       <c r="I46" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 10:13</t>
+          <t>12/08/2026 10:31</t>
         </is>
       </c>
       <c r="J46" s="29" t="n">
@@ -48753,47 +48753,47 @@
     <row r="47">
       <c r="A47" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B47" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C47" s="30" t="inlineStr">
         <is>
-          <t>16762591</t>
+          <t>16938750</t>
         </is>
       </c>
       <c r="D47" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E47" s="29" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="F47" s="29" t="inlineStr">
         <is>
-          <t>Rua ROBERTO BUENO DA SILVA</t>
+          <t>Rua SAO CRISTOVAO</t>
         </is>
       </c>
       <c r="G47" s="29" t="inlineStr">
         <is>
-          <t>486 - OU</t>
+          <t>14 - 1 - R</t>
         </is>
       </c>
       <c r="H47" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 08:45</t>
+          <t>14/08/2026 09:53</t>
         </is>
       </c>
       <c r="I47" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 09:05</t>
+          <t>14/08/2026 10:13</t>
         </is>
       </c>
       <c r="J47" s="29" t="n">
@@ -48803,47 +48803,47 @@
     <row r="48">
       <c r="A48" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B48" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C48" s="30" t="inlineStr">
         <is>
-          <t>17098947</t>
+          <t>16783019</t>
         </is>
       </c>
       <c r="D48" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E48" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F48" s="29" t="inlineStr">
         <is>
-          <t>Rua FELIPE DE BRUM</t>
+          <t>Rua MONTEVIDEO</t>
         </is>
       </c>
       <c r="G48" s="29" t="inlineStr">
         <is>
-          <t>75 - R</t>
+          <t>301 - R</t>
         </is>
       </c>
       <c r="H48" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:26</t>
+          <t>06/08/2026 16:07</t>
         </is>
       </c>
       <c r="I48" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:46</t>
+          <t>06/08/2026 16:27</t>
         </is>
       </c>
       <c r="J48" s="29" t="n">
@@ -48853,7 +48853,7 @@
     <row r="49">
       <c r="A49" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B49" s="29" t="inlineStr">
@@ -48863,37 +48863,37 @@
       </c>
       <c r="C49" s="30" t="inlineStr">
         <is>
-          <t>17112709</t>
+          <t>17098947</t>
         </is>
       </c>
       <c r="D49" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E49" s="29" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F49" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA AZUL</t>
+          <t>Rua FELIPE DE BRUM</t>
         </is>
       </c>
       <c r="G49" s="29" t="inlineStr">
         <is>
-          <t>295 - 1 - R</t>
+          <t>75 - R</t>
         </is>
       </c>
       <c r="H49" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:00</t>
+          <t>24/08/2026 09:26</t>
         </is>
       </c>
       <c r="I49" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:20</t>
+          <t>24/08/2026 09:46</t>
         </is>
       </c>
       <c r="J49" s="29" t="n">
@@ -48953,47 +48953,47 @@
     <row r="51">
       <c r="A51" s="29" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B51" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C51" s="30" t="inlineStr">
         <is>
-          <t>16879459</t>
+          <t>16762591</t>
         </is>
       </c>
       <c r="D51" s="29" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E51" s="29" t="inlineStr">
         <is>
-          <t>Q025</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="F51" s="29" t="inlineStr">
         <is>
-          <t>Rua EPTACIO PESSOA</t>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
         </is>
       </c>
       <c r="G51" s="29" t="inlineStr">
         <is>
-          <t>245 - 1 - R</t>
+          <t>486 - OU</t>
         </is>
       </c>
       <c r="H51" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 10:11</t>
+          <t>05/08/2026 08:45</t>
         </is>
       </c>
       <c r="I51" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 10:31</t>
+          <t>05/08/2026 09:05</t>
         </is>
       </c>
       <c r="J51" s="29" t="n">
@@ -49003,51 +49003,51 @@
     <row r="52">
       <c r="A52" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="B52" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C52" s="30" t="inlineStr">
         <is>
-          <t>16783019</t>
+          <t>16758244</t>
         </is>
       </c>
       <c r="D52" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
       <c r="E52" s="29" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="F52" s="29" t="inlineStr">
         <is>
-          <t>Rua MONTEVIDEO</t>
+          <t>Avenida PROCURADOR DR. WILSON DIAS DE PINHO</t>
         </is>
       </c>
       <c r="G52" s="29" t="inlineStr">
         <is>
-          <t>301 - R</t>
+          <t>175 - 1 - C</t>
         </is>
       </c>
       <c r="H52" s="29" t="inlineStr">
         <is>
-          <t>06/08/2026 16:07</t>
+          <t>05/08/2026 07:41</t>
         </is>
       </c>
       <c r="I52" s="29" t="inlineStr">
         <is>
-          <t>06/08/2026 16:27</t>
+          <t>05/08/2026 08:00</t>
         </is>
       </c>
       <c r="J52" s="29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53">
@@ -49103,47 +49103,47 @@
     <row r="54">
       <c r="A54" s="29" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="B54" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C54" s="30" t="inlineStr">
         <is>
-          <t>17068744</t>
+          <t>16947422</t>
         </is>
       </c>
       <c r="D54" s="29" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇÕES</t>
+          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E54" s="29" t="inlineStr">
         <is>
-          <t>Q037</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="F54" s="29" t="inlineStr">
         <is>
-          <t>Rua CORONEL PONCE</t>
+          <t>Avenida BELMIRO DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="G54" s="29" t="inlineStr">
         <is>
-          <t>04 - OU</t>
+          <t>2727 - R</t>
         </is>
       </c>
       <c r="H54" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 15:05</t>
+          <t>14/08/2026 08:56</t>
         </is>
       </c>
       <c r="I54" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 15:24</t>
+          <t>14/08/2026 09:15</t>
         </is>
       </c>
       <c r="J54" s="29" t="n">
@@ -49153,7 +49153,7 @@
     <row r="55">
       <c r="A55" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B55" s="29" t="inlineStr">
@@ -49163,37 +49163,37 @@
       </c>
       <c r="C55" s="30" t="inlineStr">
         <is>
-          <t>17098960</t>
+          <t>16759239</t>
         </is>
       </c>
       <c r="D55" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E55" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="F55" s="29" t="inlineStr">
         <is>
-          <t>Avenida COMANDANTE CARDOSO</t>
+          <t>Rua AEROPORTO VIRACOPOS</t>
         </is>
       </c>
       <c r="G55" s="29" t="inlineStr">
         <is>
-          <t>360 - 1 - R</t>
+          <t>920 - 1 - R</t>
         </is>
       </c>
       <c r="H55" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:24</t>
+          <t>05/08/2026 15:01</t>
         </is>
       </c>
       <c r="I55" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:43</t>
+          <t>05/08/2026 15:20</t>
         </is>
       </c>
       <c r="J55" s="29" t="n">
@@ -49203,47 +49203,47 @@
     <row r="56">
       <c r="A56" s="29" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B56" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C56" s="30" t="inlineStr">
         <is>
-          <t>16947422</t>
+          <t>17098960</t>
         </is>
       </c>
       <c r="D56" s="29" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E56" s="29" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F56" s="29" t="inlineStr">
         <is>
-          <t>Avenida BELMIRO DE ALBUQUERQUE</t>
+          <t>Avenida COMANDANTE CARDOSO</t>
         </is>
       </c>
       <c r="G56" s="29" t="inlineStr">
         <is>
-          <t>2727 - R</t>
+          <t>360 - 1 - R</t>
         </is>
       </c>
       <c r="H56" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 08:56</t>
+          <t>24/08/2026 15:24</t>
         </is>
       </c>
       <c r="I56" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 09:15</t>
+          <t>24/08/2026 15:43</t>
         </is>
       </c>
       <c r="J56" s="29" t="n">
@@ -49253,47 +49253,47 @@
     <row r="57">
       <c r="A57" s="29" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B57" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C57" s="30" t="inlineStr">
         <is>
-          <t>16759717</t>
+          <t>17066233</t>
         </is>
       </c>
       <c r="D57" s="29" t="inlineStr">
         <is>
-          <t>421 - JARDIM IPANEMA</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E57" s="29" t="inlineStr">
         <is>
-          <t>Q035</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="F57" s="29" t="inlineStr">
         <is>
-          <t>Rua BALTAZAR SALDANHA</t>
+          <t>Rua CAPÃO BONITO</t>
         </is>
       </c>
       <c r="G57" s="29" t="inlineStr">
         <is>
-          <t>779 - OU</t>
+          <t>191 - R</t>
         </is>
       </c>
       <c r="H57" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 09:03</t>
+          <t>17/08/2026 09:01</t>
         </is>
       </c>
       <c r="I57" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 09:22</t>
+          <t>17/08/2026 09:20</t>
         </is>
       </c>
       <c r="J57" s="29" t="n">
@@ -49303,7 +49303,7 @@
     <row r="58">
       <c r="A58" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="B58" s="29" t="inlineStr">
@@ -49313,37 +49313,37 @@
       </c>
       <c r="C58" s="30" t="inlineStr">
         <is>
-          <t>16759239</t>
+          <t>16759717</t>
         </is>
       </c>
       <c r="D58" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>421 - JARDIM IPANEMA</t>
         </is>
       </c>
       <c r="E58" s="29" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q035</t>
         </is>
       </c>
       <c r="F58" s="29" t="inlineStr">
         <is>
-          <t>Rua AEROPORTO VIRACOPOS</t>
+          <t>Rua BALTAZAR SALDANHA</t>
         </is>
       </c>
       <c r="G58" s="29" t="inlineStr">
         <is>
-          <t>920 - 1 - R</t>
+          <t>779 - OU</t>
         </is>
       </c>
       <c r="H58" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 15:01</t>
+          <t>05/08/2026 09:03</t>
         </is>
       </c>
       <c r="I58" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 15:20</t>
+          <t>05/08/2026 09:22</t>
         </is>
       </c>
       <c r="J58" s="29" t="n">
@@ -49363,7 +49363,7 @@
       </c>
       <c r="C59" s="30" t="inlineStr">
         <is>
-          <t>16758244</t>
+          <t>17068744</t>
         </is>
       </c>
       <c r="D59" s="29" t="inlineStr">
@@ -49373,27 +49373,27 @@
       </c>
       <c r="E59" s="29" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q037</t>
         </is>
       </c>
       <c r="F59" s="29" t="inlineStr">
         <is>
-          <t>Avenida PROCURADOR DR. WILSON DIAS DE PINHO</t>
+          <t>Rua CORONEL PONCE</t>
         </is>
       </c>
       <c r="G59" s="29" t="inlineStr">
         <is>
-          <t>175 - 1 - C</t>
+          <t>04 - OU</t>
         </is>
       </c>
       <c r="H59" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 07:41</t>
+          <t>21/08/2026 15:05</t>
         </is>
       </c>
       <c r="I59" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 08:00</t>
+          <t>21/08/2026 15:24</t>
         </is>
       </c>
       <c r="J59" s="29" t="n">
@@ -49403,7 +49403,7 @@
     <row r="60">
       <c r="A60" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B60" s="29" t="inlineStr">
@@ -49413,7 +49413,7 @@
       </c>
       <c r="C60" s="30" t="inlineStr">
         <is>
-          <t>17066233</t>
+          <t>17130027</t>
         </is>
       </c>
       <c r="D60" s="29" t="inlineStr">
@@ -49423,77 +49423,77 @@
       </c>
       <c r="E60" s="29" t="inlineStr">
         <is>
-          <t>Q005</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="F60" s="29" t="inlineStr">
         <is>
-          <t>Rua CAPÃO BONITO</t>
+          <t>Rua BARRA VELHA</t>
         </is>
       </c>
       <c r="G60" s="29" t="inlineStr">
         <is>
-          <t>191 - R</t>
+          <t>1154 - R</t>
         </is>
       </c>
       <c r="H60" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:01</t>
+          <t>25/08/2026 09:31</t>
         </is>
       </c>
       <c r="I60" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:20</t>
+          <t>25/08/2026 09:49</t>
         </is>
       </c>
       <c r="J60" s="29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="B61" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C61" s="30" t="inlineStr">
         <is>
-          <t>17092097</t>
+          <t>16935897</t>
         </is>
       </c>
       <c r="D61" s="29" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>417 - CENTRO 3</t>
         </is>
       </c>
       <c r="E61" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F61" s="29" t="inlineStr">
         <is>
-          <t>Rua ARNALDO VASQUES</t>
+          <t>Avenida PRESIDENTE VARGAS</t>
         </is>
       </c>
       <c r="G61" s="29" t="inlineStr">
         <is>
-          <t>347 - R</t>
+          <t>725 - OU</t>
         </is>
       </c>
       <c r="H61" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:00</t>
+          <t>14/08/2026 09:40</t>
         </is>
       </c>
       <c r="I61" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:18</t>
+          <t>14/08/2026 09:58</t>
         </is>
       </c>
       <c r="J61" s="29" t="n">
@@ -49503,7 +49503,7 @@
     <row r="62">
       <c r="A62" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B62" s="29" t="inlineStr">
@@ -49513,37 +49513,37 @@
       </c>
       <c r="C62" s="30" t="inlineStr">
         <is>
-          <t>17130027</t>
+          <t>17092097</t>
         </is>
       </c>
       <c r="D62" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E62" s="29" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F62" s="29" t="inlineStr">
         <is>
-          <t>Rua BARRA VELHA</t>
+          <t>Rua ARNALDO VASQUES</t>
         </is>
       </c>
       <c r="G62" s="29" t="inlineStr">
         <is>
-          <t>1154 - R</t>
+          <t>347 - R</t>
         </is>
       </c>
       <c r="H62" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:31</t>
+          <t>24/08/2026 09:00</t>
         </is>
       </c>
       <c r="I62" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:49</t>
+          <t>24/08/2026 09:18</t>
         </is>
       </c>
       <c r="J62" s="29" t="n">
@@ -49553,47 +49553,47 @@
     <row r="63">
       <c r="A63" s="29" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B63" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C63" s="30" t="inlineStr">
         <is>
-          <t>17043615</t>
+          <t>17034408</t>
         </is>
       </c>
       <c r="D63" s="29" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E63" s="29" t="inlineStr">
         <is>
-          <t>Q035</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F63" s="29" t="inlineStr">
         <is>
-          <t>Rua FELIPE DE BRUM</t>
+          <t>Rua JABAQUARA</t>
         </is>
       </c>
       <c r="G63" s="29" t="inlineStr">
         <is>
-          <t>900 - R</t>
+          <t>1370 - 4 - R</t>
         </is>
       </c>
       <c r="H63" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 14:30</t>
+          <t>19/08/2026 10:05</t>
         </is>
       </c>
       <c r="I63" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 14:48</t>
+          <t>19/08/2026 10:23</t>
         </is>
       </c>
       <c r="J63" s="29" t="n">
@@ -49603,7 +49603,7 @@
     <row r="64">
       <c r="A64" s="29" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B64" s="29" t="inlineStr">
@@ -49613,12 +49613,12 @@
       </c>
       <c r="C64" s="30" t="inlineStr">
         <is>
-          <t>16758314</t>
+          <t>17051418</t>
         </is>
       </c>
       <c r="D64" s="29" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇÕES</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E64" s="29" t="inlineStr">
@@ -49628,22 +49628,22 @@
       </c>
       <c r="F64" s="29" t="inlineStr">
         <is>
-          <t>Rua CAMANDANTE LINCON PAIVA</t>
+          <t>Rua AFONSO DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="G64" s="29" t="inlineStr">
         <is>
-          <t>637 - C</t>
+          <t>231 - 3 - R</t>
         </is>
       </c>
       <c r="H64" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 16:25</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="I64" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 16:43</t>
+          <t>19/08/2026 14:36</t>
         </is>
       </c>
       <c r="J64" s="29" t="n">
@@ -49653,47 +49653,47 @@
     <row r="65">
       <c r="A65" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B65" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C65" s="30" t="inlineStr">
         <is>
-          <t>17051418</t>
+          <t>16986947</t>
         </is>
       </c>
       <c r="D65" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>420 - FERROVIARIA</t>
         </is>
       </c>
       <c r="E65" s="29" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="F65" s="29" t="inlineStr">
         <is>
-          <t>Rua AFONSO DE ALBUQUERQUE</t>
+          <t>Beco PROJETADA 06 FERROVIARIA</t>
         </is>
       </c>
       <c r="G65" s="29" t="inlineStr">
         <is>
-          <t>231 - 3 - R</t>
+          <t>113 - R</t>
         </is>
       </c>
       <c r="H65" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 14:18</t>
+          <t>18/08/2026 08:15</t>
         </is>
       </c>
       <c r="I65" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 14:36</t>
+          <t>18/08/2026 08:33</t>
         </is>
       </c>
       <c r="J65" s="29" t="n">
@@ -49703,47 +49703,47 @@
     <row r="66">
       <c r="A66" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="B66" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C66" s="30" t="inlineStr">
         <is>
-          <t>16986947</t>
+          <t>16758314</t>
         </is>
       </c>
       <c r="D66" s="29" t="inlineStr">
         <is>
-          <t>420 - FERROVIARIA</t>
+          <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
       <c r="E66" s="29" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="F66" s="29" t="inlineStr">
         <is>
-          <t>Beco PROJETADA 06 FERROVIARIA</t>
+          <t>Rua CAMANDANTE LINCON PAIVA</t>
         </is>
       </c>
       <c r="G66" s="29" t="inlineStr">
         <is>
-          <t>113 - R</t>
+          <t>637 - C</t>
         </is>
       </c>
       <c r="H66" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 08:15</t>
+          <t>05/08/2026 16:25</t>
         </is>
       </c>
       <c r="I66" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 08:33</t>
+          <t>05/08/2026 16:43</t>
         </is>
       </c>
       <c r="J66" s="29" t="n">
@@ -49763,37 +49763,37 @@
       </c>
       <c r="C67" s="30" t="inlineStr">
         <is>
-          <t>17034408</t>
+          <t>16910075</t>
         </is>
       </c>
       <c r="D67" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E67" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="F67" s="29" t="inlineStr">
         <is>
-          <t>Rua JABAQUARA</t>
+          <t>Rua CATANDUVA</t>
         </is>
       </c>
       <c r="G67" s="29" t="inlineStr">
         <is>
-          <t>1370 - 4 - R</t>
+          <t>490 - R</t>
         </is>
       </c>
       <c r="H67" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:05</t>
+          <t>13/08/2026 15:31</t>
         </is>
       </c>
       <c r="I67" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:23</t>
+          <t>13/08/2026 15:49</t>
         </is>
       </c>
       <c r="J67" s="29" t="n">
@@ -49803,7 +49803,7 @@
     <row r="68">
       <c r="A68" s="29" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B68" s="29" t="inlineStr">
@@ -49813,37 +49813,37 @@
       </c>
       <c r="C68" s="30" t="inlineStr">
         <is>
-          <t>16935897</t>
+          <t>16879448</t>
         </is>
       </c>
       <c r="D68" s="29" t="inlineStr">
         <is>
-          <t>417 - CENTRO 3</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E68" s="29" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q025</t>
         </is>
       </c>
       <c r="F68" s="29" t="inlineStr">
         <is>
-          <t>Avenida PRESIDENTE VARGAS</t>
+          <t>Rua MODESTO DAUZACKER</t>
         </is>
       </c>
       <c r="G68" s="29" t="inlineStr">
         <is>
-          <t>725 - OU</t>
+          <t>62 - 1 - R</t>
         </is>
       </c>
       <c r="H68" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 09:40</t>
+          <t>12/08/2026 09:07</t>
         </is>
       </c>
       <c r="I68" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 09:58</t>
+          <t>12/08/2026 09:25</t>
         </is>
       </c>
       <c r="J68" s="29" t="n">
@@ -49863,7 +49863,7 @@
       </c>
       <c r="C69" s="30" t="inlineStr">
         <is>
-          <t>16879448</t>
+          <t>17043615</t>
         </is>
       </c>
       <c r="D69" s="29" t="inlineStr">
@@ -49873,27 +49873,27 @@
       </c>
       <c r="E69" s="29" t="inlineStr">
         <is>
-          <t>Q025</t>
+          <t>Q035</t>
         </is>
       </c>
       <c r="F69" s="29" t="inlineStr">
         <is>
-          <t>Rua MODESTO DAUZACKER</t>
+          <t>Rua FELIPE DE BRUM</t>
         </is>
       </c>
       <c r="G69" s="29" t="inlineStr">
         <is>
-          <t>62 - 1 - R</t>
+          <t>900 - R</t>
         </is>
       </c>
       <c r="H69" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 09:07</t>
+          <t>20/08/2026 14:30</t>
         </is>
       </c>
       <c r="I69" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 09:25</t>
+          <t>20/08/2026 14:48</t>
         </is>
       </c>
       <c r="J69" s="29" t="n">
@@ -49903,97 +49903,97 @@
     <row r="70">
       <c r="A70" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
       <c r="B70" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>16910075</t>
+          <t>17133115</t>
         </is>
       </c>
       <c r="D70" s="29" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>412 - COHAB</t>
         </is>
       </c>
       <c r="E70" s="29" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="F70" s="29" t="inlineStr">
         <is>
-          <t>Rua CATANDUVA</t>
+          <t>Rua VALENCIO DE BRUM</t>
         </is>
       </c>
       <c r="G70" s="29" t="inlineStr">
         <is>
-          <t>490 - R</t>
+          <t>536 - R</t>
         </is>
       </c>
       <c r="H70" s="29" t="inlineStr">
         <is>
-          <t>13/08/2026 15:31</t>
+          <t>25/08/2026 09:33</t>
         </is>
       </c>
       <c r="I70" s="29" t="inlineStr">
         <is>
-          <t>13/08/2026 15:49</t>
+          <t>25/08/2026 09:50</t>
         </is>
       </c>
       <c r="J70" s="29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="29" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="B71" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C71" s="30" t="inlineStr">
         <is>
-          <t>17043629</t>
+          <t>16960075</t>
         </is>
       </c>
       <c r="D71" s="29" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>443 - KAMEL SAAD 1</t>
         </is>
       </c>
       <c r="E71" s="29" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F71" s="29" t="inlineStr">
         <is>
-          <t>Rua ARAPONGAS</t>
+          <t>Rua SALIM DERZI</t>
         </is>
       </c>
       <c r="G71" s="29" t="inlineStr">
         <is>
-          <t>142 - R</t>
+          <t>58 - R</t>
         </is>
       </c>
       <c r="H71" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 15:52</t>
+          <t>17/08/2026 15:47</t>
         </is>
       </c>
       <c r="I71" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 16:09</t>
+          <t>17/08/2026 16:04</t>
         </is>
       </c>
       <c r="J71" s="29" t="n">
@@ -50013,7 +50013,7 @@
       </c>
       <c r="C72" s="30" t="inlineStr">
         <is>
-          <t>17072136</t>
+          <t>16960061</t>
         </is>
       </c>
       <c r="D72" s="29" t="inlineStr">
@@ -50023,27 +50023,27 @@
       </c>
       <c r="E72" s="29" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F72" s="29" t="inlineStr">
         <is>
-          <t>Rua TOMBADOR</t>
+          <t>Rua SALIM DERZI</t>
         </is>
       </c>
       <c r="G72" s="29" t="inlineStr">
         <is>
-          <t>684 - R</t>
+          <t>118 - R</t>
         </is>
       </c>
       <c r="H72" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 10:12</t>
+          <t>17/08/2026 10:37</t>
         </is>
       </c>
       <c r="I72" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 10:29</t>
+          <t>17/08/2026 10:54</t>
         </is>
       </c>
       <c r="J72" s="29" t="n">
@@ -50053,47 +50053,47 @@
     <row r="73">
       <c r="A73" s="29" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B73" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C73" s="30" t="inlineStr">
         <is>
-          <t>16960075</t>
+          <t>17073314</t>
         </is>
       </c>
       <c r="D73" s="29" t="inlineStr">
         <is>
-          <t>443 - KAMEL SAAD 1</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E73" s="29" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F73" s="29" t="inlineStr">
         <is>
-          <t>Rua SALIM DERZI</t>
+          <t>Avenida ANTONIO JOAO</t>
         </is>
       </c>
       <c r="G73" s="29" t="inlineStr">
         <is>
-          <t>58 - R</t>
+          <t>1371 - OU</t>
         </is>
       </c>
       <c r="H73" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 15:47</t>
+          <t>20/08/2026 15:23</t>
         </is>
       </c>
       <c r="I73" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 16:04</t>
+          <t>20/08/2026 15:40</t>
         </is>
       </c>
       <c r="J73" s="29" t="n">
@@ -50103,7 +50103,7 @@
     <row r="74">
       <c r="A74" s="29" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B74" s="29" t="inlineStr">
@@ -50113,37 +50113,37 @@
       </c>
       <c r="C74" s="30" t="inlineStr">
         <is>
-          <t>17133115</t>
+          <t>17098963</t>
         </is>
       </c>
       <c r="D74" s="29" t="inlineStr">
         <is>
-          <t>412 - COHAB</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E74" s="29" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F74" s="29" t="inlineStr">
         <is>
-          <t>Rua VALENCIO DE BRUM</t>
+          <t>Rua ARINO MOREIRA</t>
         </is>
       </c>
       <c r="G74" s="29" t="inlineStr">
         <is>
-          <t>536 - R</t>
+          <t>39 - R</t>
         </is>
       </c>
       <c r="H74" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:33</t>
+          <t>24/08/2026 15:46</t>
         </is>
       </c>
       <c r="I74" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:50</t>
+          <t>24/08/2026 16:03</t>
         </is>
       </c>
       <c r="J74" s="29" t="n">
@@ -50153,47 +50153,47 @@
     <row r="75">
       <c r="A75" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B75" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C75" s="30" t="inlineStr">
         <is>
-          <t>17098963</t>
+          <t>16910076</t>
         </is>
       </c>
       <c r="D75" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E75" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="F75" s="29" t="inlineStr">
         <is>
-          <t>Rua ARINO MOREIRA</t>
+          <t>Rua CATANDUVA</t>
         </is>
       </c>
       <c r="G75" s="29" t="inlineStr">
         <is>
-          <t>39 - R</t>
+          <t>166 - R</t>
         </is>
       </c>
       <c r="H75" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:46</t>
+          <t>13/08/2026 15:49</t>
         </is>
       </c>
       <c r="I75" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 16:03</t>
+          <t>13/08/2026 16:06</t>
         </is>
       </c>
       <c r="J75" s="29" t="n">
@@ -50203,47 +50203,47 @@
     <row r="76">
       <c r="A76" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B76" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C76" s="30" t="inlineStr">
         <is>
-          <t>16904092</t>
+          <t>16757326</t>
         </is>
       </c>
       <c r="D76" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E76" s="29" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="F76" s="29" t="inlineStr">
         <is>
-          <t>Rua SÃO JOÃO DEL REI</t>
+          <t>Rua RECIFE</t>
         </is>
       </c>
       <c r="G76" s="29" t="inlineStr">
         <is>
-          <t>300 - R</t>
+          <t>168 - R</t>
         </is>
       </c>
       <c r="H76" s="29" t="inlineStr">
         <is>
-          <t>13/08/2026 15:14</t>
+          <t>05/08/2026 14:36</t>
         </is>
       </c>
       <c r="I76" s="29" t="inlineStr">
         <is>
-          <t>13/08/2026 15:31</t>
+          <t>05/08/2026 14:53</t>
         </is>
       </c>
       <c r="J76" s="29" t="n">
@@ -50253,47 +50253,47 @@
     <row r="77">
       <c r="A77" s="29" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B77" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C77" s="30" t="inlineStr">
         <is>
-          <t>16757326</t>
+          <t>16760781</t>
         </is>
       </c>
       <c r="D77" s="29" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E77" s="29" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F77" s="29" t="inlineStr">
         <is>
-          <t>Rua RECIFE</t>
+          <t>Rua JOAQUIM PEREIRA TEIXEIRA</t>
         </is>
       </c>
       <c r="G77" s="29" t="inlineStr">
         <is>
-          <t>168 - R</t>
+          <t>355 - 1 - R</t>
         </is>
       </c>
       <c r="H77" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 14:36</t>
+          <t>05/08/2026 13:52</t>
         </is>
       </c>
       <c r="I77" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 14:53</t>
+          <t>05/08/2026 14:09</t>
         </is>
       </c>
       <c r="J77" s="29" t="n">
@@ -50303,47 +50303,47 @@
     <row r="78">
       <c r="A78" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B78" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C78" s="30" t="inlineStr">
         <is>
-          <t>16760781</t>
+          <t>16971696</t>
         </is>
       </c>
       <c r="D78" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E78" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="F78" s="29" t="inlineStr">
         <is>
-          <t>Rua JOAQUIM PEREIRA TEIXEIRA</t>
+          <t>Rua TENENTE SAMUEL DE ALMEIDA</t>
         </is>
       </c>
       <c r="G78" s="29" t="inlineStr">
         <is>
-          <t>355 - 1 - R</t>
+          <t>630 - 1 - R</t>
         </is>
       </c>
       <c r="H78" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 13:52</t>
+          <t>17/08/2026 10:58</t>
         </is>
       </c>
       <c r="I78" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 14:09</t>
+          <t>17/08/2026 11:15</t>
         </is>
       </c>
       <c r="J78" s="29" t="n">
@@ -50353,7 +50353,7 @@
     <row r="79">
       <c r="A79" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B79" s="29" t="inlineStr">
@@ -50363,37 +50363,37 @@
       </c>
       <c r="C79" s="30" t="inlineStr">
         <is>
-          <t>17022532</t>
+          <t>17064916</t>
         </is>
       </c>
       <c r="D79" s="29" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E79" s="29" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="F79" s="29" t="inlineStr">
         <is>
-          <t>Rua MARINGA</t>
+          <t>Rua RIACHO DOCE</t>
         </is>
       </c>
       <c r="G79" s="29" t="inlineStr">
         <is>
-          <t>807 - R</t>
+          <t>78 - R</t>
         </is>
       </c>
       <c r="H79" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:53</t>
+          <t>18/08/2026 14:00</t>
         </is>
       </c>
       <c r="I79" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 10:10</t>
+          <t>18/08/2026 14:17</t>
         </is>
       </c>
       <c r="J79" s="29" t="n">
@@ -50403,7 +50403,7 @@
     <row r="80">
       <c r="A80" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
       <c r="B80" s="29" t="inlineStr">
@@ -50413,37 +50413,37 @@
       </c>
       <c r="C80" s="30" t="inlineStr">
         <is>
-          <t>17070288</t>
+          <t>16881755</t>
         </is>
       </c>
       <c r="D80" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>406 - JARDIM PRIMAVERA</t>
         </is>
       </c>
       <c r="E80" s="29" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="F80" s="29" t="inlineStr">
         <is>
-          <t>Rua JABAQUARA</t>
+          <t>Rua ELOAH VIEIRA DA SILVA</t>
         </is>
       </c>
       <c r="G80" s="29" t="inlineStr">
         <is>
-          <t>1490 - C</t>
+          <t>26 - 2 - TB</t>
         </is>
       </c>
       <c r="H80" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 15:07</t>
+          <t>12/08/2026 16:12</t>
         </is>
       </c>
       <c r="I80" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 15:24</t>
+          <t>12/08/2026 16:29</t>
         </is>
       </c>
       <c r="J80" s="29" t="n">
@@ -50463,37 +50463,37 @@
       </c>
       <c r="C81" s="30" t="inlineStr">
         <is>
-          <t>16910076</t>
+          <t>16739131</t>
         </is>
       </c>
       <c r="D81" s="29" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E81" s="29" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="F81" s="29" t="inlineStr">
         <is>
-          <t>Rua CATANDUVA</t>
+          <t>Rua BARRA BONITA</t>
         </is>
       </c>
       <c r="G81" s="29" t="inlineStr">
         <is>
-          <t>166 - R</t>
+          <t>50 - R</t>
         </is>
       </c>
       <c r="H81" s="29" t="inlineStr">
         <is>
-          <t>13/08/2026 15:49</t>
+          <t>04/08/2026 15:37</t>
         </is>
       </c>
       <c r="I81" s="29" t="inlineStr">
         <is>
-          <t>13/08/2026 16:06</t>
+          <t>04/08/2026 15:54</t>
         </is>
       </c>
       <c r="J81" s="29" t="n">
@@ -50503,47 +50503,47 @@
     <row r="82">
       <c r="A82" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="B82" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C82" s="30" t="inlineStr">
         <is>
-          <t>16739131</t>
+          <t>17014581</t>
         </is>
       </c>
       <c r="D82" s="29" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>433 - ÁREA A - RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E82" s="29" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F82" s="29" t="inlineStr">
         <is>
-          <t>Rua BARRA BONITA</t>
+          <t>Rua GUARANTA</t>
         </is>
       </c>
       <c r="G82" s="29" t="inlineStr">
         <is>
-          <t>50 - R</t>
+          <t>295 - 1 - TB</t>
         </is>
       </c>
       <c r="H82" s="29" t="inlineStr">
         <is>
-          <t>04/08/2026 15:37</t>
+          <t>19/08/2026 09:45</t>
         </is>
       </c>
       <c r="I82" s="29" t="inlineStr">
         <is>
-          <t>04/08/2026 15:54</t>
+          <t>19/08/2026 10:02</t>
         </is>
       </c>
       <c r="J82" s="29" t="n">
@@ -50553,47 +50553,47 @@
     <row r="83">
       <c r="A83" s="29" t="inlineStr">
         <is>
-          <t>Raquel Ortiz dos Santos</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B83" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C83" s="30" t="inlineStr">
         <is>
-          <t>16881755</t>
+          <t>17043629</t>
         </is>
       </c>
       <c r="D83" s="29" t="inlineStr">
         <is>
-          <t>406 - JARDIM PRIMAVERA</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E83" s="29" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="F83" s="29" t="inlineStr">
         <is>
-          <t>Rua ELOAH VIEIRA DA SILVA</t>
+          <t>Rua ARAPONGAS</t>
         </is>
       </c>
       <c r="G83" s="29" t="inlineStr">
         <is>
-          <t>26 - 2 - TB</t>
+          <t>142 - R</t>
         </is>
       </c>
       <c r="H83" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 16:12</t>
+          <t>20/08/2026 15:52</t>
         </is>
       </c>
       <c r="I83" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 16:29</t>
+          <t>20/08/2026 16:09</t>
         </is>
       </c>
       <c r="J83" s="29" t="n">
@@ -50603,47 +50603,47 @@
     <row r="84">
       <c r="A84" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B84" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C84" s="30" t="inlineStr">
         <is>
-          <t>16971696</t>
+          <t>17027724</t>
         </is>
       </c>
       <c r="D84" s="29" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E84" s="29" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q026</t>
         </is>
       </c>
       <c r="F84" s="29" t="inlineStr">
         <is>
-          <t>Rua TENENTE SAMUEL DE ALMEIDA</t>
+          <t>Rua ROSA VERMELHA JDR</t>
         </is>
       </c>
       <c r="G84" s="29" t="inlineStr">
         <is>
-          <t>630 - 1 - R</t>
+          <t>292 - R</t>
         </is>
       </c>
       <c r="H84" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 10:58</t>
+          <t>20/08/2026 09:26</t>
         </is>
       </c>
       <c r="I84" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 11:15</t>
+          <t>20/08/2026 09:43</t>
         </is>
       </c>
       <c r="J84" s="29" t="n">
@@ -50653,47 +50653,47 @@
     <row r="85">
       <c r="A85" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B85" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C85" s="30" t="inlineStr">
         <is>
-          <t>17027724</t>
+          <t>17070286</t>
         </is>
       </c>
       <c r="D85" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E85" s="29" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F85" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA VERMELHA JDR</t>
+          <t>Rua GUAÍBA</t>
         </is>
       </c>
       <c r="G85" s="29" t="inlineStr">
         <is>
-          <t>292 - R</t>
+          <t>1262 - C</t>
         </is>
       </c>
       <c r="H85" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 09:26</t>
+          <t>21/08/2026 14:40</t>
         </is>
       </c>
       <c r="I85" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 09:43</t>
+          <t>21/08/2026 14:57</t>
         </is>
       </c>
       <c r="J85" s="29" t="n">
@@ -50703,47 +50703,47 @@
     <row r="86">
       <c r="A86" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B86" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C86" s="30" t="inlineStr">
         <is>
-          <t>17073314</t>
+          <t>17070288</t>
         </is>
       </c>
       <c r="D86" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E86" s="29" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="F86" s="29" t="inlineStr">
         <is>
-          <t>Avenida ANTONIO JOAO</t>
+          <t>Rua JABAQUARA</t>
         </is>
       </c>
       <c r="G86" s="29" t="inlineStr">
         <is>
-          <t>1371 - OU</t>
+          <t>1490 - C</t>
         </is>
       </c>
       <c r="H86" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 15:23</t>
+          <t>21/08/2026 15:07</t>
         </is>
       </c>
       <c r="I86" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 15:40</t>
+          <t>21/08/2026 15:24</t>
         </is>
       </c>
       <c r="J86" s="29" t="n">
@@ -50753,47 +50753,47 @@
     <row r="87">
       <c r="A87" s="29" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B87" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C87" s="30" t="inlineStr">
         <is>
-          <t>17014581</t>
+          <t>17022532</t>
         </is>
       </c>
       <c r="D87" s="29" t="inlineStr">
         <is>
-          <t>433 - ÁREA A - RESIDENCIAL PONTA PORÃ 1</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E87" s="29" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F87" s="29" t="inlineStr">
         <is>
-          <t>Rua GUARANTA</t>
+          <t>Rua MARINGA</t>
         </is>
       </c>
       <c r="G87" s="29" t="inlineStr">
         <is>
-          <t>295 - 1 - TB</t>
+          <t>807 - R</t>
         </is>
       </c>
       <c r="H87" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:45</t>
+          <t>17/08/2026 09:53</t>
         </is>
       </c>
       <c r="I87" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:02</t>
+          <t>17/08/2026 10:10</t>
         </is>
       </c>
       <c r="J87" s="29" t="n">
@@ -50803,47 +50803,47 @@
     <row r="88">
       <c r="A88" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B88" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C88" s="30" t="inlineStr">
         <is>
-          <t>17064916</t>
+          <t>16932380</t>
         </is>
       </c>
       <c r="D88" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E88" s="29" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="F88" s="29" t="inlineStr">
         <is>
-          <t>Rua RIACHO DOCE</t>
+          <t>Rua CURITIBA</t>
         </is>
       </c>
       <c r="G88" s="29" t="inlineStr">
         <is>
-          <t>78 - R</t>
+          <t>01 - TB</t>
         </is>
       </c>
       <c r="H88" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 14:00</t>
+          <t>14/08/2026 15:51</t>
         </is>
       </c>
       <c r="I88" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 14:17</t>
+          <t>14/08/2026 16:08</t>
         </is>
       </c>
       <c r="J88" s="29" t="n">
@@ -50853,47 +50853,47 @@
     <row r="89">
       <c r="A89" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B89" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C89" s="30" t="inlineStr">
         <is>
-          <t>17070286</t>
+          <t>16904092</t>
         </is>
       </c>
       <c r="D89" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E89" s="29" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="F89" s="29" t="inlineStr">
         <is>
-          <t>Rua GUAÍBA</t>
+          <t>Rua SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="G89" s="29" t="inlineStr">
         <is>
-          <t>1262 - C</t>
+          <t>300 - R</t>
         </is>
       </c>
       <c r="H89" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 14:40</t>
+          <t>13/08/2026 15:14</t>
         </is>
       </c>
       <c r="I89" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 14:57</t>
+          <t>13/08/2026 15:31</t>
         </is>
       </c>
       <c r="J89" s="29" t="n">
@@ -50953,7 +50953,7 @@
     <row r="91">
       <c r="A91" s="29" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="B91" s="29" t="inlineStr">
@@ -50963,37 +50963,37 @@
       </c>
       <c r="C91" s="30" t="inlineStr">
         <is>
-          <t>16932380</t>
+          <t>17072136</t>
         </is>
       </c>
       <c r="D91" s="29" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>443 - KAMEL SAAD 1</t>
         </is>
       </c>
       <c r="E91" s="29" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="F91" s="29" t="inlineStr">
         <is>
-          <t>Rua CURITIBA</t>
+          <t>Rua TOMBADOR</t>
         </is>
       </c>
       <c r="G91" s="29" t="inlineStr">
         <is>
-          <t>01 - TB</t>
+          <t>684 - R</t>
         </is>
       </c>
       <c r="H91" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 15:51</t>
+          <t>21/08/2026 10:12</t>
         </is>
       </c>
       <c r="I91" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 16:08</t>
+          <t>21/08/2026 10:29</t>
         </is>
       </c>
       <c r="J91" s="29" t="n">
@@ -51053,47 +51053,47 @@
     <row r="93">
       <c r="A93" s="29" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B93" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C93" s="30" t="inlineStr">
         <is>
-          <t>16960061</t>
+          <t>17073270</t>
         </is>
       </c>
       <c r="D93" s="29" t="inlineStr">
         <is>
-          <t>443 - KAMEL SAAD 1</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E93" s="29" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F93" s="29" t="inlineStr">
         <is>
-          <t>Rua SALIM DERZI</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="G93" s="29" t="inlineStr">
         <is>
-          <t>118 - R</t>
+          <t>3974 - 33 - R - 30</t>
         </is>
       </c>
       <c r="H93" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 10:37</t>
+          <t>19/08/2026 09:22</t>
         </is>
       </c>
       <c r="I93" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 10:54</t>
+          <t>19/08/2026 09:39</t>
         </is>
       </c>
       <c r="J93" s="29" t="n">
@@ -51103,47 +51103,47 @@
     <row r="94">
       <c r="A94" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B94" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C94" s="30" t="inlineStr">
         <is>
-          <t>17073307</t>
+          <t>17041447</t>
         </is>
       </c>
       <c r="D94" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E94" s="29" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q038</t>
         </is>
       </c>
       <c r="F94" s="29" t="inlineStr">
         <is>
-          <t>Avenida ANTONIO JOAO</t>
+          <t>Rua DAS PEROBAS</t>
         </is>
       </c>
       <c r="G94" s="29" t="inlineStr">
         <is>
-          <t>1477 - R</t>
+          <t>1018 - R</t>
         </is>
       </c>
       <c r="H94" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 13:54</t>
+          <t>20/08/2026 14:48</t>
         </is>
       </c>
       <c r="I94" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 14:11</t>
+          <t>20/08/2026 15:05</t>
         </is>
       </c>
       <c r="J94" s="29" t="n">
@@ -51153,47 +51153,47 @@
     <row r="95">
       <c r="A95" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B95" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C95" s="30" t="inlineStr">
         <is>
-          <t>17041447</t>
+          <t>17073307</t>
         </is>
       </c>
       <c r="D95" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E95" s="29" t="inlineStr">
         <is>
-          <t>Q038</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F95" s="29" t="inlineStr">
         <is>
-          <t>Rua DAS PEROBAS</t>
+          <t>Avenida ANTONIO JOAO</t>
         </is>
       </c>
       <c r="G95" s="29" t="inlineStr">
         <is>
-          <t>1018 - R</t>
+          <t>1477 - R</t>
         </is>
       </c>
       <c r="H95" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 14:48</t>
+          <t>20/08/2026 13:54</t>
         </is>
       </c>
       <c r="I95" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 15:05</t>
+          <t>20/08/2026 14:11</t>
         </is>
       </c>
       <c r="J95" s="29" t="n">
@@ -51213,7 +51213,7 @@
       </c>
       <c r="C96" s="30" t="inlineStr">
         <is>
-          <t>17073270</t>
+          <t>16928880</t>
         </is>
       </c>
       <c r="D96" s="29" t="inlineStr">
@@ -51223,77 +51223,77 @@
       </c>
       <c r="E96" s="29" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="F96" s="29" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Rua CALOGERAS</t>
         </is>
       </c>
       <c r="G96" s="29" t="inlineStr">
         <is>
-          <t>3974 - 33 - R - 30</t>
+          <t>1325 - C</t>
         </is>
       </c>
       <c r="H96" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:22</t>
+          <t>12/08/2026 13:48</t>
         </is>
       </c>
       <c r="I96" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:39</t>
+          <t>12/08/2026 14:04</t>
         </is>
       </c>
       <c r="J96" s="29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B97" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C97" s="30" t="inlineStr">
         <is>
-          <t>16928880</t>
+          <t>17076991</t>
         </is>
       </c>
       <c r="D97" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
       <c r="E97" s="29" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q012</t>
         </is>
       </c>
       <c r="F97" s="29" t="inlineStr">
         <is>
-          <t>Rua CALOGERAS</t>
+          <t>Rua Anselmo Soares</t>
         </is>
       </c>
       <c r="G97" s="29" t="inlineStr">
         <is>
-          <t>1325 - C</t>
+          <t>700 - OU</t>
         </is>
       </c>
       <c r="H97" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 13:48</t>
+          <t>19/08/2026 15:29</t>
         </is>
       </c>
       <c r="I97" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 14:04</t>
+          <t>19/08/2026 15:45</t>
         </is>
       </c>
       <c r="J97" s="29" t="n">
@@ -51303,47 +51303,47 @@
     <row r="98">
       <c r="A98" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B98" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C98" s="30" t="inlineStr">
         <is>
-          <t>16971669</t>
+          <t>16932419</t>
         </is>
       </c>
       <c r="D98" s="29" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E98" s="29" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F98" s="29" t="inlineStr">
         <is>
-          <t>Rua SAO CRISTOVAO</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="G98" s="29" t="inlineStr">
         <is>
-          <t>652 - R</t>
+          <t>451 - R</t>
         </is>
       </c>
       <c r="H98" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:08</t>
+          <t>14/08/2026 14:33</t>
         </is>
       </c>
       <c r="I98" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:24</t>
+          <t>14/08/2026 14:49</t>
         </is>
       </c>
       <c r="J98" s="29" t="n">
@@ -51353,7 +51353,7 @@
     <row r="99">
       <c r="A99" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="B99" s="29" t="inlineStr">
@@ -51363,37 +51363,37 @@
       </c>
       <c r="C99" s="30" t="inlineStr">
         <is>
-          <t>16932419</t>
+          <t>16759754</t>
         </is>
       </c>
       <c r="D99" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>421 - JARDIM IPANEMA</t>
         </is>
       </c>
       <c r="E99" s="29" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="F99" s="29" t="inlineStr">
         <is>
-          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
+          <t>Rua TUIUTI</t>
         </is>
       </c>
       <c r="G99" s="29" t="inlineStr">
         <is>
-          <t>451 - R</t>
+          <t>360 - R</t>
         </is>
       </c>
       <c r="H99" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 14:33</t>
+          <t>05/08/2026 15:15</t>
         </is>
       </c>
       <c r="I99" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 14:49</t>
+          <t>05/08/2026 15:31</t>
         </is>
       </c>
       <c r="J99" s="29" t="n">
@@ -51403,47 +51403,47 @@
     <row r="100">
       <c r="A100" s="29" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B100" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C100" s="30" t="inlineStr">
         <is>
-          <t>16759754</t>
+          <t>16762597</t>
         </is>
       </c>
       <c r="D100" s="29" t="inlineStr">
         <is>
-          <t>421 - JARDIM IPANEMA</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E100" s="29" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="F100" s="29" t="inlineStr">
         <is>
-          <t>Rua TUIUTI</t>
+          <t>Rua FRANCISCO FAUSTO MACENAS</t>
         </is>
       </c>
       <c r="G100" s="29" t="inlineStr">
         <is>
-          <t>360 - R</t>
+          <t>651 - R</t>
         </is>
       </c>
       <c r="H100" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 15:15</t>
+          <t>05/08/2026 09:49</t>
         </is>
       </c>
       <c r="I100" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 15:31</t>
+          <t>05/08/2026 10:05</t>
         </is>
       </c>
       <c r="J100" s="29" t="n">
@@ -51453,47 +51453,47 @@
     <row r="101">
       <c r="A101" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B101" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C101" s="30" t="inlineStr">
         <is>
-          <t>16762597</t>
+          <t>16887154</t>
         </is>
       </c>
       <c r="D101" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E101" s="29" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q012</t>
         </is>
       </c>
       <c r="F101" s="29" t="inlineStr">
         <is>
-          <t>Rua FRANCISCO FAUSTO MACENAS</t>
+          <t>Rua DR. MIGUEL MARCONDES ARMANDO</t>
         </is>
       </c>
       <c r="G101" s="29" t="inlineStr">
         <is>
-          <t>651 - R</t>
+          <t>950 - R</t>
         </is>
       </c>
       <c r="H101" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 09:49</t>
+          <t>12/08/2026 09:04</t>
         </is>
       </c>
       <c r="I101" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 10:05</t>
+          <t>12/08/2026 09:20</t>
         </is>
       </c>
       <c r="J101" s="29" t="n">
@@ -51503,47 +51503,47 @@
     <row r="102">
       <c r="A102" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="B102" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C102" s="30" t="inlineStr">
         <is>
-          <t>16887154</t>
+          <t>16733193</t>
         </is>
       </c>
       <c r="D102" s="29" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>421 - JARDIM IPANEMA</t>
         </is>
       </c>
       <c r="E102" s="29" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F102" s="29" t="inlineStr">
         <is>
-          <t>Rua DR. MIGUEL MARCONDES ARMANDO</t>
+          <t>Rua BALTAZAR SALDANHA</t>
         </is>
       </c>
       <c r="G102" s="29" t="inlineStr">
         <is>
-          <t>950 - R</t>
+          <t>1501 - OU</t>
         </is>
       </c>
       <c r="H102" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 09:04</t>
+          <t>04/08/2026 14:46</t>
         </is>
       </c>
       <c r="I102" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 09:20</t>
+          <t>04/08/2026 15:02</t>
         </is>
       </c>
       <c r="J102" s="29" t="n">
@@ -51553,7 +51553,7 @@
     <row r="103">
       <c r="A103" s="29" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="B103" s="29" t="inlineStr">
@@ -51563,37 +51563,37 @@
       </c>
       <c r="C103" s="30" t="inlineStr">
         <is>
-          <t>16733193</t>
+          <t>16929550</t>
         </is>
       </c>
       <c r="D103" s="29" t="inlineStr">
         <is>
-          <t>421 - JARDIM IPANEMA</t>
+          <t>420 - FERROVIARIA</t>
         </is>
       </c>
       <c r="E103" s="29" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q003</t>
         </is>
       </c>
       <c r="F103" s="29" t="inlineStr">
         <is>
-          <t>Rua BALTAZAR SALDANHA</t>
+          <t>Rua ALAMEDA DOS TROLLES</t>
         </is>
       </c>
       <c r="G103" s="29" t="inlineStr">
         <is>
-          <t>1501 - OU</t>
+          <t>190 - R</t>
         </is>
       </c>
       <c r="H103" s="29" t="inlineStr">
         <is>
-          <t>04/08/2026 14:46</t>
+          <t>14/08/2026 14:31</t>
         </is>
       </c>
       <c r="I103" s="29" t="inlineStr">
         <is>
-          <t>04/08/2026 15:02</t>
+          <t>14/08/2026 14:47</t>
         </is>
       </c>
       <c r="J103" s="29" t="n">
@@ -51603,7 +51603,7 @@
     <row r="104">
       <c r="A104" s="29" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B104" s="29" t="inlineStr">
@@ -51613,37 +51613,37 @@
       </c>
       <c r="C104" s="30" t="inlineStr">
         <is>
-          <t>16929550</t>
+          <t>16932420</t>
         </is>
       </c>
       <c r="D104" s="29" t="inlineStr">
         <is>
-          <t>420 - FERROVIARIA</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E104" s="29" t="inlineStr">
         <is>
-          <t>Q003</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F104" s="29" t="inlineStr">
         <is>
-          <t>Rua ALAMEDA DOS TROLLES</t>
+          <t>Rua 18 DE JULHO</t>
         </is>
       </c>
       <c r="G104" s="29" t="inlineStr">
         <is>
-          <t>190 - R</t>
+          <t>187 - R</t>
         </is>
       </c>
       <c r="H104" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 14:31</t>
+          <t>14/08/2026 14:52</t>
         </is>
       </c>
       <c r="I104" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 14:47</t>
+          <t>14/08/2026 15:08</t>
         </is>
       </c>
       <c r="J104" s="29" t="n">
@@ -51653,7 +51653,7 @@
     <row r="105">
       <c r="A105" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B105" s="29" t="inlineStr">
@@ -51663,37 +51663,37 @@
       </c>
       <c r="C105" s="30" t="inlineStr">
         <is>
-          <t>16932420</t>
+          <t>16945204</t>
         </is>
       </c>
       <c r="D105" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E105" s="29" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F105" s="29" t="inlineStr">
         <is>
-          <t>Rua 18 DE JULHO</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="G105" s="29" t="inlineStr">
         <is>
-          <t>187 - R</t>
+          <t>3974 - 9 - R - 150</t>
         </is>
       </c>
       <c r="H105" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 14:52</t>
+          <t>14/08/2026 13:23</t>
         </is>
       </c>
       <c r="I105" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 15:08</t>
+          <t>14/08/2026 13:39</t>
         </is>
       </c>
       <c r="J105" s="29" t="n">
@@ -51703,47 +51703,47 @@
     <row r="106">
       <c r="A106" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="B106" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C106" s="30" t="inlineStr">
         <is>
-          <t>16945204</t>
+          <t>16990893</t>
         </is>
       </c>
       <c r="D106" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E106" s="29" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F106" s="29" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Rua ENGENHEIRO MAURICIO DUTRA</t>
         </is>
       </c>
       <c r="G106" s="29" t="inlineStr">
         <is>
-          <t>3974 - 9 - R - 150</t>
+          <t>375 - R</t>
         </is>
       </c>
       <c r="H106" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 13:23</t>
+          <t>17/08/2026 08:47</t>
         </is>
       </c>
       <c r="I106" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 13:39</t>
+          <t>17/08/2026 09:03</t>
         </is>
       </c>
       <c r="J106" s="29" t="n">
@@ -51753,7 +51753,7 @@
     <row r="107">
       <c r="A107" s="29" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B107" s="29" t="inlineStr">
@@ -51763,7 +51763,7 @@
       </c>
       <c r="C107" s="30" t="inlineStr">
         <is>
-          <t>16990893</t>
+          <t>16971669</t>
         </is>
       </c>
       <c r="D107" s="29" t="inlineStr">
@@ -51773,27 +51773,27 @@
       </c>
       <c r="E107" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="F107" s="29" t="inlineStr">
         <is>
-          <t>Rua ENGENHEIRO MAURICIO DUTRA</t>
+          <t>Rua SAO CRISTOVAO</t>
         </is>
       </c>
       <c r="G107" s="29" t="inlineStr">
         <is>
-          <t>375 - R</t>
+          <t>652 - R</t>
         </is>
       </c>
       <c r="H107" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 08:47</t>
+          <t>17/08/2026 09:08</t>
         </is>
       </c>
       <c r="I107" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:03</t>
+          <t>17/08/2026 09:24</t>
         </is>
       </c>
       <c r="J107" s="29" t="n">
@@ -51803,7 +51803,7 @@
     <row r="108">
       <c r="A108" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B108" s="29" t="inlineStr">
@@ -51813,37 +51813,37 @@
       </c>
       <c r="C108" s="30" t="inlineStr">
         <is>
-          <t>17033729</t>
+          <t>16971668</t>
         </is>
       </c>
       <c r="D108" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E108" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="F108" s="29" t="inlineStr">
         <is>
-          <t>Rua VICENTE  AZAMBUJA</t>
+          <t>Rua SAO CRISTOVAO</t>
         </is>
       </c>
       <c r="G108" s="29" t="inlineStr">
         <is>
-          <t>1407 - R</t>
+          <t>917 - 8 - R</t>
         </is>
       </c>
       <c r="H108" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 08:45</t>
+          <t>17/08/2026 08:51</t>
         </is>
       </c>
       <c r="I108" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:01</t>
+          <t>17/08/2026 09:07</t>
         </is>
       </c>
       <c r="J108" s="29" t="n">
@@ -51853,47 +51853,47 @@
     <row r="109">
       <c r="A109" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B109" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C109" s="30" t="inlineStr">
         <is>
-          <t>16971668</t>
+          <t>17017093</t>
         </is>
       </c>
       <c r="D109" s="29" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>420 - FERROVIARIA</t>
         </is>
       </c>
       <c r="E109" s="29" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F109" s="29" t="inlineStr">
         <is>
-          <t>Rua SAO CRISTOVAO</t>
+          <t>Travessa PROJETADA 06 FERROVIARIA</t>
         </is>
       </c>
       <c r="G109" s="29" t="inlineStr">
         <is>
-          <t>917 - 8 - R</t>
+          <t>69 - R</t>
         </is>
       </c>
       <c r="H109" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 08:51</t>
+          <t>17/08/2026 15:44</t>
         </is>
       </c>
       <c r="I109" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:07</t>
+          <t>17/08/2026 16:00</t>
         </is>
       </c>
       <c r="J109" s="29" t="n">
@@ -51903,7 +51903,7 @@
     <row r="110">
       <c r="A110" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B110" s="29" t="inlineStr">
@@ -51913,37 +51913,37 @@
       </c>
       <c r="C110" s="30" t="inlineStr">
         <is>
-          <t>17073275</t>
+          <t>17017079</t>
         </is>
       </c>
       <c r="D110" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>420 - FERROVIARIA</t>
         </is>
       </c>
       <c r="E110" s="29" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F110" s="29" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Travessa PROJETADA 06 FERROVIARIA</t>
         </is>
       </c>
       <c r="G110" s="29" t="inlineStr">
         <is>
-          <t>3986 - R</t>
+          <t>57 - R</t>
         </is>
       </c>
       <c r="H110" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:19</t>
+          <t>17/08/2026 09:16</t>
         </is>
       </c>
       <c r="I110" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:35</t>
+          <t>17/08/2026 09:32</t>
         </is>
       </c>
       <c r="J110" s="29" t="n">
@@ -51953,47 +51953,47 @@
     <row r="111">
       <c r="A111" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="B111" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C111" s="30" t="inlineStr">
         <is>
-          <t>17017093</t>
+          <t>16957579</t>
         </is>
       </c>
       <c r="D111" s="29" t="inlineStr">
         <is>
-          <t>420 - FERROVIARIA</t>
+          <t>407 - MOOCA</t>
         </is>
       </c>
       <c r="E111" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q041</t>
         </is>
       </c>
       <c r="F111" s="29" t="inlineStr">
         <is>
-          <t>Travessa PROJETADA 06 FERROVIARIA</t>
+          <t>Rua VALPARAISO</t>
         </is>
       </c>
       <c r="G111" s="29" t="inlineStr">
         <is>
-          <t>69 - R</t>
+          <t>335 - R</t>
         </is>
       </c>
       <c r="H111" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 15:44</t>
+          <t>17/08/2026 08:59</t>
         </is>
       </c>
       <c r="I111" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 16:00</t>
+          <t>17/08/2026 09:15</t>
         </is>
       </c>
       <c r="J111" s="29" t="n">
@@ -52003,7 +52003,7 @@
     <row r="112">
       <c r="A112" s="29" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B112" s="29" t="inlineStr">
@@ -52013,37 +52013,37 @@
       </c>
       <c r="C112" s="30" t="inlineStr">
         <is>
-          <t>17055208</t>
+          <t>17033729</t>
         </is>
       </c>
       <c r="D112" s="29" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇÕES</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E112" s="29" t="inlineStr">
         <is>
-          <t>Q036</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F112" s="29" t="inlineStr">
         <is>
-          <t>Rua DIGNO TORRES GIMENEZ</t>
+          <t>Rua VICENTE  AZAMBUJA</t>
         </is>
       </c>
       <c r="G112" s="29" t="inlineStr">
         <is>
-          <t>590 - 2 - R</t>
+          <t>1407 - R</t>
         </is>
       </c>
       <c r="H112" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 08:57</t>
+          <t>19/08/2026 08:45</t>
         </is>
       </c>
       <c r="I112" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 09:13</t>
+          <t>19/08/2026 09:01</t>
         </is>
       </c>
       <c r="J112" s="29" t="n">
@@ -52053,47 +52053,47 @@
     <row r="113">
       <c r="A113" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B113" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C113" s="30" t="inlineStr">
         <is>
-          <t>17076991</t>
+          <t>17073275</t>
         </is>
       </c>
       <c r="D113" s="29" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E113" s="29" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F113" s="29" t="inlineStr">
         <is>
-          <t>Rua Anselmo Soares</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="G113" s="29" t="inlineStr">
         <is>
-          <t>700 - OU</t>
+          <t>3986 - R</t>
         </is>
       </c>
       <c r="H113" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 15:29</t>
+          <t>19/08/2026 10:19</t>
         </is>
       </c>
       <c r="I113" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 15:45</t>
+          <t>19/08/2026 10:35</t>
         </is>
       </c>
       <c r="J113" s="29" t="n">
@@ -52103,47 +52103,47 @@
     <row r="114">
       <c r="A114" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="B114" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C114" s="30" t="inlineStr">
         <is>
-          <t>17017079</t>
+          <t>17055208</t>
         </is>
       </c>
       <c r="D114" s="29" t="inlineStr">
         <is>
-          <t>420 - FERROVIARIA</t>
+          <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
       <c r="E114" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q036</t>
         </is>
       </c>
       <c r="F114" s="29" t="inlineStr">
         <is>
-          <t>Travessa PROJETADA 06 FERROVIARIA</t>
+          <t>Rua DIGNO TORRES GIMENEZ</t>
         </is>
       </c>
       <c r="G114" s="29" t="inlineStr">
         <is>
-          <t>57 - R</t>
+          <t>590 - 2 - R</t>
         </is>
       </c>
       <c r="H114" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:16</t>
+          <t>21/08/2026 08:57</t>
         </is>
       </c>
       <c r="I114" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:32</t>
+          <t>21/08/2026 09:13</t>
         </is>
       </c>
       <c r="J114" s="29" t="n">
@@ -52153,7 +52153,7 @@
     <row r="115">
       <c r="A115" s="29" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="B115" s="29" t="inlineStr">
@@ -52163,37 +52163,37 @@
       </c>
       <c r="C115" s="30" t="inlineStr">
         <is>
-          <t>16957579</t>
+          <t>17137370</t>
         </is>
       </c>
       <c r="D115" s="29" t="inlineStr">
         <is>
-          <t>407 - MOOCA</t>
+          <t>402 - JARDIM MARAMBAIA</t>
         </is>
       </c>
       <c r="E115" s="29" t="inlineStr">
         <is>
-          <t>Q041</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F115" s="29" t="inlineStr">
         <is>
-          <t>Rua VALPARAISO</t>
+          <t>Rua DR HELIO BRANDAO</t>
         </is>
       </c>
       <c r="G115" s="29" t="inlineStr">
         <is>
-          <t>335 - R</t>
+          <t>647 - R</t>
         </is>
       </c>
       <c r="H115" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 08:59</t>
+          <t>25/08/2026 16:03</t>
         </is>
       </c>
       <c r="I115" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:15</t>
+          <t>25/08/2026 16:19</t>
         </is>
       </c>
       <c r="J115" s="29" t="n">
@@ -52203,47 +52203,47 @@
     <row r="116">
       <c r="A116" s="29" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B116" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C116" s="30" t="inlineStr">
         <is>
-          <t>17137370</t>
+          <t>17011680</t>
         </is>
       </c>
       <c r="D116" s="29" t="inlineStr">
         <is>
-          <t>402 - JARDIM MARAMBAIA</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E116" s="29" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q035</t>
         </is>
       </c>
       <c r="F116" s="29" t="inlineStr">
         <is>
-          <t>Rua DR HELIO BRANDAO</t>
+          <t>Rua HONOROPOLIS</t>
         </is>
       </c>
       <c r="G116" s="29" t="inlineStr">
         <is>
-          <t>647 - R</t>
+          <t>427 - R</t>
         </is>
       </c>
       <c r="H116" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 16:03</t>
+          <t>19/08/2026 10:33</t>
         </is>
       </c>
       <c r="I116" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 16:19</t>
+          <t>19/08/2026 10:49</t>
         </is>
       </c>
       <c r="J116" s="29" t="n">
@@ -52263,7 +52263,7 @@
       </c>
       <c r="C117" s="30" t="inlineStr">
         <is>
-          <t>17011680</t>
+          <t>16982670</t>
         </is>
       </c>
       <c r="D117" s="29" t="inlineStr">
@@ -52273,27 +52273,27 @@
       </c>
       <c r="E117" s="29" t="inlineStr">
         <is>
-          <t>Q035</t>
+          <t>Q037</t>
         </is>
       </c>
       <c r="F117" s="29" t="inlineStr">
         <is>
-          <t>Rua HONOROPOLIS</t>
+          <t>Rua SALVADOR</t>
         </is>
       </c>
       <c r="G117" s="29" t="inlineStr">
         <is>
-          <t>427 - R</t>
+          <t>479 - R</t>
         </is>
       </c>
       <c r="H117" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:33</t>
+          <t>17/08/2026 14:14</t>
         </is>
       </c>
       <c r="I117" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:49</t>
+          <t>17/08/2026 14:30</t>
         </is>
       </c>
       <c r="J117" s="29" t="n">
@@ -52353,47 +52353,47 @@
     <row r="119">
       <c r="A119" s="29" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B119" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C119" s="30" t="inlineStr">
         <is>
-          <t>16982670</t>
+          <t>17098959</t>
         </is>
       </c>
       <c r="D119" s="29" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E119" s="29" t="inlineStr">
         <is>
-          <t>Q037</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F119" s="29" t="inlineStr">
         <is>
-          <t>Rua SALVADOR</t>
+          <t>Avenida COMANDANTE CARDOSO</t>
         </is>
       </c>
       <c r="G119" s="29" t="inlineStr">
         <is>
-          <t>479 - R</t>
+          <t>332 - R</t>
         </is>
       </c>
       <c r="H119" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 14:14</t>
+          <t>24/08/2026 15:05</t>
         </is>
       </c>
       <c r="I119" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 14:30</t>
+          <t>24/08/2026 15:21</t>
         </is>
       </c>
       <c r="J119" s="29" t="n">
@@ -52413,7 +52413,7 @@
       </c>
       <c r="C120" s="30" t="inlineStr">
         <is>
-          <t>17098959</t>
+          <t>17098958</t>
         </is>
       </c>
       <c r="D120" s="29" t="inlineStr">
@@ -52433,17 +52433,17 @@
       </c>
       <c r="G120" s="29" t="inlineStr">
         <is>
-          <t>332 - R</t>
+          <t>258 - 2 - OU</t>
         </is>
       </c>
       <c r="H120" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:05</t>
+          <t>24/08/2026 14:47</t>
         </is>
       </c>
       <c r="I120" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:21</t>
+          <t>24/08/2026 15:03</t>
         </is>
       </c>
       <c r="J120" s="29" t="n">
@@ -52463,7 +52463,7 @@
       </c>
       <c r="C121" s="30" t="inlineStr">
         <is>
-          <t>17098958</t>
+          <t>17098957</t>
         </is>
       </c>
       <c r="D121" s="29" t="inlineStr">
@@ -52483,17 +52483,17 @@
       </c>
       <c r="G121" s="29" t="inlineStr">
         <is>
-          <t>258 - 2 - OU</t>
+          <t>258 - R</t>
         </is>
       </c>
       <c r="H121" s="29" t="inlineStr">
         <is>
+          <t>24/08/2026 14:31</t>
+        </is>
+      </c>
+      <c r="I121" s="29" t="inlineStr">
+        <is>
           <t>24/08/2026 14:47</t>
-        </is>
-      </c>
-      <c r="I121" s="29" t="inlineStr">
-        <is>
-          <t>24/08/2026 15:03</t>
         </is>
       </c>
       <c r="J121" s="29" t="n">
@@ -52503,105 +52503,55 @@
     <row r="122">
       <c r="A122" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B122" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C122" s="30" t="inlineStr">
         <is>
-          <t>17098957</t>
+          <t>17130878</t>
         </is>
       </c>
       <c r="D122" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E122" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q044</t>
         </is>
       </c>
       <c r="F122" s="29" t="inlineStr">
         <is>
-          <t>Avenida COMANDANTE CARDOSO</t>
+          <t>Rua BENJAMIN CONSTANT</t>
         </is>
       </c>
       <c r="G122" s="29" t="inlineStr">
         <is>
-          <t>258 - R</t>
+          <t>512 - 1 - R</t>
         </is>
       </c>
       <c r="H122" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 14:31</t>
+          <t>25/08/2026 10:27</t>
         </is>
       </c>
       <c r="I122" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 14:47</t>
+          <t>25/08/2026 10:43</t>
         </is>
       </c>
       <c r="J122" s="29" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="29" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-      <c r="B123" s="29" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C123" s="30" t="inlineStr">
-        <is>
-          <t>17130878</t>
-        </is>
-      </c>
-      <c r="D123" s="29" t="inlineStr">
-        <is>
-          <t>434 - VILA AUREA</t>
-        </is>
-      </c>
-      <c r="E123" s="29" t="inlineStr">
-        <is>
-          <t>Q044</t>
-        </is>
-      </c>
-      <c r="F123" s="29" t="inlineStr">
-        <is>
-          <t>Rua BENJAMIN CONSTANT</t>
-        </is>
-      </c>
-      <c r="G123" s="29" t="inlineStr">
-        <is>
-          <t>512 - 1 - R</t>
-        </is>
-      </c>
-      <c r="H123" s="29" t="inlineStr">
-        <is>
-          <t>25/08/2026 10:27</t>
-        </is>
-      </c>
-      <c r="I123" s="29" t="inlineStr">
-        <is>
-          <t>25/08/2026 10:43</t>
-        </is>
-      </c>
-      <c r="J123" s="29" t="n">
-        <v>16</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:J123"/>
+  <autoFilter ref="A2:J122"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -52726,7 +52676,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId121"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/historico/semanas_318-321.xlsx
+++ b/data/historico/semanas_318-321.xlsx
@@ -25,8 +25,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo Geral'!$A$2:$AC$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por Área'!$A$2:$N$123</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Visitas Duplicadas'!$A$2:$J$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Visitas Suspeitas'!$A$2:$K$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Visitas Duplicadas'!$A$2:$J$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Visitas Suspeitas'!$A$2:$K$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Visitas Negativas'!$A$2:$K$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 15min'!$A$2:$J$126</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$159</definedName>
@@ -3450,25 +3450,25 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E26" s="4" t="n">
         <v>14</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>23.86</v>
+        <v>23.71</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.39</v>
+        <v>5.42</v>
       </c>
       <c r="H26" s="4" t="n">
         <v>5</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.99</v>
+        <v>2.41</v>
       </c>
       <c r="K26" s="4" t="n">
         <v>0</v>
@@ -3480,10 +3480,10 @@
         <v>10</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="P26" s="4" t="n">
         <v>12</v>
@@ -3498,10 +3498,10 @@
         <v>0</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>47.48</v>
+        <v>47.63</v>
       </c>
       <c r="V26" s="4" t="n">
         <v>4.62</v>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="C26" s="29" t="n">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D26" s="29" t="n">
         <v>302</v>
@@ -6831,10 +6831,10 @@
         <v>0</v>
       </c>
       <c r="F26" s="29" t="n">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G26" s="29" t="n">
-        <v>47.48</v>
+        <v>47.63</v>
       </c>
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="n"/>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="C45" s="26" t="n">
-        <v>12724</v>
+        <v>12722</v>
       </c>
       <c r="D45" s="26" t="n">
         <v>5967</v>
@@ -7382,10 +7382,10 @@
         <v>19</v>
       </c>
       <c r="F45" s="26" t="n">
-        <v>18710</v>
+        <v>18708</v>
       </c>
       <c r="G45" s="26" t="n">
-        <v>31.99</v>
+        <v>32</v>
       </c>
       <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="n"/>
@@ -12660,25 +12660,25 @@
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G34" s="4" t="n">
         <v>5</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>25.4</v>
+        <v>25</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>5.28</v>
+        <v>5.36</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>3.94</v>
+        <v>2.4</v>
       </c>
       <c r="M34" s="4" t="n">
         <v>0</v>
@@ -12690,10 +12690,10 @@
         <v>5</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R34" s="4" t="n">
         <v>0</v>
@@ -26328,7 +26328,7 @@
       </c>
       <c r="B30" s="38" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C30" s="38" t="inlineStr">
@@ -26343,10 +26343,10 @@
         <v>17</v>
       </c>
       <c r="F30" s="38" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G30" s="38" t="n">
-        <v>62.09</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="H30" s="38" t="inlineStr">
         <is>
@@ -26360,61 +26360,61 @@
       </c>
       <c r="B31" s="38" t="inlineStr">
         <is>
+          <t>Emidio Rainer Vilhalba</t>
+        </is>
+      </c>
+      <c r="C31" s="38" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="D31" s="38" t="n">
+        <v>14</v>
+      </c>
+      <c r="E31" s="38" t="n">
+        <v>17</v>
+      </c>
+      <c r="F31" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="G31" s="38" t="n">
+        <v>62.09</v>
+      </c>
+      <c r="H31" s="38" t="inlineStr">
+        <is>
+          <t>🟠 ATENÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="38" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="38" t="inlineStr">
+        <is>
           <t>Carlos Alberto Albiero</t>
         </is>
       </c>
-      <c r="C31" s="38" t="inlineStr">
+      <c r="C32" s="38" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="D31" s="38" t="n">
+      <c r="D32" s="38" t="n">
         <v>15</v>
       </c>
-      <c r="E31" s="38" t="n">
+      <c r="E32" s="38" t="n">
         <v>18</v>
       </c>
-      <c r="F31" s="38" t="n">
+      <c r="F32" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="G31" s="38" t="n">
+      <c r="G32" s="38" t="n">
         <v>61.36</v>
       </c>
-      <c r="H31" s="38" t="inlineStr">
+      <c r="H32" s="38" t="inlineStr">
         <is>
           <t>🟠 ATENÇÃO</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="E32" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>57.85</v>
-      </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
         </is>
       </c>
     </row>
@@ -29423,7 +29423,7 @@
         </is>
       </c>
       <c r="D128" s="52" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E128" s="52" t="n">
         <v>0.3</v>
@@ -29435,7 +29435,7 @@
         <v>0.3643</v>
       </c>
       <c r="H128" s="52" t="n">
-        <v>-3.64</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="129">
@@ -29455,7 +29455,7 @@
         </is>
       </c>
       <c r="D129" s="52" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E129" s="52" t="n">
         <v>1</v>
@@ -29467,7 +29467,7 @@
         <v>1.2143</v>
       </c>
       <c r="H129" s="52" t="n">
-        <v>-13.36</v>
+        <v>-8.5</v>
       </c>
     </row>
     <row r="130">
@@ -29551,7 +29551,7 @@
         </is>
       </c>
       <c r="D132" s="52" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E132" s="52" t="n">
         <v>0.2</v>
@@ -29563,7 +29563,7 @@
         <v>0.2429</v>
       </c>
       <c r="H132" s="52" t="n">
-        <v>-2.43</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="133">
@@ -41468,40 +41468,40 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>429 - COOPHA FRONTEIRA</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>5.18</v>
+        <v>5.37</v>
       </c>
       <c r="F62" s="4" t="n">
         <v>5</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>Q014, Q015, Q029, Q030</t>
+          <t>Q004, Q005, Q006, Q012, Q013, Q036, Q037, Q038, Q039, Q040</t>
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>6.82</v>
+        <v>0.85</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="L62" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>51.11</v>
+        <v>44.6</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
@@ -41522,40 +41522,40 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="D63" s="4" t="n">
-        <v>118</v>
+        <v>42</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>5.37</v>
+        <v>5.43</v>
       </c>
       <c r="F63" s="4" t="n">
         <v>5</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>Q004, Q005, Q006, Q012, Q013, Q036, Q037, Q038, Q039, Q040</t>
+          <t>Q014, Q015, Q029, Q030</t>
         </is>
       </c>
       <c r="I63" s="4" t="n">
         <v>1</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>0.85</v>
+        <v>2.38</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="L63" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M63" s="4" t="n">
-        <v>44.6</v>
+        <v>52.27</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
@@ -44932,7 +44932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -44940,7 +44940,7 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="41" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
@@ -44950,7 +44950,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VISITAS DUPLICADAS (10 registros) — CONFIRME E EXCLUA NO SISTEMA</t>
+          <t>VISITAS DUPLICADAS (6 registros) — CONFIRME E EXCLUA NO SISTEMA</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -45236,7 +45236,7 @@
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>17019173</t>
+          <t>17019195</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -45246,27 +45246,27 @@
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Rua CARAMBOLEIRA</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
-          <t>105 - 1 - TB</t>
+          <t>106 - 2 - TB</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
         <is>
-          <t>19/08/2026 09:36</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
         <is>
-          <t>19/08/2026 09:36</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -45288,7 +45288,7 @@
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>17019174</t>
+          <t>17019196</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -45298,27 +45298,27 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>Rua CARAMBOLEIRA</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>105 - 1 - TB</t>
+          <t>106 - 2 - TB</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
         <is>
-          <t>19/08/2026 09:36</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
         <is>
-          <t>19/08/2026 09:42</t>
+          <t>19/08/2026 14:24</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -45327,216 +45327,8 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>17019195</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="G9" s="20" t="inlineStr">
-        <is>
-          <t>106 - 2 - TB</t>
-        </is>
-      </c>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:18</t>
-        </is>
-      </c>
-      <c r="I9" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:18</t>
-        </is>
-      </c>
-      <c r="J9" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>17019196</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="G10" s="20" t="inlineStr">
-        <is>
-          <t>106 - 2 - TB</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:18</t>
-        </is>
-      </c>
-      <c r="I10" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:24</t>
-        </is>
-      </c>
-      <c r="J10" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>17019200</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="G11" s="20" t="inlineStr">
-        <is>
-          <t>55 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H11" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:33</t>
-        </is>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:33</t>
-        </is>
-      </c>
-      <c r="J11" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>17019201</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="inlineStr">
-        <is>
-          <t>Q030</t>
-        </is>
-      </c>
-      <c r="F12" s="20" t="inlineStr">
-        <is>
-          <t>Rua AMEIXEIRA</t>
-        </is>
-      </c>
-      <c r="G12" s="20" t="inlineStr">
-        <is>
-          <t>55 - 1 - TB</t>
-        </is>
-      </c>
-      <c r="H12" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:33</t>
-        </is>
-      </c>
-      <c r="I12" s="20" t="inlineStr">
-        <is>
-          <t>19/08/2026 14:38</t>
-        </is>
-      </c>
-      <c r="J12" s="20" t="inlineStr">
-        <is>
-          <t>Mesmo horário de chegada + imóvel</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:J12"/>
+  <autoFilter ref="A2:J8"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -45547,10 +45339,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45562,7 +45350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -45581,7 +45369,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VISITAS EM SEQUÊNCIA SUSPEITA (36 registros) — CHEGADA NO MESMO MINUTO DA VISITA ANTERIOR</t>
+          <t>VISITAS EM SEQUÊNCIA SUSPEITA (32 registros) — CHEGADA NO MESMO MINUTO DA VISITA ANTERIOR</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -46349,7 +46137,7 @@
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>17019173</t>
+          <t>17019195</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -46359,27 +46147,27 @@
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="G16" s="23" t="inlineStr">
         <is>
-          <t>Rua CARAMBOLEIRA</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">
         <is>
-          <t>105 - 1 - TB</t>
+          <t>106 - 2 - TB</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:36</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:36</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="K16" s="23" t="inlineStr"/>
@@ -46400,7 +46188,7 @@
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>17019174</t>
+          <t>17019196</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -46410,27 +46198,27 @@
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
         <is>
-          <t>Rua CARAMBOLEIRA</t>
+          <t>Rua AMEIXEIRA</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
         <is>
-          <t>105 - 1 - TB</t>
+          <t>106 - 2 - TB</t>
         </is>
       </c>
       <c r="I17" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:36</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="J17" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 09:42</t>
+          <t>19/08/2026 14:24</t>
         </is>
       </c>
       <c r="K17" s="23" t="n">
@@ -46449,41 +46237,41 @@
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>17019195</t>
+          <t>17177121</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>433 - ÁREA A - RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
         <is>
-          <t>Rua AMEIXEIRA</t>
+          <t>Rua GUARANTA</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
         <is>
-          <t>106 - 2 - TB</t>
+          <t>429 - 1 - TB</t>
         </is>
       </c>
       <c r="I18" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:18</t>
+          <t>27/08/2026 11:44</t>
         </is>
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:18</t>
+          <t>27/08/2026 11:44</t>
         </is>
       </c>
       <c r="K18" s="23" t="inlineStr"/>
@@ -46500,41 +46288,41 @@
         </is>
       </c>
       <c r="C19" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>17019196</t>
+          <t>17177122</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>433 - ÁREA A - RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
         <is>
-          <t>Rua AMEIXEIRA</t>
+          <t>Rua GUARANTA</t>
         </is>
       </c>
       <c r="H19" s="23" t="inlineStr">
         <is>
-          <t>106 - 2 - TB</t>
+          <t>429 - 1 - TB</t>
         </is>
       </c>
       <c r="I19" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:18</t>
+          <t>27/08/2026 11:44</t>
         </is>
       </c>
       <c r="J19" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:24</t>
+          <t>27/08/2026 11:50</t>
         </is>
       </c>
       <c r="K19" s="23" t="n">
@@ -46553,41 +46341,41 @@
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>17019200</t>
+          <t>17177128</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>433 - ÁREA A - RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>Rua AMEIXEIRA</t>
+          <t>Rua GUARANTA</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
         <is>
-          <t>55 - 1 - TB</t>
+          <t>436 - 1 - TB</t>
         </is>
       </c>
       <c r="I20" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:33</t>
+          <t>27/08/2026 11:58</t>
         </is>
       </c>
       <c r="J20" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:33</t>
+          <t>27/08/2026 12:04</t>
         </is>
       </c>
       <c r="K20" s="23" t="inlineStr"/>
@@ -46604,41 +46392,41 @@
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>17019201</t>
+          <t>17177127</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>433 - ÁREA A - RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
         <is>
-          <t>Rua AMEIXEIRA</t>
+          <t>Rua GUARANTA</t>
         </is>
       </c>
       <c r="H21" s="23" t="inlineStr">
         <is>
-          <t>55 - 1 - TB</t>
+          <t>436 - 1 - TB</t>
         </is>
       </c>
       <c r="I21" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:33</t>
+          <t>27/08/2026 11:58</t>
         </is>
       </c>
       <c r="J21" s="23" t="inlineStr">
         <is>
-          <t>19/08/2026 14:38</t>
+          <t>27/08/2026 11:58</t>
         </is>
       </c>
       <c r="K21" s="23" t="n">
@@ -46657,11 +46445,11 @@
         </is>
       </c>
       <c r="C22" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>17177121</t>
+          <t>17177126</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -46681,25 +46469,27 @@
       </c>
       <c r="H22" s="23" t="inlineStr">
         <is>
-          <t>429 - 1 - TB</t>
+          <t>436 - 2 - TB</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
         <is>
-          <t>27/08/2026 11:44</t>
+          <t>27/08/2026 11:58</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t>27/08/2026 11:44</t>
-        </is>
-      </c>
-      <c r="K22" s="23" t="inlineStr"/>
+          <t>27/08/2026 11:58</t>
+        </is>
+      </c>
+      <c r="K22" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="B23" s="23" t="inlineStr">
@@ -46712,47 +46502,45 @@
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>17177122</t>
+          <t>16959229</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
         <is>
-          <t>433 - ÁREA A - RESIDENCIAL PONTA PORÃ 1</t>
+          <t>430 - VILA RENÔ</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="G23" s="23" t="inlineStr">
         <is>
-          <t>Rua GUARANTA</t>
+          <t>Avenida URUMBELA</t>
         </is>
       </c>
       <c r="H23" s="23" t="inlineStr">
         <is>
-          <t>429 - 1 - TB</t>
+          <t>890 - 10 - R</t>
         </is>
       </c>
       <c r="I23" s="23" t="inlineStr">
         <is>
-          <t>27/08/2026 11:44</t>
+          <t>18/08/2026 09:50</t>
         </is>
       </c>
       <c r="J23" s="23" t="inlineStr">
         <is>
-          <t>27/08/2026 11:50</t>
-        </is>
-      </c>
-      <c r="K23" s="23" t="n">
-        <v>0</v>
-      </c>
+          <t>18/08/2026 09:51</t>
+        </is>
+      </c>
+      <c r="K23" s="23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="23" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="B24" s="23" t="inlineStr">
@@ -46761,49 +46549,51 @@
         </is>
       </c>
       <c r="C24" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>17177128</t>
+          <t>16959228</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
-          <t>433 - ÁREA A - RESIDENCIAL PONTA PORÃ 1</t>
+          <t>430 - VILA RENÔ</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="G24" s="23" t="inlineStr">
         <is>
-          <t>Rua GUARANTA</t>
+          <t>Avenida URUMBELA</t>
         </is>
       </c>
       <c r="H24" s="23" t="inlineStr">
         <is>
-          <t>436 - 1 - TB</t>
+          <t>890 - 9 - C</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
         <is>
-          <t>27/08/2026 11:58</t>
+          <t>18/08/2026 09:50</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
         <is>
-          <t>27/08/2026 12:04</t>
-        </is>
-      </c>
-      <c r="K24" s="23" t="inlineStr"/>
+          <t>18/08/2026 09:50</t>
+        </is>
+      </c>
+      <c r="K24" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="B25" s="23" t="inlineStr">
@@ -46812,51 +46602,49 @@
         </is>
       </c>
       <c r="C25" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>17177127</t>
+          <t>17127482</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
         <is>
-          <t>433 - ÁREA A - RESIDENCIAL PONTA PORÃ 1</t>
+          <t>429 - COOPHA FRONTEIRA</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
         <is>
-          <t>Rua GUARANTA</t>
+          <t>Rua SAMAMBAIA</t>
         </is>
       </c>
       <c r="H25" s="23" t="inlineStr">
         <is>
-          <t>436 - 1 - TB</t>
+          <t>214 - 3 - R</t>
         </is>
       </c>
       <c r="I25" s="23" t="inlineStr">
         <is>
-          <t>27/08/2026 11:58</t>
+          <t>25/08/2026 14:20</t>
         </is>
       </c>
       <c r="J25" s="23" t="inlineStr">
         <is>
-          <t>27/08/2026 11:58</t>
-        </is>
-      </c>
-      <c r="K25" s="23" t="n">
-        <v>0</v>
-      </c>
+          <t>25/08/2026 14:20</t>
+        </is>
+      </c>
+      <c r="K25" s="23" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="23" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="B26" s="23" t="inlineStr">
@@ -46865,41 +46653,41 @@
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>17177126</t>
+          <t>17127483</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>433 - ÁREA A - RESIDENCIAL PONTA PORÃ 1</t>
+          <t>429 - COOPHA FRONTEIRA</t>
         </is>
       </c>
       <c r="F26" s="23" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">
         <is>
-          <t>Rua GUARANTA</t>
+          <t>Rua SAMAMBAIA</t>
         </is>
       </c>
       <c r="H26" s="23" t="inlineStr">
         <is>
-          <t>436 - 2 - TB</t>
+          <t>214 - 4 - R</t>
         </is>
       </c>
       <c r="I26" s="23" t="inlineStr">
         <is>
-          <t>27/08/2026 11:58</t>
+          <t>25/08/2026 14:20</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
         <is>
-          <t>27/08/2026 11:58</t>
+          <t>25/08/2026 14:21</t>
         </is>
       </c>
       <c r="K26" s="23" t="n">
@@ -46909,12 +46697,12 @@
     <row r="27">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C27" s="23" t="n">
@@ -46922,37 +46710,37 @@
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>16959229</t>
+          <t>16920467</t>
         </is>
       </c>
       <c r="E27" s="23" t="inlineStr">
         <is>
-          <t>430 - VILA RENÔ</t>
+          <t>435 - JARDIM PRIMOR</t>
         </is>
       </c>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="G27" s="23" t="inlineStr">
         <is>
-          <t>Avenida URUMBELA</t>
+          <t>Rua PARANAGUA</t>
         </is>
       </c>
       <c r="H27" s="23" t="inlineStr">
         <is>
-          <t>890 - 10 - R</t>
+          <t>20 - 3 - C</t>
         </is>
       </c>
       <c r="I27" s="23" t="inlineStr">
         <is>
-          <t>18/08/2026 09:50</t>
+          <t>13/08/2026 16:30</t>
         </is>
       </c>
       <c r="J27" s="23" t="inlineStr">
         <is>
-          <t>18/08/2026 09:51</t>
+          <t>13/08/2026 16:30</t>
         </is>
       </c>
       <c r="K27" s="23" t="inlineStr"/>
@@ -46960,12 +46748,12 @@
     <row r="28">
       <c r="A28" s="23" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C28" s="23" t="n">
@@ -46973,37 +46761,37 @@
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>16959228</t>
+          <t>16920468</t>
         </is>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
-          <t>430 - VILA RENÔ</t>
+          <t>435 - JARDIM PRIMOR</t>
         </is>
       </c>
       <c r="F28" s="23" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
-          <t>Avenida URUMBELA</t>
+          <t>Rua PARANAGUA</t>
         </is>
       </c>
       <c r="H28" s="23" t="inlineStr">
         <is>
-          <t>890 - 9 - C</t>
+          <t>20 - 5 - C</t>
         </is>
       </c>
       <c r="I28" s="23" t="inlineStr">
         <is>
-          <t>18/08/2026 09:50</t>
+          <t>13/08/2026 16:30</t>
         </is>
       </c>
       <c r="J28" s="23" t="inlineStr">
         <is>
-          <t>18/08/2026 09:50</t>
+          <t>13/08/2026 16:30</t>
         </is>
       </c>
       <c r="K28" s="23" t="n">
@@ -47013,7 +46801,7 @@
     <row r="29">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="B29" s="23" t="inlineStr">
@@ -47026,37 +46814,37 @@
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>17127482</t>
+          <t>17131125</t>
         </is>
       </c>
       <c r="E29" s="23" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>431 - PANAMBI</t>
         </is>
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
         <is>
-          <t>Rua SAMAMBAIA</t>
+          <t>Rua CAMPO GRANDE</t>
         </is>
       </c>
       <c r="H29" s="23" t="inlineStr">
         <is>
-          <t>214 - 3 - R</t>
+          <t>55 - R</t>
         </is>
       </c>
       <c r="I29" s="23" t="inlineStr">
         <is>
-          <t>25/08/2026 14:20</t>
+          <t>25/08/2026 14:19</t>
         </is>
       </c>
       <c r="J29" s="23" t="inlineStr">
         <is>
-          <t>25/08/2026 14:20</t>
+          <t>25/08/2026 14:25</t>
         </is>
       </c>
       <c r="K29" s="23" t="inlineStr"/>
@@ -47064,7 +46852,7 @@
     <row r="30">
       <c r="A30" s="23" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="B30" s="23" t="inlineStr">
@@ -47077,37 +46865,37 @@
       </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
-          <t>17127483</t>
+          <t>17131126</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
-          <t>429 - COOPHA FRONTEIRA</t>
+          <t>431 - PANAMBI</t>
         </is>
       </c>
       <c r="F30" s="23" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
         <is>
-          <t>Rua SAMAMBAIA</t>
+          <t>Rua CAMPO GRANDE</t>
         </is>
       </c>
       <c r="H30" s="23" t="inlineStr">
         <is>
-          <t>214 - 4 - R</t>
+          <t>23 - 1 - R</t>
         </is>
       </c>
       <c r="I30" s="23" t="inlineStr">
         <is>
-          <t>25/08/2026 14:20</t>
+          <t>25/08/2026 14:19</t>
         </is>
       </c>
       <c r="J30" s="23" t="inlineStr">
         <is>
-          <t>25/08/2026 14:21</t>
+          <t>25/08/2026 14:25</t>
         </is>
       </c>
       <c r="K30" s="23" t="n">
@@ -47117,12 +46905,12 @@
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C31" s="23" t="n">
@@ -47130,37 +46918,37 @@
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>16920467</t>
+          <t>16932408</t>
         </is>
       </c>
       <c r="E31" s="23" t="inlineStr">
         <is>
-          <t>435 - JARDIM PRIMOR</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="F31" s="23" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="G31" s="23" t="inlineStr">
         <is>
-          <t>Rua PARANAGUA</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="H31" s="23" t="inlineStr">
         <is>
-          <t>20 - 3 - C</t>
+          <t>491 - TB</t>
         </is>
       </c>
       <c r="I31" s="23" t="inlineStr">
         <is>
-          <t>13/08/2026 16:30</t>
+          <t>14/08/2026 10:00</t>
         </is>
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>13/08/2026 16:30</t>
+          <t>14/08/2026 10:06</t>
         </is>
       </c>
       <c r="K31" s="23" t="inlineStr"/>
@@ -47168,12 +46956,12 @@
     <row r="32">
       <c r="A32" s="23" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C32" s="23" t="n">
@@ -47181,37 +46969,37 @@
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>16920468</t>
+          <t>16932412</t>
         </is>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
-          <t>435 - JARDIM PRIMOR</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="F32" s="23" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
-          <t>Rua PARANAGUA</t>
+          <t>Rua MARACAJU</t>
         </is>
       </c>
       <c r="H32" s="23" t="inlineStr">
         <is>
-          <t>20 - 5 - C</t>
+          <t>194 - 3 - R</t>
         </is>
       </c>
       <c r="I32" s="23" t="inlineStr">
         <is>
-          <t>13/08/2026 16:30</t>
+          <t>14/08/2026 10:00</t>
         </is>
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>13/08/2026 16:30</t>
+          <t>14/08/2026 10:07</t>
         </is>
       </c>
       <c r="K32" s="23" t="n">
@@ -47221,12 +47009,12 @@
     <row r="33">
       <c r="A33" s="23" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C33" s="23" t="n">
@@ -47234,37 +47022,37 @@
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>17131125</t>
+          <t>17149957</t>
         </is>
       </c>
       <c r="E33" s="23" t="inlineStr">
         <is>
-          <t>431 - PANAMBI</t>
+          <t>416 - CENTRO 2</t>
         </is>
       </c>
       <c r="F33" s="23" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q012</t>
         </is>
       </c>
       <c r="G33" s="23" t="inlineStr">
         <is>
-          <t>Rua CAMPO GRANDE</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="H33" s="23" t="inlineStr">
         <is>
-          <t>55 - R</t>
+          <t>01 - OU</t>
         </is>
       </c>
       <c r="I33" s="23" t="inlineStr">
         <is>
-          <t>25/08/2026 14:19</t>
+          <t>26/08/2026 17:51</t>
         </is>
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>25/08/2026 14:25</t>
+          <t>26/08/2026 17:51</t>
         </is>
       </c>
       <c r="K33" s="23" t="inlineStr"/>
@@ -47272,12 +47060,12 @@
     <row r="34">
       <c r="A34" s="23" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C34" s="23" t="n">
@@ -47285,368 +47073,160 @@
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>17131126</t>
+          <t>17149955</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
-          <t>431 - PANAMBI</t>
+          <t>416 - CENTRO 2</t>
         </is>
       </c>
       <c r="F34" s="23" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="G34" s="23" t="inlineStr">
         <is>
-          <t>Rua CAMPO GRANDE</t>
+          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
         </is>
       </c>
       <c r="H34" s="23" t="inlineStr">
         <is>
-          <t>23 - 1 - R</t>
+          <t>1854 - C</t>
         </is>
       </c>
       <c r="I34" s="23" t="inlineStr">
         <is>
-          <t>25/08/2026 14:19</t>
+          <t>26/08/2026 17:51</t>
         </is>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>25/08/2026 14:25</t>
+          <t>26/08/2026 17:51</t>
         </is>
       </c>
       <c r="K34" s="23" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="23" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B35" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C35" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="24" t="inlineStr">
-        <is>
-          <t>16932408</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="inlineStr">
-        <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
-        </is>
-      </c>
-      <c r="F35" s="23" t="inlineStr">
-        <is>
-          <t>Q016</t>
-        </is>
-      </c>
-      <c r="G35" s="23" t="inlineStr">
-        <is>
-          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
-        </is>
-      </c>
-      <c r="H35" s="23" t="inlineStr">
-        <is>
-          <t>491 - TB</t>
-        </is>
-      </c>
-      <c r="I35" s="23" t="inlineStr">
-        <is>
-          <t>14/08/2026 10:00</t>
-        </is>
-      </c>
-      <c r="J35" s="23" t="inlineStr">
-        <is>
-          <t>14/08/2026 10:06</t>
-        </is>
-      </c>
-      <c r="K35" s="23" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="23" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B36" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C36" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="24" t="inlineStr">
-        <is>
-          <t>16932412</t>
-        </is>
-      </c>
-      <c r="E36" s="23" t="inlineStr">
-        <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
-        </is>
-      </c>
-      <c r="F36" s="23" t="inlineStr">
-        <is>
-          <t>Q016</t>
-        </is>
-      </c>
-      <c r="G36" s="23" t="inlineStr">
-        <is>
-          <t>Rua MARACAJU</t>
-        </is>
-      </c>
-      <c r="H36" s="23" t="inlineStr">
-        <is>
-          <t>194 - 3 - R</t>
-        </is>
-      </c>
-      <c r="I36" s="23" t="inlineStr">
-        <is>
-          <t>14/08/2026 10:00</t>
-        </is>
-      </c>
-      <c r="J36" s="23" t="inlineStr">
-        <is>
-          <t>14/08/2026 10:07</t>
-        </is>
-      </c>
-      <c r="K36" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="37">
-      <c r="A37" s="23" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B37" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C37" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" s="24" t="inlineStr">
-        <is>
-          <t>17149957</t>
-        </is>
-      </c>
-      <c r="E37" s="23" t="inlineStr">
-        <is>
-          <t>416 - CENTRO 2</t>
-        </is>
-      </c>
-      <c r="F37" s="23" t="inlineStr">
-        <is>
-          <t>Q012</t>
-        </is>
-      </c>
-      <c r="G37" s="23" t="inlineStr">
-        <is>
-          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
-        </is>
-      </c>
-      <c r="H37" s="23" t="inlineStr">
-        <is>
-          <t>01 - OU</t>
-        </is>
-      </c>
-      <c r="I37" s="23" t="inlineStr">
-        <is>
-          <t>26/08/2026 17:51</t>
-        </is>
-      </c>
-      <c r="J37" s="23" t="inlineStr">
-        <is>
-          <t>26/08/2026 17:51</t>
-        </is>
-      </c>
-      <c r="K37" s="23" t="inlineStr"/>
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>LEGENDA — CLASSIFICAÇÃO (baseada em % de Visitas Rápidas)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="23" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B38" s="23" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C38" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="24" t="inlineStr">
-        <is>
-          <t>17149955</t>
-        </is>
-      </c>
-      <c r="E38" s="23" t="inlineStr">
-        <is>
-          <t>416 - CENTRO 2</t>
-        </is>
-      </c>
-      <c r="F38" s="23" t="inlineStr">
-        <is>
-          <t>Q006</t>
-        </is>
-      </c>
-      <c r="G38" s="23" t="inlineStr">
-        <is>
-          <t>Avenida MARECHAL FLORIANO PEIXOTO</t>
-        </is>
-      </c>
-      <c r="H38" s="23" t="inlineStr">
-        <is>
-          <t>1854 - C</t>
-        </is>
-      </c>
-      <c r="I38" s="23" t="inlineStr">
-        <is>
-          <t>26/08/2026 17:51</t>
-        </is>
-      </c>
-      <c r="J38" s="23" t="inlineStr">
-        <is>
-          <t>26/08/2026 17:51</t>
-        </is>
-      </c>
-      <c r="K38" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>LEGENDA — CLASSIFICAÇÃO (baseada em % de Visitas Rápidas)</t>
-        </is>
-      </c>
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>🟢 NORMAL</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>% Rápidas até 10%</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>🟡 ATENÇÃO</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>% Rápidas entre 11% e 20%</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>🔴 CRÍTICO</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>% Rápidas acima de 20%</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>🟢 NORMAL</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t>% Rápidas até 10%</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>🟡 ATENÇÃO</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>% Rápidas entre 11% e 20%</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>🔴 CRÍTICO</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>% Rápidas acima de 20%</t>
-        </is>
-      </c>
-      <c r="C44" s="10" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="13" t="inlineStr">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>⚠️ SEQUÊNCIA SUSPEITA</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="45" customHeight="1">
-      <c r="A47" s="14" t="inlineStr">
+    <row r="43" ht="45" customHeight="1">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>Duas ou mais visitas consecutivas do mesmo agente registradas no MESMO MINUTO de chegada são marcadas como suspeitas (o e-Visita não registra segundos, então o critério de negócio de 50s de diferença equivale, na prática, a 'mesmo minuto') — sugere lançamento em lote no sistema, não visita real de campo. Colunas: 'Visitas em Sequência Suspeita' (total de visitas envolvidas) e 'Maior Sequência Suspeita' (maior número de visitas seguidas nessa condição). Na aba 'Visitas Suspeitas', a coluna 'Diferença p/ Anterior (s)*' fica em branco quando o alerta da linha veio do par com a visita SEGUINTE (não da anterior).</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>🍽️ VISITAS NO HORÁRIO DE ALMOÇO</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="70" customHeight="1">
-      <c r="A50" s="14" t="inlineStr">
+    <row r="46" ht="70" customHeight="1">
+      <c r="A46" s="14" t="inlineStr">
         <is>
           <t>Coluna 'Visitas no Almoço (11h15-12h45)' conta as visitas com chegada registrada nesse intervalo — o horário oficial de almoço é 11h15 às 12h45, JÁ COM 15 MINUTOS DE TOLERÂNCIA em cada borda (visitas entre 11h-11h15 ou 12h45-13h não são tratadas como violação, só como 'fora do expediente' genérico) — use para checar se o agente está trabalhando no horário de almoço ou se há erro de lançamento. Essas visitas ficam de fora do cálculo de 'Início/Fim Manhã' e 'Início/Fim Tarde', que usam a primeira chegada e a última saída de cada dia (não a média de todos os horários), para refletir melhor o início e o fim reais do expediente.</t>
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>💰 HORAS TRABALHADAS, HORAS ÚTEIS E CUSTO DA HORA ÚTIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>'Horas Trabalhadas' = jornada total do dia (primeira chegada até a última saída), descontando a sobreposição com o horário de almoço — depois tira-se a média entre os dias/semanas trabalhados, 'Horas Úteis' = soma das durações de visita no dia (tempo realmente dentro de imóveis), sem contar deslocamento entre visitas, 'Custo Hora Útil' = salário mensal do agente (R$ 4863,00, equivalente a 3 salários mínimos federais) dividido pelas horas úteis mensais estimadas (Média Horas Úteis/Dia × 22 dias úteis/mês). Quanto menos tempo o agente passa efetivamente em visita por dia, mais caro fica o custo por hora útil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
+        </is>
+      </c>
+    </row>
     <row r="52">
-      <c r="A52" s="16" t="inlineStr">
-        <is>
-          <t>💰 HORAS TRABALHADAS, HORAS ÚTEIS E CUSTO DA HORA ÚTIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" s="14" t="inlineStr">
-        <is>
-          <t>'Horas Trabalhadas' = jornada total do dia (primeira chegada até a última saída), descontando a sobreposição com o horário de almoço — depois tira-se a média entre os dias/semanas trabalhados, 'Horas Úteis' = soma das durações de visita no dia (tempo realmente dentro de imóveis), sem contar deslocamento entre visitas, 'Custo Hora Útil' = salário mensal do agente (R$ 4863,00, equivalente a 3 salários mínimos federais) dividido pelas horas úteis mensais estimadas (Média Horas Úteis/Dia × 22 dias úteis/mês). Quanto menos tempo o agente passa efetivamente em visita por dia, mais caro fica o custo por hora útil.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="17" t="inlineStr">
-        <is>
-          <t>ℹ️ A lista detalhada de visitas duplicadas (com endereço) está na aba 'Visitas Duplicadas' — use-a para localizar e excluir os registros repetidos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="17" t="inlineStr">
+      <c r="A52" s="17" t="inlineStr">
         <is>
           <t>ℹ️ Visitas com duração NEGATIVA (saída antes da chegada — provável bug do sistema) foram excluídas do cálculo de Média/Mediana e estão detalhadas na aba 'Visitas Negativas', para investigação junto ao suporte do e-Visita.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:K38"/>
+  <autoFilter ref="A2:K34"/>
   <mergeCells count="13">
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="B38:C38"/>
     <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A43:C43"/>
     <mergeCell ref="A46:C46"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="A48:C48"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="A51:C51"/>
     <mergeCell ref="A52:C52"/>
   </mergeCells>
   <hyperlinks>
@@ -47682,10 +47262,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D38" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -48690,7 +48266,7 @@
       </c>
       <c r="G15" s="29" t="inlineStr">
         <is>
-          <t>76 - 1 - TB</t>
+          <t>76 - 1 - OU</t>
         </is>
       </c>
       <c r="H15" s="29" t="inlineStr">
@@ -48710,47 +48286,47 @@
     <row r="16">
       <c r="A16" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B16" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C16" s="30" t="inlineStr">
         <is>
-          <t>16910074</t>
+          <t>17175604</t>
         </is>
       </c>
       <c r="D16" s="29" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E16" s="29" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="F16" s="29" t="inlineStr">
         <is>
-          <t>Rua CATANDUVA</t>
+          <t>Rua NATAL</t>
         </is>
       </c>
       <c r="G16" s="29" t="inlineStr">
         <is>
-          <t>165 - R</t>
+          <t>276 - R</t>
         </is>
       </c>
       <c r="H16" s="29" t="inlineStr">
         <is>
-          <t>13/08/2026 15:00</t>
+          <t>27/08/2026 16:35</t>
         </is>
       </c>
       <c r="I16" s="29" t="inlineStr">
         <is>
-          <t>13/08/2026 15:31</t>
+          <t>27/08/2026 17:06</t>
         </is>
       </c>
       <c r="J16" s="29" t="n">
@@ -48760,47 +48336,47 @@
     <row r="17">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B17" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C17" s="30" t="inlineStr">
         <is>
-          <t>17175604</t>
+          <t>16910074</t>
         </is>
       </c>
       <c r="D17" s="29" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E17" s="29" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="F17" s="29" t="inlineStr">
         <is>
-          <t>Rua NATAL</t>
+          <t>Rua CATANDUVA</t>
         </is>
       </c>
       <c r="G17" s="29" t="inlineStr">
         <is>
-          <t>276 - R</t>
+          <t>165 - R</t>
         </is>
       </c>
       <c r="H17" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 16:35</t>
+          <t>13/08/2026 15:00</t>
         </is>
       </c>
       <c r="I17" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 17:06</t>
+          <t>13/08/2026 15:31</t>
         </is>
       </c>
       <c r="J17" s="29" t="n">
@@ -48810,47 +48386,47 @@
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B18" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C18" s="30" t="inlineStr">
         <is>
-          <t>16928890</t>
+          <t>17070282</t>
         </is>
       </c>
       <c r="D18" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E18" s="29" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="F18" s="29" t="inlineStr">
         <is>
-          <t>Rua JOAQUIM PEREIRA TEIXEIRA</t>
+          <t>Rua BARRA VELHA</t>
         </is>
       </c>
       <c r="G18" s="29" t="inlineStr">
         <is>
-          <t>707 - R</t>
+          <t>696 - R</t>
         </is>
       </c>
       <c r="H18" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 16:28</t>
+          <t>21/08/2026 09:59</t>
         </is>
       </c>
       <c r="I18" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 16:56</t>
+          <t>21/08/2026 10:27</t>
         </is>
       </c>
       <c r="J18" s="29" t="n">
@@ -48860,47 +48436,47 @@
     <row r="19">
       <c r="A19" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B19" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C19" s="30" t="inlineStr">
         <is>
-          <t>17070282</t>
+          <t>16928890</t>
         </is>
       </c>
       <c r="D19" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E19" s="29" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="F19" s="29" t="inlineStr">
         <is>
-          <t>Rua BARRA VELHA</t>
+          <t>Rua JOAQUIM PEREIRA TEIXEIRA</t>
         </is>
       </c>
       <c r="G19" s="29" t="inlineStr">
         <is>
-          <t>696 - R</t>
+          <t>707 - R</t>
         </is>
       </c>
       <c r="H19" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 09:59</t>
+          <t>12/08/2026 16:28</t>
         </is>
       </c>
       <c r="I19" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 10:27</t>
+          <t>12/08/2026 16:56</t>
         </is>
       </c>
       <c r="J19" s="29" t="n">
@@ -48910,47 +48486,47 @@
     <row r="20">
       <c r="A20" s="29" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B20" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C20" s="30" t="inlineStr">
         <is>
-          <t>17128500</t>
+          <t>17076987</t>
         </is>
       </c>
       <c r="D20" s="29" t="inlineStr">
         <is>
-          <t>443 - KAMEL SAAD 1</t>
+          <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
       <c r="E20" s="29" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q012</t>
         </is>
       </c>
       <c r="F20" s="29" t="inlineStr">
         <is>
-          <t>Rua DAS ROSAS</t>
+          <t>Rua Anselmo Soares</t>
         </is>
       </c>
       <c r="G20" s="29" t="inlineStr">
         <is>
-          <t>03 - R</t>
+          <t>700 - 9 - TB</t>
         </is>
       </c>
       <c r="H20" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 10:11</t>
+          <t>19/08/2026 14:12</t>
         </is>
       </c>
       <c r="I20" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 10:38</t>
+          <t>19/08/2026 14:39</t>
         </is>
       </c>
       <c r="J20" s="29" t="n">
@@ -49010,47 +48586,47 @@
     <row r="22">
       <c r="A22" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="B22" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C22" s="30" t="inlineStr">
         <is>
-          <t>17076987</t>
+          <t>17128500</t>
         </is>
       </c>
       <c r="D22" s="29" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL</t>
+          <t>443 - KAMEL SAAD 1</t>
         </is>
       </c>
       <c r="E22" s="29" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="F22" s="29" t="inlineStr">
         <is>
-          <t>Rua Anselmo Soares</t>
+          <t>Rua DAS ROSAS</t>
         </is>
       </c>
       <c r="G22" s="29" t="inlineStr">
         <is>
-          <t>700 - 9 - TB</t>
+          <t>03 - R</t>
         </is>
       </c>
       <c r="H22" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 14:12</t>
+          <t>25/08/2026 10:11</t>
         </is>
       </c>
       <c r="I22" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 14:39</t>
+          <t>25/08/2026 10:38</t>
         </is>
       </c>
       <c r="J22" s="29" t="n">
@@ -49060,47 +48636,47 @@
     <row r="23">
       <c r="A23" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="B23" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C23" s="30" t="inlineStr">
         <is>
-          <t>17027677</t>
+          <t>17026385</t>
         </is>
       </c>
       <c r="D23" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E23" s="29" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F23" s="29" t="inlineStr">
         <is>
-          <t>Rua SÃO JOÃO DEL REI</t>
+          <t>Rua JABAQUARA</t>
         </is>
       </c>
       <c r="G23" s="29" t="inlineStr">
         <is>
-          <t>20 - R</t>
+          <t>26 - 2 - OU</t>
         </is>
       </c>
       <c r="H23" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 10:24</t>
+          <t>19/08/2026 09:27</t>
         </is>
       </c>
       <c r="I23" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 10:50</t>
+          <t>19/08/2026 09:53</t>
         </is>
       </c>
       <c r="J23" s="29" t="n">
@@ -49110,47 +48686,47 @@
     <row r="24">
       <c r="A24" s="29" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B24" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C24" s="30" t="inlineStr">
         <is>
-          <t>17026385</t>
+          <t>17027677</t>
         </is>
       </c>
       <c r="D24" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F24" s="29" t="inlineStr">
         <is>
-          <t>Rua JABAQUARA</t>
+          <t>Rua SÃO JOÃO DEL REI</t>
         </is>
       </c>
       <c r="G24" s="29" t="inlineStr">
         <is>
-          <t>26 - 2 - OU</t>
+          <t>20 - R</t>
         </is>
       </c>
       <c r="H24" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:27</t>
+          <t>18/08/2026 10:24</t>
         </is>
       </c>
       <c r="I24" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:53</t>
+          <t>18/08/2026 10:50</t>
         </is>
       </c>
       <c r="J24" s="29" t="n">
@@ -49310,7 +48886,7 @@
     <row r="28">
       <c r="A28" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Cris Milene Cardenas da Silva</t>
         </is>
       </c>
       <c r="B28" s="29" t="inlineStr">
@@ -49320,37 +48896,37 @@
       </c>
       <c r="C28" s="30" t="inlineStr">
         <is>
-          <t>17077037</t>
+          <t>17102942</t>
         </is>
       </c>
       <c r="D28" s="29" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL</t>
+          <t>403 - JARDIM UNIVERSITARIO</t>
         </is>
       </c>
       <c r="E28" s="29" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q036</t>
         </is>
       </c>
       <c r="F28" s="29" t="inlineStr">
         <is>
-          <t>Rua INÁCIO SUBTIL OLIVEIRA</t>
+          <t>Rua NELSON HUNGRIA</t>
         </is>
       </c>
       <c r="G28" s="29" t="inlineStr">
         <is>
-          <t>517 - R</t>
+          <t>194 - R</t>
         </is>
       </c>
       <c r="H28" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 08:51</t>
+          <t>24/08/2026 08:29</t>
         </is>
       </c>
       <c r="I28" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 09:14</t>
+          <t>24/08/2026 08:52</t>
         </is>
       </c>
       <c r="J28" s="29" t="n">
@@ -49470,7 +49046,7 @@
       </c>
       <c r="C31" s="30" t="inlineStr">
         <is>
-          <t>17071087</t>
+          <t>16986159</t>
         </is>
       </c>
       <c r="D31" s="29" t="inlineStr">
@@ -49480,27 +49056,27 @@
       </c>
       <c r="E31" s="29" t="inlineStr">
         <is>
-          <t>Q042</t>
+          <t>Q036</t>
         </is>
       </c>
       <c r="F31" s="29" t="inlineStr">
         <is>
-          <t>Rua POLICARPO DAVILA</t>
+          <t>Avenida ADJALMA SALDANHA</t>
         </is>
       </c>
       <c r="G31" s="29" t="inlineStr">
         <is>
-          <t>769 - R</t>
+          <t>873 - R</t>
         </is>
       </c>
       <c r="H31" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 14:34</t>
+          <t>18/08/2026 13:15</t>
         </is>
       </c>
       <c r="I31" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 14:57</t>
+          <t>18/08/2026 13:38</t>
         </is>
       </c>
       <c r="J31" s="29" t="n">
@@ -49510,7 +49086,7 @@
     <row r="32">
       <c r="A32" s="29" t="inlineStr">
         <is>
-          <t>Cris Milene Cardenas da Silva</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B32" s="29" t="inlineStr">
@@ -49520,37 +49096,37 @@
       </c>
       <c r="C32" s="30" t="inlineStr">
         <is>
-          <t>17102942</t>
+          <t>17077037</t>
         </is>
       </c>
       <c r="D32" s="29" t="inlineStr">
         <is>
-          <t>403 - JARDIM UNIVERSITARIO</t>
+          <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
       <c r="E32" s="29" t="inlineStr">
         <is>
-          <t>Q036</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="F32" s="29" t="inlineStr">
         <is>
-          <t>Rua NELSON HUNGRIA</t>
+          <t>Rua INÁCIO SUBTIL OLIVEIRA</t>
         </is>
       </c>
       <c r="G32" s="29" t="inlineStr">
         <is>
-          <t>194 - R</t>
+          <t>517 - R</t>
         </is>
       </c>
       <c r="H32" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 08:29</t>
+          <t>21/08/2026 08:51</t>
         </is>
       </c>
       <c r="I32" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 08:52</t>
+          <t>21/08/2026 09:14</t>
         </is>
       </c>
       <c r="J32" s="29" t="n">
@@ -49570,7 +49146,7 @@
       </c>
       <c r="C33" s="30" t="inlineStr">
         <is>
-          <t>16986159</t>
+          <t>17071087</t>
         </is>
       </c>
       <c r="D33" s="29" t="inlineStr">
@@ -49580,27 +49156,27 @@
       </c>
       <c r="E33" s="29" t="inlineStr">
         <is>
-          <t>Q036</t>
+          <t>Q042</t>
         </is>
       </c>
       <c r="F33" s="29" t="inlineStr">
         <is>
-          <t>Avenida ADJALMA SALDANHA</t>
+          <t>Rua POLICARPO DAVILA</t>
         </is>
       </c>
       <c r="G33" s="29" t="inlineStr">
         <is>
-          <t>873 - R</t>
+          <t>769 - R</t>
         </is>
       </c>
       <c r="H33" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 13:15</t>
+          <t>21/08/2026 14:34</t>
         </is>
       </c>
       <c r="I33" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 13:38</t>
+          <t>21/08/2026 14:57</t>
         </is>
       </c>
       <c r="J33" s="29" t="n">
@@ -49610,47 +49186,47 @@
     <row r="34">
       <c r="A34" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B34" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C34" s="30" t="inlineStr">
         <is>
-          <t>17148181</t>
+          <t>17011667</t>
         </is>
       </c>
       <c r="D34" s="29" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E34" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="F34" s="29" t="inlineStr">
         <is>
-          <t>Rua ARNALDO VASQUES</t>
+          <t>Rua HONOROPOLIS</t>
         </is>
       </c>
       <c r="G34" s="29" t="inlineStr">
         <is>
-          <t>325 - R</t>
+          <t>541 - R</t>
         </is>
       </c>
       <c r="H34" s="29" t="inlineStr">
         <is>
-          <t>26/08/2026 13:43</t>
+          <t>19/08/2026 08:55</t>
         </is>
       </c>
       <c r="I34" s="29" t="inlineStr">
         <is>
-          <t>26/08/2026 14:05</t>
+          <t>19/08/2026 09:17</t>
         </is>
       </c>
       <c r="J34" s="29" t="n">
@@ -49660,47 +49236,47 @@
     <row r="35">
       <c r="A35" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B35" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C35" s="30" t="inlineStr">
         <is>
-          <t>17130213</t>
+          <t>16762598</t>
         </is>
       </c>
       <c r="D35" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E35" s="29" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="F35" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA AZUL</t>
+          <t>Rua FRANCISCO FAUSTO MACENAS</t>
         </is>
       </c>
       <c r="G35" s="29" t="inlineStr">
         <is>
-          <t>222 - R</t>
+          <t>651 - 1 - R</t>
         </is>
       </c>
       <c r="H35" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:33</t>
+          <t>05/08/2026 10:06</t>
         </is>
       </c>
       <c r="I35" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:55</t>
+          <t>05/08/2026 10:28</t>
         </is>
       </c>
       <c r="J35" s="29" t="n">
@@ -49760,7 +49336,7 @@
     <row r="37">
       <c r="A37" s="29" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="B37" s="29" t="inlineStr">
@@ -49770,37 +49346,37 @@
       </c>
       <c r="C37" s="30" t="inlineStr">
         <is>
-          <t>17011667</t>
+          <t>17125360</t>
         </is>
       </c>
       <c r="D37" s="29" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>439 - BOSQUE CARANDÁ</t>
         </is>
       </c>
       <c r="E37" s="29" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="F37" s="29" t="inlineStr">
         <is>
-          <t>Rua HONOROPOLIS</t>
+          <t>Avenida PERPETUO SOCORRO</t>
         </is>
       </c>
       <c r="G37" s="29" t="inlineStr">
         <is>
-          <t>541 - R</t>
+          <t>03 - OU</t>
         </is>
       </c>
       <c r="H37" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 08:55</t>
+          <t>25/08/2026 09:35</t>
         </is>
       </c>
       <c r="I37" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:17</t>
+          <t>25/08/2026 09:57</t>
         </is>
       </c>
       <c r="J37" s="29" t="n">
@@ -49810,47 +49386,47 @@
     <row r="38">
       <c r="A38" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B38" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C38" s="30" t="inlineStr">
         <is>
-          <t>16762598</t>
+          <t>17148181</t>
         </is>
       </c>
       <c r="D38" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E38" s="29" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F38" s="29" t="inlineStr">
         <is>
-          <t>Rua FRANCISCO FAUSTO MACENAS</t>
+          <t>Rua ARNALDO VASQUES</t>
         </is>
       </c>
       <c r="G38" s="29" t="inlineStr">
         <is>
-          <t>651 - 1 - R</t>
+          <t>325 - R</t>
         </is>
       </c>
       <c r="H38" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 10:06</t>
+          <t>26/08/2026 13:43</t>
         </is>
       </c>
       <c r="I38" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 10:28</t>
+          <t>26/08/2026 14:05</t>
         </is>
       </c>
       <c r="J38" s="29" t="n">
@@ -49860,47 +49436,47 @@
     <row r="39">
       <c r="A39" s="29" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B39" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>17125360</t>
+          <t>17130213</t>
         </is>
       </c>
       <c r="D39" s="29" t="inlineStr">
         <is>
-          <t>439 - BOSQUE CARANDÁ</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E39" s="29" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F39" s="29" t="inlineStr">
         <is>
-          <t>Avenida PERPETUO SOCORRO</t>
+          <t>Rua ROSA AZUL</t>
         </is>
       </c>
       <c r="G39" s="29" t="inlineStr">
         <is>
-          <t>03 - OU</t>
+          <t>222 - R</t>
         </is>
       </c>
       <c r="H39" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:35</t>
+          <t>25/08/2026 15:33</t>
         </is>
       </c>
       <c r="I39" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:57</t>
+          <t>25/08/2026 15:55</t>
         </is>
       </c>
       <c r="J39" s="29" t="n">
@@ -49960,47 +49536,47 @@
     <row r="41">
       <c r="A41" s="29" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="B41" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C41" s="30" t="inlineStr">
         <is>
-          <t>16804508</t>
+          <t>17009505</t>
         </is>
       </c>
       <c r="D41" s="29" t="inlineStr">
         <is>
-          <t>407 - MOOCA</t>
+          <t>422 - VILA TORRES</t>
         </is>
       </c>
       <c r="E41" s="29" t="inlineStr">
         <is>
-          <t>Q038</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="F41" s="29" t="inlineStr">
         <is>
-          <t>Rua CEARÁ</t>
+          <t>Rua MANOEL DIAS DE PINHO</t>
         </is>
       </c>
       <c r="G41" s="29" t="inlineStr">
         <is>
-          <t>01 - TB</t>
+          <t>625 - 1 - C</t>
         </is>
       </c>
       <c r="H41" s="29" t="inlineStr">
         <is>
-          <t>06/08/2026 15:16</t>
+          <t>19/08/2026 15:31</t>
         </is>
       </c>
       <c r="I41" s="29" t="inlineStr">
         <is>
-          <t>06/08/2026 15:37</t>
+          <t>19/08/2026 15:52</t>
         </is>
       </c>
       <c r="J41" s="29" t="n">
@@ -50010,47 +49586,47 @@
     <row r="42">
       <c r="A42" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B42" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C42" s="30" t="inlineStr">
         <is>
-          <t>17027695</t>
+          <t>17130068</t>
         </is>
       </c>
       <c r="D42" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E42" s="29" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="F42" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA BRANCA</t>
+          <t>Rua AREIA BRANCA</t>
         </is>
       </c>
       <c r="G42" s="29" t="inlineStr">
         <is>
-          <t>140 - R</t>
+          <t>1194 - R</t>
         </is>
       </c>
       <c r="H42" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 08:57</t>
+          <t>25/08/2026 15:16</t>
         </is>
       </c>
       <c r="I42" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:18</t>
+          <t>25/08/2026 15:37</t>
         </is>
       </c>
       <c r="J42" s="29" t="n">
@@ -50110,47 +49686,47 @@
     <row r="44">
       <c r="A44" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B44" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C44" s="30" t="inlineStr">
         <is>
-          <t>17130068</t>
+          <t>17027695</t>
         </is>
       </c>
       <c r="D44" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E44" s="29" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="F44" s="29" t="inlineStr">
         <is>
-          <t>Rua AREIA BRANCA</t>
+          <t>Rua ROSA BRANCA</t>
         </is>
       </c>
       <c r="G44" s="29" t="inlineStr">
         <is>
-          <t>1194 - R</t>
+          <t>140 - R</t>
         </is>
       </c>
       <c r="H44" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:16</t>
+          <t>19/08/2026 08:57</t>
         </is>
       </c>
       <c r="I44" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:37</t>
+          <t>19/08/2026 09:18</t>
         </is>
       </c>
       <c r="J44" s="29" t="n">
@@ -50160,47 +49736,47 @@
     <row r="45">
       <c r="A45" s="29" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="B45" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C45" s="30" t="inlineStr">
         <is>
-          <t>17009505</t>
+          <t>16804508</t>
         </is>
       </c>
       <c r="D45" s="29" t="inlineStr">
         <is>
-          <t>422 - VILA TORRES</t>
+          <t>407 - MOOCA</t>
         </is>
       </c>
       <c r="E45" s="29" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q038</t>
         </is>
       </c>
       <c r="F45" s="29" t="inlineStr">
         <is>
-          <t>Rua MANOEL DIAS DE PINHO</t>
+          <t>Rua CEARÁ</t>
         </is>
       </c>
       <c r="G45" s="29" t="inlineStr">
         <is>
-          <t>625 - 1 - C</t>
+          <t>01 - TB</t>
         </is>
       </c>
       <c r="H45" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 15:31</t>
+          <t>06/08/2026 15:16</t>
         </is>
       </c>
       <c r="I45" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 15:52</t>
+          <t>06/08/2026 15:37</t>
         </is>
       </c>
       <c r="J45" s="29" t="n">
@@ -50210,7 +49786,7 @@
     <row r="46">
       <c r="A46" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B46" s="29" t="inlineStr">
@@ -50220,37 +49796,37 @@
       </c>
       <c r="C46" s="30" t="inlineStr">
         <is>
-          <t>17112709</t>
+          <t>17098947</t>
         </is>
       </c>
       <c r="D46" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E46" s="29" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F46" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA AZUL</t>
+          <t>Rua FELIPE DE BRUM</t>
         </is>
       </c>
       <c r="G46" s="29" t="inlineStr">
         <is>
-          <t>295 - 1 - R</t>
+          <t>75 - R</t>
         </is>
       </c>
       <c r="H46" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:00</t>
+          <t>24/08/2026 09:26</t>
         </is>
       </c>
       <c r="I46" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:20</t>
+          <t>24/08/2026 09:46</t>
         </is>
       </c>
       <c r="J46" s="29" t="n">
@@ -50260,47 +49836,47 @@
     <row r="47">
       <c r="A47" s="29" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B47" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C47" s="30" t="inlineStr">
         <is>
-          <t>17153643</t>
+          <t>16879459</t>
         </is>
       </c>
       <c r="D47" s="29" t="inlineStr">
         <is>
-          <t>402 - JARDIM MARAMBAIA</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E47" s="29" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q025</t>
         </is>
       </c>
       <c r="F47" s="29" t="inlineStr">
         <is>
-          <t>Rua CORONEL ORLANDO SAPUCAIA</t>
+          <t>Rua EPTACIO PESSOA</t>
         </is>
       </c>
       <c r="G47" s="29" t="inlineStr">
         <is>
-          <t>17 - R</t>
+          <t>245 - 1 - R</t>
         </is>
       </c>
       <c r="H47" s="29" t="inlineStr">
         <is>
-          <t>26/08/2026 14:07</t>
+          <t>12/08/2026 10:11</t>
         </is>
       </c>
       <c r="I47" s="29" t="inlineStr">
         <is>
-          <t>26/08/2026 14:27</t>
+          <t>12/08/2026 10:31</t>
         </is>
       </c>
       <c r="J47" s="29" t="n">
@@ -50310,47 +49886,47 @@
     <row r="48">
       <c r="A48" s="29" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B48" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C48" s="30" t="inlineStr">
         <is>
-          <t>16879459</t>
+          <t>16762591</t>
         </is>
       </c>
       <c r="D48" s="29" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E48" s="29" t="inlineStr">
         <is>
-          <t>Q025</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="F48" s="29" t="inlineStr">
         <is>
-          <t>Rua EPTACIO PESSOA</t>
+          <t>Rua ROBERTO BUENO DA SILVA</t>
         </is>
       </c>
       <c r="G48" s="29" t="inlineStr">
         <is>
-          <t>245 - 1 - R</t>
+          <t>486 - OU</t>
         </is>
       </c>
       <c r="H48" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 10:11</t>
+          <t>05/08/2026 08:45</t>
         </is>
       </c>
       <c r="I48" s="29" t="inlineStr">
         <is>
-          <t>12/08/2026 10:31</t>
+          <t>05/08/2026 09:05</t>
         </is>
       </c>
       <c r="J48" s="29" t="n">
@@ -50360,47 +49936,47 @@
     <row r="49">
       <c r="A49" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B49" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C49" s="30" t="inlineStr">
         <is>
-          <t>16783019</t>
+          <t>16938750</t>
         </is>
       </c>
       <c r="D49" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E49" s="29" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="F49" s="29" t="inlineStr">
         <is>
-          <t>Rua MONTEVIDEO</t>
+          <t>Rua SAO CRISTOVAO</t>
         </is>
       </c>
       <c r="G49" s="29" t="inlineStr">
         <is>
-          <t>301 - R</t>
+          <t>14 - 1 - R</t>
         </is>
       </c>
       <c r="H49" s="29" t="inlineStr">
         <is>
-          <t>06/08/2026 16:07</t>
+          <t>14/08/2026 09:53</t>
         </is>
       </c>
       <c r="I49" s="29" t="inlineStr">
         <is>
-          <t>06/08/2026 16:27</t>
+          <t>14/08/2026 10:13</t>
         </is>
       </c>
       <c r="J49" s="29" t="n">
@@ -50410,47 +49986,47 @@
     <row r="50">
       <c r="A50" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B50" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C50" s="30" t="inlineStr">
         <is>
-          <t>16938750</t>
+          <t>16783019</t>
         </is>
       </c>
       <c r="D50" s="29" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E50" s="29" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F50" s="29" t="inlineStr">
         <is>
-          <t>Rua SAO CRISTOVAO</t>
+          <t>Rua MONTEVIDEO</t>
         </is>
       </c>
       <c r="G50" s="29" t="inlineStr">
         <is>
-          <t>14 - 1 - R</t>
+          <t>301 - R</t>
         </is>
       </c>
       <c r="H50" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 09:53</t>
+          <t>06/08/2026 16:07</t>
         </is>
       </c>
       <c r="I50" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 10:13</t>
+          <t>06/08/2026 16:27</t>
         </is>
       </c>
       <c r="J50" s="29" t="n">
@@ -50460,47 +50036,47 @@
     <row r="51">
       <c r="A51" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="B51" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C51" s="30" t="inlineStr">
         <is>
-          <t>16762591</t>
+          <t>17028733</t>
         </is>
       </c>
       <c r="D51" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>407 - MOOCA</t>
         </is>
       </c>
       <c r="E51" s="29" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q043</t>
         </is>
       </c>
       <c r="F51" s="29" t="inlineStr">
         <is>
-          <t>Rua ROBERTO BUENO DA SILVA</t>
+          <t>Rua GEOVAI</t>
         </is>
       </c>
       <c r="G51" s="29" t="inlineStr">
         <is>
-          <t>486 - OU</t>
+          <t>213 - 1 - R</t>
         </is>
       </c>
       <c r="H51" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 08:45</t>
+          <t>19/08/2026 14:39</t>
         </is>
       </c>
       <c r="I51" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 09:05</t>
+          <t>19/08/2026 14:59</t>
         </is>
       </c>
       <c r="J51" s="29" t="n">
@@ -50510,7 +50086,7 @@
     <row r="52">
       <c r="A52" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B52" s="29" t="inlineStr">
@@ -50520,37 +50096,37 @@
       </c>
       <c r="C52" s="30" t="inlineStr">
         <is>
-          <t>17098947</t>
+          <t>17112709</t>
         </is>
       </c>
       <c r="D52" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E52" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F52" s="29" t="inlineStr">
         <is>
-          <t>Rua FELIPE DE BRUM</t>
+          <t>Rua ROSA AZUL</t>
         </is>
       </c>
       <c r="G52" s="29" t="inlineStr">
         <is>
-          <t>75 - R</t>
+          <t>295 - 1 - R</t>
         </is>
       </c>
       <c r="H52" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:26</t>
+          <t>24/08/2026 15:00</t>
         </is>
       </c>
       <c r="I52" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:46</t>
+          <t>24/08/2026 15:20</t>
         </is>
       </c>
       <c r="J52" s="29" t="n">
@@ -50560,7 +50136,7 @@
     <row r="53">
       <c r="A53" s="29" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="B53" s="29" t="inlineStr">
@@ -50570,37 +50146,37 @@
       </c>
       <c r="C53" s="30" t="inlineStr">
         <is>
-          <t>17028733</t>
+          <t>17153643</t>
         </is>
       </c>
       <c r="D53" s="29" t="inlineStr">
         <is>
-          <t>407 - MOOCA</t>
+          <t>402 - JARDIM MARAMBAIA</t>
         </is>
       </c>
       <c r="E53" s="29" t="inlineStr">
         <is>
-          <t>Q043</t>
+          <t>Q032</t>
         </is>
       </c>
       <c r="F53" s="29" t="inlineStr">
         <is>
-          <t>Rua GEOVAI</t>
+          <t>Rua CORONEL ORLANDO SAPUCAIA</t>
         </is>
       </c>
       <c r="G53" s="29" t="inlineStr">
         <is>
-          <t>213 - 1 - R</t>
+          <t>17 - R</t>
         </is>
       </c>
       <c r="H53" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 14:39</t>
+          <t>26/08/2026 14:07</t>
         </is>
       </c>
       <c r="I53" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 14:59</t>
+          <t>26/08/2026 14:27</t>
         </is>
       </c>
       <c r="J53" s="29" t="n">
@@ -50660,47 +50236,47 @@
     <row r="55">
       <c r="A55" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="B55" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C55" s="30" t="inlineStr">
         <is>
-          <t>16971726</t>
+          <t>16947422</t>
         </is>
       </c>
       <c r="D55" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E55" s="29" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="F55" s="29" t="inlineStr">
         <is>
-          <t>Rua VICENTE  AZAMBUJA</t>
+          <t>Avenida BELMIRO DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="G55" s="29" t="inlineStr">
         <is>
-          <t>15 - R</t>
+          <t>2727 - R</t>
         </is>
       </c>
       <c r="H55" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 08:29</t>
+          <t>14/08/2026 08:56</t>
         </is>
       </c>
       <c r="I55" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 08:48</t>
+          <t>14/08/2026 09:15</t>
         </is>
       </c>
       <c r="J55" s="29" t="n">
@@ -50710,7 +50286,7 @@
     <row r="56">
       <c r="A56" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B56" s="29" t="inlineStr">
@@ -50720,7 +50296,7 @@
       </c>
       <c r="C56" s="30" t="inlineStr">
         <is>
-          <t>17066233</t>
+          <t>16971726</t>
         </is>
       </c>
       <c r="D56" s="29" t="inlineStr">
@@ -50730,27 +50306,27 @@
       </c>
       <c r="E56" s="29" t="inlineStr">
         <is>
-          <t>Q005</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="F56" s="29" t="inlineStr">
         <is>
-          <t>Rua CAPÃO BONITO</t>
+          <t>Rua VICENTE  AZAMBUJA</t>
         </is>
       </c>
       <c r="G56" s="29" t="inlineStr">
         <is>
-          <t>191 - R</t>
+          <t>15 - R</t>
         </is>
       </c>
       <c r="H56" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:01</t>
+          <t>18/08/2026 08:29</t>
         </is>
       </c>
       <c r="I56" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:20</t>
+          <t>18/08/2026 08:48</t>
         </is>
       </c>
       <c r="J56" s="29" t="n">
@@ -50760,47 +50336,47 @@
     <row r="57">
       <c r="A57" s="29" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B57" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C57" s="30" t="inlineStr">
         <is>
-          <t>16947422</t>
+          <t>17098960</t>
         </is>
       </c>
       <c r="D57" s="29" t="inlineStr">
         <is>
-          <t>449 - ÁREA C RESIDENCIAL PONTA PORÃ 1</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E57" s="29" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F57" s="29" t="inlineStr">
         <is>
-          <t>Avenida BELMIRO DE ALBUQUERQUE</t>
+          <t>Avenida COMANDANTE CARDOSO</t>
         </is>
       </c>
       <c r="G57" s="29" t="inlineStr">
         <is>
-          <t>2727 - R</t>
+          <t>360 - 1 - R</t>
         </is>
       </c>
       <c r="H57" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 08:56</t>
+          <t>24/08/2026 15:24</t>
         </is>
       </c>
       <c r="I57" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 09:15</t>
+          <t>24/08/2026 15:43</t>
         </is>
       </c>
       <c r="J57" s="29" t="n">
@@ -50810,47 +50386,47 @@
     <row r="58">
       <c r="A58" s="29" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B58" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C58" s="30" t="inlineStr">
         <is>
-          <t>16759717</t>
+          <t>17066233</t>
         </is>
       </c>
       <c r="D58" s="29" t="inlineStr">
         <is>
-          <t>421 - JARDIM IPANEMA</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E58" s="29" t="inlineStr">
         <is>
-          <t>Q035</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="F58" s="29" t="inlineStr">
         <is>
-          <t>Rua BALTAZAR SALDANHA</t>
+          <t>Rua CAPÃO BONITO</t>
         </is>
       </c>
       <c r="G58" s="29" t="inlineStr">
         <is>
-          <t>779 - OU</t>
+          <t>191 - R</t>
         </is>
       </c>
       <c r="H58" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 09:03</t>
+          <t>17/08/2026 09:01</t>
         </is>
       </c>
       <c r="I58" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 09:22</t>
+          <t>17/08/2026 09:20</t>
         </is>
       </c>
       <c r="J58" s="29" t="n">
@@ -50860,7 +50436,7 @@
     <row r="59">
       <c r="A59" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B59" s="29" t="inlineStr">
@@ -50870,37 +50446,37 @@
       </c>
       <c r="C59" s="30" t="inlineStr">
         <is>
-          <t>17098960</t>
+          <t>16759239</t>
         </is>
       </c>
       <c r="D59" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E59" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="F59" s="29" t="inlineStr">
         <is>
-          <t>Avenida COMANDANTE CARDOSO</t>
+          <t>Rua AEROPORTO VIRACOPOS</t>
         </is>
       </c>
       <c r="G59" s="29" t="inlineStr">
         <is>
-          <t>360 - 1 - R</t>
+          <t>920 - 1 - R</t>
         </is>
       </c>
       <c r="H59" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:24</t>
+          <t>05/08/2026 15:01</t>
         </is>
       </c>
       <c r="I59" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:43</t>
+          <t>05/08/2026 15:20</t>
         </is>
       </c>
       <c r="J59" s="29" t="n">
@@ -50910,7 +50486,7 @@
     <row r="60">
       <c r="A60" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="B60" s="29" t="inlineStr">
@@ -50920,37 +50496,37 @@
       </c>
       <c r="C60" s="30" t="inlineStr">
         <is>
-          <t>16759239</t>
+          <t>16759717</t>
         </is>
       </c>
       <c r="D60" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>421 - JARDIM IPANEMA</t>
         </is>
       </c>
       <c r="E60" s="29" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q035</t>
         </is>
       </c>
       <c r="F60" s="29" t="inlineStr">
         <is>
-          <t>Rua AEROPORTO VIRACOPOS</t>
+          <t>Rua BALTAZAR SALDANHA</t>
         </is>
       </c>
       <c r="G60" s="29" t="inlineStr">
         <is>
-          <t>920 - 1 - R</t>
+          <t>779 - OU</t>
         </is>
       </c>
       <c r="H60" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 15:01</t>
+          <t>05/08/2026 09:03</t>
         </is>
       </c>
       <c r="I60" s="29" t="inlineStr">
         <is>
-          <t>05/08/2026 15:20</t>
+          <t>05/08/2026 09:22</t>
         </is>
       </c>
       <c r="J60" s="29" t="n">
@@ -51010,7 +50586,7 @@
     <row r="62">
       <c r="A62" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B62" s="29" t="inlineStr">
@@ -51020,7 +50596,7 @@
       </c>
       <c r="C62" s="30" t="inlineStr">
         <is>
-          <t>17051418</t>
+          <t>17034408</t>
         </is>
       </c>
       <c r="D62" s="29" t="inlineStr">
@@ -51030,27 +50606,27 @@
       </c>
       <c r="E62" s="29" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F62" s="29" t="inlineStr">
         <is>
-          <t>Rua AFONSO DE ALBUQUERQUE</t>
+          <t>Rua JABAQUARA</t>
         </is>
       </c>
       <c r="G62" s="29" t="inlineStr">
         <is>
-          <t>231 - 3 - R</t>
+          <t>1370 - 4 - R</t>
         </is>
       </c>
       <c r="H62" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 14:18</t>
+          <t>19/08/2026 10:05</t>
         </is>
       </c>
       <c r="I62" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 14:36</t>
+          <t>19/08/2026 10:23</t>
         </is>
       </c>
       <c r="J62" s="29" t="n">
@@ -51110,47 +50686,47 @@
     <row r="64">
       <c r="A64" s="29" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B64" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C64" s="30" t="inlineStr">
         <is>
-          <t>16935897</t>
+          <t>17130027</t>
         </is>
       </c>
       <c r="D64" s="29" t="inlineStr">
         <is>
-          <t>417 - CENTRO 3</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E64" s="29" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="F64" s="29" t="inlineStr">
         <is>
-          <t>Avenida PRESIDENTE VARGAS</t>
+          <t>Rua BARRA VELHA</t>
         </is>
       </c>
       <c r="G64" s="29" t="inlineStr">
         <is>
-          <t>725 - OU</t>
+          <t>1154 - R</t>
         </is>
       </c>
       <c r="H64" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 09:40</t>
+          <t>25/08/2026 09:31</t>
         </is>
       </c>
       <c r="I64" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 09:58</t>
+          <t>25/08/2026 09:49</t>
         </is>
       </c>
       <c r="J64" s="29" t="n">
@@ -51260,47 +50836,47 @@
     <row r="67">
       <c r="A67" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B67" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C67" s="30" t="inlineStr">
         <is>
-          <t>16986947</t>
+          <t>17051418</t>
         </is>
       </c>
       <c r="D67" s="29" t="inlineStr">
         <is>
-          <t>420 - FERROVIARIA</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E67" s="29" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="F67" s="29" t="inlineStr">
         <is>
-          <t>Beco PROJETADA 06 FERROVIARIA</t>
+          <t>Rua AFONSO DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="G67" s="29" t="inlineStr">
         <is>
-          <t>113 - R</t>
+          <t>231 - 3 - R</t>
         </is>
       </c>
       <c r="H67" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 08:15</t>
+          <t>19/08/2026 14:18</t>
         </is>
       </c>
       <c r="I67" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 08:33</t>
+          <t>19/08/2026 14:36</t>
         </is>
       </c>
       <c r="J67" s="29" t="n">
@@ -51310,7 +50886,7 @@
     <row r="68">
       <c r="A68" s="29" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="B68" s="29" t="inlineStr">
@@ -51320,37 +50896,37 @@
       </c>
       <c r="C68" s="30" t="inlineStr">
         <is>
-          <t>17043615</t>
+          <t>16935897</t>
         </is>
       </c>
       <c r="D68" s="29" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>417 - CENTRO 3</t>
         </is>
       </c>
       <c r="E68" s="29" t="inlineStr">
         <is>
-          <t>Q035</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F68" s="29" t="inlineStr">
         <is>
-          <t>Rua FELIPE DE BRUM</t>
+          <t>Avenida PRESIDENTE VARGAS</t>
         </is>
       </c>
       <c r="G68" s="29" t="inlineStr">
         <is>
-          <t>900 - R</t>
+          <t>725 - OU</t>
         </is>
       </c>
       <c r="H68" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 14:30</t>
+          <t>14/08/2026 09:40</t>
         </is>
       </c>
       <c r="I68" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 14:48</t>
+          <t>14/08/2026 09:58</t>
         </is>
       </c>
       <c r="J68" s="29" t="n">
@@ -51360,47 +50936,47 @@
     <row r="69">
       <c r="A69" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B69" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C69" s="30" t="inlineStr">
         <is>
-          <t>17130027</t>
+          <t>17043615</t>
         </is>
       </c>
       <c r="D69" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E69" s="29" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q035</t>
         </is>
       </c>
       <c r="F69" s="29" t="inlineStr">
         <is>
-          <t>Rua BARRA VELHA</t>
+          <t>Rua FELIPE DE BRUM</t>
         </is>
       </c>
       <c r="G69" s="29" t="inlineStr">
         <is>
-          <t>1154 - R</t>
+          <t>900 - R</t>
         </is>
       </c>
       <c r="H69" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:31</t>
+          <t>20/08/2026 14:30</t>
         </is>
       </c>
       <c r="I69" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:49</t>
+          <t>20/08/2026 14:48</t>
         </is>
       </c>
       <c r="J69" s="29" t="n">
@@ -51410,47 +50986,47 @@
     <row r="70">
       <c r="A70" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B70" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>17034408</t>
+          <t>16986947</t>
         </is>
       </c>
       <c r="D70" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>420 - FERROVIARIA</t>
         </is>
       </c>
       <c r="E70" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="F70" s="29" t="inlineStr">
         <is>
-          <t>Rua JABAQUARA</t>
+          <t>Beco PROJETADA 06 FERROVIARIA</t>
         </is>
       </c>
       <c r="G70" s="29" t="inlineStr">
         <is>
-          <t>1370 - 4 - R</t>
+          <t>113 - R</t>
         </is>
       </c>
       <c r="H70" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:05</t>
+          <t>18/08/2026 08:15</t>
         </is>
       </c>
       <c r="I70" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:23</t>
+          <t>18/08/2026 08:33</t>
         </is>
       </c>
       <c r="J70" s="29" t="n">
@@ -51510,47 +51086,47 @@
     <row r="72">
       <c r="A72" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B72" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C72" s="30" t="inlineStr">
         <is>
-          <t>17070288</t>
+          <t>17043629</t>
         </is>
       </c>
       <c r="D72" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E72" s="29" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q034</t>
         </is>
       </c>
       <c r="F72" s="29" t="inlineStr">
         <is>
-          <t>Rua JABAQUARA</t>
+          <t>Rua ARAPONGAS</t>
         </is>
       </c>
       <c r="G72" s="29" t="inlineStr">
         <is>
-          <t>1490 - C</t>
+          <t>142 - R</t>
         </is>
       </c>
       <c r="H72" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 15:07</t>
+          <t>20/08/2026 15:52</t>
         </is>
       </c>
       <c r="I72" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 15:24</t>
+          <t>20/08/2026 16:09</t>
         </is>
       </c>
       <c r="J72" s="29" t="n">
@@ -51560,47 +51136,47 @@
     <row r="73">
       <c r="A73" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B73" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C73" s="30" t="inlineStr">
         <is>
-          <t>17022532</t>
+          <t>17027724</t>
         </is>
       </c>
       <c r="D73" s="29" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E73" s="29" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q026</t>
         </is>
       </c>
       <c r="F73" s="29" t="inlineStr">
         <is>
-          <t>Rua MARINGA</t>
+          <t>Rua ROSA VERMELHA JDR</t>
         </is>
       </c>
       <c r="G73" s="29" t="inlineStr">
         <is>
-          <t>807 - R</t>
+          <t>292 - R</t>
         </is>
       </c>
       <c r="H73" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:53</t>
+          <t>20/08/2026 09:26</t>
         </is>
       </c>
       <c r="I73" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 10:10</t>
+          <t>20/08/2026 09:43</t>
         </is>
       </c>
       <c r="J73" s="29" t="n">
@@ -51810,47 +51386,47 @@
     <row r="78">
       <c r="A78" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="B78" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C78" s="30" t="inlineStr">
         <is>
-          <t>17041447</t>
+          <t>17100546</t>
         </is>
       </c>
       <c r="D78" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>440 - JARDIM IBIRAPUERA</t>
         </is>
       </c>
       <c r="E78" s="29" t="inlineStr">
         <is>
-          <t>Q038</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="F78" s="29" t="inlineStr">
         <is>
-          <t>Rua DAS PEROBAS</t>
+          <t>Avenida BELMIRO DE ALBUQUERQUE</t>
         </is>
       </c>
       <c r="G78" s="29" t="inlineStr">
         <is>
-          <t>1018 - R</t>
+          <t>3933 - R</t>
         </is>
       </c>
       <c r="H78" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 14:48</t>
+          <t>21/08/2026 14:04</t>
         </is>
       </c>
       <c r="I78" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 15:05</t>
+          <t>21/08/2026 14:21</t>
         </is>
       </c>
       <c r="J78" s="29" t="n">
@@ -52010,7 +51586,7 @@
     <row r="82">
       <c r="A82" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B82" s="29" t="inlineStr">
@@ -52020,37 +51596,37 @@
       </c>
       <c r="C82" s="30" t="inlineStr">
         <is>
-          <t>17070286</t>
+          <t>17022532</t>
         </is>
       </c>
       <c r="D82" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E82" s="29" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F82" s="29" t="inlineStr">
         <is>
-          <t>Rua GUAÍBA</t>
+          <t>Rua MARINGA</t>
         </is>
       </c>
       <c r="G82" s="29" t="inlineStr">
         <is>
-          <t>1262 - C</t>
+          <t>807 - R</t>
         </is>
       </c>
       <c r="H82" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 14:40</t>
+          <t>17/08/2026 09:53</t>
         </is>
       </c>
       <c r="I82" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 14:57</t>
+          <t>17/08/2026 10:10</t>
         </is>
       </c>
       <c r="J82" s="29" t="n">
@@ -52060,7 +51636,7 @@
     <row r="83">
       <c r="A83" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B83" s="29" t="inlineStr">
@@ -52070,7 +51646,7 @@
       </c>
       <c r="C83" s="30" t="inlineStr">
         <is>
-          <t>17064916</t>
+          <t>17070286</t>
         </is>
       </c>
       <c r="D83" s="29" t="inlineStr">
@@ -52080,27 +51656,27 @@
       </c>
       <c r="E83" s="29" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F83" s="29" t="inlineStr">
         <is>
-          <t>Rua RIACHO DOCE</t>
+          <t>Rua GUAÍBA</t>
         </is>
       </c>
       <c r="G83" s="29" t="inlineStr">
         <is>
-          <t>78 - R</t>
+          <t>1262 - C</t>
         </is>
       </c>
       <c r="H83" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 14:00</t>
+          <t>21/08/2026 14:40</t>
         </is>
       </c>
       <c r="I83" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 14:17</t>
+          <t>21/08/2026 14:57</t>
         </is>
       </c>
       <c r="J83" s="29" t="n">
@@ -52260,47 +51836,47 @@
     <row r="87">
       <c r="A87" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B87" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C87" s="30" t="inlineStr">
         <is>
-          <t>17073307</t>
+          <t>16971696</t>
         </is>
       </c>
       <c r="D87" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E87" s="29" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="F87" s="29" t="inlineStr">
         <is>
-          <t>Avenida ANTONIO JOAO</t>
+          <t>Rua TENENTE SAMUEL DE ALMEIDA</t>
         </is>
       </c>
       <c r="G87" s="29" t="inlineStr">
         <is>
-          <t>1477 - R</t>
+          <t>630 - 1 - R</t>
         </is>
       </c>
       <c r="H87" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 13:54</t>
+          <t>17/08/2026 10:58</t>
         </is>
       </c>
       <c r="I87" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 14:11</t>
+          <t>17/08/2026 11:15</t>
         </is>
       </c>
       <c r="J87" s="29" t="n">
@@ -52360,47 +51936,47 @@
     <row r="89">
       <c r="A89" s="29" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B89" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C89" s="30" t="inlineStr">
         <is>
-          <t>17043629</t>
+          <t>17064916</t>
         </is>
       </c>
       <c r="D89" s="29" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E89" s="29" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="F89" s="29" t="inlineStr">
         <is>
-          <t>Rua ARAPONGAS</t>
+          <t>Rua RIACHO DOCE</t>
         </is>
       </c>
       <c r="G89" s="29" t="inlineStr">
         <is>
-          <t>142 - R</t>
+          <t>78 - R</t>
         </is>
       </c>
       <c r="H89" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 15:52</t>
+          <t>18/08/2026 14:00</t>
         </is>
       </c>
       <c r="I89" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 16:09</t>
+          <t>18/08/2026 14:17</t>
         </is>
       </c>
       <c r="J89" s="29" t="n">
@@ -52410,22 +51986,22 @@
     <row r="90">
       <c r="A90" s="29" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="B90" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C90" s="30" t="inlineStr">
         <is>
-          <t>17014581</t>
+          <t>16960061</t>
         </is>
       </c>
       <c r="D90" s="29" t="inlineStr">
         <is>
-          <t>433 - ÁREA A - RESIDENCIAL PONTA PORÃ 1</t>
+          <t>443 - KAMEL SAAD 1</t>
         </is>
       </c>
       <c r="E90" s="29" t="inlineStr">
@@ -52435,22 +52011,22 @@
       </c>
       <c r="F90" s="29" t="inlineStr">
         <is>
-          <t>Rua GUARANTA</t>
+          <t>Rua SALIM DERZI</t>
         </is>
       </c>
       <c r="G90" s="29" t="inlineStr">
         <is>
-          <t>295 - 1 - TB</t>
+          <t>118 - R</t>
         </is>
       </c>
       <c r="H90" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:45</t>
+          <t>17/08/2026 10:37</t>
         </is>
       </c>
       <c r="I90" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:02</t>
+          <t>17/08/2026 10:54</t>
         </is>
       </c>
       <c r="J90" s="29" t="n">
@@ -52460,47 +52036,47 @@
     <row r="91">
       <c r="A91" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Alana Amanda Fernandes Ovelar</t>
         </is>
       </c>
       <c r="B91" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C91" s="30" t="inlineStr">
         <is>
-          <t>17027724</t>
+          <t>17014581</t>
         </is>
       </c>
       <c r="D91" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>433 - ÁREA A - RESIDENCIAL PONTA PORÃ 1</t>
         </is>
       </c>
       <c r="E91" s="29" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F91" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA VERMELHA JDR</t>
+          <t>Rua GUARANTA</t>
         </is>
       </c>
       <c r="G91" s="29" t="inlineStr">
         <is>
-          <t>292 - R</t>
+          <t>295 - 1 - TB</t>
         </is>
       </c>
       <c r="H91" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 09:26</t>
+          <t>19/08/2026 09:45</t>
         </is>
       </c>
       <c r="I91" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 09:43</t>
+          <t>19/08/2026 10:02</t>
         </is>
       </c>
       <c r="J91" s="29" t="n">
@@ -52510,47 +52086,47 @@
     <row r="92">
       <c r="A92" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B92" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C92" s="30" t="inlineStr">
         <is>
-          <t>16971696</t>
+          <t>16945205</t>
         </is>
       </c>
       <c r="D92" s="29" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E92" s="29" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F92" s="29" t="inlineStr">
         <is>
-          <t>Rua TENENTE SAMUEL DE ALMEIDA</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="G92" s="29" t="inlineStr">
         <is>
-          <t>630 - 1 - R</t>
+          <t>3974 - 10 - R - 151</t>
         </is>
       </c>
       <c r="H92" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 10:58</t>
+          <t>14/08/2026 13:40</t>
         </is>
       </c>
       <c r="I92" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 11:15</t>
+          <t>14/08/2026 13:57</t>
         </is>
       </c>
       <c r="J92" s="29" t="n">
@@ -52560,47 +52136,47 @@
     <row r="93">
       <c r="A93" s="29" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B93" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C93" s="30" t="inlineStr">
         <is>
-          <t>16932380</t>
+          <t>17070288</t>
         </is>
       </c>
       <c r="D93" s="29" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E93" s="29" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="F93" s="29" t="inlineStr">
         <is>
-          <t>Rua CURITIBA</t>
+          <t>Rua JABAQUARA</t>
         </is>
       </c>
       <c r="G93" s="29" t="inlineStr">
         <is>
-          <t>01 - TB</t>
+          <t>1490 - C</t>
         </is>
       </c>
       <c r="H93" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 15:51</t>
+          <t>21/08/2026 15:07</t>
         </is>
       </c>
       <c r="I93" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 16:08</t>
+          <t>21/08/2026 15:24</t>
         </is>
       </c>
       <c r="J93" s="29" t="n">
@@ -52610,47 +52186,47 @@
     <row r="94">
       <c r="A94" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B94" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C94" s="30" t="inlineStr">
         <is>
-          <t>16945205</t>
+          <t>16932380</t>
         </is>
       </c>
       <c r="D94" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E94" s="29" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="F94" s="29" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Rua CURITIBA</t>
         </is>
       </c>
       <c r="G94" s="29" t="inlineStr">
         <is>
-          <t>3974 - 10 - R - 151</t>
+          <t>01 - TB</t>
         </is>
       </c>
       <c r="H94" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 13:40</t>
+          <t>14/08/2026 15:51</t>
         </is>
       </c>
       <c r="I94" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 13:57</t>
+          <t>14/08/2026 16:08</t>
         </is>
       </c>
       <c r="J94" s="29" t="n">
@@ -52660,47 +52236,47 @@
     <row r="95">
       <c r="A95" s="29" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B95" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C95" s="30" t="inlineStr">
         <is>
-          <t>17100546</t>
+          <t>17073314</t>
         </is>
       </c>
       <c r="D95" s="29" t="inlineStr">
         <is>
-          <t>440 - JARDIM IBIRAPUERA</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E95" s="29" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F95" s="29" t="inlineStr">
         <is>
-          <t>Avenida BELMIRO DE ALBUQUERQUE</t>
+          <t>Avenida ANTONIO JOAO</t>
         </is>
       </c>
       <c r="G95" s="29" t="inlineStr">
         <is>
-          <t>3933 - R</t>
+          <t>1371 - OU</t>
         </is>
       </c>
       <c r="H95" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 14:04</t>
+          <t>20/08/2026 15:23</t>
         </is>
       </c>
       <c r="I95" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 14:21</t>
+          <t>20/08/2026 15:40</t>
         </is>
       </c>
       <c r="J95" s="29" t="n">
@@ -52720,7 +52296,7 @@
       </c>
       <c r="C96" s="30" t="inlineStr">
         <is>
-          <t>17073314</t>
+          <t>17073307</t>
         </is>
       </c>
       <c r="D96" s="29" t="inlineStr">
@@ -52740,17 +52316,17 @@
       </c>
       <c r="G96" s="29" t="inlineStr">
         <is>
-          <t>1371 - OU</t>
+          <t>1477 - R</t>
         </is>
       </c>
       <c r="H96" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 15:23</t>
+          <t>20/08/2026 13:54</t>
         </is>
       </c>
       <c r="I96" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 15:40</t>
+          <t>20/08/2026 14:11</t>
         </is>
       </c>
       <c r="J96" s="29" t="n">
@@ -52760,47 +52336,47 @@
     <row r="97">
       <c r="A97" s="29" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B97" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C97" s="30" t="inlineStr">
         <is>
-          <t>16960061</t>
+          <t>17041447</t>
         </is>
       </c>
       <c r="D97" s="29" t="inlineStr">
         <is>
-          <t>443 - KAMEL SAAD 1</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E97" s="29" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q038</t>
         </is>
       </c>
       <c r="F97" s="29" t="inlineStr">
         <is>
-          <t>Rua SALIM DERZI</t>
+          <t>Rua DAS PEROBAS</t>
         </is>
       </c>
       <c r="G97" s="29" t="inlineStr">
         <is>
-          <t>118 - R</t>
+          <t>1018 - R</t>
         </is>
       </c>
       <c r="H97" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 10:37</t>
+          <t>20/08/2026 14:48</t>
         </is>
       </c>
       <c r="I97" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 10:54</t>
+          <t>20/08/2026 15:05</t>
         </is>
       </c>
       <c r="J97" s="29" t="n">
@@ -52810,7 +52386,7 @@
     <row r="98">
       <c r="A98" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B98" s="29" t="inlineStr">
@@ -52820,37 +52396,37 @@
       </c>
       <c r="C98" s="30" t="inlineStr">
         <is>
-          <t>16971669</t>
+          <t>17033729</t>
         </is>
       </c>
       <c r="D98" s="29" t="inlineStr">
         <is>
-          <t>410 - SALGADO FILHO</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E98" s="29" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F98" s="29" t="inlineStr">
         <is>
-          <t>Rua SAO CRISTOVAO</t>
+          <t>Rua VICENTE  AZAMBUJA</t>
         </is>
       </c>
       <c r="G98" s="29" t="inlineStr">
         <is>
-          <t>652 - R</t>
+          <t>1407 - R</t>
         </is>
       </c>
       <c r="H98" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:08</t>
+          <t>19/08/2026 08:45</t>
         </is>
       </c>
       <c r="I98" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:24</t>
+          <t>19/08/2026 09:01</t>
         </is>
       </c>
       <c r="J98" s="29" t="n">
@@ -52920,7 +52496,7 @@
       </c>
       <c r="C100" s="30" t="inlineStr">
         <is>
-          <t>16971668</t>
+          <t>16971669</t>
         </is>
       </c>
       <c r="D100" s="29" t="inlineStr">
@@ -52940,17 +52516,17 @@
       </c>
       <c r="G100" s="29" t="inlineStr">
         <is>
-          <t>917 - 8 - R</t>
+          <t>652 - R</t>
         </is>
       </c>
       <c r="H100" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 08:51</t>
+          <t>17/08/2026 09:08</t>
         </is>
       </c>
       <c r="I100" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:07</t>
+          <t>17/08/2026 09:24</t>
         </is>
       </c>
       <c r="J100" s="29" t="n">
@@ -52960,47 +52536,47 @@
     <row r="101">
       <c r="A101" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B101" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C101" s="30" t="inlineStr">
         <is>
-          <t>17076991</t>
+          <t>16932420</t>
         </is>
       </c>
       <c r="D101" s="29" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E101" s="29" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F101" s="29" t="inlineStr">
         <is>
-          <t>Rua Anselmo Soares</t>
+          <t>Rua 18 DE JULHO</t>
         </is>
       </c>
       <c r="G101" s="29" t="inlineStr">
         <is>
-          <t>700 - OU</t>
+          <t>187 - R</t>
         </is>
       </c>
       <c r="H101" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 15:29</t>
+          <t>14/08/2026 14:52</t>
         </is>
       </c>
       <c r="I101" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 15:45</t>
+          <t>14/08/2026 15:08</t>
         </is>
       </c>
       <c r="J101" s="29" t="n">
@@ -53360,47 +52936,47 @@
     <row r="109">
       <c r="A109" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="B109" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C109" s="30" t="inlineStr">
         <is>
-          <t>16932420</t>
+          <t>16990893</t>
         </is>
       </c>
       <c r="D109" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>410 - SALGADO FILHO</t>
         </is>
       </c>
       <c r="E109" s="29" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F109" s="29" t="inlineStr">
         <is>
-          <t>Rua 18 DE JULHO</t>
+          <t>Rua ENGENHEIRO MAURICIO DUTRA</t>
         </is>
       </c>
       <c r="G109" s="29" t="inlineStr">
         <is>
-          <t>187 - R</t>
+          <t>375 - R</t>
         </is>
       </c>
       <c r="H109" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 14:52</t>
+          <t>17/08/2026 08:47</t>
         </is>
       </c>
       <c r="I109" s="29" t="inlineStr">
         <is>
-          <t>14/08/2026 15:08</t>
+          <t>17/08/2026 09:03</t>
         </is>
       </c>
       <c r="J109" s="29" t="n">
@@ -53410,7 +52986,7 @@
     <row r="110">
       <c r="A110" s="29" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B110" s="29" t="inlineStr">
@@ -53420,7 +52996,7 @@
       </c>
       <c r="C110" s="30" t="inlineStr">
         <is>
-          <t>16990893</t>
+          <t>16971668</t>
         </is>
       </c>
       <c r="D110" s="29" t="inlineStr">
@@ -53430,27 +53006,27 @@
       </c>
       <c r="E110" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="F110" s="29" t="inlineStr">
         <is>
-          <t>Rua ENGENHEIRO MAURICIO DUTRA</t>
+          <t>Rua SAO CRISTOVAO</t>
         </is>
       </c>
       <c r="G110" s="29" t="inlineStr">
         <is>
-          <t>375 - R</t>
+          <t>917 - 8 - R</t>
         </is>
       </c>
       <c r="H110" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 08:47</t>
+          <t>17/08/2026 08:51</t>
         </is>
       </c>
       <c r="I110" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:03</t>
+          <t>17/08/2026 09:07</t>
         </is>
       </c>
       <c r="J110" s="29" t="n">
@@ -53510,7 +53086,7 @@
     <row r="112">
       <c r="A112" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B112" s="29" t="inlineStr">
@@ -53520,37 +53096,37 @@
       </c>
       <c r="C112" s="30" t="inlineStr">
         <is>
-          <t>17017093</t>
+          <t>17073275</t>
         </is>
       </c>
       <c r="D112" s="29" t="inlineStr">
         <is>
-          <t>420 - FERROVIARIA</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E112" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F112" s="29" t="inlineStr">
         <is>
-          <t>Travessa PROJETADA 06 FERROVIARIA</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="G112" s="29" t="inlineStr">
         <is>
-          <t>69 - R</t>
+          <t>3986 - R</t>
         </is>
       </c>
       <c r="H112" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 15:44</t>
+          <t>19/08/2026 10:19</t>
         </is>
       </c>
       <c r="I112" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 16:00</t>
+          <t>19/08/2026 10:35</t>
         </is>
       </c>
       <c r="J112" s="29" t="n">
@@ -53560,7 +53136,7 @@
     <row r="113">
       <c r="A113" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B113" s="29" t="inlineStr">
@@ -53570,37 +53146,37 @@
       </c>
       <c r="C113" s="30" t="inlineStr">
         <is>
-          <t>17073275</t>
+          <t>17017079</t>
         </is>
       </c>
       <c r="D113" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>420 - FERROVIARIA</t>
         </is>
       </c>
       <c r="E113" s="29" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F113" s="29" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Travessa PROJETADA 06 FERROVIARIA</t>
         </is>
       </c>
       <c r="G113" s="29" t="inlineStr">
         <is>
-          <t>3986 - R</t>
+          <t>57 - R</t>
         </is>
       </c>
       <c r="H113" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:19</t>
+          <t>17/08/2026 09:16</t>
         </is>
       </c>
       <c r="I113" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:35</t>
+          <t>17/08/2026 09:32</t>
         </is>
       </c>
       <c r="J113" s="29" t="n">
@@ -53610,47 +53186,47 @@
     <row r="114">
       <c r="A114" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B114" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C114" s="30" t="inlineStr">
         <is>
-          <t>17017079</t>
+          <t>17076991</t>
         </is>
       </c>
       <c r="D114" s="29" t="inlineStr">
         <is>
-          <t>420 - FERROVIARIA</t>
+          <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
       <c r="E114" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q012</t>
         </is>
       </c>
       <c r="F114" s="29" t="inlineStr">
         <is>
-          <t>Travessa PROJETADA 06 FERROVIARIA</t>
+          <t>Rua Anselmo Soares</t>
         </is>
       </c>
       <c r="G114" s="29" t="inlineStr">
         <is>
-          <t>57 - R</t>
+          <t>700 - OU</t>
         </is>
       </c>
       <c r="H114" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:16</t>
+          <t>19/08/2026 15:29</t>
         </is>
       </c>
       <c r="I114" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 09:32</t>
+          <t>19/08/2026 15:45</t>
         </is>
       </c>
       <c r="J114" s="29" t="n">
@@ -53710,7 +53286,7 @@
     <row r="116">
       <c r="A116" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="B116" s="29" t="inlineStr">
@@ -53720,37 +53296,37 @@
       </c>
       <c r="C116" s="30" t="inlineStr">
         <is>
-          <t>17033729</t>
+          <t>17055208</t>
         </is>
       </c>
       <c r="D116" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>408 - PARQUE DE EXPOSIÇÕES</t>
         </is>
       </c>
       <c r="E116" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q036</t>
         </is>
       </c>
       <c r="F116" s="29" t="inlineStr">
         <is>
-          <t>Rua VICENTE  AZAMBUJA</t>
+          <t>Rua DIGNO TORRES GIMENEZ</t>
         </is>
       </c>
       <c r="G116" s="29" t="inlineStr">
         <is>
-          <t>1407 - R</t>
+          <t>590 - 2 - R</t>
         </is>
       </c>
       <c r="H116" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 08:45</t>
+          <t>21/08/2026 08:57</t>
         </is>
       </c>
       <c r="I116" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:01</t>
+          <t>21/08/2026 09:13</t>
         </is>
       </c>
       <c r="J116" s="29" t="n">
@@ -53760,47 +53336,47 @@
     <row r="117">
       <c r="A117" s="29" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B117" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C117" s="30" t="inlineStr">
         <is>
-          <t>17055208</t>
+          <t>17017093</t>
         </is>
       </c>
       <c r="D117" s="29" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇÕES</t>
+          <t>420 - FERROVIARIA</t>
         </is>
       </c>
       <c r="E117" s="29" t="inlineStr">
         <is>
-          <t>Q036</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F117" s="29" t="inlineStr">
         <is>
-          <t>Rua DIGNO TORRES GIMENEZ</t>
+          <t>Travessa PROJETADA 06 FERROVIARIA</t>
         </is>
       </c>
       <c r="G117" s="29" t="inlineStr">
         <is>
-          <t>590 - 2 - R</t>
+          <t>69 - R</t>
         </is>
       </c>
       <c r="H117" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 08:57</t>
+          <t>17/08/2026 15:44</t>
         </is>
       </c>
       <c r="I117" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 09:13</t>
+          <t>17/08/2026 16:00</t>
         </is>
       </c>
       <c r="J117" s="29" t="n">

--- a/data/historico/semanas_318-321.xlsx
+++ b/data/historico/semanas_318-321.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 15min'!$A$2:$J$143</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$186</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$95</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$247</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$246</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Resumo Semanal'!$A$2:$AE$154</definedName>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="B6" s="41" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="C6" s="41" t="inlineStr">
@@ -6106,7 +6106,7 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="G57" s="46" t="inlineStr">
         <is>
-          <t>378 - 2 - R</t>
+          <t>239 - R</t>
         </is>
       </c>
       <c r="H57" s="46" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="G69" s="46" t="inlineStr">
         <is>
-          <t>775 - 3 - TB</t>
+          <t>775 - 2 - R</t>
         </is>
       </c>
       <c r="H69" s="46" t="inlineStr">
@@ -25629,7 +25629,7 @@
         <v>20</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>100</v>
@@ -27521,7 +27521,7 @@
       </c>
       <c r="C65" s="51" t="inlineStr">
         <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D65" s="51" t="n">
@@ -27553,55 +27553,55 @@
       </c>
       <c r="C66" s="51" t="inlineStr">
         <is>
-          <t>Dia com meta diária batida</t>
+          <t>Bônus: nenhuma visita rápida no período</t>
         </is>
       </c>
       <c r="D66" s="51" t="n">
         <v>1</v>
       </c>
       <c r="E66" s="51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F66" s="51" t="n">
         <v>1</v>
       </c>
       <c r="G66" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="H66" s="51" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="51" t="inlineStr">
+        <is>
+          <t>Alana Amanda Fernandes Ovelar</t>
+        </is>
+      </c>
+      <c r="B67" s="51" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C67" s="51" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D67" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="H66" s="51" t="n">
+      <c r="E67" s="51" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="52" t="inlineStr">
-        <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
-        </is>
-      </c>
-      <c r="B67" s="52" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C67" s="52" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D67" s="52" t="n">
+      <c r="F67" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E67" s="52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F67" s="52" t="n">
+      <c r="G67" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="G67" s="52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H67" s="52" t="n">
-        <v>-0.5</v>
+      <c r="H67" s="51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -27617,23 +27617,23 @@
       </c>
       <c r="C68" s="52" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D68" s="52" t="n">
         <v>1</v>
       </c>
       <c r="E68" s="52" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F68" s="52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G68" s="52" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H68" s="52" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="69">
@@ -27649,23 +27649,23 @@
       </c>
       <c r="C69" s="52" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D69" s="52" t="n">
         <v>1</v>
       </c>
       <c r="E69" s="52" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F69" s="52" t="n">
         <v>2</v>
       </c>
       <c r="G69" s="52" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H69" s="52" t="n">
-        <v>-3</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="70">
@@ -51314,47 +51314,47 @@
     <row r="54">
       <c r="A54" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B54" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C54" s="30" t="inlineStr">
         <is>
-          <t>17197913</t>
+          <t>17195999</t>
         </is>
       </c>
       <c r="D54" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E54" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q050</t>
         </is>
       </c>
       <c r="F54" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Avenida COSTA E SILVA</t>
         </is>
       </c>
       <c r="G54" s="29" t="inlineStr">
         <is>
-          <t>1542 - R</t>
+          <t>843 - R</t>
         </is>
       </c>
       <c r="H54" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:32</t>
+          <t>28/08/2026 08:55</t>
         </is>
       </c>
       <c r="I54" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:52</t>
+          <t>28/08/2026 09:15</t>
         </is>
       </c>
       <c r="J54" s="29" t="n">
@@ -51364,47 +51364,47 @@
     <row r="55">
       <c r="A55" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B55" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C55" s="30" t="inlineStr">
         <is>
-          <t>17195999</t>
+          <t>17197913</t>
         </is>
       </c>
       <c r="D55" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E55" s="29" t="inlineStr">
         <is>
-          <t>Q050</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F55" s="29" t="inlineStr">
         <is>
-          <t>Avenida COSTA E SILVA</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G55" s="29" t="inlineStr">
         <is>
-          <t>843 - R</t>
+          <t>1542 - R</t>
         </is>
       </c>
       <c r="H55" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 08:55</t>
+          <t>28/08/2026 14:32</t>
         </is>
       </c>
       <c r="I55" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:15</t>
+          <t>28/08/2026 14:52</t>
         </is>
       </c>
       <c r="J55" s="29" t="n">
@@ -52114,47 +52114,47 @@
     <row r="70">
       <c r="A70" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B70" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>17197904</t>
+          <t>17196006</t>
         </is>
       </c>
       <c r="D70" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E70" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q050</t>
         </is>
       </c>
       <c r="F70" s="29" t="inlineStr">
         <is>
-          <t>Rua BALTAZAR SALDANHA</t>
+          <t>Rua 01 DE MARÇO</t>
         </is>
       </c>
       <c r="G70" s="29" t="inlineStr">
         <is>
-          <t>645 - R</t>
+          <t>69 - 1 - OU</t>
         </is>
       </c>
       <c r="H70" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 10:02</t>
+          <t>28/08/2026 09:32</t>
         </is>
       </c>
       <c r="I70" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 10:20</t>
+          <t>28/08/2026 09:50</t>
         </is>
       </c>
       <c r="J70" s="29" t="n">
@@ -52224,7 +52224,7 @@
       </c>
       <c r="C72" s="30" t="inlineStr">
         <is>
-          <t>17197903</t>
+          <t>17197904</t>
         </is>
       </c>
       <c r="D72" s="29" t="inlineStr">
@@ -52244,17 +52244,17 @@
       </c>
       <c r="G72" s="29" t="inlineStr">
         <is>
-          <t>669 - R</t>
+          <t>645 - R</t>
         </is>
       </c>
       <c r="H72" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:41</t>
+          <t>28/08/2026 10:02</t>
         </is>
       </c>
       <c r="I72" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:59</t>
+          <t>28/08/2026 10:20</t>
         </is>
       </c>
       <c r="J72" s="29" t="n">
@@ -52264,47 +52264,47 @@
     <row r="73">
       <c r="A73" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B73" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C73" s="30" t="inlineStr">
         <is>
-          <t>17196006</t>
+          <t>17197908</t>
         </is>
       </c>
       <c r="D73" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E73" s="29" t="inlineStr">
         <is>
-          <t>Q050</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F73" s="29" t="inlineStr">
         <is>
-          <t>Rua 01 DE MARÇO</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G73" s="29" t="inlineStr">
         <is>
-          <t>69 - 1 - OU</t>
+          <t>1486 - R</t>
         </is>
       </c>
       <c r="H73" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:32</t>
+          <t>28/08/2026 13:55</t>
         </is>
       </c>
       <c r="I73" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:50</t>
+          <t>28/08/2026 14:13</t>
         </is>
       </c>
       <c r="J73" s="29" t="n">
@@ -52324,7 +52324,7 @@
       </c>
       <c r="C74" s="30" t="inlineStr">
         <is>
-          <t>17197908</t>
+          <t>17197903</t>
         </is>
       </c>
       <c r="D74" s="29" t="inlineStr">
@@ -52339,22 +52339,22 @@
       </c>
       <c r="F74" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Rua BALTAZAR SALDANHA</t>
         </is>
       </c>
       <c r="G74" s="29" t="inlineStr">
         <is>
-          <t>1486 - R</t>
+          <t>669 - R</t>
         </is>
       </c>
       <c r="H74" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 13:55</t>
+          <t>28/08/2026 09:41</t>
         </is>
       </c>
       <c r="I74" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:13</t>
+          <t>28/08/2026 09:59</t>
         </is>
       </c>
       <c r="J74" s="29" t="n">
@@ -55714,7 +55714,7 @@
     <row r="142">
       <c r="A142" s="29" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="B142" s="29" t="inlineStr">
@@ -55724,37 +55724,37 @@
       </c>
       <c r="C142" s="30" t="inlineStr">
         <is>
-          <t>17130878</t>
+          <t>17170026</t>
         </is>
       </c>
       <c r="D142" s="29" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>446 - GUY VILELA</t>
         </is>
       </c>
       <c r="E142" s="29" t="inlineStr">
         <is>
-          <t>Q044</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="F142" s="29" t="inlineStr">
         <is>
-          <t>Rua BENJAMIN CONSTANT</t>
+          <t>Avenida TAMANDARE</t>
         </is>
       </c>
       <c r="G142" s="29" t="inlineStr">
         <is>
-          <t>512 - 1 - R</t>
+          <t>466 - R</t>
         </is>
       </c>
       <c r="H142" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 10:27</t>
+          <t>27/08/2026 14:46</t>
         </is>
       </c>
       <c r="I142" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 10:43</t>
+          <t>27/08/2026 15:02</t>
         </is>
       </c>
       <c r="J142" s="29" t="n">
@@ -55764,7 +55764,7 @@
     <row r="143">
       <c r="A143" s="29" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B143" s="29" t="inlineStr">
@@ -55774,37 +55774,37 @@
       </c>
       <c r="C143" s="30" t="inlineStr">
         <is>
-          <t>17170026</t>
+          <t>17130878</t>
         </is>
       </c>
       <c r="D143" s="29" t="inlineStr">
         <is>
-          <t>446 - GUY VILELA</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E143" s="29" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q044</t>
         </is>
       </c>
       <c r="F143" s="29" t="inlineStr">
         <is>
-          <t>Avenida TAMANDARE</t>
+          <t>Rua BENJAMIN CONSTANT</t>
         </is>
       </c>
       <c r="G143" s="29" t="inlineStr">
         <is>
-          <t>466 - R</t>
+          <t>512 - 1 - R</t>
         </is>
       </c>
       <c r="H143" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 14:46</t>
+          <t>25/08/2026 10:27</t>
         </is>
       </c>
       <c r="I143" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 15:02</t>
+          <t>25/08/2026 10:43</t>
         </is>
       </c>
       <c r="J143" s="29" t="n">
@@ -59175,7 +59175,7 @@
       </c>
       <c r="H57" s="32" t="inlineStr">
         <is>
-          <t>553 - R</t>
+          <t>496 - 2 - TB</t>
         </is>
       </c>
       <c r="I57" s="32" t="inlineStr">
@@ -64875,7 +64875,7 @@
       </c>
       <c r="H157" s="32" t="inlineStr">
         <is>
-          <t>396 - R</t>
+          <t>376 - R</t>
         </is>
       </c>
       <c r="I157" s="32" t="inlineStr">
@@ -66015,7 +66015,7 @@
       </c>
       <c r="H177" s="32" t="inlineStr">
         <is>
-          <t>180 - 7 - TB</t>
+          <t>240 - 1 - TB</t>
         </is>
       </c>
       <c r="I177" s="32" t="inlineStr">
@@ -67938,7 +67938,7 @@
       </c>
       <c r="G26" s="35" t="inlineStr">
         <is>
-          <t>553 - R</t>
+          <t>496 - 2 - TB</t>
         </is>
       </c>
       <c r="H26" s="35" t="inlineStr">
@@ -70570,7 +70570,7 @@
       </c>
       <c r="G82" s="35" t="inlineStr">
         <is>
-          <t>396 - R</t>
+          <t>376 - R</t>
         </is>
       </c>
       <c r="H82" s="35" t="inlineStr">
@@ -71087,7 +71087,7 @@
       </c>
       <c r="G93" s="35" t="inlineStr">
         <is>
-          <t>180 - 7 - TB</t>
+          <t>240 - 1 - TB</t>
         </is>
       </c>
       <c r="H93" s="35" t="inlineStr">
@@ -71305,7 +71305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G247"/>
+  <dimension ref="A1:G246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -71320,7 +71320,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (245 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
+          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (244 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -76654,11 +76654,11 @@
     </row>
     <row r="154">
       <c r="A154" s="39" t="n">
-        <v>2951</v>
+        <v>1938</v>
       </c>
       <c r="B154" s="39" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C154" s="39" t="inlineStr">
@@ -76689,11 +76689,11 @@
     </row>
     <row r="155">
       <c r="A155" s="39" t="n">
-        <v>1938</v>
+        <v>120</v>
       </c>
       <c r="B155" s="39" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C155" s="39" t="inlineStr">
@@ -76713,7 +76713,7 @@
       </c>
       <c r="F155" s="39" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G155" s="39" t="inlineStr">
@@ -76724,11 +76724,11 @@
     </row>
     <row r="156">
       <c r="A156" s="39" t="n">
-        <v>120</v>
+        <v>1938</v>
       </c>
       <c r="B156" s="39" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C156" s="39" t="inlineStr">
@@ -76759,11 +76759,11 @@
     </row>
     <row r="157">
       <c r="A157" s="39" t="n">
-        <v>1938</v>
+        <v>120</v>
       </c>
       <c r="B157" s="39" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C157" s="39" t="inlineStr">
@@ -76773,17 +76773,17 @@
       </c>
       <c r="D157" s="39" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E157" s="39" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F157" s="39" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G157" s="39" t="inlineStr">
@@ -76794,11 +76794,11 @@
     </row>
     <row r="158">
       <c r="A158" s="39" t="n">
-        <v>120</v>
+        <v>1938</v>
       </c>
       <c r="B158" s="39" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C158" s="39" t="inlineStr">
@@ -76853,7 +76853,7 @@
       </c>
       <c r="F159" s="39" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G159" s="39" t="inlineStr">
@@ -76864,11 +76864,11 @@
     </row>
     <row r="160">
       <c r="A160" s="39" t="n">
-        <v>1938</v>
+        <v>2918</v>
       </c>
       <c r="B160" s="39" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C160" s="39" t="inlineStr">
@@ -76878,17 +76878,17 @@
       </c>
       <c r="D160" s="39" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E160" s="39" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F160" s="39" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G160" s="39" t="inlineStr">
@@ -76899,11 +76899,11 @@
     </row>
     <row r="161">
       <c r="A161" s="39" t="n">
-        <v>2918</v>
+        <v>1938</v>
       </c>
       <c r="B161" s="39" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C161" s="39" t="inlineStr">
@@ -76934,11 +76934,11 @@
     </row>
     <row r="162">
       <c r="A162" s="39" t="n">
-        <v>1938</v>
+        <v>3038</v>
       </c>
       <c r="B162" s="39" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C162" s="39" t="inlineStr">
@@ -76969,11 +76969,11 @@
     </row>
     <row r="163">
       <c r="A163" s="39" t="n">
-        <v>3038</v>
+        <v>3128</v>
       </c>
       <c r="B163" s="39" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C163" s="39" t="inlineStr">
@@ -77004,11 +77004,11 @@
     </row>
     <row r="164">
       <c r="A164" s="39" t="n">
-        <v>3128</v>
+        <v>1938</v>
       </c>
       <c r="B164" s="39" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C164" s="39" t="inlineStr">
@@ -77028,7 +77028,7 @@
       </c>
       <c r="F164" s="39" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G164" s="39" t="inlineStr">
@@ -77053,12 +77053,12 @@
       </c>
       <c r="D165" s="39" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E165" s="39" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F165" s="39" t="inlineStr">
@@ -77074,11 +77074,11 @@
     </row>
     <row r="166">
       <c r="A166" s="39" t="n">
-        <v>1938</v>
+        <v>2721</v>
       </c>
       <c r="B166" s="39" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C166" s="39" t="inlineStr">
@@ -77088,17 +77088,17 @@
       </c>
       <c r="D166" s="39" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E166" s="39" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F166" s="39" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G166" s="39" t="inlineStr">
@@ -77109,11 +77109,11 @@
     </row>
     <row r="167">
       <c r="A167" s="39" t="n">
-        <v>2721</v>
+        <v>1938</v>
       </c>
       <c r="B167" s="39" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C167" s="39" t="inlineStr">
@@ -77133,7 +77133,7 @@
       </c>
       <c r="F167" s="39" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G167" s="39" t="inlineStr">
@@ -77144,11 +77144,11 @@
     </row>
     <row r="168">
       <c r="A168" s="39" t="n">
-        <v>1938</v>
+        <v>2721</v>
       </c>
       <c r="B168" s="39" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C168" s="39" t="inlineStr">
@@ -77179,11 +77179,11 @@
     </row>
     <row r="169">
       <c r="A169" s="39" t="n">
-        <v>2721</v>
+        <v>2918</v>
       </c>
       <c r="B169" s="39" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C169" s="39" t="inlineStr">
@@ -77193,17 +77193,17 @@
       </c>
       <c r="D169" s="39" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E169" s="39" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F169" s="39" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G169" s="39" t="inlineStr">
@@ -77214,11 +77214,11 @@
     </row>
     <row r="170">
       <c r="A170" s="39" t="n">
-        <v>2918</v>
+        <v>120</v>
       </c>
       <c r="B170" s="39" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C170" s="39" t="inlineStr">
@@ -77249,11 +77249,11 @@
     </row>
     <row r="171">
       <c r="A171" s="39" t="n">
-        <v>120</v>
+        <v>1936</v>
       </c>
       <c r="B171" s="39" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C171" s="39" t="inlineStr">
@@ -77284,11 +77284,11 @@
     </row>
     <row r="172">
       <c r="A172" s="39" t="n">
-        <v>1936</v>
+        <v>1938</v>
       </c>
       <c r="B172" s="39" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C172" s="39" t="inlineStr">
@@ -77319,11 +77319,11 @@
     </row>
     <row r="173">
       <c r="A173" s="39" t="n">
-        <v>1938</v>
+        <v>2721</v>
       </c>
       <c r="B173" s="39" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C173" s="39" t="inlineStr">
@@ -77354,11 +77354,11 @@
     </row>
     <row r="174">
       <c r="A174" s="39" t="n">
-        <v>2721</v>
+        <v>3038</v>
       </c>
       <c r="B174" s="39" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C174" s="39" t="inlineStr">
@@ -77389,11 +77389,11 @@
     </row>
     <row r="175">
       <c r="A175" s="39" t="n">
-        <v>3038</v>
+        <v>3128</v>
       </c>
       <c r="B175" s="39" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C175" s="39" t="inlineStr">
@@ -77424,11 +77424,11 @@
     </row>
     <row r="176">
       <c r="A176" s="39" t="n">
-        <v>3128</v>
+        <v>113</v>
       </c>
       <c r="B176" s="39" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C176" s="39" t="inlineStr">
@@ -77459,11 +77459,11 @@
     </row>
     <row r="177">
       <c r="A177" s="39" t="n">
-        <v>113</v>
+        <v>1938</v>
       </c>
       <c r="B177" s="39" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C177" s="39" t="inlineStr">
@@ -77483,7 +77483,7 @@
       </c>
       <c r="F177" s="39" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G177" s="39" t="inlineStr">
@@ -77508,17 +77508,17 @@
       </c>
       <c r="D178" s="39" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E178" s="39" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F178" s="39" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G178" s="39" t="inlineStr">
@@ -77529,11 +77529,11 @@
     </row>
     <row r="179">
       <c r="A179" s="39" t="n">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="B179" s="39" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C179" s="39" t="inlineStr">
@@ -77543,17 +77543,17 @@
       </c>
       <c r="D179" s="39" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E179" s="39" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F179" s="39" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G179" s="39" t="inlineStr">
@@ -77564,31 +77564,31 @@
     </row>
     <row r="180">
       <c r="A180" s="39" t="n">
-        <v>1936</v>
+        <v>110</v>
       </c>
       <c r="B180" s="39" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C180" s="39" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D180" s="39" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>11/08/2026</t>
         </is>
       </c>
       <c r="E180" s="39" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F180" s="39" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G180" s="39" t="inlineStr">
@@ -77599,11 +77599,11 @@
     </row>
     <row r="181">
       <c r="A181" s="39" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="B181" s="39" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C181" s="39" t="inlineStr">
@@ -77634,11 +77634,11 @@
     </row>
     <row r="182">
       <c r="A182" s="39" t="n">
-        <v>80</v>
+        <v>1943</v>
       </c>
       <c r="B182" s="39" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C182" s="39" t="inlineStr">
@@ -77669,11 +77669,11 @@
     </row>
     <row r="183">
       <c r="A183" s="39" t="n">
-        <v>1943</v>
+        <v>2789</v>
       </c>
       <c r="B183" s="39" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C183" s="39" t="inlineStr">
@@ -77704,11 +77704,11 @@
     </row>
     <row r="184">
       <c r="A184" s="39" t="n">
-        <v>2789</v>
+        <v>149</v>
       </c>
       <c r="B184" s="39" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C184" s="39" t="inlineStr">
@@ -77739,11 +77739,11 @@
     </row>
     <row r="185">
       <c r="A185" s="39" t="n">
-        <v>149</v>
+        <v>1942</v>
       </c>
       <c r="B185" s="39" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C185" s="39" t="inlineStr">
@@ -77774,11 +77774,11 @@
     </row>
     <row r="186">
       <c r="A186" s="39" t="n">
-        <v>1942</v>
+        <v>161</v>
       </c>
       <c r="B186" s="39" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C186" s="39" t="inlineStr">
@@ -77809,11 +77809,11 @@
     </row>
     <row r="187">
       <c r="A187" s="39" t="n">
-        <v>161</v>
+        <v>1996</v>
       </c>
       <c r="B187" s="39" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C187" s="39" t="inlineStr">
@@ -77844,11 +77844,11 @@
     </row>
     <row r="188">
       <c r="A188" s="39" t="n">
-        <v>1996</v>
+        <v>86</v>
       </c>
       <c r="B188" s="39" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C188" s="39" t="inlineStr">
@@ -77879,11 +77879,11 @@
     </row>
     <row r="189">
       <c r="A189" s="39" t="n">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="B189" s="39" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C189" s="39" t="inlineStr">
@@ -77903,7 +77903,7 @@
       </c>
       <c r="F189" s="39" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G189" s="39" t="inlineStr">
@@ -77914,11 +77914,11 @@
     </row>
     <row r="190">
       <c r="A190" s="39" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="B190" s="39" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C190" s="39" t="inlineStr">
@@ -77949,11 +77949,11 @@
     </row>
     <row r="191">
       <c r="A191" s="39" t="n">
-        <v>80</v>
+        <v>1943</v>
       </c>
       <c r="B191" s="39" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C191" s="39" t="inlineStr">
@@ -77984,11 +77984,11 @@
     </row>
     <row r="192">
       <c r="A192" s="39" t="n">
-        <v>1943</v>
+        <v>2789</v>
       </c>
       <c r="B192" s="39" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C192" s="39" t="inlineStr">
@@ -78019,11 +78019,11 @@
     </row>
     <row r="193">
       <c r="A193" s="39" t="n">
-        <v>2789</v>
+        <v>149</v>
       </c>
       <c r="B193" s="39" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C193" s="39" t="inlineStr">
@@ -78054,11 +78054,11 @@
     </row>
     <row r="194">
       <c r="A194" s="39" t="n">
-        <v>149</v>
+        <v>1942</v>
       </c>
       <c r="B194" s="39" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C194" s="39" t="inlineStr">
@@ -78089,11 +78089,11 @@
     </row>
     <row r="195">
       <c r="A195" s="39" t="n">
-        <v>1942</v>
+        <v>161</v>
       </c>
       <c r="B195" s="39" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C195" s="39" t="inlineStr">
@@ -78124,11 +78124,11 @@
     </row>
     <row r="196">
       <c r="A196" s="39" t="n">
-        <v>161</v>
+        <v>1996</v>
       </c>
       <c r="B196" s="39" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C196" s="39" t="inlineStr">
@@ -78159,11 +78159,11 @@
     </row>
     <row r="197">
       <c r="A197" s="39" t="n">
-        <v>1996</v>
+        <v>86</v>
       </c>
       <c r="B197" s="39" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C197" s="39" t="inlineStr">
@@ -78194,11 +78194,11 @@
     </row>
     <row r="198">
       <c r="A198" s="39" t="n">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c r="B198" s="39" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C198" s="39" t="inlineStr">
@@ -78229,11 +78229,11 @@
     </row>
     <row r="199">
       <c r="A199" s="39" t="n">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="B199" s="39" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C199" s="39" t="inlineStr">
@@ -78243,17 +78243,17 @@
       </c>
       <c r="D199" s="39" t="inlineStr">
         <is>
-          <t>11/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="E199" s="39" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F199" s="39" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G199" s="39" t="inlineStr">
@@ -78264,11 +78264,11 @@
     </row>
     <row r="200">
       <c r="A200" s="39" t="n">
-        <v>110</v>
+        <v>1943</v>
       </c>
       <c r="B200" s="39" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C200" s="39" t="inlineStr">
@@ -78299,11 +78299,11 @@
     </row>
     <row r="201">
       <c r="A201" s="39" t="n">
-        <v>1943</v>
+        <v>110</v>
       </c>
       <c r="B201" s="39" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C201" s="39" t="inlineStr">
@@ -78323,7 +78323,7 @@
       </c>
       <c r="F201" s="39" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G201" s="39" t="inlineStr">
@@ -78348,17 +78348,17 @@
       </c>
       <c r="D202" s="39" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="E202" s="39" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F202" s="39" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G202" s="39" t="inlineStr">
@@ -78369,11 +78369,11 @@
     </row>
     <row r="203">
       <c r="A203" s="39" t="n">
-        <v>110</v>
+        <v>1943</v>
       </c>
       <c r="B203" s="39" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C203" s="39" t="inlineStr">
@@ -78404,11 +78404,11 @@
     </row>
     <row r="204">
       <c r="A204" s="39" t="n">
-        <v>1943</v>
+        <v>161</v>
       </c>
       <c r="B204" s="39" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C204" s="39" t="inlineStr">
@@ -78439,11 +78439,11 @@
     </row>
     <row r="205">
       <c r="A205" s="39" t="n">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="B205" s="39" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C205" s="39" t="inlineStr">
@@ -78463,7 +78463,7 @@
       </c>
       <c r="F205" s="39" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G205" s="39" t="inlineStr">
@@ -78474,11 +78474,11 @@
     </row>
     <row r="206">
       <c r="A206" s="39" t="n">
-        <v>110</v>
+        <v>1943</v>
       </c>
       <c r="B206" s="39" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C206" s="39" t="inlineStr">
@@ -78509,11 +78509,11 @@
     </row>
     <row r="207">
       <c r="A207" s="39" t="n">
-        <v>1943</v>
+        <v>161</v>
       </c>
       <c r="B207" s="39" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C207" s="39" t="inlineStr">
@@ -78544,11 +78544,11 @@
     </row>
     <row r="208">
       <c r="A208" s="39" t="n">
-        <v>161</v>
+        <v>1943</v>
       </c>
       <c r="B208" s="39" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C208" s="39" t="inlineStr">
@@ -78558,17 +78558,17 @@
       </c>
       <c r="D208" s="39" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="E208" s="39" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F208" s="39" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G208" s="39" t="inlineStr">
@@ -78603,7 +78603,7 @@
       </c>
       <c r="F209" s="39" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G209" s="39" t="inlineStr">
@@ -78628,17 +78628,17 @@
       </c>
       <c r="D210" s="39" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="E210" s="39" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F210" s="39" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G210" s="39" t="inlineStr">
@@ -78649,11 +78649,11 @@
     </row>
     <row r="211">
       <c r="A211" s="39" t="n">
-        <v>1943</v>
+        <v>110</v>
       </c>
       <c r="B211" s="39" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C211" s="39" t="inlineStr">
@@ -78673,7 +78673,7 @@
       </c>
       <c r="F211" s="39" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G211" s="39" t="inlineStr">
@@ -78684,11 +78684,11 @@
     </row>
     <row r="212">
       <c r="A212" s="39" t="n">
-        <v>110</v>
+        <v>1943</v>
       </c>
       <c r="B212" s="39" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C212" s="39" t="inlineStr">
@@ -78719,11 +78719,11 @@
     </row>
     <row r="213">
       <c r="A213" s="39" t="n">
-        <v>1943</v>
+        <v>149</v>
       </c>
       <c r="B213" s="39" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C213" s="39" t="inlineStr">
@@ -78754,11 +78754,11 @@
     </row>
     <row r="214">
       <c r="A214" s="39" t="n">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="B214" s="39" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C214" s="39" t="inlineStr">
@@ -78768,17 +78768,17 @@
       </c>
       <c r="D214" s="39" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>20/08/2026</t>
         </is>
       </c>
       <c r="E214" s="39" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F214" s="39" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G214" s="39" t="inlineStr">
@@ -78789,11 +78789,11 @@
     </row>
     <row r="215">
       <c r="A215" s="39" t="n">
-        <v>80</v>
+        <v>1943</v>
       </c>
       <c r="B215" s="39" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C215" s="39" t="inlineStr">
@@ -78824,11 +78824,11 @@
     </row>
     <row r="216">
       <c r="A216" s="39" t="n">
-        <v>1943</v>
+        <v>2789</v>
       </c>
       <c r="B216" s="39" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C216" s="39" t="inlineStr">
@@ -78859,11 +78859,11 @@
     </row>
     <row r="217">
       <c r="A217" s="39" t="n">
-        <v>2789</v>
+        <v>149</v>
       </c>
       <c r="B217" s="39" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C217" s="39" t="inlineStr">
@@ -78894,11 +78894,11 @@
     </row>
     <row r="218">
       <c r="A218" s="39" t="n">
-        <v>149</v>
+        <v>1942</v>
       </c>
       <c r="B218" s="39" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C218" s="39" t="inlineStr">
@@ -78929,11 +78929,11 @@
     </row>
     <row r="219">
       <c r="A219" s="39" t="n">
-        <v>1942</v>
+        <v>1996</v>
       </c>
       <c r="B219" s="39" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C219" s="39" t="inlineStr">
@@ -78964,11 +78964,11 @@
     </row>
     <row r="220">
       <c r="A220" s="39" t="n">
-        <v>1996</v>
+        <v>86</v>
       </c>
       <c r="B220" s="39" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C220" s="39" t="inlineStr">
@@ -78999,11 +78999,11 @@
     </row>
     <row r="221">
       <c r="A221" s="39" t="n">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c r="B221" s="39" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C221" s="39" t="inlineStr">
@@ -79034,11 +79034,11 @@
     </row>
     <row r="222">
       <c r="A222" s="39" t="n">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="B222" s="39" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C222" s="39" t="inlineStr">
@@ -79048,12 +79048,12 @@
       </c>
       <c r="D222" s="39" t="inlineStr">
         <is>
-          <t>20/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="E222" s="39" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F222" s="39" t="inlineStr">
@@ -79069,11 +79069,11 @@
     </row>
     <row r="223">
       <c r="A223" s="39" t="n">
-        <v>80</v>
+        <v>1942</v>
       </c>
       <c r="B223" s="39" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C223" s="39" t="inlineStr">
@@ -79104,11 +79104,11 @@
     </row>
     <row r="224">
       <c r="A224" s="39" t="n">
-        <v>1942</v>
+        <v>1996</v>
       </c>
       <c r="B224" s="39" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C224" s="39" t="inlineStr">
@@ -79139,11 +79139,11 @@
     </row>
     <row r="225">
       <c r="A225" s="39" t="n">
-        <v>1996</v>
+        <v>1943</v>
       </c>
       <c r="B225" s="39" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C225" s="39" t="inlineStr">
@@ -79153,12 +79153,12 @@
       </c>
       <c r="D225" s="39" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="E225" s="39" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="F225" s="39" t="inlineStr">
@@ -79174,11 +79174,11 @@
     </row>
     <row r="226">
       <c r="A226" s="39" t="n">
-        <v>1943</v>
+        <v>2789</v>
       </c>
       <c r="B226" s="39" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C226" s="39" t="inlineStr">
@@ -79209,11 +79209,11 @@
     </row>
     <row r="227">
       <c r="A227" s="39" t="n">
-        <v>2789</v>
+        <v>1943</v>
       </c>
       <c r="B227" s="39" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C227" s="39" t="inlineStr">
@@ -79233,7 +79233,7 @@
       </c>
       <c r="F227" s="39" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G227" s="39" t="inlineStr">
@@ -79244,11 +79244,11 @@
     </row>
     <row r="228">
       <c r="A228" s="39" t="n">
-        <v>1943</v>
+        <v>2789</v>
       </c>
       <c r="B228" s="39" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C228" s="39" t="inlineStr">
@@ -79279,11 +79279,11 @@
     </row>
     <row r="229">
       <c r="A229" s="39" t="n">
-        <v>2789</v>
+        <v>1943</v>
       </c>
       <c r="B229" s="39" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C229" s="39" t="inlineStr">
@@ -79293,17 +79293,17 @@
       </c>
       <c r="D229" s="39" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="E229" s="39" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F229" s="39" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G229" s="39" t="inlineStr">
@@ -79338,7 +79338,7 @@
       </c>
       <c r="F230" s="39" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G230" s="39" t="inlineStr">
@@ -79349,11 +79349,11 @@
     </row>
     <row r="231">
       <c r="A231" s="39" t="n">
-        <v>1943</v>
+        <v>110</v>
       </c>
       <c r="B231" s="39" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C231" s="39" t="inlineStr">
@@ -79363,17 +79363,17 @@
       </c>
       <c r="D231" s="39" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="E231" s="39" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F231" s="39" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G231" s="39" t="inlineStr">
@@ -79384,11 +79384,11 @@
     </row>
     <row r="232">
       <c r="A232" s="39" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="B232" s="39" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C232" s="39" t="inlineStr">
@@ -79419,11 +79419,11 @@
     </row>
     <row r="233">
       <c r="A233" s="39" t="n">
-        <v>80</v>
+        <v>1943</v>
       </c>
       <c r="B233" s="39" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C233" s="39" t="inlineStr">
@@ -79454,11 +79454,11 @@
     </row>
     <row r="234">
       <c r="A234" s="39" t="n">
-        <v>1943</v>
+        <v>2789</v>
       </c>
       <c r="B234" s="39" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C234" s="39" t="inlineStr">
@@ -79489,11 +79489,11 @@
     </row>
     <row r="235">
       <c r="A235" s="39" t="n">
-        <v>2789</v>
+        <v>149</v>
       </c>
       <c r="B235" s="39" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C235" s="39" t="inlineStr">
@@ -79524,11 +79524,11 @@
     </row>
     <row r="236">
       <c r="A236" s="39" t="n">
-        <v>149</v>
+        <v>1942</v>
       </c>
       <c r="B236" s="39" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C236" s="39" t="inlineStr">
@@ -79559,11 +79559,11 @@
     </row>
     <row r="237">
       <c r="A237" s="39" t="n">
-        <v>1942</v>
+        <v>161</v>
       </c>
       <c r="B237" s="39" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C237" s="39" t="inlineStr">
@@ -79594,11 +79594,11 @@
     </row>
     <row r="238">
       <c r="A238" s="39" t="n">
-        <v>161</v>
+        <v>1996</v>
       </c>
       <c r="B238" s="39" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C238" s="39" t="inlineStr">
@@ -79629,11 +79629,11 @@
     </row>
     <row r="239">
       <c r="A239" s="39" t="n">
-        <v>1996</v>
+        <v>86</v>
       </c>
       <c r="B239" s="39" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C239" s="39" t="inlineStr">
@@ -79664,11 +79664,11 @@
     </row>
     <row r="240">
       <c r="A240" s="39" t="n">
-        <v>86</v>
+        <v>157</v>
       </c>
       <c r="B240" s="39" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C240" s="39" t="inlineStr">
@@ -79699,11 +79699,11 @@
     </row>
     <row r="241">
       <c r="A241" s="39" t="n">
-        <v>157</v>
+        <v>1996</v>
       </c>
       <c r="B241" s="39" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C241" s="39" t="inlineStr">
@@ -79723,7 +79723,7 @@
       </c>
       <c r="F241" s="39" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G241" s="39" t="inlineStr">
@@ -79734,11 +79734,11 @@
     </row>
     <row r="242">
       <c r="A242" s="39" t="n">
-        <v>1996</v>
+        <v>1943</v>
       </c>
       <c r="B242" s="39" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C242" s="39" t="inlineStr">
@@ -79748,17 +79748,17 @@
       </c>
       <c r="D242" s="39" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="E242" s="39" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F242" s="39" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G242" s="39" t="inlineStr">
@@ -79769,11 +79769,11 @@
     </row>
     <row r="243">
       <c r="A243" s="39" t="n">
-        <v>1943</v>
+        <v>1996</v>
       </c>
       <c r="B243" s="39" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C243" s="39" t="inlineStr">
@@ -79828,7 +79828,7 @@
       </c>
       <c r="F244" s="39" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G244" s="39" t="inlineStr">
@@ -79839,11 +79839,11 @@
     </row>
     <row r="245">
       <c r="A245" s="39" t="n">
-        <v>1996</v>
+        <v>1943</v>
       </c>
       <c r="B245" s="39" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C245" s="39" t="inlineStr">
@@ -79853,17 +79853,17 @@
       </c>
       <c r="D245" s="39" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="E245" s="39" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F245" s="39" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G245" s="39" t="inlineStr">
@@ -79874,11 +79874,11 @@
     </row>
     <row r="246">
       <c r="A246" s="39" t="n">
-        <v>1943</v>
+        <v>80</v>
       </c>
       <c r="B246" s="39" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C246" s="39" t="inlineStr">
@@ -79898,7 +79898,7 @@
       </c>
       <c r="F246" s="39" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G246" s="39" t="inlineStr">
@@ -79907,43 +79907,8 @@
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="39" t="n">
-        <v>80</v>
-      </c>
-      <c r="B247" s="39" t="inlineStr">
-        <is>
-          <t>Gisele Lopes Justiniano</t>
-        </is>
-      </c>
-      <c r="C247" s="39" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D247" s="39" t="inlineStr">
-        <is>
-          <t>28/08/2026</t>
-        </is>
-      </c>
-      <c r="E247" s="39" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F247" s="39" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G247" s="39" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G247"/>
+  <autoFilter ref="A2:G246"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/data/historico/semanas_318-321.xlsx
+++ b/data/historico/semanas_318-321.xlsx
@@ -3072,16 +3072,16 @@
         <v>13</v>
       </c>
       <c r="R22" s="5" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="S22" s="5" t="n">
         <v>1</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="U22" s="5" t="n">
-        <v>68.31999999999999</v>
+        <v>67.92</v>
       </c>
       <c r="V22" s="5" t="n">
         <v>3.07</v>
@@ -6731,16 +6731,16 @@
         <v>51</v>
       </c>
       <c r="D22" s="29" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E22" s="29" t="n">
         <v>1</v>
       </c>
       <c r="F22" s="29" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G22" s="29" t="n">
-        <v>68.31999999999999</v>
+        <v>67.92</v>
       </c>
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
@@ -7398,13 +7398,13 @@
         <v>13752</v>
       </c>
       <c r="D45" s="26" t="n">
-        <v>6653</v>
+        <v>6651</v>
       </c>
       <c r="E45" s="26" t="n">
         <v>21</v>
       </c>
       <c r="F45" s="26" t="n">
-        <v>20426</v>
+        <v>20424</v>
       </c>
       <c r="G45" s="26" t="n">
         <v>32.67</v>
@@ -41707,13 +41707,13 @@
         <v>21.21</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L59" s="5" t="n">
         <v>1</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>71.05</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="N59" s="5" t="inlineStr">
         <is>
@@ -51314,47 +51314,47 @@
     <row r="54">
       <c r="A54" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B54" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C54" s="30" t="inlineStr">
         <is>
-          <t>17195999</t>
+          <t>17197913</t>
         </is>
       </c>
       <c r="D54" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E54" s="29" t="inlineStr">
         <is>
-          <t>Q050</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F54" s="29" t="inlineStr">
         <is>
-          <t>Avenida COSTA E SILVA</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G54" s="29" t="inlineStr">
         <is>
-          <t>843 - R</t>
+          <t>1542 - R</t>
         </is>
       </c>
       <c r="H54" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 08:55</t>
+          <t>28/08/2026 14:32</t>
         </is>
       </c>
       <c r="I54" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:15</t>
+          <t>28/08/2026 14:52</t>
         </is>
       </c>
       <c r="J54" s="29" t="n">
@@ -51364,47 +51364,47 @@
     <row r="55">
       <c r="A55" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B55" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C55" s="30" t="inlineStr">
         <is>
-          <t>17197913</t>
+          <t>17195999</t>
         </is>
       </c>
       <c r="D55" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E55" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q050</t>
         </is>
       </c>
       <c r="F55" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Avenida COSTA E SILVA</t>
         </is>
       </c>
       <c r="G55" s="29" t="inlineStr">
         <is>
-          <t>1542 - R</t>
+          <t>843 - R</t>
         </is>
       </c>
       <c r="H55" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:32</t>
+          <t>28/08/2026 08:55</t>
         </is>
       </c>
       <c r="I55" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:52</t>
+          <t>28/08/2026 09:15</t>
         </is>
       </c>
       <c r="J55" s="29" t="n">
@@ -52114,47 +52114,47 @@
     <row r="70">
       <c r="A70" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B70" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>17196006</t>
+          <t>17197904</t>
         </is>
       </c>
       <c r="D70" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E70" s="29" t="inlineStr">
         <is>
-          <t>Q050</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F70" s="29" t="inlineStr">
         <is>
-          <t>Rua 01 DE MARÇO</t>
+          <t>Rua BALTAZAR SALDANHA</t>
         </is>
       </c>
       <c r="G70" s="29" t="inlineStr">
         <is>
-          <t>69 - 1 - OU</t>
+          <t>645 - R</t>
         </is>
       </c>
       <c r="H70" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:32</t>
+          <t>28/08/2026 10:02</t>
         </is>
       </c>
       <c r="I70" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:50</t>
+          <t>28/08/2026 10:20</t>
         </is>
       </c>
       <c r="J70" s="29" t="n">
@@ -52224,7 +52224,7 @@
       </c>
       <c r="C72" s="30" t="inlineStr">
         <is>
-          <t>17197904</t>
+          <t>17197903</t>
         </is>
       </c>
       <c r="D72" s="29" t="inlineStr">
@@ -52244,17 +52244,17 @@
       </c>
       <c r="G72" s="29" t="inlineStr">
         <is>
-          <t>645 - R</t>
+          <t>669 - R</t>
         </is>
       </c>
       <c r="H72" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 10:02</t>
+          <t>28/08/2026 09:41</t>
         </is>
       </c>
       <c r="I72" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 10:20</t>
+          <t>28/08/2026 09:59</t>
         </is>
       </c>
       <c r="J72" s="29" t="n">
@@ -52264,47 +52264,47 @@
     <row r="73">
       <c r="A73" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B73" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C73" s="30" t="inlineStr">
         <is>
-          <t>17197908</t>
+          <t>17196006</t>
         </is>
       </c>
       <c r="D73" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E73" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q050</t>
         </is>
       </c>
       <c r="F73" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Rua 01 DE MARÇO</t>
         </is>
       </c>
       <c r="G73" s="29" t="inlineStr">
         <is>
-          <t>1486 - R</t>
+          <t>69 - 1 - OU</t>
         </is>
       </c>
       <c r="H73" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 13:55</t>
+          <t>28/08/2026 09:32</t>
         </is>
       </c>
       <c r="I73" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:13</t>
+          <t>28/08/2026 09:50</t>
         </is>
       </c>
       <c r="J73" s="29" t="n">
@@ -52324,7 +52324,7 @@
       </c>
       <c r="C74" s="30" t="inlineStr">
         <is>
-          <t>17197903</t>
+          <t>17197908</t>
         </is>
       </c>
       <c r="D74" s="29" t="inlineStr">
@@ -52339,22 +52339,22 @@
       </c>
       <c r="F74" s="29" t="inlineStr">
         <is>
-          <t>Rua BALTAZAR SALDANHA</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G74" s="29" t="inlineStr">
         <is>
-          <t>669 - R</t>
+          <t>1486 - R</t>
         </is>
       </c>
       <c r="H74" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:41</t>
+          <t>28/08/2026 13:55</t>
         </is>
       </c>
       <c r="I74" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 09:59</t>
+          <t>28/08/2026 14:13</t>
         </is>
       </c>
       <c r="J74" s="29" t="n">
@@ -55714,7 +55714,7 @@
     <row r="142">
       <c r="A142" s="29" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B142" s="29" t="inlineStr">
@@ -55724,37 +55724,37 @@
       </c>
       <c r="C142" s="30" t="inlineStr">
         <is>
-          <t>17170026</t>
+          <t>17130878</t>
         </is>
       </c>
       <c r="D142" s="29" t="inlineStr">
         <is>
-          <t>446 - GUY VILELA</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E142" s="29" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q044</t>
         </is>
       </c>
       <c r="F142" s="29" t="inlineStr">
         <is>
-          <t>Avenida TAMANDARE</t>
+          <t>Rua BENJAMIN CONSTANT</t>
         </is>
       </c>
       <c r="G142" s="29" t="inlineStr">
         <is>
-          <t>466 - R</t>
+          <t>512 - 1 - R</t>
         </is>
       </c>
       <c r="H142" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 14:46</t>
+          <t>25/08/2026 10:27</t>
         </is>
       </c>
       <c r="I142" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 15:02</t>
+          <t>25/08/2026 10:43</t>
         </is>
       </c>
       <c r="J142" s="29" t="n">
@@ -55764,7 +55764,7 @@
     <row r="143">
       <c r="A143" s="29" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="B143" s="29" t="inlineStr">
@@ -55774,37 +55774,37 @@
       </c>
       <c r="C143" s="30" t="inlineStr">
         <is>
-          <t>17130878</t>
+          <t>17170026</t>
         </is>
       </c>
       <c r="D143" s="29" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>446 - GUY VILELA</t>
         </is>
       </c>
       <c r="E143" s="29" t="inlineStr">
         <is>
-          <t>Q044</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="F143" s="29" t="inlineStr">
         <is>
-          <t>Rua BENJAMIN CONSTANT</t>
+          <t>Avenida TAMANDARE</t>
         </is>
       </c>
       <c r="G143" s="29" t="inlineStr">
         <is>
-          <t>512 - 1 - R</t>
+          <t>466 - R</t>
         </is>
       </c>
       <c r="H143" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 10:27</t>
+          <t>27/08/2026 14:46</t>
         </is>
       </c>
       <c r="I143" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 10:43</t>
+          <t>27/08/2026 15:02</t>
         </is>
       </c>
       <c r="J143" s="29" t="n">

--- a/data/historico/semanas_318-321.xlsx
+++ b/data/historico/semanas_318-321.xlsx
@@ -50464,47 +50464,47 @@
     <row r="37">
       <c r="A37" s="29" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B37" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C37" s="30" t="inlineStr">
         <is>
-          <t>17131247</t>
+          <t>17148181</t>
         </is>
       </c>
       <c r="D37" s="29" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E37" s="29" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F37" s="29" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Rua ARNALDO VASQUES</t>
         </is>
       </c>
       <c r="G37" s="29" t="inlineStr">
         <is>
-          <t>210 - C</t>
+          <t>325 - R</t>
         </is>
       </c>
       <c r="H37" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 08:43</t>
+          <t>26/08/2026 13:43</t>
         </is>
       </c>
       <c r="I37" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:05</t>
+          <t>26/08/2026 14:05</t>
         </is>
       </c>
       <c r="J37" s="29" t="n">
@@ -50514,47 +50514,47 @@
     <row r="38">
       <c r="A38" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B38" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C38" s="30" t="inlineStr">
         <is>
-          <t>17148181</t>
+          <t>17131247</t>
         </is>
       </c>
       <c r="D38" s="29" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E38" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F38" s="29" t="inlineStr">
         <is>
-          <t>Rua ARNALDO VASQUES</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="G38" s="29" t="inlineStr">
         <is>
-          <t>325 - R</t>
+          <t>210 - C</t>
         </is>
       </c>
       <c r="H38" s="29" t="inlineStr">
         <is>
-          <t>26/08/2026 13:43</t>
+          <t>25/08/2026 08:43</t>
         </is>
       </c>
       <c r="I38" s="29" t="inlineStr">
         <is>
-          <t>26/08/2026 14:05</t>
+          <t>25/08/2026 09:05</t>
         </is>
       </c>
       <c r="J38" s="29" t="n">
@@ -50814,22 +50814,22 @@
     <row r="44">
       <c r="A44" s="29" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
       <c r="B44" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C44" s="30" t="inlineStr">
         <is>
-          <t>16960082</t>
+          <t>17179885</t>
         </is>
       </c>
       <c r="D44" s="29" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>412 - COHAB</t>
         </is>
       </c>
       <c r="E44" s="29" t="inlineStr">
@@ -50839,22 +50839,22 @@
       </c>
       <c r="F44" s="29" t="inlineStr">
         <is>
-          <t>Rua FORTALEZA</t>
+          <t>Rua DOURADOS</t>
         </is>
       </c>
       <c r="G44" s="29" t="inlineStr">
         <is>
-          <t>622 - R</t>
+          <t>16 - B - R</t>
         </is>
       </c>
       <c r="H44" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 09:32</t>
+          <t>27/08/2026 15:04</t>
         </is>
       </c>
       <c r="I44" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 09:53</t>
+          <t>27/08/2026 15:25</t>
         </is>
       </c>
       <c r="J44" s="29" t="n">
@@ -50864,47 +50864,47 @@
     <row r="45">
       <c r="A45" s="29" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B45" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C45" s="30" t="inlineStr">
         <is>
-          <t>17179885</t>
+          <t>17130068</t>
         </is>
       </c>
       <c r="D45" s="29" t="inlineStr">
         <is>
-          <t>412 - COHAB</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E45" s="29" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="F45" s="29" t="inlineStr">
         <is>
-          <t>Rua DOURADOS</t>
+          <t>Rua AREIA BRANCA</t>
         </is>
       </c>
       <c r="G45" s="29" t="inlineStr">
         <is>
-          <t>16 - B - R</t>
+          <t>1194 - R</t>
         </is>
       </c>
       <c r="H45" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 15:04</t>
+          <t>25/08/2026 15:16</t>
         </is>
       </c>
       <c r="I45" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 15:25</t>
+          <t>25/08/2026 15:37</t>
         </is>
       </c>
       <c r="J45" s="29" t="n">
@@ -51074,7 +51074,7 @@
       </c>
       <c r="C49" s="30" t="inlineStr">
         <is>
-          <t>17130068</t>
+          <t>17182224</t>
         </is>
       </c>
       <c r="D49" s="29" t="inlineStr">
@@ -51084,27 +51084,27 @@
       </c>
       <c r="E49" s="29" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F49" s="29" t="inlineStr">
         <is>
-          <t>Rua AREIA BRANCA</t>
+          <t>Rua GUAÍBA</t>
         </is>
       </c>
       <c r="G49" s="29" t="inlineStr">
         <is>
-          <t>1194 - R</t>
+          <t>361 - 8 - R</t>
         </is>
       </c>
       <c r="H49" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:16</t>
+          <t>27/08/2026 14:42</t>
         </is>
       </c>
       <c r="I49" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:37</t>
+          <t>27/08/2026 15:03</t>
         </is>
       </c>
       <c r="J49" s="29" t="n">
@@ -51114,47 +51114,47 @@
     <row r="50">
       <c r="A50" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="B50" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C50" s="30" t="inlineStr">
         <is>
-          <t>17182224</t>
+          <t>16960082</t>
         </is>
       </c>
       <c r="D50" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E50" s="29" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F50" s="29" t="inlineStr">
         <is>
-          <t>Rua GUAÍBA</t>
+          <t>Rua FORTALEZA</t>
         </is>
       </c>
       <c r="G50" s="29" t="inlineStr">
         <is>
-          <t>361 - 8 - R</t>
+          <t>622 - R</t>
         </is>
       </c>
       <c r="H50" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 14:42</t>
+          <t>18/08/2026 09:32</t>
         </is>
       </c>
       <c r="I50" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 15:03</t>
+          <t>18/08/2026 09:53</t>
         </is>
       </c>
       <c r="J50" s="29" t="n">
@@ -52124,7 +52124,7 @@
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>17197904</t>
+          <t>17184336</t>
         </is>
       </c>
       <c r="D70" s="29" t="inlineStr">
@@ -52134,27 +52134,27 @@
       </c>
       <c r="E70" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="F70" s="29" t="inlineStr">
         <is>
-          <t>Rua BALTAZAR SALDANHA</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G70" s="29" t="inlineStr">
         <is>
-          <t>645 - R</t>
+          <t>1391 - R</t>
         </is>
       </c>
       <c r="H70" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 10:02</t>
+          <t>27/08/2026 13:23</t>
         </is>
       </c>
       <c r="I70" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 10:20</t>
+          <t>27/08/2026 13:41</t>
         </is>
       </c>
       <c r="J70" s="29" t="n">
@@ -52374,7 +52374,7 @@
       </c>
       <c r="C75" s="30" t="inlineStr">
         <is>
-          <t>17184336</t>
+          <t>17197904</t>
         </is>
       </c>
       <c r="D75" s="29" t="inlineStr">
@@ -52384,27 +52384,27 @@
       </c>
       <c r="E75" s="29" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F75" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Rua BALTAZAR SALDANHA</t>
         </is>
       </c>
       <c r="G75" s="29" t="inlineStr">
         <is>
-          <t>1391 - R</t>
+          <t>645 - R</t>
         </is>
       </c>
       <c r="H75" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 13:23</t>
+          <t>28/08/2026 10:02</t>
         </is>
       </c>
       <c r="I75" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 13:41</t>
+          <t>28/08/2026 10:20</t>
         </is>
       </c>
       <c r="J75" s="29" t="n">
@@ -52714,7 +52714,7 @@
     <row r="82">
       <c r="A82" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B82" s="29" t="inlineStr">
@@ -52724,37 +52724,37 @@
       </c>
       <c r="C82" s="30" t="inlineStr">
         <is>
-          <t>17130027</t>
+          <t>17092097</t>
         </is>
       </c>
       <c r="D82" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E82" s="29" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F82" s="29" t="inlineStr">
         <is>
-          <t>Rua BARRA VELHA</t>
+          <t>Rua ARNALDO VASQUES</t>
         </is>
       </c>
       <c r="G82" s="29" t="inlineStr">
         <is>
-          <t>1154 - R</t>
+          <t>347 - R</t>
         </is>
       </c>
       <c r="H82" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:31</t>
+          <t>24/08/2026 09:00</t>
         </is>
       </c>
       <c r="I82" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:49</t>
+          <t>24/08/2026 09:18</t>
         </is>
       </c>
       <c r="J82" s="29" t="n">
@@ -52814,7 +52814,7 @@
     <row r="84">
       <c r="A84" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B84" s="29" t="inlineStr">
@@ -52824,37 +52824,37 @@
       </c>
       <c r="C84" s="30" t="inlineStr">
         <is>
-          <t>17092097</t>
+          <t>17130027</t>
         </is>
       </c>
       <c r="D84" s="29" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E84" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="F84" s="29" t="inlineStr">
         <is>
-          <t>Rua ARNALDO VASQUES</t>
+          <t>Rua BARRA VELHA</t>
         </is>
       </c>
       <c r="G84" s="29" t="inlineStr">
         <is>
-          <t>347 - R</t>
+          <t>1154 - R</t>
         </is>
       </c>
       <c r="H84" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:00</t>
+          <t>25/08/2026 09:31</t>
         </is>
       </c>
       <c r="I84" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:18</t>
+          <t>25/08/2026 09:49</t>
         </is>
       </c>
       <c r="J84" s="29" t="n">
@@ -52914,7 +52914,7 @@
     <row r="86">
       <c r="A86" s="29" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B86" s="29" t="inlineStr">
@@ -52924,37 +52924,37 @@
       </c>
       <c r="C86" s="30" t="inlineStr">
         <is>
-          <t>17133115</t>
+          <t>17098963</t>
         </is>
       </c>
       <c r="D86" s="29" t="inlineStr">
         <is>
-          <t>412 - COHAB</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E86" s="29" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F86" s="29" t="inlineStr">
         <is>
-          <t>Rua VALENCIO DE BRUM</t>
+          <t>Rua ARINO MOREIRA</t>
         </is>
       </c>
       <c r="G86" s="29" t="inlineStr">
         <is>
-          <t>536 - R</t>
+          <t>39 - R</t>
         </is>
       </c>
       <c r="H86" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:33</t>
+          <t>24/08/2026 15:46</t>
         </is>
       </c>
       <c r="I86" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:50</t>
+          <t>24/08/2026 16:03</t>
         </is>
       </c>
       <c r="J86" s="29" t="n">
@@ -53064,7 +53064,7 @@
     <row r="89">
       <c r="A89" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
       <c r="B89" s="29" t="inlineStr">
@@ -53074,37 +53074,37 @@
       </c>
       <c r="C89" s="30" t="inlineStr">
         <is>
-          <t>17195900</t>
+          <t>17133115</t>
         </is>
       </c>
       <c r="D89" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>412 - COHAB</t>
         </is>
       </c>
       <c r="E89" s="29" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="F89" s="29" t="inlineStr">
         <is>
-          <t>Rua 13 DE SETEMBRO</t>
+          <t>Rua VALENCIO DE BRUM</t>
         </is>
       </c>
       <c r="G89" s="29" t="inlineStr">
         <is>
-          <t>1502 - R</t>
+          <t>536 - R</t>
         </is>
       </c>
       <c r="H89" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:53</t>
+          <t>25/08/2026 09:33</t>
         </is>
       </c>
       <c r="I89" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 15:10</t>
+          <t>25/08/2026 09:50</t>
         </is>
       </c>
       <c r="J89" s="29" t="n">
@@ -53264,7 +53264,7 @@
     <row r="93">
       <c r="A93" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B93" s="29" t="inlineStr">
@@ -53274,37 +53274,37 @@
       </c>
       <c r="C93" s="30" t="inlineStr">
         <is>
-          <t>17098963</t>
+          <t>17073307</t>
         </is>
       </c>
       <c r="D93" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E93" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F93" s="29" t="inlineStr">
         <is>
-          <t>Rua ARINO MOREIRA</t>
+          <t>Avenida ANTONIO JOAO</t>
         </is>
       </c>
       <c r="G93" s="29" t="inlineStr">
         <is>
-          <t>39 - R</t>
+          <t>1477 - R</t>
         </is>
       </c>
       <c r="H93" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:46</t>
+          <t>20/08/2026 13:54</t>
         </is>
       </c>
       <c r="I93" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 16:03</t>
+          <t>20/08/2026 14:11</t>
         </is>
       </c>
       <c r="J93" s="29" t="n">
@@ -53374,7 +53374,7 @@
       </c>
       <c r="C95" s="30" t="inlineStr">
         <is>
-          <t>17073307</t>
+          <t>17184338</t>
         </is>
       </c>
       <c r="D95" s="29" t="inlineStr">
@@ -53384,27 +53384,27 @@
       </c>
       <c r="E95" s="29" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="F95" s="29" t="inlineStr">
         <is>
-          <t>Avenida ANTONIO JOAO</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G95" s="29" t="inlineStr">
         <is>
-          <t>1477 - R</t>
+          <t>1353 - C</t>
         </is>
       </c>
       <c r="H95" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 13:54</t>
+          <t>27/08/2026 13:50</t>
         </is>
       </c>
       <c r="I95" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 14:11</t>
+          <t>27/08/2026 14:07</t>
         </is>
       </c>
       <c r="J95" s="29" t="n">
@@ -53964,47 +53964,47 @@
     <row r="107">
       <c r="A107" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B107" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C107" s="30" t="inlineStr">
         <is>
-          <t>17041447</t>
+          <t>17073270</t>
         </is>
       </c>
       <c r="D107" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E107" s="29" t="inlineStr">
         <is>
-          <t>Q038</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F107" s="29" t="inlineStr">
         <is>
-          <t>Rua DAS PEROBAS</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="G107" s="29" t="inlineStr">
         <is>
-          <t>1018 - R</t>
+          <t>3974 - 33 - R - 30</t>
         </is>
       </c>
       <c r="H107" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 14:48</t>
+          <t>19/08/2026 09:22</t>
         </is>
       </c>
       <c r="I107" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 15:05</t>
+          <t>19/08/2026 09:39</t>
         </is>
       </c>
       <c r="J107" s="29" t="n">
@@ -54114,47 +54114,47 @@
     <row r="110">
       <c r="A110" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="B110" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C110" s="30" t="inlineStr">
         <is>
-          <t>17073270</t>
+          <t>17072136</t>
         </is>
       </c>
       <c r="D110" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>443 - KAMEL SAAD 1</t>
         </is>
       </c>
       <c r="E110" s="29" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="F110" s="29" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Rua TOMBADOR</t>
         </is>
       </c>
       <c r="G110" s="29" t="inlineStr">
         <is>
-          <t>3974 - 33 - R - 30</t>
+          <t>684 - R</t>
         </is>
       </c>
       <c r="H110" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:22</t>
+          <t>21/08/2026 10:12</t>
         </is>
       </c>
       <c r="I110" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:39</t>
+          <t>21/08/2026 10:29</t>
         </is>
       </c>
       <c r="J110" s="29" t="n">
@@ -54214,47 +54214,47 @@
     <row r="112">
       <c r="A112" s="29" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B112" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C112" s="30" t="inlineStr">
         <is>
-          <t>17072136</t>
+          <t>17041447</t>
         </is>
       </c>
       <c r="D112" s="29" t="inlineStr">
         <is>
-          <t>443 - KAMEL SAAD 1</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E112" s="29" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q038</t>
         </is>
       </c>
       <c r="F112" s="29" t="inlineStr">
         <is>
-          <t>Rua TOMBADOR</t>
+          <t>Rua DAS PEROBAS</t>
         </is>
       </c>
       <c r="G112" s="29" t="inlineStr">
         <is>
-          <t>684 - R</t>
+          <t>1018 - R</t>
         </is>
       </c>
       <c r="H112" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 10:12</t>
+          <t>20/08/2026 14:48</t>
         </is>
       </c>
       <c r="I112" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 10:29</t>
+          <t>20/08/2026 15:05</t>
         </is>
       </c>
       <c r="J112" s="29" t="n">
@@ -54264,7 +54264,7 @@
     <row r="113">
       <c r="A113" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B113" s="29" t="inlineStr">
@@ -54274,37 +54274,37 @@
       </c>
       <c r="C113" s="30" t="inlineStr">
         <is>
-          <t>17184338</t>
+          <t>17195900</t>
         </is>
       </c>
       <c r="D113" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E113" s="29" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F113" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Rua 13 DE SETEMBRO</t>
         </is>
       </c>
       <c r="G113" s="29" t="inlineStr">
         <is>
-          <t>1353 - C</t>
+          <t>1502 - R</t>
         </is>
       </c>
       <c r="H113" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 13:50</t>
+          <t>28/08/2026 14:53</t>
         </is>
       </c>
       <c r="I113" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 14:07</t>
+          <t>28/08/2026 15:10</t>
         </is>
       </c>
       <c r="J113" s="29" t="n">
@@ -55214,47 +55214,47 @@
     <row r="132">
       <c r="A132" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B132" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C132" s="30" t="inlineStr">
         <is>
-          <t>17073275</t>
+          <t>16982670</t>
         </is>
       </c>
       <c r="D132" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E132" s="29" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q037</t>
         </is>
       </c>
       <c r="F132" s="29" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Rua SALVADOR</t>
         </is>
       </c>
       <c r="G132" s="29" t="inlineStr">
         <is>
-          <t>3986 - R</t>
+          <t>479 - R</t>
         </is>
       </c>
       <c r="H132" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:19</t>
+          <t>17/08/2026 14:14</t>
         </is>
       </c>
       <c r="I132" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:35</t>
+          <t>17/08/2026 14:30</t>
         </is>
       </c>
       <c r="J132" s="29" t="n">
@@ -55314,47 +55314,47 @@
     <row r="134">
       <c r="A134" s="29" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B134" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C134" s="30" t="inlineStr">
         <is>
-          <t>16982670</t>
+          <t>17073275</t>
         </is>
       </c>
       <c r="D134" s="29" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E134" s="29" t="inlineStr">
         <is>
-          <t>Q037</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F134" s="29" t="inlineStr">
         <is>
-          <t>Rua SALVADOR</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="G134" s="29" t="inlineStr">
         <is>
-          <t>479 - R</t>
+          <t>3986 - R</t>
         </is>
       </c>
       <c r="H134" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 14:14</t>
+          <t>19/08/2026 10:19</t>
         </is>
       </c>
       <c r="I134" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 14:30</t>
+          <t>19/08/2026 10:35</t>
         </is>
       </c>
       <c r="J134" s="29" t="n">
@@ -55414,47 +55414,47 @@
     <row r="136">
       <c r="A136" s="29" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B136" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C136" s="30" t="inlineStr">
         <is>
-          <t>17137370</t>
+          <t>17098958</t>
         </is>
       </c>
       <c r="D136" s="29" t="inlineStr">
         <is>
-          <t>402 - JARDIM MARAMBAIA</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E136" s="29" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F136" s="29" t="inlineStr">
         <is>
-          <t>Rua DR HELIO BRANDAO</t>
+          <t>Avenida COMANDANTE CARDOSO</t>
         </is>
       </c>
       <c r="G136" s="29" t="inlineStr">
         <is>
-          <t>647 - R</t>
+          <t>258 - 2 - OU</t>
         </is>
       </c>
       <c r="H136" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 16:03</t>
+          <t>24/08/2026 14:47</t>
         </is>
       </c>
       <c r="I136" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 16:19</t>
+          <t>24/08/2026 15:03</t>
         </is>
       </c>
       <c r="J136" s="29" t="n">
@@ -55614,47 +55614,47 @@
     <row r="140">
       <c r="A140" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="B140" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C140" s="30" t="inlineStr">
         <is>
-          <t>17098958</t>
+          <t>17137370</t>
         </is>
       </c>
       <c r="D140" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>402 - JARDIM MARAMBAIA</t>
         </is>
       </c>
       <c r="E140" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F140" s="29" t="inlineStr">
         <is>
-          <t>Avenida COMANDANTE CARDOSO</t>
+          <t>Rua DR HELIO BRANDAO</t>
         </is>
       </c>
       <c r="G140" s="29" t="inlineStr">
         <is>
-          <t>258 - 2 - OU</t>
+          <t>647 - R</t>
         </is>
       </c>
       <c r="H140" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 14:47</t>
+          <t>25/08/2026 16:03</t>
         </is>
       </c>
       <c r="I140" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:03</t>
+          <t>25/08/2026 16:19</t>
         </is>
       </c>
       <c r="J140" s="29" t="n">

--- a/data/historico/semanas_318-321.xlsx
+++ b/data/historico/semanas_318-321.xlsx
@@ -1665,13 +1665,13 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>17</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>20.47</v>
+        <v>20.65</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>5.7</v>
@@ -1683,7 +1683,7 @@
         <v>14</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>1</v>
@@ -1713,23 +1713,23 @@
         <v>0</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>28.98</v>
+        <v>28.8</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>6.87</v>
+        <v>6.88</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>29.22</v>
+        <v>29.25</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Y9" s="4" t="inlineStr">
         <is>
-          <t>R$ 113,59</t>
+          <t>R$ 112,79</t>
         </is>
       </c>
       <c r="Z9" s="4" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AC9" s="4" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:34</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
         </is>
       </c>
       <c r="C9" s="29" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D9" s="29" t="n">
         <v>142</v>
@@ -6360,10 +6360,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="G9" s="29" t="n">
-        <v>28.98</v>
+        <v>28.8</v>
       </c>
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
@@ -7395,7 +7395,7 @@
         </is>
       </c>
       <c r="C45" s="26" t="n">
-        <v>13752</v>
+        <v>13755</v>
       </c>
       <c r="D45" s="26" t="n">
         <v>6651</v>
@@ -7404,10 +7404,10 @@
         <v>21</v>
       </c>
       <c r="F45" s="26" t="n">
-        <v>20424</v>
+        <v>20427</v>
       </c>
       <c r="G45" s="26" t="n">
-        <v>32.67</v>
+        <v>32.66</v>
       </c>
       <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="n"/>
@@ -14975,16 +14975,16 @@
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G55" s="4" t="n">
         <v>5</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>31.8</v>
+        <v>32.4</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>4</v>
@@ -14993,7 +14993,7 @@
         <v>10</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>6.29</v>
+        <v>6.17</v>
       </c>
       <c r="M55" s="4" t="n">
         <v>0</v>
@@ -15021,17 +15021,17 @@
       <c r="V55" s="4" t="inlineStr"/>
       <c r="W55" s="4" t="inlineStr"/>
       <c r="X55" s="4" t="n">
-        <v>5.41</v>
+        <v>5.43</v>
       </c>
       <c r="Y55" s="4" t="n">
-        <v>27.03</v>
+        <v>27.17</v>
       </c>
       <c r="Z55" s="4" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AA55" s="4" t="inlineStr">
         <is>
-          <t>R$ 83,41</t>
+          <t>R$ 81,97</t>
         </is>
       </c>
       <c r="AB55" s="4" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="AE55" s="4" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:22</t>
         </is>
       </c>
     </row>
@@ -39902,27 +39902,27 @@
         </is>
       </c>
       <c r="D26" s="4" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.4</v>
+        <v>5.39</v>
       </c>
       <c r="F26" s="4" t="n">
         <v>5</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Q005, Q014, Q015, Q016, Q017, Q018, Q019, Q020, Q021, Q022, Q023, Q024, Q025, Q026, Q027, Q028, Q029, Q030, Q031, Q032</t>
+          <t>Q005, Q013, Q014, Q015, Q016, Q017, Q018, Q019, Q020, Q021, Q022, Q023, Q024, Q025, Q026, Q027, Q028, Q029, Q030, Q031, Q032</t>
         </is>
       </c>
       <c r="I26" s="4" t="n">
         <v>10</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4.69</v>
+        <v>4.63</v>
       </c>
       <c r="K26" s="4" t="n">
         <v>118</v>
@@ -39931,7 +39931,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>35.65</v>
+        <v>35.33</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>

--- a/data/historico/semanas_318-321.xlsx
+++ b/data/historico/semanas_318-321.xlsx
@@ -50514,7 +50514,7 @@
     <row r="38">
       <c r="A38" s="29" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B38" s="29" t="inlineStr">
@@ -50524,37 +50524,37 @@
       </c>
       <c r="C38" s="30" t="inlineStr">
         <is>
-          <t>17131247</t>
+          <t>17130213</t>
         </is>
       </c>
       <c r="D38" s="29" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E38" s="29" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F38" s="29" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Rua ROSA AZUL</t>
         </is>
       </c>
       <c r="G38" s="29" t="inlineStr">
         <is>
-          <t>210 - C</t>
+          <t>222 - R</t>
         </is>
       </c>
       <c r="H38" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 08:43</t>
+          <t>25/08/2026 15:33</t>
         </is>
       </c>
       <c r="I38" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:05</t>
+          <t>25/08/2026 15:55</t>
         </is>
       </c>
       <c r="J38" s="29" t="n">
@@ -50714,7 +50714,7 @@
     <row r="42">
       <c r="A42" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B42" s="29" t="inlineStr">
@@ -50724,37 +50724,37 @@
       </c>
       <c r="C42" s="30" t="inlineStr">
         <is>
-          <t>17130213</t>
+          <t>17131247</t>
         </is>
       </c>
       <c r="D42" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E42" s="29" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F42" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA AZUL</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="G42" s="29" t="inlineStr">
         <is>
-          <t>222 - R</t>
+          <t>210 - C</t>
         </is>
       </c>
       <c r="H42" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:33</t>
+          <t>25/08/2026 08:43</t>
         </is>
       </c>
       <c r="I42" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:55</t>
+          <t>25/08/2026 09:05</t>
         </is>
       </c>
       <c r="J42" s="29" t="n">

--- a/data/historico/semanas_318-321.xlsx
+++ b/data/historico/semanas_318-321.xlsx
@@ -50464,47 +50464,47 @@
     <row r="37">
       <c r="A37" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="B37" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C37" s="30" t="inlineStr">
         <is>
-          <t>17148181</t>
+          <t>17131247</t>
         </is>
       </c>
       <c r="D37" s="29" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>413 - BAIRRO DA GRANJA</t>
         </is>
       </c>
       <c r="E37" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F37" s="29" t="inlineStr">
         <is>
-          <t>Rua ARNALDO VASQUES</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="G37" s="29" t="inlineStr">
         <is>
-          <t>325 - R</t>
+          <t>210 - C</t>
         </is>
       </c>
       <c r="H37" s="29" t="inlineStr">
         <is>
-          <t>26/08/2026 13:43</t>
+          <t>25/08/2026 08:43</t>
         </is>
       </c>
       <c r="I37" s="29" t="inlineStr">
         <is>
-          <t>26/08/2026 14:05</t>
+          <t>25/08/2026 09:05</t>
         </is>
       </c>
       <c r="J37" s="29" t="n">
@@ -50514,47 +50514,47 @@
     <row r="38">
       <c r="A38" s="29" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B38" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C38" s="30" t="inlineStr">
         <is>
-          <t>17130213</t>
+          <t>17148181</t>
         </is>
       </c>
       <c r="D38" s="29" t="inlineStr">
         <is>
-          <t>411 - JARDIM AEROPORTO</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E38" s="29" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F38" s="29" t="inlineStr">
         <is>
-          <t>Rua ROSA AZUL</t>
+          <t>Rua ARNALDO VASQUES</t>
         </is>
       </c>
       <c r="G38" s="29" t="inlineStr">
         <is>
-          <t>222 - R</t>
+          <t>325 - R</t>
         </is>
       </c>
       <c r="H38" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:33</t>
+          <t>26/08/2026 13:43</t>
         </is>
       </c>
       <c r="I38" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:55</t>
+          <t>26/08/2026 14:05</t>
         </is>
       </c>
       <c r="J38" s="29" t="n">
@@ -50714,7 +50714,7 @@
     <row r="42">
       <c r="A42" s="29" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="B42" s="29" t="inlineStr">
@@ -50724,37 +50724,37 @@
       </c>
       <c r="C42" s="30" t="inlineStr">
         <is>
-          <t>17131247</t>
+          <t>17130213</t>
         </is>
       </c>
       <c r="D42" s="29" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA</t>
+          <t>411 - JARDIM AEROPORTO</t>
         </is>
       </c>
       <c r="E42" s="29" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F42" s="29" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Rua ROSA AZUL</t>
         </is>
       </c>
       <c r="G42" s="29" t="inlineStr">
         <is>
-          <t>210 - C</t>
+          <t>222 - R</t>
         </is>
       </c>
       <c r="H42" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 08:43</t>
+          <t>25/08/2026 15:33</t>
         </is>
       </c>
       <c r="I42" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:05</t>
+          <t>25/08/2026 15:55</t>
         </is>
       </c>
       <c r="J42" s="29" t="n">
@@ -50814,22 +50814,22 @@
     <row r="44">
       <c r="A44" s="29" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="B44" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C44" s="30" t="inlineStr">
         <is>
-          <t>17179885</t>
+          <t>16960082</t>
         </is>
       </c>
       <c r="D44" s="29" t="inlineStr">
         <is>
-          <t>412 - COHAB</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E44" s="29" t="inlineStr">
@@ -50839,22 +50839,22 @@
       </c>
       <c r="F44" s="29" t="inlineStr">
         <is>
-          <t>Rua DOURADOS</t>
+          <t>Rua FORTALEZA</t>
         </is>
       </c>
       <c r="G44" s="29" t="inlineStr">
         <is>
-          <t>16 - B - R</t>
+          <t>622 - R</t>
         </is>
       </c>
       <c r="H44" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 15:04</t>
+          <t>18/08/2026 09:32</t>
         </is>
       </c>
       <c r="I44" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 15:25</t>
+          <t>18/08/2026 09:53</t>
         </is>
       </c>
       <c r="J44" s="29" t="n">
@@ -50864,47 +50864,47 @@
     <row r="45">
       <c r="A45" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
       <c r="B45" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C45" s="30" t="inlineStr">
         <is>
-          <t>17130068</t>
+          <t>17179885</t>
         </is>
       </c>
       <c r="D45" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>412 - COHAB</t>
         </is>
       </c>
       <c r="E45" s="29" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="F45" s="29" t="inlineStr">
         <is>
-          <t>Rua AREIA BRANCA</t>
+          <t>Rua DOURADOS</t>
         </is>
       </c>
       <c r="G45" s="29" t="inlineStr">
         <is>
-          <t>1194 - R</t>
+          <t>16 - B - R</t>
         </is>
       </c>
       <c r="H45" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:16</t>
+          <t>27/08/2026 15:04</t>
         </is>
       </c>
       <c r="I45" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 15:37</t>
+          <t>27/08/2026 15:25</t>
         </is>
       </c>
       <c r="J45" s="29" t="n">
@@ -51074,7 +51074,7 @@
       </c>
       <c r="C49" s="30" t="inlineStr">
         <is>
-          <t>17182224</t>
+          <t>17130068</t>
         </is>
       </c>
       <c r="D49" s="29" t="inlineStr">
@@ -51084,27 +51084,27 @@
       </c>
       <c r="E49" s="29" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="F49" s="29" t="inlineStr">
         <is>
-          <t>Rua GUAÍBA</t>
+          <t>Rua AREIA BRANCA</t>
         </is>
       </c>
       <c r="G49" s="29" t="inlineStr">
         <is>
-          <t>361 - 8 - R</t>
+          <t>1194 - R</t>
         </is>
       </c>
       <c r="H49" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 14:42</t>
+          <t>25/08/2026 15:16</t>
         </is>
       </c>
       <c r="I49" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 15:03</t>
+          <t>25/08/2026 15:37</t>
         </is>
       </c>
       <c r="J49" s="29" t="n">
@@ -51114,47 +51114,47 @@
     <row r="50">
       <c r="A50" s="29" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B50" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C50" s="30" t="inlineStr">
         <is>
-          <t>16960082</t>
+          <t>17182224</t>
         </is>
       </c>
       <c r="D50" s="29" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E50" s="29" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="F50" s="29" t="inlineStr">
         <is>
-          <t>Rua FORTALEZA</t>
+          <t>Rua GUAÍBA</t>
         </is>
       </c>
       <c r="G50" s="29" t="inlineStr">
         <is>
-          <t>622 - R</t>
+          <t>361 - 8 - R</t>
         </is>
       </c>
       <c r="H50" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 09:32</t>
+          <t>27/08/2026 14:42</t>
         </is>
       </c>
       <c r="I50" s="29" t="inlineStr">
         <is>
-          <t>18/08/2026 09:53</t>
+          <t>27/08/2026 15:03</t>
         </is>
       </c>
       <c r="J50" s="29" t="n">
@@ -52124,7 +52124,7 @@
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>17184336</t>
+          <t>17197904</t>
         </is>
       </c>
       <c r="D70" s="29" t="inlineStr">
@@ -52134,27 +52134,27 @@
       </c>
       <c r="E70" s="29" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="F70" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Rua BALTAZAR SALDANHA</t>
         </is>
       </c>
       <c r="G70" s="29" t="inlineStr">
         <is>
-          <t>1391 - R</t>
+          <t>645 - R</t>
         </is>
       </c>
       <c r="H70" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 13:23</t>
+          <t>28/08/2026 10:02</t>
         </is>
       </c>
       <c r="I70" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 13:41</t>
+          <t>28/08/2026 10:20</t>
         </is>
       </c>
       <c r="J70" s="29" t="n">
@@ -52374,7 +52374,7 @@
       </c>
       <c r="C75" s="30" t="inlineStr">
         <is>
-          <t>17197904</t>
+          <t>17184336</t>
         </is>
       </c>
       <c r="D75" s="29" t="inlineStr">
@@ -52384,27 +52384,27 @@
       </c>
       <c r="E75" s="29" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="F75" s="29" t="inlineStr">
         <is>
-          <t>Rua BALTAZAR SALDANHA</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G75" s="29" t="inlineStr">
         <is>
-          <t>645 - R</t>
+          <t>1391 - R</t>
         </is>
       </c>
       <c r="H75" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 10:02</t>
+          <t>27/08/2026 13:23</t>
         </is>
       </c>
       <c r="I75" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 10:20</t>
+          <t>27/08/2026 13:41</t>
         </is>
       </c>
       <c r="J75" s="29" t="n">
@@ -52714,7 +52714,7 @@
     <row r="82">
       <c r="A82" s="29" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B82" s="29" t="inlineStr">
@@ -52724,37 +52724,37 @@
       </c>
       <c r="C82" s="30" t="inlineStr">
         <is>
-          <t>17092097</t>
+          <t>17130027</t>
         </is>
       </c>
       <c r="D82" s="29" t="inlineStr">
         <is>
-          <t>405 - ALTOS DA GLÓRIA</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E82" s="29" t="inlineStr">
         <is>
-          <t>Q013</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="F82" s="29" t="inlineStr">
         <is>
-          <t>Rua ARNALDO VASQUES</t>
+          <t>Rua BARRA VELHA</t>
         </is>
       </c>
       <c r="G82" s="29" t="inlineStr">
         <is>
-          <t>347 - R</t>
+          <t>1154 - R</t>
         </is>
       </c>
       <c r="H82" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:00</t>
+          <t>25/08/2026 09:31</t>
         </is>
       </c>
       <c r="I82" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 09:18</t>
+          <t>25/08/2026 09:49</t>
         </is>
       </c>
       <c r="J82" s="29" t="n">
@@ -52814,7 +52814,7 @@
     <row r="84">
       <c r="A84" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Evelyn Santana Santos Oliveira</t>
         </is>
       </c>
       <c r="B84" s="29" t="inlineStr">
@@ -52824,37 +52824,37 @@
       </c>
       <c r="C84" s="30" t="inlineStr">
         <is>
-          <t>17130027</t>
+          <t>17092097</t>
         </is>
       </c>
       <c r="D84" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>405 - ALTOS DA GLÓRIA</t>
         </is>
       </c>
       <c r="E84" s="29" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q013</t>
         </is>
       </c>
       <c r="F84" s="29" t="inlineStr">
         <is>
-          <t>Rua BARRA VELHA</t>
+          <t>Rua ARNALDO VASQUES</t>
         </is>
       </c>
       <c r="G84" s="29" t="inlineStr">
         <is>
-          <t>1154 - R</t>
+          <t>347 - R</t>
         </is>
       </c>
       <c r="H84" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:31</t>
+          <t>24/08/2026 09:00</t>
         </is>
       </c>
       <c r="I84" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:49</t>
+          <t>24/08/2026 09:18</t>
         </is>
       </c>
       <c r="J84" s="29" t="n">
@@ -52914,7 +52914,7 @@
     <row r="86">
       <c r="A86" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Cicero Isrrael Sanabria</t>
         </is>
       </c>
       <c r="B86" s="29" t="inlineStr">
@@ -52924,37 +52924,37 @@
       </c>
       <c r="C86" s="30" t="inlineStr">
         <is>
-          <t>17098963</t>
+          <t>17133115</t>
         </is>
       </c>
       <c r="D86" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>412 - COHAB</t>
         </is>
       </c>
       <c r="E86" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="F86" s="29" t="inlineStr">
         <is>
-          <t>Rua ARINO MOREIRA</t>
+          <t>Rua VALENCIO DE BRUM</t>
         </is>
       </c>
       <c r="G86" s="29" t="inlineStr">
         <is>
-          <t>39 - R</t>
+          <t>536 - R</t>
         </is>
       </c>
       <c r="H86" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:46</t>
+          <t>25/08/2026 09:33</t>
         </is>
       </c>
       <c r="I86" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 16:03</t>
+          <t>25/08/2026 09:50</t>
         </is>
       </c>
       <c r="J86" s="29" t="n">
@@ -53064,7 +53064,7 @@
     <row r="89">
       <c r="A89" s="29" t="inlineStr">
         <is>
-          <t>Cicero Isrrael Sanabria</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B89" s="29" t="inlineStr">
@@ -53074,37 +53074,37 @@
       </c>
       <c r="C89" s="30" t="inlineStr">
         <is>
-          <t>17133115</t>
+          <t>17195900</t>
         </is>
       </c>
       <c r="D89" s="29" t="inlineStr">
         <is>
-          <t>412 - COHAB</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E89" s="29" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="F89" s="29" t="inlineStr">
         <is>
-          <t>Rua VALENCIO DE BRUM</t>
+          <t>Rua 13 DE SETEMBRO</t>
         </is>
       </c>
       <c r="G89" s="29" t="inlineStr">
         <is>
-          <t>536 - R</t>
+          <t>1502 - R</t>
         </is>
       </c>
       <c r="H89" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:33</t>
+          <t>28/08/2026 14:53</t>
         </is>
       </c>
       <c r="I89" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 09:50</t>
+          <t>28/08/2026 15:10</t>
         </is>
       </c>
       <c r="J89" s="29" t="n">
@@ -53264,7 +53264,7 @@
     <row r="93">
       <c r="A93" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B93" s="29" t="inlineStr">
@@ -53274,37 +53274,37 @@
       </c>
       <c r="C93" s="30" t="inlineStr">
         <is>
-          <t>17073307</t>
+          <t>17098963</t>
         </is>
       </c>
       <c r="D93" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E93" s="29" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F93" s="29" t="inlineStr">
         <is>
-          <t>Avenida ANTONIO JOAO</t>
+          <t>Rua ARINO MOREIRA</t>
         </is>
       </c>
       <c r="G93" s="29" t="inlineStr">
         <is>
-          <t>1477 - R</t>
+          <t>39 - R</t>
         </is>
       </c>
       <c r="H93" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 13:54</t>
+          <t>24/08/2026 15:46</t>
         </is>
       </c>
       <c r="I93" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 14:11</t>
+          <t>24/08/2026 16:03</t>
         </is>
       </c>
       <c r="J93" s="29" t="n">
@@ -53374,7 +53374,7 @@
       </c>
       <c r="C95" s="30" t="inlineStr">
         <is>
-          <t>17184338</t>
+          <t>17073307</t>
         </is>
       </c>
       <c r="D95" s="29" t="inlineStr">
@@ -53384,27 +53384,27 @@
       </c>
       <c r="E95" s="29" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F95" s="29" t="inlineStr">
         <is>
-          <t>Rua GENERAL OSORIO</t>
+          <t>Avenida ANTONIO JOAO</t>
         </is>
       </c>
       <c r="G95" s="29" t="inlineStr">
         <is>
-          <t>1353 - C</t>
+          <t>1477 - R</t>
         </is>
       </c>
       <c r="H95" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 13:50</t>
+          <t>20/08/2026 13:54</t>
         </is>
       </c>
       <c r="I95" s="29" t="inlineStr">
         <is>
-          <t>27/08/2026 14:07</t>
+          <t>20/08/2026 14:11</t>
         </is>
       </c>
       <c r="J95" s="29" t="n">
@@ -53964,47 +53964,47 @@
     <row r="107">
       <c r="A107" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B107" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C107" s="30" t="inlineStr">
         <is>
-          <t>17073270</t>
+          <t>17041447</t>
         </is>
       </c>
       <c r="D107" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E107" s="29" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q038</t>
         </is>
       </c>
       <c r="F107" s="29" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Rua DAS PEROBAS</t>
         </is>
       </c>
       <c r="G107" s="29" t="inlineStr">
         <is>
-          <t>3974 - 33 - R - 30</t>
+          <t>1018 - R</t>
         </is>
       </c>
       <c r="H107" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:22</t>
+          <t>20/08/2026 14:48</t>
         </is>
       </c>
       <c r="I107" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 09:39</t>
+          <t>20/08/2026 15:05</t>
         </is>
       </c>
       <c r="J107" s="29" t="n">
@@ -54114,47 +54114,47 @@
     <row r="110">
       <c r="A110" s="29" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B110" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C110" s="30" t="inlineStr">
         <is>
-          <t>17072136</t>
+          <t>17073270</t>
         </is>
       </c>
       <c r="D110" s="29" t="inlineStr">
         <is>
-          <t>443 - KAMEL SAAD 1</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E110" s="29" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F110" s="29" t="inlineStr">
         <is>
-          <t>Rua TOMBADOR</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="G110" s="29" t="inlineStr">
         <is>
-          <t>684 - R</t>
+          <t>3974 - 33 - R - 30</t>
         </is>
       </c>
       <c r="H110" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 10:12</t>
+          <t>19/08/2026 09:22</t>
         </is>
       </c>
       <c r="I110" s="29" t="inlineStr">
         <is>
-          <t>21/08/2026 10:29</t>
+          <t>19/08/2026 09:39</t>
         </is>
       </c>
       <c r="J110" s="29" t="n">
@@ -54214,47 +54214,47 @@
     <row r="112">
       <c r="A112" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="B112" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C112" s="30" t="inlineStr">
         <is>
-          <t>17041447</t>
+          <t>17072136</t>
         </is>
       </c>
       <c r="D112" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>443 - KAMEL SAAD 1</t>
         </is>
       </c>
       <c r="E112" s="29" t="inlineStr">
         <is>
-          <t>Q038</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="F112" s="29" t="inlineStr">
         <is>
-          <t>Rua DAS PEROBAS</t>
+          <t>Rua TOMBADOR</t>
         </is>
       </c>
       <c r="G112" s="29" t="inlineStr">
         <is>
-          <t>1018 - R</t>
+          <t>684 - R</t>
         </is>
       </c>
       <c r="H112" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 14:48</t>
+          <t>21/08/2026 10:12</t>
         </is>
       </c>
       <c r="I112" s="29" t="inlineStr">
         <is>
-          <t>20/08/2026 15:05</t>
+          <t>21/08/2026 10:29</t>
         </is>
       </c>
       <c r="J112" s="29" t="n">
@@ -54264,7 +54264,7 @@
     <row r="113">
       <c r="A113" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B113" s="29" t="inlineStr">
@@ -54274,37 +54274,37 @@
       </c>
       <c r="C113" s="30" t="inlineStr">
         <is>
-          <t>17195900</t>
+          <t>17184338</t>
         </is>
       </c>
       <c r="D113" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E113" s="29" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="F113" s="29" t="inlineStr">
         <is>
-          <t>Rua 13 DE SETEMBRO</t>
+          <t>Rua GENERAL OSORIO</t>
         </is>
       </c>
       <c r="G113" s="29" t="inlineStr">
         <is>
-          <t>1502 - R</t>
+          <t>1353 - C</t>
         </is>
       </c>
       <c r="H113" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 14:53</t>
+          <t>27/08/2026 13:50</t>
         </is>
       </c>
       <c r="I113" s="29" t="inlineStr">
         <is>
-          <t>28/08/2026 15:10</t>
+          <t>27/08/2026 14:07</t>
         </is>
       </c>
       <c r="J113" s="29" t="n">
@@ -55214,47 +55214,47 @@
     <row r="132">
       <c r="A132" s="29" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
       <c r="B132" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C132" s="30" t="inlineStr">
         <is>
-          <t>16982670</t>
+          <t>17073275</t>
         </is>
       </c>
       <c r="D132" s="29" t="inlineStr">
         <is>
-          <t>434 - VILA AUREA</t>
+          <t>418 - CENTRO 4</t>
         </is>
       </c>
       <c r="E132" s="29" t="inlineStr">
         <is>
-          <t>Q037</t>
+          <t>Q011</t>
         </is>
       </c>
       <c r="F132" s="29" t="inlineStr">
         <is>
-          <t>Rua SALVADOR</t>
+          <t>Avenida BRASIL</t>
         </is>
       </c>
       <c r="G132" s="29" t="inlineStr">
         <is>
-          <t>479 - R</t>
+          <t>3986 - R</t>
         </is>
       </c>
       <c r="H132" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 14:14</t>
+          <t>19/08/2026 10:19</t>
         </is>
       </c>
       <c r="I132" s="29" t="inlineStr">
         <is>
-          <t>17/08/2026 14:30</t>
+          <t>19/08/2026 10:35</t>
         </is>
       </c>
       <c r="J132" s="29" t="n">
@@ -55314,47 +55314,47 @@
     <row r="134">
       <c r="A134" s="29" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="B134" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C134" s="30" t="inlineStr">
         <is>
-          <t>17073275</t>
+          <t>16982670</t>
         </is>
       </c>
       <c r="D134" s="29" t="inlineStr">
         <is>
-          <t>418 - CENTRO 4</t>
+          <t>434 - VILA AUREA</t>
         </is>
       </c>
       <c r="E134" s="29" t="inlineStr">
         <is>
-          <t>Q011</t>
+          <t>Q037</t>
         </is>
       </c>
       <c r="F134" s="29" t="inlineStr">
         <is>
-          <t>Avenida BRASIL</t>
+          <t>Rua SALVADOR</t>
         </is>
       </c>
       <c r="G134" s="29" t="inlineStr">
         <is>
-          <t>3986 - R</t>
+          <t>479 - R</t>
         </is>
       </c>
       <c r="H134" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:19</t>
+          <t>17/08/2026 14:14</t>
         </is>
       </c>
       <c r="I134" s="29" t="inlineStr">
         <is>
-          <t>19/08/2026 10:35</t>
+          <t>17/08/2026 14:30</t>
         </is>
       </c>
       <c r="J134" s="29" t="n">
@@ -55414,47 +55414,47 @@
     <row r="136">
       <c r="A136" s="29" t="inlineStr">
         <is>
-          <t>Suely Aguiar Alves Luiz</t>
+          <t>Gabriel Alan de Oliveira Martins</t>
         </is>
       </c>
       <c r="B136" s="29" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C136" s="30" t="inlineStr">
         <is>
-          <t>17098958</t>
+          <t>17137370</t>
         </is>
       </c>
       <c r="D136" s="29" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS</t>
+          <t>402 - JARDIM MARAMBAIA</t>
         </is>
       </c>
       <c r="E136" s="29" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q029</t>
         </is>
       </c>
       <c r="F136" s="29" t="inlineStr">
         <is>
-          <t>Avenida COMANDANTE CARDOSO</t>
+          <t>Rua DR HELIO BRANDAO</t>
         </is>
       </c>
       <c r="G136" s="29" t="inlineStr">
         <is>
-          <t>258 - 2 - OU</t>
+          <t>647 - R</t>
         </is>
       </c>
       <c r="H136" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 14:47</t>
+          <t>25/08/2026 16:03</t>
         </is>
       </c>
       <c r="I136" s="29" t="inlineStr">
         <is>
-          <t>24/08/2026 15:03</t>
+          <t>25/08/2026 16:19</t>
         </is>
       </c>
       <c r="J136" s="29" t="n">
@@ -55614,47 +55614,47 @@
     <row r="140">
       <c r="A140" s="29" t="inlineStr">
         <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B140" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="C140" s="30" t="inlineStr">
         <is>
-          <t>17137370</t>
+          <t>17098958</t>
         </is>
       </c>
       <c r="D140" s="29" t="inlineStr">
         <is>
-          <t>402 - JARDIM MARAMBAIA</t>
+          <t>414 - PARQUE DOS ERVAIS</t>
         </is>
       </c>
       <c r="E140" s="29" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="F140" s="29" t="inlineStr">
         <is>
-          <t>Rua DR HELIO BRANDAO</t>
+          <t>Avenida COMANDANTE CARDOSO</t>
         </is>
       </c>
       <c r="G140" s="29" t="inlineStr">
         <is>
-          <t>647 - R</t>
+          <t>258 - 2 - OU</t>
         </is>
       </c>
       <c r="H140" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 16:03</t>
+          <t>24/08/2026 14:47</t>
         </is>
       </c>
       <c r="I140" s="29" t="inlineStr">
         <is>
-          <t>25/08/2026 16:19</t>
+          <t>24/08/2026 15:03</t>
         </is>
       </c>
       <c r="J140" s="29" t="n">
